--- a/wwwroot/ExcelModel/Jako_PHY_sheet.xlsx
+++ b/wwwroot/ExcelModel/Jako_PHY_sheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\source\NX-lims Softlines Command System\wwwroot\ExcelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BD211E7-B723-4FFD-B724-229830FA83C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A4CC30A-F544-44E2-AB99-373DBF2DC652}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="6" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Weight" sheetId="3" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="223">
   <si>
     <t>Test Report Number 报告编号:</t>
   </si>
@@ -1611,6 +1611,7 @@
     <font>
       <sz val="9"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1825,7 +1826,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="225">
+  <cellXfs count="227">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2071,6 +2072,12 @@
     <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2317,44 +2324,44 @@
     <xf numFmtId="0" fontId="38" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="55" fillId="3" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="55" fillId="3" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2748,25 +2755,25 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="2"/>
-      <c r="J1" s="100"/>
-      <c r="K1" s="100"/>
-      <c r="L1" s="100"/>
-      <c r="M1" s="100"/>
-      <c r="N1" s="100"/>
-      <c r="O1" s="100"/>
-      <c r="P1" s="100"/>
-      <c r="Q1" s="100"/>
-      <c r="R1" s="100"/>
-      <c r="S1" s="100"/>
-      <c r="T1" s="100"/>
-      <c r="U1" s="100"/>
-      <c r="V1" s="100"/>
-      <c r="W1" s="100"/>
-      <c r="X1" s="100"/>
-      <c r="Y1" s="100"/>
-      <c r="Z1" s="100"/>
-      <c r="AA1" s="100"/>
-      <c r="AB1" s="100"/>
+      <c r="J1" s="102"/>
+      <c r="K1" s="102"/>
+      <c r="L1" s="102"/>
+      <c r="M1" s="102"/>
+      <c r="N1" s="102"/>
+      <c r="O1" s="102"/>
+      <c r="P1" s="102"/>
+      <c r="Q1" s="102"/>
+      <c r="R1" s="102"/>
+      <c r="S1" s="102"/>
+      <c r="T1" s="102"/>
+      <c r="U1" s="102"/>
+      <c r="V1" s="102"/>
+      <c r="W1" s="102"/>
+      <c r="X1" s="102"/>
+      <c r="Y1" s="102"/>
+      <c r="Z1" s="102"/>
+      <c r="AA1" s="102"/>
+      <c r="AB1" s="102"/>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -2798,18 +2805,18 @@
       <c r="AB2" s="1"/>
     </row>
     <row r="3" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="115"/>
-      <c r="B3" s="115"/>
-      <c r="C3" s="115"/>
-      <c r="D3" s="115"/>
-      <c r="E3" s="115"/>
-      <c r="F3" s="115"/>
-      <c r="G3" s="115"/>
-      <c r="H3" s="115"/>
-      <c r="I3" s="115"/>
-      <c r="J3" s="115"/>
-      <c r="K3" s="115"/>
-      <c r="L3" s="115"/>
+      <c r="A3" s="117"/>
+      <c r="B3" s="117"/>
+      <c r="C3" s="117"/>
+      <c r="D3" s="117"/>
+      <c r="E3" s="117"/>
+      <c r="F3" s="117"/>
+      <c r="G3" s="117"/>
+      <c r="H3" s="117"/>
+      <c r="I3" s="117"/>
+      <c r="J3" s="117"/>
+      <c r="K3" s="117"/>
+      <c r="L3" s="117"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
@@ -3002,230 +3009,230 @@
       <c r="AB9" s="1"/>
     </row>
     <row r="10" spans="1:28" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A10" s="109" t="s">
+      <c r="A10" s="111" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="110"/>
-      <c r="C10" s="110"/>
-      <c r="D10" s="111"/>
-      <c r="E10" s="101" t="s">
+      <c r="B10" s="112"/>
+      <c r="C10" s="112"/>
+      <c r="D10" s="113"/>
+      <c r="E10" s="103" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="102"/>
-      <c r="G10" s="102"/>
-      <c r="H10" s="102"/>
-      <c r="I10" s="102"/>
-      <c r="J10" s="102"/>
-      <c r="K10" s="102"/>
-      <c r="L10" s="102"/>
-      <c r="M10" s="102"/>
-      <c r="N10" s="102"/>
-      <c r="O10" s="102"/>
-      <c r="P10" s="102"/>
-      <c r="Q10" s="102"/>
-      <c r="R10" s="102"/>
-      <c r="S10" s="102"/>
-      <c r="T10" s="102"/>
-      <c r="U10" s="102"/>
-      <c r="V10" s="102"/>
-      <c r="W10" s="102"/>
-      <c r="X10" s="102"/>
-      <c r="Y10" s="103" t="s">
+      <c r="F10" s="104"/>
+      <c r="G10" s="104"/>
+      <c r="H10" s="104"/>
+      <c r="I10" s="104"/>
+      <c r="J10" s="104"/>
+      <c r="K10" s="104"/>
+      <c r="L10" s="104"/>
+      <c r="M10" s="104"/>
+      <c r="N10" s="104"/>
+      <c r="O10" s="104"/>
+      <c r="P10" s="104"/>
+      <c r="Q10" s="104"/>
+      <c r="R10" s="104"/>
+      <c r="S10" s="104"/>
+      <c r="T10" s="104"/>
+      <c r="U10" s="104"/>
+      <c r="V10" s="104"/>
+      <c r="W10" s="104"/>
+      <c r="X10" s="104"/>
+      <c r="Y10" s="105" t="s">
         <v>14</v>
       </c>
-      <c r="Z10" s="104"/>
-      <c r="AA10" s="104"/>
-      <c r="AB10" s="105"/>
+      <c r="Z10" s="106"/>
+      <c r="AA10" s="106"/>
+      <c r="AB10" s="107"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A11" s="112"/>
-      <c r="B11" s="113"/>
-      <c r="C11" s="113"/>
-      <c r="D11" s="114"/>
-      <c r="E11" s="101" t="s">
+      <c r="A11" s="114"/>
+      <c r="B11" s="115"/>
+      <c r="C11" s="115"/>
+      <c r="D11" s="116"/>
+      <c r="E11" s="103" t="s">
         <v>9</v>
       </c>
-      <c r="F11" s="102"/>
-      <c r="G11" s="102"/>
-      <c r="H11" s="99"/>
-      <c r="I11" s="101" t="s">
+      <c r="F11" s="104"/>
+      <c r="G11" s="104"/>
+      <c r="H11" s="101"/>
+      <c r="I11" s="103" t="s">
         <v>10</v>
       </c>
-      <c r="J11" s="102"/>
-      <c r="K11" s="102"/>
-      <c r="L11" s="99"/>
-      <c r="M11" s="101" t="s">
+      <c r="J11" s="104"/>
+      <c r="K11" s="104"/>
+      <c r="L11" s="101"/>
+      <c r="M11" s="103" t="s">
         <v>11</v>
       </c>
-      <c r="N11" s="102"/>
-      <c r="O11" s="102"/>
-      <c r="P11" s="99"/>
-      <c r="Q11" s="101" t="s">
+      <c r="N11" s="104"/>
+      <c r="O11" s="104"/>
+      <c r="P11" s="101"/>
+      <c r="Q11" s="103" t="s">
         <v>12</v>
       </c>
-      <c r="R11" s="102"/>
-      <c r="S11" s="102"/>
-      <c r="T11" s="99"/>
-      <c r="U11" s="101" t="s">
+      <c r="R11" s="104"/>
+      <c r="S11" s="104"/>
+      <c r="T11" s="101"/>
+      <c r="U11" s="103" t="s">
         <v>13</v>
       </c>
-      <c r="V11" s="102"/>
-      <c r="W11" s="102"/>
-      <c r="X11" s="98"/>
-      <c r="Y11" s="106"/>
-      <c r="Z11" s="107"/>
-      <c r="AA11" s="107"/>
-      <c r="AB11" s="108"/>
+      <c r="V11" s="104"/>
+      <c r="W11" s="104"/>
+      <c r="X11" s="100"/>
+      <c r="Y11" s="108"/>
+      <c r="Z11" s="109"/>
+      <c r="AA11" s="109"/>
+      <c r="AB11" s="110"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A12" s="116"/>
-      <c r="B12" s="117"/>
-      <c r="C12" s="117"/>
-      <c r="D12" s="118"/>
-      <c r="E12" s="97"/>
-      <c r="F12" s="98"/>
-      <c r="G12" s="98"/>
-      <c r="H12" s="99"/>
-      <c r="I12" s="97"/>
-      <c r="J12" s="98"/>
-      <c r="K12" s="98"/>
-      <c r="L12" s="99"/>
-      <c r="M12" s="97"/>
-      <c r="N12" s="98"/>
-      <c r="O12" s="98"/>
-      <c r="P12" s="99"/>
-      <c r="Q12" s="97"/>
-      <c r="R12" s="98"/>
-      <c r="S12" s="98"/>
-      <c r="T12" s="99"/>
-      <c r="U12" s="97"/>
-      <c r="V12" s="98"/>
-      <c r="W12" s="98"/>
-      <c r="X12" s="99"/>
-      <c r="Y12" s="97"/>
-      <c r="Z12" s="98"/>
-      <c r="AA12" s="98"/>
-      <c r="AB12" s="99"/>
+      <c r="A12" s="118"/>
+      <c r="B12" s="119"/>
+      <c r="C12" s="119"/>
+      <c r="D12" s="120"/>
+      <c r="E12" s="99"/>
+      <c r="F12" s="100"/>
+      <c r="G12" s="100"/>
+      <c r="H12" s="101"/>
+      <c r="I12" s="99"/>
+      <c r="J12" s="100"/>
+      <c r="K12" s="100"/>
+      <c r="L12" s="101"/>
+      <c r="M12" s="99"/>
+      <c r="N12" s="100"/>
+      <c r="O12" s="100"/>
+      <c r="P12" s="101"/>
+      <c r="Q12" s="99"/>
+      <c r="R12" s="100"/>
+      <c r="S12" s="100"/>
+      <c r="T12" s="101"/>
+      <c r="U12" s="99"/>
+      <c r="V12" s="100"/>
+      <c r="W12" s="100"/>
+      <c r="X12" s="101"/>
+      <c r="Y12" s="99"/>
+      <c r="Z12" s="100"/>
+      <c r="AA12" s="100"/>
+      <c r="AB12" s="101"/>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A13" s="116"/>
-      <c r="B13" s="117"/>
-      <c r="C13" s="117"/>
-      <c r="D13" s="118"/>
-      <c r="E13" s="97"/>
-      <c r="F13" s="98"/>
-      <c r="G13" s="98"/>
-      <c r="H13" s="99"/>
-      <c r="I13" s="97"/>
-      <c r="J13" s="98"/>
-      <c r="K13" s="98"/>
-      <c r="L13" s="99"/>
-      <c r="M13" s="97"/>
-      <c r="N13" s="98"/>
-      <c r="O13" s="98"/>
-      <c r="P13" s="99"/>
-      <c r="Q13" s="97"/>
-      <c r="R13" s="98"/>
-      <c r="S13" s="98"/>
-      <c r="T13" s="99"/>
-      <c r="U13" s="97"/>
-      <c r="V13" s="98"/>
-      <c r="W13" s="98"/>
-      <c r="X13" s="99"/>
-      <c r="Y13" s="97"/>
-      <c r="Z13" s="98"/>
-      <c r="AA13" s="98"/>
-      <c r="AB13" s="99"/>
+      <c r="A13" s="118"/>
+      <c r="B13" s="119"/>
+      <c r="C13" s="119"/>
+      <c r="D13" s="120"/>
+      <c r="E13" s="99"/>
+      <c r="F13" s="100"/>
+      <c r="G13" s="100"/>
+      <c r="H13" s="101"/>
+      <c r="I13" s="99"/>
+      <c r="J13" s="100"/>
+      <c r="K13" s="100"/>
+      <c r="L13" s="101"/>
+      <c r="M13" s="99"/>
+      <c r="N13" s="100"/>
+      <c r="O13" s="100"/>
+      <c r="P13" s="101"/>
+      <c r="Q13" s="99"/>
+      <c r="R13" s="100"/>
+      <c r="S13" s="100"/>
+      <c r="T13" s="101"/>
+      <c r="U13" s="99"/>
+      <c r="V13" s="100"/>
+      <c r="W13" s="100"/>
+      <c r="X13" s="101"/>
+      <c r="Y13" s="99"/>
+      <c r="Z13" s="100"/>
+      <c r="AA13" s="100"/>
+      <c r="AB13" s="101"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A14" s="116"/>
-      <c r="B14" s="117"/>
-      <c r="C14" s="117"/>
-      <c r="D14" s="118"/>
-      <c r="E14" s="97"/>
-      <c r="F14" s="98"/>
-      <c r="G14" s="98"/>
-      <c r="H14" s="99"/>
-      <c r="I14" s="97"/>
-      <c r="J14" s="98"/>
-      <c r="K14" s="98"/>
-      <c r="L14" s="99"/>
-      <c r="M14" s="97"/>
-      <c r="N14" s="98"/>
-      <c r="O14" s="98"/>
-      <c r="P14" s="99"/>
-      <c r="Q14" s="97"/>
-      <c r="R14" s="98"/>
-      <c r="S14" s="98"/>
-      <c r="T14" s="99"/>
-      <c r="U14" s="97"/>
-      <c r="V14" s="98"/>
-      <c r="W14" s="98"/>
-      <c r="X14" s="99"/>
-      <c r="Y14" s="97"/>
-      <c r="Z14" s="98"/>
-      <c r="AA14" s="98"/>
-      <c r="AB14" s="99"/>
+      <c r="A14" s="118"/>
+      <c r="B14" s="119"/>
+      <c r="C14" s="119"/>
+      <c r="D14" s="120"/>
+      <c r="E14" s="99"/>
+      <c r="F14" s="100"/>
+      <c r="G14" s="100"/>
+      <c r="H14" s="101"/>
+      <c r="I14" s="99"/>
+      <c r="J14" s="100"/>
+      <c r="K14" s="100"/>
+      <c r="L14" s="101"/>
+      <c r="M14" s="99"/>
+      <c r="N14" s="100"/>
+      <c r="O14" s="100"/>
+      <c r="P14" s="101"/>
+      <c r="Q14" s="99"/>
+      <c r="R14" s="100"/>
+      <c r="S14" s="100"/>
+      <c r="T14" s="101"/>
+      <c r="U14" s="99"/>
+      <c r="V14" s="100"/>
+      <c r="W14" s="100"/>
+      <c r="X14" s="101"/>
+      <c r="Y14" s="99"/>
+      <c r="Z14" s="100"/>
+      <c r="AA14" s="100"/>
+      <c r="AB14" s="101"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A15" s="116"/>
-      <c r="B15" s="117"/>
-      <c r="C15" s="117"/>
-      <c r="D15" s="118"/>
-      <c r="E15" s="97"/>
-      <c r="F15" s="98"/>
-      <c r="G15" s="98"/>
-      <c r="H15" s="99"/>
-      <c r="I15" s="97"/>
-      <c r="J15" s="98"/>
-      <c r="K15" s="98"/>
-      <c r="L15" s="99"/>
-      <c r="M15" s="97"/>
-      <c r="N15" s="98"/>
-      <c r="O15" s="98"/>
-      <c r="P15" s="99"/>
-      <c r="Q15" s="97"/>
-      <c r="R15" s="98"/>
-      <c r="S15" s="98"/>
-      <c r="T15" s="99"/>
-      <c r="U15" s="97"/>
-      <c r="V15" s="98"/>
-      <c r="W15" s="98"/>
-      <c r="X15" s="99"/>
-      <c r="Y15" s="97"/>
-      <c r="Z15" s="98"/>
-      <c r="AA15" s="98"/>
-      <c r="AB15" s="99"/>
+      <c r="A15" s="118"/>
+      <c r="B15" s="119"/>
+      <c r="C15" s="119"/>
+      <c r="D15" s="120"/>
+      <c r="E15" s="99"/>
+      <c r="F15" s="100"/>
+      <c r="G15" s="100"/>
+      <c r="H15" s="101"/>
+      <c r="I15" s="99"/>
+      <c r="J15" s="100"/>
+      <c r="K15" s="100"/>
+      <c r="L15" s="101"/>
+      <c r="M15" s="99"/>
+      <c r="N15" s="100"/>
+      <c r="O15" s="100"/>
+      <c r="P15" s="101"/>
+      <c r="Q15" s="99"/>
+      <c r="R15" s="100"/>
+      <c r="S15" s="100"/>
+      <c r="T15" s="101"/>
+      <c r="U15" s="99"/>
+      <c r="V15" s="100"/>
+      <c r="W15" s="100"/>
+      <c r="X15" s="101"/>
+      <c r="Y15" s="99"/>
+      <c r="Z15" s="100"/>
+      <c r="AA15" s="100"/>
+      <c r="AB15" s="101"/>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A16" s="116"/>
-      <c r="B16" s="117"/>
-      <c r="C16" s="117"/>
-      <c r="D16" s="118"/>
-      <c r="E16" s="97"/>
-      <c r="F16" s="98"/>
-      <c r="G16" s="98"/>
-      <c r="H16" s="99"/>
-      <c r="I16" s="97"/>
-      <c r="J16" s="98"/>
-      <c r="K16" s="98"/>
-      <c r="L16" s="99"/>
-      <c r="M16" s="97"/>
-      <c r="N16" s="98"/>
-      <c r="O16" s="98"/>
-      <c r="P16" s="99"/>
-      <c r="Q16" s="97"/>
-      <c r="R16" s="98"/>
-      <c r="S16" s="98"/>
-      <c r="T16" s="99"/>
-      <c r="U16" s="97"/>
-      <c r="V16" s="98"/>
-      <c r="W16" s="98"/>
-      <c r="X16" s="99"/>
-      <c r="Y16" s="97"/>
-      <c r="Z16" s="98"/>
-      <c r="AA16" s="98"/>
-      <c r="AB16" s="99"/>
+      <c r="A16" s="118"/>
+      <c r="B16" s="119"/>
+      <c r="C16" s="119"/>
+      <c r="D16" s="120"/>
+      <c r="E16" s="99"/>
+      <c r="F16" s="100"/>
+      <c r="G16" s="100"/>
+      <c r="H16" s="101"/>
+      <c r="I16" s="99"/>
+      <c r="J16" s="100"/>
+      <c r="K16" s="100"/>
+      <c r="L16" s="101"/>
+      <c r="M16" s="99"/>
+      <c r="N16" s="100"/>
+      <c r="O16" s="100"/>
+      <c r="P16" s="101"/>
+      <c r="Q16" s="99"/>
+      <c r="R16" s="100"/>
+      <c r="S16" s="100"/>
+      <c r="T16" s="101"/>
+      <c r="U16" s="99"/>
+      <c r="V16" s="100"/>
+      <c r="W16" s="100"/>
+      <c r="X16" s="101"/>
+      <c r="Y16" s="99"/>
+      <c r="Z16" s="100"/>
+      <c r="AA16" s="100"/>
+      <c r="AB16" s="101"/>
     </row>
     <row r="17" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
@@ -3456,32 +3463,32 @@
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
-      <c r="M1" s="125"/>
-      <c r="N1" s="125"/>
-      <c r="O1" s="125"/>
-      <c r="P1" s="125"/>
-      <c r="Q1" s="125"/>
-      <c r="R1" s="125"/>
-      <c r="S1" s="125"/>
-      <c r="T1" s="125"/>
-      <c r="U1" s="125"/>
-      <c r="V1" s="125"/>
-      <c r="W1" s="125"/>
-      <c r="X1" s="125"/>
-      <c r="Y1" s="125"/>
-      <c r="Z1" s="125"/>
-      <c r="AA1" s="125"/>
-      <c r="AB1" s="125"/>
-      <c r="AC1" s="125"/>
-      <c r="AD1" s="125"/>
-      <c r="AE1" s="125"/>
-      <c r="AF1" s="125"/>
-      <c r="AG1" s="125"/>
-      <c r="AH1" s="125"/>
-      <c r="AI1" s="125"/>
-      <c r="AJ1" s="125"/>
-      <c r="AK1" s="125"/>
-      <c r="AL1" s="125"/>
+      <c r="M1" s="127"/>
+      <c r="N1" s="127"/>
+      <c r="O1" s="127"/>
+      <c r="P1" s="127"/>
+      <c r="Q1" s="127"/>
+      <c r="R1" s="127"/>
+      <c r="S1" s="127"/>
+      <c r="T1" s="127"/>
+      <c r="U1" s="127"/>
+      <c r="V1" s="127"/>
+      <c r="W1" s="127"/>
+      <c r="X1" s="127"/>
+      <c r="Y1" s="127"/>
+      <c r="Z1" s="127"/>
+      <c r="AA1" s="127"/>
+      <c r="AB1" s="127"/>
+      <c r="AC1" s="127"/>
+      <c r="AD1" s="127"/>
+      <c r="AE1" s="127"/>
+      <c r="AF1" s="127"/>
+      <c r="AG1" s="127"/>
+      <c r="AH1" s="127"/>
+      <c r="AI1" s="127"/>
+      <c r="AJ1" s="127"/>
+      <c r="AK1" s="127"/>
+      <c r="AL1" s="127"/>
     </row>
     <row r="2" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A2" s="46" t="s">
@@ -3526,26 +3533,26 @@
       <c r="AL2"/>
     </row>
     <row r="3" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A3" s="126"/>
-      <c r="B3" s="126"/>
-      <c r="C3" s="126"/>
-      <c r="D3" s="126"/>
-      <c r="E3" s="126"/>
-      <c r="F3" s="126"/>
-      <c r="G3" s="126"/>
-      <c r="H3" s="126"/>
-      <c r="I3" s="126"/>
-      <c r="J3" s="126"/>
-      <c r="K3" s="126"/>
-      <c r="L3" s="126"/>
-      <c r="M3" s="126"/>
-      <c r="N3" s="126"/>
-      <c r="O3" s="126"/>
-      <c r="P3" s="126"/>
-      <c r="Q3" s="126"/>
-      <c r="R3" s="126"/>
-      <c r="S3" s="126"/>
-      <c r="T3" s="126"/>
+      <c r="A3" s="128"/>
+      <c r="B3" s="128"/>
+      <c r="C3" s="128"/>
+      <c r="D3" s="128"/>
+      <c r="E3" s="128"/>
+      <c r="F3" s="128"/>
+      <c r="G3" s="128"/>
+      <c r="H3" s="128"/>
+      <c r="I3" s="128"/>
+      <c r="J3" s="128"/>
+      <c r="K3" s="128"/>
+      <c r="L3" s="128"/>
+      <c r="M3" s="128"/>
+      <c r="N3" s="128"/>
+      <c r="O3" s="128"/>
+      <c r="P3" s="128"/>
+      <c r="Q3" s="128"/>
+      <c r="R3" s="128"/>
+      <c r="S3" s="128"/>
+      <c r="T3" s="128"/>
       <c r="U3"/>
       <c r="V3"/>
       <c r="W3"/>
@@ -3648,214 +3655,214 @@
       <c r="AL5"/>
     </row>
     <row r="6" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A6" s="207" t="s">
+      <c r="A6" s="209" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="208"/>
-      <c r="C6" s="208"/>
-      <c r="D6" s="208"/>
-      <c r="E6" s="208"/>
-      <c r="F6" s="209"/>
-      <c r="G6" s="213" t="s">
+      <c r="B6" s="210"/>
+      <c r="C6" s="210"/>
+      <c r="D6" s="210"/>
+      <c r="E6" s="210"/>
+      <c r="F6" s="211"/>
+      <c r="G6" s="215" t="s">
         <v>118</v>
       </c>
-      <c r="H6" s="214"/>
-      <c r="I6" s="214"/>
-      <c r="J6" s="214"/>
-      <c r="K6" s="214"/>
-      <c r="L6" s="214"/>
-      <c r="M6" s="214"/>
-      <c r="N6" s="214"/>
-      <c r="O6" s="214"/>
-      <c r="P6" s="214"/>
-      <c r="Q6" s="214"/>
-      <c r="R6" s="214"/>
-      <c r="S6" s="214"/>
-      <c r="T6" s="214"/>
-      <c r="U6" s="214"/>
-      <c r="V6" s="214"/>
-      <c r="W6" s="214"/>
-      <c r="X6" s="214"/>
-      <c r="Y6" s="214"/>
-      <c r="Z6" s="214"/>
-      <c r="AA6" s="214"/>
-      <c r="AB6" s="214"/>
-      <c r="AC6" s="214"/>
-      <c r="AD6" s="214"/>
-      <c r="AE6" s="214"/>
-      <c r="AF6" s="214"/>
-      <c r="AG6" s="214"/>
-      <c r="AH6" s="214"/>
-      <c r="AI6" s="214"/>
-      <c r="AJ6" s="214"/>
-      <c r="AK6" s="214"/>
-      <c r="AL6" s="215"/>
+      <c r="H6" s="216"/>
+      <c r="I6" s="216"/>
+      <c r="J6" s="216"/>
+      <c r="K6" s="216"/>
+      <c r="L6" s="216"/>
+      <c r="M6" s="216"/>
+      <c r="N6" s="216"/>
+      <c r="O6" s="216"/>
+      <c r="P6" s="216"/>
+      <c r="Q6" s="216"/>
+      <c r="R6" s="216"/>
+      <c r="S6" s="216"/>
+      <c r="T6" s="216"/>
+      <c r="U6" s="216"/>
+      <c r="V6" s="216"/>
+      <c r="W6" s="216"/>
+      <c r="X6" s="216"/>
+      <c r="Y6" s="216"/>
+      <c r="Z6" s="216"/>
+      <c r="AA6" s="216"/>
+      <c r="AB6" s="216"/>
+      <c r="AC6" s="216"/>
+      <c r="AD6" s="216"/>
+      <c r="AE6" s="216"/>
+      <c r="AF6" s="216"/>
+      <c r="AG6" s="216"/>
+      <c r="AH6" s="216"/>
+      <c r="AI6" s="216"/>
+      <c r="AJ6" s="216"/>
+      <c r="AK6" s="216"/>
+      <c r="AL6" s="217"/>
     </row>
     <row r="7" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A7" s="210"/>
-      <c r="B7" s="211"/>
-      <c r="C7" s="211"/>
-      <c r="D7" s="211"/>
-      <c r="E7" s="211"/>
-      <c r="F7" s="212"/>
-      <c r="G7" s="124" t="s">
+      <c r="A7" s="212"/>
+      <c r="B7" s="213"/>
+      <c r="C7" s="213"/>
+      <c r="D7" s="213"/>
+      <c r="E7" s="213"/>
+      <c r="F7" s="214"/>
+      <c r="G7" s="126" t="s">
         <v>204</v>
       </c>
-      <c r="H7" s="119"/>
-      <c r="I7" s="119"/>
-      <c r="J7" s="119"/>
-      <c r="K7" s="119"/>
-      <c r="L7" s="119"/>
-      <c r="M7" s="119"/>
-      <c r="N7" s="119"/>
-      <c r="O7" s="119"/>
-      <c r="P7" s="119"/>
-      <c r="Q7" s="119"/>
-      <c r="R7" s="124" t="s">
+      <c r="H7" s="121"/>
+      <c r="I7" s="121"/>
+      <c r="J7" s="121"/>
+      <c r="K7" s="121"/>
+      <c r="L7" s="121"/>
+      <c r="M7" s="121"/>
+      <c r="N7" s="121"/>
+      <c r="O7" s="121"/>
+      <c r="P7" s="121"/>
+      <c r="Q7" s="121"/>
+      <c r="R7" s="126" t="s">
         <v>205</v>
       </c>
-      <c r="S7" s="119"/>
-      <c r="T7" s="119"/>
-      <c r="U7" s="119"/>
-      <c r="V7" s="119"/>
-      <c r="W7" s="119"/>
-      <c r="X7" s="119"/>
-      <c r="Y7" s="119"/>
-      <c r="Z7" s="119"/>
-      <c r="AA7" s="119"/>
-      <c r="AB7" s="119"/>
-      <c r="AC7" s="124" t="s">
+      <c r="S7" s="121"/>
+      <c r="T7" s="121"/>
+      <c r="U7" s="121"/>
+      <c r="V7" s="121"/>
+      <c r="W7" s="121"/>
+      <c r="X7" s="121"/>
+      <c r="Y7" s="121"/>
+      <c r="Z7" s="121"/>
+      <c r="AA7" s="121"/>
+      <c r="AB7" s="121"/>
+      <c r="AC7" s="126" t="s">
         <v>206</v>
       </c>
-      <c r="AD7" s="119"/>
-      <c r="AE7" s="119"/>
-      <c r="AF7" s="119"/>
-      <c r="AG7" s="119"/>
-      <c r="AH7" s="119"/>
-      <c r="AI7" s="119"/>
-      <c r="AJ7" s="119"/>
-      <c r="AK7" s="119"/>
-      <c r="AL7" s="119"/>
+      <c r="AD7" s="121"/>
+      <c r="AE7" s="121"/>
+      <c r="AF7" s="121"/>
+      <c r="AG7" s="121"/>
+      <c r="AH7" s="121"/>
+      <c r="AI7" s="121"/>
+      <c r="AJ7" s="121"/>
+      <c r="AK7" s="121"/>
+      <c r="AL7" s="121"/>
     </row>
     <row r="8" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A8" s="216"/>
-      <c r="B8" s="216"/>
-      <c r="C8" s="216"/>
-      <c r="D8" s="216"/>
-      <c r="E8" s="216"/>
-      <c r="F8" s="216"/>
-      <c r="G8" s="119"/>
-      <c r="H8" s="119"/>
-      <c r="I8" s="119"/>
-      <c r="J8" s="119"/>
-      <c r="K8" s="119"/>
-      <c r="L8" s="119"/>
-      <c r="M8" s="119"/>
-      <c r="N8" s="119"/>
-      <c r="O8" s="119"/>
-      <c r="P8" s="119"/>
-      <c r="Q8" s="119"/>
-      <c r="R8" s="119"/>
-      <c r="S8" s="119"/>
-      <c r="T8" s="119"/>
-      <c r="U8" s="119"/>
-      <c r="V8" s="119"/>
-      <c r="W8" s="119"/>
-      <c r="X8" s="119"/>
-      <c r="Y8" s="119"/>
-      <c r="Z8" s="119"/>
-      <c r="AA8" s="119"/>
-      <c r="AB8" s="119"/>
-      <c r="AC8" s="119"/>
-      <c r="AD8" s="119"/>
-      <c r="AE8" s="119"/>
-      <c r="AF8" s="119"/>
-      <c r="AG8" s="119"/>
-      <c r="AH8" s="119"/>
-      <c r="AI8" s="119"/>
-      <c r="AJ8" s="119"/>
-      <c r="AK8" s="119"/>
-      <c r="AL8" s="119"/>
+      <c r="A8" s="218"/>
+      <c r="B8" s="218"/>
+      <c r="C8" s="218"/>
+      <c r="D8" s="218"/>
+      <c r="E8" s="218"/>
+      <c r="F8" s="218"/>
+      <c r="G8" s="121"/>
+      <c r="H8" s="121"/>
+      <c r="I8" s="121"/>
+      <c r="J8" s="121"/>
+      <c r="K8" s="121"/>
+      <c r="L8" s="121"/>
+      <c r="M8" s="121"/>
+      <c r="N8" s="121"/>
+      <c r="O8" s="121"/>
+      <c r="P8" s="121"/>
+      <c r="Q8" s="121"/>
+      <c r="R8" s="121"/>
+      <c r="S8" s="121"/>
+      <c r="T8" s="121"/>
+      <c r="U8" s="121"/>
+      <c r="V8" s="121"/>
+      <c r="W8" s="121"/>
+      <c r="X8" s="121"/>
+      <c r="Y8" s="121"/>
+      <c r="Z8" s="121"/>
+      <c r="AA8" s="121"/>
+      <c r="AB8" s="121"/>
+      <c r="AC8" s="121"/>
+      <c r="AD8" s="121"/>
+      <c r="AE8" s="121"/>
+      <c r="AF8" s="121"/>
+      <c r="AG8" s="121"/>
+      <c r="AH8" s="121"/>
+      <c r="AI8" s="121"/>
+      <c r="AJ8" s="121"/>
+      <c r="AK8" s="121"/>
+      <c r="AL8" s="121"/>
     </row>
     <row r="9" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A9" s="216"/>
-      <c r="B9" s="216"/>
-      <c r="C9" s="216"/>
-      <c r="D9" s="216"/>
-      <c r="E9" s="216"/>
-      <c r="F9" s="216"/>
-      <c r="G9" s="119"/>
-      <c r="H9" s="119"/>
-      <c r="I9" s="119"/>
-      <c r="J9" s="119"/>
-      <c r="K9" s="119"/>
-      <c r="L9" s="119"/>
-      <c r="M9" s="119"/>
-      <c r="N9" s="119"/>
-      <c r="O9" s="119"/>
-      <c r="P9" s="119"/>
-      <c r="Q9" s="119"/>
-      <c r="R9" s="119"/>
-      <c r="S9" s="119"/>
-      <c r="T9" s="119"/>
-      <c r="U9" s="119"/>
-      <c r="V9" s="119"/>
-      <c r="W9" s="119"/>
-      <c r="X9" s="119"/>
-      <c r="Y9" s="119"/>
-      <c r="Z9" s="119"/>
-      <c r="AA9" s="119"/>
-      <c r="AB9" s="119"/>
-      <c r="AC9" s="119"/>
-      <c r="AD9" s="119"/>
-      <c r="AE9" s="119"/>
-      <c r="AF9" s="119"/>
-      <c r="AG9" s="119"/>
-      <c r="AH9" s="119"/>
-      <c r="AI9" s="119"/>
-      <c r="AJ9" s="119"/>
-      <c r="AK9" s="119"/>
-      <c r="AL9" s="119"/>
+      <c r="A9" s="218"/>
+      <c r="B9" s="218"/>
+      <c r="C9" s="218"/>
+      <c r="D9" s="218"/>
+      <c r="E9" s="218"/>
+      <c r="F9" s="218"/>
+      <c r="G9" s="121"/>
+      <c r="H9" s="121"/>
+      <c r="I9" s="121"/>
+      <c r="J9" s="121"/>
+      <c r="K9" s="121"/>
+      <c r="L9" s="121"/>
+      <c r="M9" s="121"/>
+      <c r="N9" s="121"/>
+      <c r="O9" s="121"/>
+      <c r="P9" s="121"/>
+      <c r="Q9" s="121"/>
+      <c r="R9" s="121"/>
+      <c r="S9" s="121"/>
+      <c r="T9" s="121"/>
+      <c r="U9" s="121"/>
+      <c r="V9" s="121"/>
+      <c r="W9" s="121"/>
+      <c r="X9" s="121"/>
+      <c r="Y9" s="121"/>
+      <c r="Z9" s="121"/>
+      <c r="AA9" s="121"/>
+      <c r="AB9" s="121"/>
+      <c r="AC9" s="121"/>
+      <c r="AD9" s="121"/>
+      <c r="AE9" s="121"/>
+      <c r="AF9" s="121"/>
+      <c r="AG9" s="121"/>
+      <c r="AH9" s="121"/>
+      <c r="AI9" s="121"/>
+      <c r="AJ9" s="121"/>
+      <c r="AK9" s="121"/>
+      <c r="AL9" s="121"/>
     </row>
     <row r="10" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="216"/>
-      <c r="B10" s="216"/>
-      <c r="C10" s="216"/>
-      <c r="D10" s="216"/>
-      <c r="E10" s="216"/>
-      <c r="F10" s="216"/>
-      <c r="G10" s="119"/>
-      <c r="H10" s="119"/>
-      <c r="I10" s="119"/>
-      <c r="J10" s="119"/>
-      <c r="K10" s="119"/>
-      <c r="L10" s="119"/>
-      <c r="M10" s="119"/>
-      <c r="N10" s="119"/>
-      <c r="O10" s="119"/>
-      <c r="P10" s="119"/>
-      <c r="Q10" s="119"/>
-      <c r="R10" s="119"/>
-      <c r="S10" s="119"/>
-      <c r="T10" s="119"/>
-      <c r="U10" s="119"/>
-      <c r="V10" s="119"/>
-      <c r="W10" s="119"/>
-      <c r="X10" s="119"/>
-      <c r="Y10" s="119"/>
-      <c r="Z10" s="119"/>
-      <c r="AA10" s="119"/>
-      <c r="AB10" s="119"/>
-      <c r="AC10" s="119"/>
-      <c r="AD10" s="119"/>
-      <c r="AE10" s="119"/>
-      <c r="AF10" s="119"/>
-      <c r="AG10" s="119"/>
-      <c r="AH10" s="119"/>
-      <c r="AI10" s="119"/>
-      <c r="AJ10" s="119"/>
-      <c r="AK10" s="119"/>
-      <c r="AL10" s="119"/>
+      <c r="A10" s="218"/>
+      <c r="B10" s="218"/>
+      <c r="C10" s="218"/>
+      <c r="D10" s="218"/>
+      <c r="E10" s="218"/>
+      <c r="F10" s="218"/>
+      <c r="G10" s="121"/>
+      <c r="H10" s="121"/>
+      <c r="I10" s="121"/>
+      <c r="J10" s="121"/>
+      <c r="K10" s="121"/>
+      <c r="L10" s="121"/>
+      <c r="M10" s="121"/>
+      <c r="N10" s="121"/>
+      <c r="O10" s="121"/>
+      <c r="P10" s="121"/>
+      <c r="Q10" s="121"/>
+      <c r="R10" s="121"/>
+      <c r="S10" s="121"/>
+      <c r="T10" s="121"/>
+      <c r="U10" s="121"/>
+      <c r="V10" s="121"/>
+      <c r="W10" s="121"/>
+      <c r="X10" s="121"/>
+      <c r="Y10" s="121"/>
+      <c r="Z10" s="121"/>
+      <c r="AA10" s="121"/>
+      <c r="AB10" s="121"/>
+      <c r="AC10" s="121"/>
+      <c r="AD10" s="121"/>
+      <c r="AE10" s="121"/>
+      <c r="AF10" s="121"/>
+      <c r="AG10" s="121"/>
+      <c r="AH10" s="121"/>
+      <c r="AI10" s="121"/>
+      <c r="AJ10" s="121"/>
+      <c r="AK10" s="121"/>
+      <c r="AL10" s="121"/>
     </row>
     <row r="11" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
@@ -3900,214 +3907,214 @@
       <c r="AL11"/>
     </row>
     <row r="12" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="207" t="s">
+      <c r="A12" s="209" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="208"/>
-      <c r="C12" s="208"/>
-      <c r="D12" s="208"/>
-      <c r="E12" s="208"/>
-      <c r="F12" s="209"/>
-      <c r="G12" s="213" t="s">
+      <c r="B12" s="210"/>
+      <c r="C12" s="210"/>
+      <c r="D12" s="210"/>
+      <c r="E12" s="210"/>
+      <c r="F12" s="211"/>
+      <c r="G12" s="215" t="s">
         <v>118</v>
       </c>
-      <c r="H12" s="214"/>
-      <c r="I12" s="214"/>
-      <c r="J12" s="214"/>
-      <c r="K12" s="214"/>
-      <c r="L12" s="214"/>
-      <c r="M12" s="214"/>
-      <c r="N12" s="214"/>
-      <c r="O12" s="214"/>
-      <c r="P12" s="214"/>
-      <c r="Q12" s="214"/>
-      <c r="R12" s="214"/>
-      <c r="S12" s="214"/>
-      <c r="T12" s="214"/>
-      <c r="U12" s="214"/>
-      <c r="V12" s="214"/>
-      <c r="W12" s="214"/>
-      <c r="X12" s="214"/>
-      <c r="Y12" s="214"/>
-      <c r="Z12" s="214"/>
-      <c r="AA12" s="214"/>
-      <c r="AB12" s="214"/>
-      <c r="AC12" s="214"/>
-      <c r="AD12" s="214"/>
-      <c r="AE12" s="214"/>
-      <c r="AF12" s="214"/>
-      <c r="AG12" s="214"/>
-      <c r="AH12" s="214"/>
-      <c r="AI12" s="214"/>
-      <c r="AJ12" s="214"/>
-      <c r="AK12" s="214"/>
-      <c r="AL12" s="215"/>
+      <c r="H12" s="216"/>
+      <c r="I12" s="216"/>
+      <c r="J12" s="216"/>
+      <c r="K12" s="216"/>
+      <c r="L12" s="216"/>
+      <c r="M12" s="216"/>
+      <c r="N12" s="216"/>
+      <c r="O12" s="216"/>
+      <c r="P12" s="216"/>
+      <c r="Q12" s="216"/>
+      <c r="R12" s="216"/>
+      <c r="S12" s="216"/>
+      <c r="T12" s="216"/>
+      <c r="U12" s="216"/>
+      <c r="V12" s="216"/>
+      <c r="W12" s="216"/>
+      <c r="X12" s="216"/>
+      <c r="Y12" s="216"/>
+      <c r="Z12" s="216"/>
+      <c r="AA12" s="216"/>
+      <c r="AB12" s="216"/>
+      <c r="AC12" s="216"/>
+      <c r="AD12" s="216"/>
+      <c r="AE12" s="216"/>
+      <c r="AF12" s="216"/>
+      <c r="AG12" s="216"/>
+      <c r="AH12" s="216"/>
+      <c r="AI12" s="216"/>
+      <c r="AJ12" s="216"/>
+      <c r="AK12" s="216"/>
+      <c r="AL12" s="217"/>
     </row>
     <row r="13" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="210"/>
-      <c r="B13" s="211"/>
-      <c r="C13" s="211"/>
-      <c r="D13" s="211"/>
-      <c r="E13" s="211"/>
-      <c r="F13" s="212"/>
-      <c r="G13" s="124" t="s">
+      <c r="A13" s="212"/>
+      <c r="B13" s="213"/>
+      <c r="C13" s="213"/>
+      <c r="D13" s="213"/>
+      <c r="E13" s="213"/>
+      <c r="F13" s="214"/>
+      <c r="G13" s="126" t="s">
         <v>204</v>
       </c>
-      <c r="H13" s="119"/>
-      <c r="I13" s="119"/>
-      <c r="J13" s="119"/>
-      <c r="K13" s="119"/>
-      <c r="L13" s="119"/>
-      <c r="M13" s="119"/>
-      <c r="N13" s="119"/>
-      <c r="O13" s="119"/>
-      <c r="P13" s="119"/>
-      <c r="Q13" s="119"/>
-      <c r="R13" s="124" t="s">
+      <c r="H13" s="121"/>
+      <c r="I13" s="121"/>
+      <c r="J13" s="121"/>
+      <c r="K13" s="121"/>
+      <c r="L13" s="121"/>
+      <c r="M13" s="121"/>
+      <c r="N13" s="121"/>
+      <c r="O13" s="121"/>
+      <c r="P13" s="121"/>
+      <c r="Q13" s="121"/>
+      <c r="R13" s="126" t="s">
         <v>205</v>
       </c>
-      <c r="S13" s="119"/>
-      <c r="T13" s="119"/>
-      <c r="U13" s="119"/>
-      <c r="V13" s="119"/>
-      <c r="W13" s="119"/>
-      <c r="X13" s="119"/>
-      <c r="Y13" s="119"/>
-      <c r="Z13" s="119"/>
-      <c r="AA13" s="119"/>
-      <c r="AB13" s="119"/>
-      <c r="AC13" s="124" t="s">
+      <c r="S13" s="121"/>
+      <c r="T13" s="121"/>
+      <c r="U13" s="121"/>
+      <c r="V13" s="121"/>
+      <c r="W13" s="121"/>
+      <c r="X13" s="121"/>
+      <c r="Y13" s="121"/>
+      <c r="Z13" s="121"/>
+      <c r="AA13" s="121"/>
+      <c r="AB13" s="121"/>
+      <c r="AC13" s="126" t="s">
         <v>206</v>
       </c>
-      <c r="AD13" s="119"/>
-      <c r="AE13" s="119"/>
-      <c r="AF13" s="119"/>
-      <c r="AG13" s="119"/>
-      <c r="AH13" s="119"/>
-      <c r="AI13" s="119"/>
-      <c r="AJ13" s="119"/>
-      <c r="AK13" s="119"/>
-      <c r="AL13" s="119"/>
+      <c r="AD13" s="121"/>
+      <c r="AE13" s="121"/>
+      <c r="AF13" s="121"/>
+      <c r="AG13" s="121"/>
+      <c r="AH13" s="121"/>
+      <c r="AI13" s="121"/>
+      <c r="AJ13" s="121"/>
+      <c r="AK13" s="121"/>
+      <c r="AL13" s="121"/>
     </row>
     <row r="14" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A14" s="216"/>
-      <c r="B14" s="216"/>
-      <c r="C14" s="216"/>
-      <c r="D14" s="216"/>
-      <c r="E14" s="216"/>
-      <c r="F14" s="216"/>
-      <c r="G14" s="119"/>
-      <c r="H14" s="119"/>
-      <c r="I14" s="119"/>
-      <c r="J14" s="119"/>
-      <c r="K14" s="119"/>
-      <c r="L14" s="119"/>
-      <c r="M14" s="119"/>
-      <c r="N14" s="119"/>
-      <c r="O14" s="119"/>
-      <c r="P14" s="119"/>
-      <c r="Q14" s="119"/>
-      <c r="R14" s="119"/>
-      <c r="S14" s="119"/>
-      <c r="T14" s="119"/>
-      <c r="U14" s="119"/>
-      <c r="V14" s="119"/>
-      <c r="W14" s="119"/>
-      <c r="X14" s="119"/>
-      <c r="Y14" s="119"/>
-      <c r="Z14" s="119"/>
-      <c r="AA14" s="119"/>
-      <c r="AB14" s="119"/>
-      <c r="AC14" s="119"/>
-      <c r="AD14" s="119"/>
-      <c r="AE14" s="119"/>
-      <c r="AF14" s="119"/>
-      <c r="AG14" s="119"/>
-      <c r="AH14" s="119"/>
-      <c r="AI14" s="119"/>
-      <c r="AJ14" s="119"/>
-      <c r="AK14" s="119"/>
-      <c r="AL14" s="119"/>
+      <c r="A14" s="218"/>
+      <c r="B14" s="218"/>
+      <c r="C14" s="218"/>
+      <c r="D14" s="218"/>
+      <c r="E14" s="218"/>
+      <c r="F14" s="218"/>
+      <c r="G14" s="121"/>
+      <c r="H14" s="121"/>
+      <c r="I14" s="121"/>
+      <c r="J14" s="121"/>
+      <c r="K14" s="121"/>
+      <c r="L14" s="121"/>
+      <c r="M14" s="121"/>
+      <c r="N14" s="121"/>
+      <c r="O14" s="121"/>
+      <c r="P14" s="121"/>
+      <c r="Q14" s="121"/>
+      <c r="R14" s="121"/>
+      <c r="S14" s="121"/>
+      <c r="T14" s="121"/>
+      <c r="U14" s="121"/>
+      <c r="V14" s="121"/>
+      <c r="W14" s="121"/>
+      <c r="X14" s="121"/>
+      <c r="Y14" s="121"/>
+      <c r="Z14" s="121"/>
+      <c r="AA14" s="121"/>
+      <c r="AB14" s="121"/>
+      <c r="AC14" s="121"/>
+      <c r="AD14" s="121"/>
+      <c r="AE14" s="121"/>
+      <c r="AF14" s="121"/>
+      <c r="AG14" s="121"/>
+      <c r="AH14" s="121"/>
+      <c r="AI14" s="121"/>
+      <c r="AJ14" s="121"/>
+      <c r="AK14" s="121"/>
+      <c r="AL14" s="121"/>
     </row>
     <row r="15" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A15" s="216"/>
-      <c r="B15" s="216"/>
-      <c r="C15" s="216"/>
-      <c r="D15" s="216"/>
-      <c r="E15" s="216"/>
-      <c r="F15" s="216"/>
-      <c r="G15" s="119"/>
-      <c r="H15" s="119"/>
-      <c r="I15" s="119"/>
-      <c r="J15" s="119"/>
-      <c r="K15" s="119"/>
-      <c r="L15" s="119"/>
-      <c r="M15" s="119"/>
-      <c r="N15" s="119"/>
-      <c r="O15" s="119"/>
-      <c r="P15" s="119"/>
-      <c r="Q15" s="119"/>
-      <c r="R15" s="119"/>
-      <c r="S15" s="119"/>
-      <c r="T15" s="119"/>
-      <c r="U15" s="119"/>
-      <c r="V15" s="119"/>
-      <c r="W15" s="119"/>
-      <c r="X15" s="119"/>
-      <c r="Y15" s="119"/>
-      <c r="Z15" s="119"/>
-      <c r="AA15" s="119"/>
-      <c r="AB15" s="119"/>
-      <c r="AC15" s="119"/>
-      <c r="AD15" s="119"/>
-      <c r="AE15" s="119"/>
-      <c r="AF15" s="119"/>
-      <c r="AG15" s="119"/>
-      <c r="AH15" s="119"/>
-      <c r="AI15" s="119"/>
-      <c r="AJ15" s="119"/>
-      <c r="AK15" s="119"/>
-      <c r="AL15" s="119"/>
+      <c r="A15" s="218"/>
+      <c r="B15" s="218"/>
+      <c r="C15" s="218"/>
+      <c r="D15" s="218"/>
+      <c r="E15" s="218"/>
+      <c r="F15" s="218"/>
+      <c r="G15" s="121"/>
+      <c r="H15" s="121"/>
+      <c r="I15" s="121"/>
+      <c r="J15" s="121"/>
+      <c r="K15" s="121"/>
+      <c r="L15" s="121"/>
+      <c r="M15" s="121"/>
+      <c r="N15" s="121"/>
+      <c r="O15" s="121"/>
+      <c r="P15" s="121"/>
+      <c r="Q15" s="121"/>
+      <c r="R15" s="121"/>
+      <c r="S15" s="121"/>
+      <c r="T15" s="121"/>
+      <c r="U15" s="121"/>
+      <c r="V15" s="121"/>
+      <c r="W15" s="121"/>
+      <c r="X15" s="121"/>
+      <c r="Y15" s="121"/>
+      <c r="Z15" s="121"/>
+      <c r="AA15" s="121"/>
+      <c r="AB15" s="121"/>
+      <c r="AC15" s="121"/>
+      <c r="AD15" s="121"/>
+      <c r="AE15" s="121"/>
+      <c r="AF15" s="121"/>
+      <c r="AG15" s="121"/>
+      <c r="AH15" s="121"/>
+      <c r="AI15" s="121"/>
+      <c r="AJ15" s="121"/>
+      <c r="AK15" s="121"/>
+      <c r="AL15" s="121"/>
     </row>
     <row r="16" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A16" s="216"/>
-      <c r="B16" s="216"/>
-      <c r="C16" s="216"/>
-      <c r="D16" s="216"/>
-      <c r="E16" s="216"/>
-      <c r="F16" s="216"/>
-      <c r="G16" s="119"/>
-      <c r="H16" s="119"/>
-      <c r="I16" s="119"/>
-      <c r="J16" s="119"/>
-      <c r="K16" s="119"/>
-      <c r="L16" s="119"/>
-      <c r="M16" s="119"/>
-      <c r="N16" s="119"/>
-      <c r="O16" s="119"/>
-      <c r="P16" s="119"/>
-      <c r="Q16" s="119"/>
-      <c r="R16" s="119"/>
-      <c r="S16" s="119"/>
-      <c r="T16" s="119"/>
-      <c r="U16" s="119"/>
-      <c r="V16" s="119"/>
-      <c r="W16" s="119"/>
-      <c r="X16" s="119"/>
-      <c r="Y16" s="119"/>
-      <c r="Z16" s="119"/>
-      <c r="AA16" s="119"/>
-      <c r="AB16" s="119"/>
-      <c r="AC16" s="119"/>
-      <c r="AD16" s="119"/>
-      <c r="AE16" s="119"/>
-      <c r="AF16" s="119"/>
-      <c r="AG16" s="119"/>
-      <c r="AH16" s="119"/>
-      <c r="AI16" s="119"/>
-      <c r="AJ16" s="119"/>
-      <c r="AK16" s="119"/>
-      <c r="AL16" s="119"/>
+      <c r="A16" s="218"/>
+      <c r="B16" s="218"/>
+      <c r="C16" s="218"/>
+      <c r="D16" s="218"/>
+      <c r="E16" s="218"/>
+      <c r="F16" s="218"/>
+      <c r="G16" s="121"/>
+      <c r="H16" s="121"/>
+      <c r="I16" s="121"/>
+      <c r="J16" s="121"/>
+      <c r="K16" s="121"/>
+      <c r="L16" s="121"/>
+      <c r="M16" s="121"/>
+      <c r="N16" s="121"/>
+      <c r="O16" s="121"/>
+      <c r="P16" s="121"/>
+      <c r="Q16" s="121"/>
+      <c r="R16" s="121"/>
+      <c r="S16" s="121"/>
+      <c r="T16" s="121"/>
+      <c r="U16" s="121"/>
+      <c r="V16" s="121"/>
+      <c r="W16" s="121"/>
+      <c r="X16" s="121"/>
+      <c r="Y16" s="121"/>
+      <c r="Z16" s="121"/>
+      <c r="AA16" s="121"/>
+      <c r="AB16" s="121"/>
+      <c r="AC16" s="121"/>
+      <c r="AD16" s="121"/>
+      <c r="AE16" s="121"/>
+      <c r="AF16" s="121"/>
+      <c r="AG16" s="121"/>
+      <c r="AH16" s="121"/>
+      <c r="AI16" s="121"/>
+      <c r="AJ16" s="121"/>
+      <c r="AK16" s="121"/>
+      <c r="AL16" s="121"/>
     </row>
     <row r="17" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A17" s="42"/>
@@ -4158,36 +4165,36 @@
       <c r="A19" s="53" t="s">
         <v>158</v>
       </c>
-      <c r="G19" s="158" t="s">
+      <c r="G19" s="160" t="s">
         <v>159</v>
       </c>
-      <c r="H19" s="158"/>
+      <c r="H19" s="160"/>
       <c r="I19" s="72" t="s">
         <v>160</v>
       </c>
-      <c r="AJ19" s="217">
+      <c r="AJ19" s="219">
         <v>40</v>
       </c>
-      <c r="AK19" s="217"/>
-      <c r="AL19" s="217"/>
+      <c r="AK19" s="219"/>
+      <c r="AL19" s="219"/>
     </row>
     <row r="20" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A20" s="53" t="s">
         <v>161</v>
       </c>
-      <c r="P20" s="217" t="s">
+      <c r="P20" s="219" t="s">
         <v>162</v>
       </c>
-      <c r="Q20" s="217"/>
-      <c r="R20" s="217"/>
-      <c r="S20" s="217"/>
-      <c r="T20" s="217"/>
-      <c r="U20" s="217"/>
-      <c r="V20" s="217"/>
-      <c r="W20" s="217"/>
-      <c r="X20" s="217"/>
-      <c r="Y20" s="217"/>
-      <c r="Z20" s="217"/>
+      <c r="Q20" s="219"/>
+      <c r="R20" s="219"/>
+      <c r="S20" s="219"/>
+      <c r="T20" s="219"/>
+      <c r="U20" s="219"/>
+      <c r="V20" s="219"/>
+      <c r="W20" s="219"/>
+      <c r="X20" s="219"/>
+      <c r="Y20" s="219"/>
+      <c r="Z20" s="219"/>
       <c r="AA20" s="66" t="s">
         <v>163</v>
       </c>
@@ -4212,16 +4219,16 @@
       <c r="O21" s="57"/>
       <c r="P21" s="57"/>
       <c r="Q21" s="57"/>
-      <c r="S21" s="218" t="s">
+      <c r="S21" s="220" t="s">
         <v>222</v>
       </c>
-      <c r="T21" s="218"/>
-      <c r="U21" s="218"/>
-      <c r="V21" s="218"/>
-      <c r="W21" s="218"/>
-      <c r="X21" s="218"/>
-      <c r="Y21" s="218"/>
-      <c r="Z21" s="218"/>
+      <c r="T21" s="220"/>
+      <c r="U21" s="220"/>
+      <c r="V21" s="220"/>
+      <c r="W21" s="220"/>
+      <c r="X21" s="220"/>
+      <c r="Y21" s="220"/>
+      <c r="Z21" s="220"/>
       <c r="AA21" s="53" t="s">
         <v>165</v>
       </c>
@@ -4897,32 +4904,32 @@
       <c r="J1" s="54"/>
       <c r="K1" s="54"/>
       <c r="L1" s="54"/>
-      <c r="M1" s="150"/>
-      <c r="N1" s="150"/>
-      <c r="O1" s="150"/>
-      <c r="P1" s="150"/>
-      <c r="Q1" s="150"/>
-      <c r="R1" s="150"/>
-      <c r="S1" s="150"/>
-      <c r="T1" s="150"/>
-      <c r="U1" s="150"/>
-      <c r="V1" s="150"/>
-      <c r="W1" s="150"/>
-      <c r="X1" s="150"/>
-      <c r="Y1" s="150"/>
-      <c r="Z1" s="150"/>
-      <c r="AA1" s="150"/>
-      <c r="AB1" s="150"/>
-      <c r="AC1" s="150"/>
-      <c r="AD1" s="150"/>
-      <c r="AE1" s="150"/>
-      <c r="AF1" s="150"/>
-      <c r="AG1" s="150"/>
-      <c r="AH1" s="150"/>
-      <c r="AI1" s="150"/>
-      <c r="AJ1" s="150"/>
-      <c r="AK1" s="150"/>
-      <c r="AL1" s="150"/>
+      <c r="M1" s="152"/>
+      <c r="N1" s="152"/>
+      <c r="O1" s="152"/>
+      <c r="P1" s="152"/>
+      <c r="Q1" s="152"/>
+      <c r="R1" s="152"/>
+      <c r="S1" s="152"/>
+      <c r="T1" s="152"/>
+      <c r="U1" s="152"/>
+      <c r="V1" s="152"/>
+      <c r="W1" s="152"/>
+      <c r="X1" s="152"/>
+      <c r="Y1" s="152"/>
+      <c r="Z1" s="152"/>
+      <c r="AA1" s="152"/>
+      <c r="AB1" s="152"/>
+      <c r="AC1" s="152"/>
+      <c r="AD1" s="152"/>
+      <c r="AE1" s="152"/>
+      <c r="AF1" s="152"/>
+      <c r="AG1" s="152"/>
+      <c r="AH1" s="152"/>
+      <c r="AI1" s="152"/>
+      <c r="AJ1" s="152"/>
+      <c r="AK1" s="152"/>
+      <c r="AL1" s="152"/>
     </row>
     <row r="2" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A2" s="55" t="s">
@@ -4964,17 +4971,17 @@
       <c r="AL2" s="56"/>
     </row>
     <row r="3" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A3" s="157"/>
-      <c r="B3" s="157"/>
-      <c r="C3" s="157"/>
-      <c r="D3" s="157"/>
-      <c r="E3" s="157"/>
-      <c r="F3" s="157"/>
-      <c r="G3" s="157"/>
-      <c r="H3" s="157"/>
-      <c r="I3" s="157"/>
-      <c r="J3" s="157"/>
-      <c r="K3" s="157"/>
+      <c r="A3" s="159"/>
+      <c r="B3" s="159"/>
+      <c r="C3" s="159"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="159"/>
+      <c r="G3" s="159"/>
+      <c r="H3" s="159"/>
+      <c r="I3" s="159"/>
+      <c r="J3" s="159"/>
+      <c r="K3" s="159"/>
       <c r="L3" s="54"/>
       <c r="M3" s="56"/>
       <c r="N3" s="56"/>
@@ -5131,9 +5138,9 @@
       <c r="A7" s="55" t="s">
         <v>143</v>
       </c>
-      <c r="E7" s="219"/>
-      <c r="F7" s="219"/>
-      <c r="G7" s="219"/>
+      <c r="E7" s="221"/>
+      <c r="F7" s="221"/>
+      <c r="G7" s="221"/>
       <c r="H7" s="63" t="s">
         <v>144</v>
       </c>
@@ -5164,270 +5171,270 @@
       <c r="AL7" s="56"/>
     </row>
     <row r="8" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A8" s="136" t="s">
+      <c r="A8" s="138" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="136"/>
-      <c r="C8" s="136"/>
-      <c r="D8" s="136"/>
-      <c r="E8" s="136"/>
-      <c r="F8" s="136" t="s">
+      <c r="B8" s="138"/>
+      <c r="C8" s="138"/>
+      <c r="D8" s="138"/>
+      <c r="E8" s="138"/>
+      <c r="F8" s="138" t="s">
         <v>146</v>
       </c>
-      <c r="G8" s="136"/>
-      <c r="H8" s="136"/>
-      <c r="I8" s="136"/>
-      <c r="J8" s="136" t="s">
+      <c r="G8" s="138"/>
+      <c r="H8" s="138"/>
+      <c r="I8" s="138"/>
+      <c r="J8" s="138" t="s">
         <v>18</v>
       </c>
-      <c r="K8" s="136"/>
-      <c r="L8" s="136"/>
-      <c r="M8" s="136"/>
-      <c r="N8" s="136"/>
-      <c r="O8" s="136"/>
-      <c r="P8" s="136"/>
-      <c r="Q8" s="136"/>
-      <c r="R8" s="136"/>
-      <c r="S8" s="136"/>
-      <c r="T8" s="136"/>
-      <c r="U8" s="136"/>
-      <c r="V8" s="136"/>
-      <c r="W8" s="136"/>
-      <c r="X8" s="136"/>
-      <c r="Y8" s="136"/>
-      <c r="Z8" s="136"/>
-      <c r="AA8" s="136"/>
-      <c r="AB8" s="136"/>
-      <c r="AC8" s="136"/>
-      <c r="AD8" s="136"/>
-      <c r="AE8" s="136"/>
-      <c r="AF8" s="136"/>
-      <c r="AG8" s="136"/>
-      <c r="AH8" s="136"/>
-      <c r="AI8" s="127" t="s">
+      <c r="K8" s="138"/>
+      <c r="L8" s="138"/>
+      <c r="M8" s="138"/>
+      <c r="N8" s="138"/>
+      <c r="O8" s="138"/>
+      <c r="P8" s="138"/>
+      <c r="Q8" s="138"/>
+      <c r="R8" s="138"/>
+      <c r="S8" s="138"/>
+      <c r="T8" s="138"/>
+      <c r="U8" s="138"/>
+      <c r="V8" s="138"/>
+      <c r="W8" s="138"/>
+      <c r="X8" s="138"/>
+      <c r="Y8" s="138"/>
+      <c r="Z8" s="138"/>
+      <c r="AA8" s="138"/>
+      <c r="AB8" s="138"/>
+      <c r="AC8" s="138"/>
+      <c r="AD8" s="138"/>
+      <c r="AE8" s="138"/>
+      <c r="AF8" s="138"/>
+      <c r="AG8" s="138"/>
+      <c r="AH8" s="138"/>
+      <c r="AI8" s="129" t="s">
         <v>147</v>
       </c>
-      <c r="AJ8" s="128"/>
-      <c r="AK8" s="128"/>
-      <c r="AL8" s="129"/>
+      <c r="AJ8" s="130"/>
+      <c r="AK8" s="130"/>
+      <c r="AL8" s="131"/>
     </row>
     <row r="9" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A9" s="136"/>
-      <c r="B9" s="136"/>
-      <c r="C9" s="136"/>
-      <c r="D9" s="136"/>
-      <c r="E9" s="136"/>
-      <c r="F9" s="136"/>
-      <c r="G9" s="136"/>
-      <c r="H9" s="136"/>
-      <c r="I9" s="136"/>
-      <c r="J9" s="136" t="s">
+      <c r="A9" s="138"/>
+      <c r="B9" s="138"/>
+      <c r="C9" s="138"/>
+      <c r="D9" s="138"/>
+      <c r="E9" s="138"/>
+      <c r="F9" s="138"/>
+      <c r="G9" s="138"/>
+      <c r="H9" s="138"/>
+      <c r="I9" s="138"/>
+      <c r="J9" s="138" t="s">
         <v>9</v>
       </c>
-      <c r="K9" s="136"/>
-      <c r="L9" s="136"/>
-      <c r="M9" s="136"/>
-      <c r="N9" s="136"/>
-      <c r="O9" s="136" t="s">
+      <c r="K9" s="138"/>
+      <c r="L9" s="138"/>
+      <c r="M9" s="138"/>
+      <c r="N9" s="138"/>
+      <c r="O9" s="138" t="s">
         <v>10</v>
       </c>
-      <c r="P9" s="136"/>
-      <c r="Q9" s="136"/>
-      <c r="R9" s="136"/>
-      <c r="S9" s="136"/>
-      <c r="T9" s="136" t="s">
+      <c r="P9" s="138"/>
+      <c r="Q9" s="138"/>
+      <c r="R9" s="138"/>
+      <c r="S9" s="138"/>
+      <c r="T9" s="138" t="s">
         <v>11</v>
       </c>
-      <c r="U9" s="136"/>
-      <c r="V9" s="136"/>
-      <c r="W9" s="136"/>
-      <c r="X9" s="136"/>
-      <c r="Y9" s="136" t="s">
+      <c r="U9" s="138"/>
+      <c r="V9" s="138"/>
+      <c r="W9" s="138"/>
+      <c r="X9" s="138"/>
+      <c r="Y9" s="138" t="s">
         <v>12</v>
       </c>
-      <c r="Z9" s="136"/>
-      <c r="AA9" s="136"/>
-      <c r="AB9" s="136"/>
-      <c r="AC9" s="136"/>
-      <c r="AD9" s="136" t="s">
+      <c r="Z9" s="138"/>
+      <c r="AA9" s="138"/>
+      <c r="AB9" s="138"/>
+      <c r="AC9" s="138"/>
+      <c r="AD9" s="138" t="s">
         <v>13</v>
       </c>
-      <c r="AE9" s="136"/>
-      <c r="AF9" s="136"/>
-      <c r="AG9" s="136"/>
-      <c r="AH9" s="136"/>
-      <c r="AI9" s="133"/>
-      <c r="AJ9" s="134"/>
-      <c r="AK9" s="134"/>
-      <c r="AL9" s="135"/>
+      <c r="AE9" s="138"/>
+      <c r="AF9" s="138"/>
+      <c r="AG9" s="138"/>
+      <c r="AH9" s="138"/>
+      <c r="AI9" s="135"/>
+      <c r="AJ9" s="136"/>
+      <c r="AK9" s="136"/>
+      <c r="AL9" s="137"/>
     </row>
     <row r="10" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="220"/>
-      <c r="B10" s="221"/>
-      <c r="C10" s="221"/>
-      <c r="D10" s="221"/>
-      <c r="E10" s="222"/>
-      <c r="F10" s="139" t="s">
+      <c r="A10" s="222"/>
+      <c r="B10" s="223"/>
+      <c r="C10" s="223"/>
+      <c r="D10" s="223"/>
+      <c r="E10" s="224"/>
+      <c r="F10" s="141" t="s">
         <v>148</v>
       </c>
-      <c r="G10" s="139"/>
-      <c r="H10" s="139"/>
-      <c r="I10" s="139"/>
-      <c r="J10" s="138"/>
-      <c r="K10" s="139"/>
-      <c r="L10" s="139"/>
-      <c r="M10" s="139"/>
-      <c r="N10" s="139"/>
-      <c r="O10" s="138"/>
-      <c r="P10" s="139"/>
-      <c r="Q10" s="139"/>
-      <c r="R10" s="139"/>
-      <c r="S10" s="139"/>
-      <c r="T10" s="138"/>
-      <c r="U10" s="139"/>
-      <c r="V10" s="139"/>
-      <c r="W10" s="139"/>
-      <c r="X10" s="139"/>
-      <c r="Y10" s="138"/>
-      <c r="Z10" s="139"/>
-      <c r="AA10" s="139"/>
-      <c r="AB10" s="139"/>
-      <c r="AC10" s="139"/>
-      <c r="AD10" s="138"/>
-      <c r="AE10" s="139"/>
-      <c r="AF10" s="139"/>
-      <c r="AG10" s="139"/>
-      <c r="AH10" s="139"/>
-      <c r="AI10" s="138"/>
-      <c r="AJ10" s="139"/>
-      <c r="AK10" s="139"/>
-      <c r="AL10" s="140"/>
+      <c r="G10" s="141"/>
+      <c r="H10" s="141"/>
+      <c r="I10" s="141"/>
+      <c r="J10" s="140"/>
+      <c r="K10" s="141"/>
+      <c r="L10" s="141"/>
+      <c r="M10" s="141"/>
+      <c r="N10" s="141"/>
+      <c r="O10" s="140"/>
+      <c r="P10" s="141"/>
+      <c r="Q10" s="141"/>
+      <c r="R10" s="141"/>
+      <c r="S10" s="141"/>
+      <c r="T10" s="140"/>
+      <c r="U10" s="141"/>
+      <c r="V10" s="141"/>
+      <c r="W10" s="141"/>
+      <c r="X10" s="141"/>
+      <c r="Y10" s="140"/>
+      <c r="Z10" s="141"/>
+      <c r="AA10" s="141"/>
+      <c r="AB10" s="141"/>
+      <c r="AC10" s="141"/>
+      <c r="AD10" s="140"/>
+      <c r="AE10" s="141"/>
+      <c r="AF10" s="141"/>
+      <c r="AG10" s="141"/>
+      <c r="AH10" s="141"/>
+      <c r="AI10" s="140"/>
+      <c r="AJ10" s="141"/>
+      <c r="AK10" s="141"/>
+      <c r="AL10" s="142"/>
     </row>
     <row r="11" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="223"/>
-      <c r="B11" s="189"/>
-      <c r="C11" s="189"/>
-      <c r="D11" s="189"/>
-      <c r="E11" s="224"/>
-      <c r="F11" s="139" t="s">
+      <c r="A11" s="225"/>
+      <c r="B11" s="193"/>
+      <c r="C11" s="193"/>
+      <c r="D11" s="193"/>
+      <c r="E11" s="226"/>
+      <c r="F11" s="141" t="s">
         <v>149</v>
       </c>
-      <c r="G11" s="139"/>
-      <c r="H11" s="139"/>
-      <c r="I11" s="139"/>
-      <c r="J11" s="138"/>
-      <c r="K11" s="139"/>
-      <c r="L11" s="139"/>
-      <c r="M11" s="139"/>
-      <c r="N11" s="139"/>
-      <c r="O11" s="138"/>
-      <c r="P11" s="139"/>
-      <c r="Q11" s="139"/>
-      <c r="R11" s="139"/>
-      <c r="S11" s="139"/>
-      <c r="T11" s="138"/>
-      <c r="U11" s="139"/>
-      <c r="V11" s="139"/>
-      <c r="W11" s="139"/>
-      <c r="X11" s="139"/>
-      <c r="Y11" s="138"/>
-      <c r="Z11" s="139"/>
-      <c r="AA11" s="139"/>
-      <c r="AB11" s="139"/>
-      <c r="AC11" s="139"/>
-      <c r="AD11" s="138"/>
-      <c r="AE11" s="139"/>
-      <c r="AF11" s="139"/>
-      <c r="AG11" s="139"/>
-      <c r="AH11" s="139"/>
-      <c r="AI11" s="138"/>
-      <c r="AJ11" s="139"/>
-      <c r="AK11" s="139"/>
-      <c r="AL11" s="140"/>
+      <c r="G11" s="141"/>
+      <c r="H11" s="141"/>
+      <c r="I11" s="141"/>
+      <c r="J11" s="140"/>
+      <c r="K11" s="141"/>
+      <c r="L11" s="141"/>
+      <c r="M11" s="141"/>
+      <c r="N11" s="141"/>
+      <c r="O11" s="140"/>
+      <c r="P11" s="141"/>
+      <c r="Q11" s="141"/>
+      <c r="R11" s="141"/>
+      <c r="S11" s="141"/>
+      <c r="T11" s="140"/>
+      <c r="U11" s="141"/>
+      <c r="V11" s="141"/>
+      <c r="W11" s="141"/>
+      <c r="X11" s="141"/>
+      <c r="Y11" s="140"/>
+      <c r="Z11" s="141"/>
+      <c r="AA11" s="141"/>
+      <c r="AB11" s="141"/>
+      <c r="AC11" s="141"/>
+      <c r="AD11" s="140"/>
+      <c r="AE11" s="141"/>
+      <c r="AF11" s="141"/>
+      <c r="AG11" s="141"/>
+      <c r="AH11" s="141"/>
+      <c r="AI11" s="140"/>
+      <c r="AJ11" s="141"/>
+      <c r="AK11" s="141"/>
+      <c r="AL11" s="142"/>
     </row>
     <row r="12" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="220"/>
-      <c r="B12" s="221"/>
-      <c r="C12" s="221"/>
-      <c r="D12" s="221"/>
-      <c r="E12" s="222"/>
-      <c r="F12" s="139" t="s">
+      <c r="A12" s="222"/>
+      <c r="B12" s="223"/>
+      <c r="C12" s="223"/>
+      <c r="D12" s="223"/>
+      <c r="E12" s="224"/>
+      <c r="F12" s="141" t="s">
         <v>148</v>
       </c>
-      <c r="G12" s="139"/>
-      <c r="H12" s="139"/>
-      <c r="I12" s="139"/>
-      <c r="J12" s="138"/>
-      <c r="K12" s="139"/>
-      <c r="L12" s="139"/>
-      <c r="M12" s="139"/>
-      <c r="N12" s="139"/>
-      <c r="O12" s="138"/>
-      <c r="P12" s="139"/>
-      <c r="Q12" s="139"/>
-      <c r="R12" s="139"/>
-      <c r="S12" s="139"/>
-      <c r="T12" s="138"/>
-      <c r="U12" s="139"/>
-      <c r="V12" s="139"/>
-      <c r="W12" s="139"/>
-      <c r="X12" s="139"/>
-      <c r="Y12" s="138"/>
-      <c r="Z12" s="139"/>
-      <c r="AA12" s="139"/>
-      <c r="AB12" s="139"/>
-      <c r="AC12" s="139"/>
-      <c r="AD12" s="138"/>
-      <c r="AE12" s="139"/>
-      <c r="AF12" s="139"/>
-      <c r="AG12" s="139"/>
-      <c r="AH12" s="139"/>
-      <c r="AI12" s="138"/>
-      <c r="AJ12" s="139"/>
-      <c r="AK12" s="139"/>
-      <c r="AL12" s="140"/>
+      <c r="G12" s="141"/>
+      <c r="H12" s="141"/>
+      <c r="I12" s="141"/>
+      <c r="J12" s="140"/>
+      <c r="K12" s="141"/>
+      <c r="L12" s="141"/>
+      <c r="M12" s="141"/>
+      <c r="N12" s="141"/>
+      <c r="O12" s="140"/>
+      <c r="P12" s="141"/>
+      <c r="Q12" s="141"/>
+      <c r="R12" s="141"/>
+      <c r="S12" s="141"/>
+      <c r="T12" s="140"/>
+      <c r="U12" s="141"/>
+      <c r="V12" s="141"/>
+      <c r="W12" s="141"/>
+      <c r="X12" s="141"/>
+      <c r="Y12" s="140"/>
+      <c r="Z12" s="141"/>
+      <c r="AA12" s="141"/>
+      <c r="AB12" s="141"/>
+      <c r="AC12" s="141"/>
+      <c r="AD12" s="140"/>
+      <c r="AE12" s="141"/>
+      <c r="AF12" s="141"/>
+      <c r="AG12" s="141"/>
+      <c r="AH12" s="141"/>
+      <c r="AI12" s="140"/>
+      <c r="AJ12" s="141"/>
+      <c r="AK12" s="141"/>
+      <c r="AL12" s="142"/>
     </row>
     <row r="13" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="223"/>
-      <c r="B13" s="189"/>
-      <c r="C13" s="189"/>
-      <c r="D13" s="189"/>
-      <c r="E13" s="224"/>
-      <c r="F13" s="139" t="s">
+      <c r="A13" s="225"/>
+      <c r="B13" s="193"/>
+      <c r="C13" s="193"/>
+      <c r="D13" s="193"/>
+      <c r="E13" s="226"/>
+      <c r="F13" s="141" t="s">
         <v>149</v>
       </c>
-      <c r="G13" s="139"/>
-      <c r="H13" s="139"/>
-      <c r="I13" s="139"/>
-      <c r="J13" s="138"/>
-      <c r="K13" s="139"/>
-      <c r="L13" s="139"/>
-      <c r="M13" s="139"/>
-      <c r="N13" s="139"/>
-      <c r="O13" s="138"/>
-      <c r="P13" s="139"/>
-      <c r="Q13" s="139"/>
-      <c r="R13" s="139"/>
-      <c r="S13" s="139"/>
-      <c r="T13" s="138"/>
-      <c r="U13" s="139"/>
-      <c r="V13" s="139"/>
-      <c r="W13" s="139"/>
-      <c r="X13" s="139"/>
-      <c r="Y13" s="138"/>
-      <c r="Z13" s="139"/>
-      <c r="AA13" s="139"/>
-      <c r="AB13" s="139"/>
-      <c r="AC13" s="139"/>
-      <c r="AD13" s="138"/>
-      <c r="AE13" s="139"/>
-      <c r="AF13" s="139"/>
-      <c r="AG13" s="139"/>
-      <c r="AH13" s="139"/>
-      <c r="AI13" s="138"/>
-      <c r="AJ13" s="139"/>
-      <c r="AK13" s="139"/>
-      <c r="AL13" s="140"/>
+      <c r="G13" s="141"/>
+      <c r="H13" s="141"/>
+      <c r="I13" s="141"/>
+      <c r="J13" s="140"/>
+      <c r="K13" s="141"/>
+      <c r="L13" s="141"/>
+      <c r="M13" s="141"/>
+      <c r="N13" s="141"/>
+      <c r="O13" s="140"/>
+      <c r="P13" s="141"/>
+      <c r="Q13" s="141"/>
+      <c r="R13" s="141"/>
+      <c r="S13" s="141"/>
+      <c r="T13" s="140"/>
+      <c r="U13" s="141"/>
+      <c r="V13" s="141"/>
+      <c r="W13" s="141"/>
+      <c r="X13" s="141"/>
+      <c r="Y13" s="140"/>
+      <c r="Z13" s="141"/>
+      <c r="AA13" s="141"/>
+      <c r="AB13" s="141"/>
+      <c r="AC13" s="141"/>
+      <c r="AD13" s="140"/>
+      <c r="AE13" s="141"/>
+      <c r="AF13" s="141"/>
+      <c r="AG13" s="141"/>
+      <c r="AH13" s="141"/>
+      <c r="AI13" s="140"/>
+      <c r="AJ13" s="141"/>
+      <c r="AK13" s="141"/>
+      <c r="AL13" s="142"/>
     </row>
     <row r="14" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A14" s="63" t="s">
@@ -5794,32 +5801,32 @@
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
-      <c r="M1" s="125"/>
-      <c r="N1" s="125"/>
-      <c r="O1" s="125"/>
-      <c r="P1" s="125"/>
-      <c r="Q1" s="125"/>
-      <c r="R1" s="125"/>
-      <c r="S1" s="125"/>
-      <c r="T1" s="125"/>
-      <c r="U1" s="125"/>
-      <c r="V1" s="125"/>
-      <c r="W1" s="125"/>
-      <c r="X1" s="125"/>
-      <c r="Y1" s="125"/>
-      <c r="Z1" s="125"/>
-      <c r="AA1" s="125"/>
-      <c r="AB1" s="125"/>
-      <c r="AC1" s="125"/>
-      <c r="AD1" s="125"/>
-      <c r="AE1" s="125"/>
-      <c r="AF1" s="125"/>
-      <c r="AG1" s="125"/>
-      <c r="AH1" s="125"/>
-      <c r="AI1" s="125"/>
-      <c r="AJ1" s="125"/>
-      <c r="AK1" s="125"/>
-      <c r="AL1" s="125"/>
+      <c r="M1" s="127"/>
+      <c r="N1" s="127"/>
+      <c r="O1" s="127"/>
+      <c r="P1" s="127"/>
+      <c r="Q1" s="127"/>
+      <c r="R1" s="127"/>
+      <c r="S1" s="127"/>
+      <c r="T1" s="127"/>
+      <c r="U1" s="127"/>
+      <c r="V1" s="127"/>
+      <c r="W1" s="127"/>
+      <c r="X1" s="127"/>
+      <c r="Y1" s="127"/>
+      <c r="Z1" s="127"/>
+      <c r="AA1" s="127"/>
+      <c r="AB1" s="127"/>
+      <c r="AC1" s="127"/>
+      <c r="AD1" s="127"/>
+      <c r="AE1" s="127"/>
+      <c r="AF1" s="127"/>
+      <c r="AG1" s="127"/>
+      <c r="AH1" s="127"/>
+      <c r="AI1" s="127"/>
+      <c r="AJ1" s="127"/>
+      <c r="AK1" s="127"/>
+      <c r="AL1" s="127"/>
     </row>
     <row r="2" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
@@ -5857,20 +5864,20 @@
       <c r="A3" s="43" t="s">
         <v>100</v>
       </c>
-      <c r="F3" s="115"/>
-      <c r="G3" s="115"/>
-      <c r="H3" s="115"/>
-      <c r="I3" s="115"/>
-      <c r="J3" s="115"/>
-      <c r="K3" s="115"/>
-      <c r="L3" s="115"/>
-      <c r="M3" s="115"/>
-      <c r="N3" s="115"/>
-      <c r="O3" s="115"/>
-      <c r="P3" s="115"/>
-      <c r="Q3" s="115"/>
-      <c r="R3" s="115"/>
-      <c r="S3" s="115"/>
+      <c r="F3" s="117"/>
+      <c r="G3" s="117"/>
+      <c r="H3" s="117"/>
+      <c r="I3" s="117"/>
+      <c r="J3" s="117"/>
+      <c r="K3" s="117"/>
+      <c r="L3" s="117"/>
+      <c r="M3" s="117"/>
+      <c r="N3" s="117"/>
+      <c r="O3" s="117"/>
+      <c r="P3" s="117"/>
+      <c r="Q3" s="117"/>
+      <c r="R3" s="117"/>
+      <c r="S3" s="117"/>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
       <c r="V3" s="1"/>
@@ -5888,13 +5895,13 @@
       <c r="A4" s="44" t="s">
         <v>93</v>
       </c>
-      <c r="D4" s="126"/>
-      <c r="E4" s="126"/>
-      <c r="F4" s="126"/>
-      <c r="G4" s="126"/>
-      <c r="H4" s="126"/>
-      <c r="I4" s="126"/>
-      <c r="J4" s="126"/>
+      <c r="D4" s="128"/>
+      <c r="E4" s="128"/>
+      <c r="F4" s="128"/>
+      <c r="G4" s="128"/>
+      <c r="H4" s="128"/>
+      <c r="I4" s="128"/>
+      <c r="J4" s="128"/>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
@@ -5960,238 +5967,238 @@
       <c r="AL5" s="1"/>
     </row>
     <row r="6" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="123" t="s">
+      <c r="A6" s="125" t="s">
         <v>101</v>
       </c>
-      <c r="B6" s="123"/>
-      <c r="C6" s="123"/>
-      <c r="D6" s="123"/>
-      <c r="E6" s="123"/>
-      <c r="F6" s="123"/>
-      <c r="G6" s="123"/>
-      <c r="H6" s="124" t="s">
+      <c r="B6" s="125"/>
+      <c r="C6" s="125"/>
+      <c r="D6" s="125"/>
+      <c r="E6" s="125"/>
+      <c r="F6" s="125"/>
+      <c r="G6" s="125"/>
+      <c r="H6" s="126" t="s">
         <v>95</v>
       </c>
-      <c r="I6" s="124"/>
-      <c r="J6" s="124"/>
-      <c r="K6" s="124"/>
-      <c r="L6" s="121" t="s">
+      <c r="I6" s="126"/>
+      <c r="J6" s="126"/>
+      <c r="K6" s="126"/>
+      <c r="L6" s="123" t="s">
         <v>96</v>
       </c>
-      <c r="M6" s="121"/>
-      <c r="N6" s="121"/>
-      <c r="O6" s="121"/>
-      <c r="P6" s="121"/>
-      <c r="Q6" s="121"/>
-      <c r="R6" s="121"/>
-      <c r="S6" s="121"/>
-      <c r="T6" s="121"/>
-      <c r="U6" s="121"/>
-      <c r="V6" s="121"/>
-      <c r="W6" s="121"/>
-      <c r="X6" s="124" t="s">
+      <c r="M6" s="123"/>
+      <c r="N6" s="123"/>
+      <c r="O6" s="123"/>
+      <c r="P6" s="123"/>
+      <c r="Q6" s="123"/>
+      <c r="R6" s="123"/>
+      <c r="S6" s="123"/>
+      <c r="T6" s="123"/>
+      <c r="U6" s="123"/>
+      <c r="V6" s="123"/>
+      <c r="W6" s="123"/>
+      <c r="X6" s="126" t="s">
         <v>95</v>
       </c>
-      <c r="Y6" s="124"/>
-      <c r="Z6" s="124"/>
-      <c r="AA6" s="124"/>
-      <c r="AB6" s="121" t="s">
+      <c r="Y6" s="126"/>
+      <c r="Z6" s="126"/>
+      <c r="AA6" s="126"/>
+      <c r="AB6" s="123" t="s">
         <v>96</v>
       </c>
-      <c r="AC6" s="121"/>
-      <c r="AD6" s="121"/>
-      <c r="AE6" s="121"/>
-      <c r="AF6" s="121"/>
-      <c r="AG6" s="121"/>
-      <c r="AH6" s="121"/>
-      <c r="AI6" s="121"/>
-      <c r="AJ6" s="121"/>
-      <c r="AK6" s="121"/>
-      <c r="AL6" s="121"/>
+      <c r="AC6" s="123"/>
+      <c r="AD6" s="123"/>
+      <c r="AE6" s="123"/>
+      <c r="AF6" s="123"/>
+      <c r="AG6" s="123"/>
+      <c r="AH6" s="123"/>
+      <c r="AI6" s="123"/>
+      <c r="AJ6" s="123"/>
+      <c r="AK6" s="123"/>
+      <c r="AL6" s="123"/>
     </row>
     <row r="7" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="123"/>
-      <c r="B7" s="123"/>
-      <c r="C7" s="123"/>
-      <c r="D7" s="123"/>
-      <c r="E7" s="123"/>
-      <c r="F7" s="123"/>
-      <c r="G7" s="123"/>
-      <c r="H7" s="124"/>
-      <c r="I7" s="124"/>
-      <c r="J7" s="124"/>
-      <c r="K7" s="124"/>
-      <c r="L7" s="121" t="s">
+      <c r="A7" s="125"/>
+      <c r="B7" s="125"/>
+      <c r="C7" s="125"/>
+      <c r="D7" s="125"/>
+      <c r="E7" s="125"/>
+      <c r="F7" s="125"/>
+      <c r="G7" s="125"/>
+      <c r="H7" s="126"/>
+      <c r="I7" s="126"/>
+      <c r="J7" s="126"/>
+      <c r="K7" s="126"/>
+      <c r="L7" s="123" t="s">
         <v>97</v>
       </c>
-      <c r="M7" s="121"/>
-      <c r="N7" s="121"/>
-      <c r="O7" s="121"/>
-      <c r="P7" s="121" t="s">
+      <c r="M7" s="123"/>
+      <c r="N7" s="123"/>
+      <c r="O7" s="123"/>
+      <c r="P7" s="123" t="s">
         <v>98</v>
       </c>
-      <c r="Q7" s="121"/>
-      <c r="R7" s="121"/>
-      <c r="S7" s="121"/>
-      <c r="T7" s="121" t="s">
+      <c r="Q7" s="123"/>
+      <c r="R7" s="123"/>
+      <c r="S7" s="123"/>
+      <c r="T7" s="123" t="s">
         <v>99</v>
       </c>
-      <c r="U7" s="121"/>
-      <c r="V7" s="121"/>
-      <c r="W7" s="121"/>
-      <c r="X7" s="124"/>
-      <c r="Y7" s="124"/>
-      <c r="Z7" s="124"/>
-      <c r="AA7" s="124"/>
-      <c r="AB7" s="121" t="s">
+      <c r="U7" s="123"/>
+      <c r="V7" s="123"/>
+      <c r="W7" s="123"/>
+      <c r="X7" s="126"/>
+      <c r="Y7" s="126"/>
+      <c r="Z7" s="126"/>
+      <c r="AA7" s="126"/>
+      <c r="AB7" s="123" t="s">
         <v>97</v>
       </c>
-      <c r="AC7" s="121"/>
-      <c r="AD7" s="121"/>
-      <c r="AE7" s="121"/>
-      <c r="AF7" s="121" t="s">
+      <c r="AC7" s="123"/>
+      <c r="AD7" s="123"/>
+      <c r="AE7" s="123"/>
+      <c r="AF7" s="123" t="s">
         <v>98</v>
       </c>
-      <c r="AG7" s="121"/>
-      <c r="AH7" s="121"/>
-      <c r="AI7" s="121"/>
-      <c r="AJ7" s="121" t="s">
+      <c r="AG7" s="123"/>
+      <c r="AH7" s="123"/>
+      <c r="AI7" s="123"/>
+      <c r="AJ7" s="123" t="s">
         <v>99</v>
       </c>
-      <c r="AK7" s="121"/>
-      <c r="AL7" s="121"/>
+      <c r="AK7" s="123"/>
+      <c r="AL7" s="123"/>
     </row>
     <row r="8" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="122"/>
-      <c r="B8" s="122"/>
-      <c r="C8" s="122"/>
-      <c r="D8" s="122"/>
-      <c r="E8" s="122"/>
-      <c r="F8" s="122"/>
-      <c r="G8" s="122"/>
-      <c r="H8" s="119">
+      <c r="A8" s="124"/>
+      <c r="B8" s="124"/>
+      <c r="C8" s="124"/>
+      <c r="D8" s="124"/>
+      <c r="E8" s="124"/>
+      <c r="F8" s="124"/>
+      <c r="G8" s="124"/>
+      <c r="H8" s="121">
         <v>125</v>
       </c>
-      <c r="I8" s="119"/>
-      <c r="J8" s="119"/>
-      <c r="K8" s="119"/>
-      <c r="L8" s="120"/>
-      <c r="M8" s="120"/>
-      <c r="N8" s="120"/>
-      <c r="O8" s="120"/>
-      <c r="P8" s="120"/>
-      <c r="Q8" s="120"/>
-      <c r="R8" s="120"/>
-      <c r="S8" s="120"/>
-      <c r="T8" s="120"/>
-      <c r="U8" s="120"/>
-      <c r="V8" s="120"/>
-      <c r="W8" s="120"/>
-      <c r="X8" s="119">
+      <c r="I8" s="121"/>
+      <c r="J8" s="121"/>
+      <c r="K8" s="121"/>
+      <c r="L8" s="122"/>
+      <c r="M8" s="122"/>
+      <c r="N8" s="122"/>
+      <c r="O8" s="122"/>
+      <c r="P8" s="122"/>
+      <c r="Q8" s="122"/>
+      <c r="R8" s="122"/>
+      <c r="S8" s="122"/>
+      <c r="T8" s="122"/>
+      <c r="U8" s="122"/>
+      <c r="V8" s="122"/>
+      <c r="W8" s="122"/>
+      <c r="X8" s="121">
         <v>2000</v>
       </c>
-      <c r="Y8" s="119"/>
-      <c r="Z8" s="119"/>
-      <c r="AA8" s="119"/>
-      <c r="AB8" s="120"/>
-      <c r="AC8" s="120"/>
-      <c r="AD8" s="120"/>
-      <c r="AE8" s="120"/>
-      <c r="AF8" s="120"/>
-      <c r="AG8" s="120"/>
-      <c r="AH8" s="120"/>
-      <c r="AI8" s="120"/>
-      <c r="AJ8" s="120"/>
-      <c r="AK8" s="120"/>
-      <c r="AL8" s="120"/>
+      <c r="Y8" s="121"/>
+      <c r="Z8" s="121"/>
+      <c r="AA8" s="121"/>
+      <c r="AB8" s="122"/>
+      <c r="AC8" s="122"/>
+      <c r="AD8" s="122"/>
+      <c r="AE8" s="122"/>
+      <c r="AF8" s="122"/>
+      <c r="AG8" s="122"/>
+      <c r="AH8" s="122"/>
+      <c r="AI8" s="122"/>
+      <c r="AJ8" s="122"/>
+      <c r="AK8" s="122"/>
+      <c r="AL8" s="122"/>
     </row>
     <row r="9" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="122"/>
-      <c r="B9" s="122"/>
-      <c r="C9" s="122"/>
-      <c r="D9" s="122"/>
-      <c r="E9" s="122"/>
-      <c r="F9" s="122"/>
-      <c r="G9" s="122"/>
-      <c r="H9" s="119">
+      <c r="A9" s="124"/>
+      <c r="B9" s="124"/>
+      <c r="C9" s="124"/>
+      <c r="D9" s="124"/>
+      <c r="E9" s="124"/>
+      <c r="F9" s="124"/>
+      <c r="G9" s="124"/>
+      <c r="H9" s="121">
         <v>500</v>
       </c>
-      <c r="I9" s="119"/>
-      <c r="J9" s="119"/>
-      <c r="K9" s="119"/>
-      <c r="L9" s="120"/>
-      <c r="M9" s="120"/>
-      <c r="N9" s="120"/>
-      <c r="O9" s="120"/>
-      <c r="P9" s="120"/>
-      <c r="Q9" s="120"/>
-      <c r="R9" s="120"/>
-      <c r="S9" s="120"/>
-      <c r="T9" s="120"/>
-      <c r="U9" s="120"/>
-      <c r="V9" s="120"/>
-      <c r="W9" s="120"/>
-      <c r="X9" s="119">
+      <c r="I9" s="121"/>
+      <c r="J9" s="121"/>
+      <c r="K9" s="121"/>
+      <c r="L9" s="122"/>
+      <c r="M9" s="122"/>
+      <c r="N9" s="122"/>
+      <c r="O9" s="122"/>
+      <c r="P9" s="122"/>
+      <c r="Q9" s="122"/>
+      <c r="R9" s="122"/>
+      <c r="S9" s="122"/>
+      <c r="T9" s="122"/>
+      <c r="U9" s="122"/>
+      <c r="V9" s="122"/>
+      <c r="W9" s="122"/>
+      <c r="X9" s="121">
         <v>5000</v>
       </c>
-      <c r="Y9" s="119"/>
-      <c r="Z9" s="119"/>
-      <c r="AA9" s="119"/>
-      <c r="AB9" s="120"/>
-      <c r="AC9" s="120"/>
-      <c r="AD9" s="120"/>
-      <c r="AE9" s="120"/>
-      <c r="AF9" s="120"/>
-      <c r="AG9" s="120"/>
-      <c r="AH9" s="120"/>
-      <c r="AI9" s="120"/>
-      <c r="AJ9" s="120"/>
-      <c r="AK9" s="120"/>
-      <c r="AL9" s="120"/>
+      <c r="Y9" s="121"/>
+      <c r="Z9" s="121"/>
+      <c r="AA9" s="121"/>
+      <c r="AB9" s="122"/>
+      <c r="AC9" s="122"/>
+      <c r="AD9" s="122"/>
+      <c r="AE9" s="122"/>
+      <c r="AF9" s="122"/>
+      <c r="AG9" s="122"/>
+      <c r="AH9" s="122"/>
+      <c r="AI9" s="122"/>
+      <c r="AJ9" s="122"/>
+      <c r="AK9" s="122"/>
+      <c r="AL9" s="122"/>
     </row>
     <row r="10" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="122"/>
-      <c r="B10" s="122"/>
-      <c r="C10" s="122"/>
-      <c r="D10" s="122"/>
-      <c r="E10" s="122"/>
-      <c r="F10" s="122"/>
-      <c r="G10" s="122"/>
-      <c r="H10" s="119">
+      <c r="A10" s="124"/>
+      <c r="B10" s="124"/>
+      <c r="C10" s="124"/>
+      <c r="D10" s="124"/>
+      <c r="E10" s="124"/>
+      <c r="F10" s="124"/>
+      <c r="G10" s="124"/>
+      <c r="H10" s="121">
         <v>1000</v>
       </c>
-      <c r="I10" s="119"/>
-      <c r="J10" s="119"/>
-      <c r="K10" s="119"/>
-      <c r="L10" s="120"/>
-      <c r="M10" s="120"/>
-      <c r="N10" s="120"/>
-      <c r="O10" s="120"/>
-      <c r="P10" s="120"/>
-      <c r="Q10" s="120"/>
-      <c r="R10" s="120"/>
-      <c r="S10" s="120"/>
-      <c r="T10" s="120"/>
-      <c r="U10" s="120"/>
-      <c r="V10" s="120"/>
-      <c r="W10" s="120"/>
-      <c r="X10" s="119">
+      <c r="I10" s="121"/>
+      <c r="J10" s="121"/>
+      <c r="K10" s="121"/>
+      <c r="L10" s="122"/>
+      <c r="M10" s="122"/>
+      <c r="N10" s="122"/>
+      <c r="O10" s="122"/>
+      <c r="P10" s="122"/>
+      <c r="Q10" s="122"/>
+      <c r="R10" s="122"/>
+      <c r="S10" s="122"/>
+      <c r="T10" s="122"/>
+      <c r="U10" s="122"/>
+      <c r="V10" s="122"/>
+      <c r="W10" s="122"/>
+      <c r="X10" s="121">
         <v>7000</v>
       </c>
-      <c r="Y10" s="119"/>
-      <c r="Z10" s="119"/>
-      <c r="AA10" s="119"/>
-      <c r="AB10" s="120"/>
-      <c r="AC10" s="120"/>
-      <c r="AD10" s="120"/>
-      <c r="AE10" s="120"/>
-      <c r="AF10" s="120"/>
-      <c r="AG10" s="120"/>
-      <c r="AH10" s="120"/>
-      <c r="AI10" s="120"/>
-      <c r="AJ10" s="120"/>
-      <c r="AK10" s="120"/>
-      <c r="AL10" s="120"/>
+      <c r="Y10" s="121"/>
+      <c r="Z10" s="121"/>
+      <c r="AA10" s="121"/>
+      <c r="AB10" s="122"/>
+      <c r="AC10" s="122"/>
+      <c r="AD10" s="122"/>
+      <c r="AE10" s="122"/>
+      <c r="AF10" s="122"/>
+      <c r="AG10" s="122"/>
+      <c r="AH10" s="122"/>
+      <c r="AI10" s="122"/>
+      <c r="AJ10" s="122"/>
+      <c r="AK10" s="122"/>
+      <c r="AL10" s="122"/>
     </row>
     <row r="11" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="44"/>
@@ -6270,238 +6277,238 @@
       <c r="AL12" s="1"/>
     </row>
     <row r="13" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="123" t="s">
+      <c r="A13" s="125" t="s">
         <v>101</v>
       </c>
-      <c r="B13" s="123"/>
-      <c r="C13" s="123"/>
-      <c r="D13" s="123"/>
-      <c r="E13" s="123"/>
-      <c r="F13" s="123"/>
-      <c r="G13" s="123"/>
-      <c r="H13" s="124" t="s">
+      <c r="B13" s="125"/>
+      <c r="C13" s="125"/>
+      <c r="D13" s="125"/>
+      <c r="E13" s="125"/>
+      <c r="F13" s="125"/>
+      <c r="G13" s="125"/>
+      <c r="H13" s="126" t="s">
         <v>95</v>
       </c>
-      <c r="I13" s="124"/>
-      <c r="J13" s="124"/>
-      <c r="K13" s="124"/>
-      <c r="L13" s="121" t="s">
+      <c r="I13" s="126"/>
+      <c r="J13" s="126"/>
+      <c r="K13" s="126"/>
+      <c r="L13" s="123" t="s">
         <v>96</v>
       </c>
-      <c r="M13" s="121"/>
-      <c r="N13" s="121"/>
-      <c r="O13" s="121"/>
-      <c r="P13" s="121"/>
-      <c r="Q13" s="121"/>
-      <c r="R13" s="121"/>
-      <c r="S13" s="121"/>
-      <c r="T13" s="121"/>
-      <c r="U13" s="121"/>
-      <c r="V13" s="121"/>
-      <c r="W13" s="121"/>
-      <c r="X13" s="124" t="s">
+      <c r="M13" s="123"/>
+      <c r="N13" s="123"/>
+      <c r="O13" s="123"/>
+      <c r="P13" s="123"/>
+      <c r="Q13" s="123"/>
+      <c r="R13" s="123"/>
+      <c r="S13" s="123"/>
+      <c r="T13" s="123"/>
+      <c r="U13" s="123"/>
+      <c r="V13" s="123"/>
+      <c r="W13" s="123"/>
+      <c r="X13" s="126" t="s">
         <v>95</v>
       </c>
-      <c r="Y13" s="124"/>
-      <c r="Z13" s="124"/>
-      <c r="AA13" s="124"/>
-      <c r="AB13" s="121" t="s">
+      <c r="Y13" s="126"/>
+      <c r="Z13" s="126"/>
+      <c r="AA13" s="126"/>
+      <c r="AB13" s="123" t="s">
         <v>96</v>
       </c>
-      <c r="AC13" s="121"/>
-      <c r="AD13" s="121"/>
-      <c r="AE13" s="121"/>
-      <c r="AF13" s="121"/>
-      <c r="AG13" s="121"/>
-      <c r="AH13" s="121"/>
-      <c r="AI13" s="121"/>
-      <c r="AJ13" s="121"/>
-      <c r="AK13" s="121"/>
-      <c r="AL13" s="121"/>
+      <c r="AC13" s="123"/>
+      <c r="AD13" s="123"/>
+      <c r="AE13" s="123"/>
+      <c r="AF13" s="123"/>
+      <c r="AG13" s="123"/>
+      <c r="AH13" s="123"/>
+      <c r="AI13" s="123"/>
+      <c r="AJ13" s="123"/>
+      <c r="AK13" s="123"/>
+      <c r="AL13" s="123"/>
     </row>
     <row r="14" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="123"/>
-      <c r="B14" s="123"/>
-      <c r="C14" s="123"/>
-      <c r="D14" s="123"/>
-      <c r="E14" s="123"/>
-      <c r="F14" s="123"/>
-      <c r="G14" s="123"/>
-      <c r="H14" s="124"/>
-      <c r="I14" s="124"/>
-      <c r="J14" s="124"/>
-      <c r="K14" s="124"/>
-      <c r="L14" s="121" t="s">
+      <c r="A14" s="125"/>
+      <c r="B14" s="125"/>
+      <c r="C14" s="125"/>
+      <c r="D14" s="125"/>
+      <c r="E14" s="125"/>
+      <c r="F14" s="125"/>
+      <c r="G14" s="125"/>
+      <c r="H14" s="126"/>
+      <c r="I14" s="126"/>
+      <c r="J14" s="126"/>
+      <c r="K14" s="126"/>
+      <c r="L14" s="123" t="s">
         <v>97</v>
       </c>
-      <c r="M14" s="121"/>
-      <c r="N14" s="121"/>
-      <c r="O14" s="121"/>
-      <c r="P14" s="121" t="s">
+      <c r="M14" s="123"/>
+      <c r="N14" s="123"/>
+      <c r="O14" s="123"/>
+      <c r="P14" s="123" t="s">
         <v>98</v>
       </c>
-      <c r="Q14" s="121"/>
-      <c r="R14" s="121"/>
-      <c r="S14" s="121"/>
-      <c r="T14" s="121" t="s">
+      <c r="Q14" s="123"/>
+      <c r="R14" s="123"/>
+      <c r="S14" s="123"/>
+      <c r="T14" s="123" t="s">
         <v>99</v>
       </c>
-      <c r="U14" s="121"/>
-      <c r="V14" s="121"/>
-      <c r="W14" s="121"/>
-      <c r="X14" s="124"/>
-      <c r="Y14" s="124"/>
-      <c r="Z14" s="124"/>
-      <c r="AA14" s="124"/>
-      <c r="AB14" s="121" t="s">
+      <c r="U14" s="123"/>
+      <c r="V14" s="123"/>
+      <c r="W14" s="123"/>
+      <c r="X14" s="126"/>
+      <c r="Y14" s="126"/>
+      <c r="Z14" s="126"/>
+      <c r="AA14" s="126"/>
+      <c r="AB14" s="123" t="s">
         <v>97</v>
       </c>
-      <c r="AC14" s="121"/>
-      <c r="AD14" s="121"/>
-      <c r="AE14" s="121"/>
-      <c r="AF14" s="121" t="s">
+      <c r="AC14" s="123"/>
+      <c r="AD14" s="123"/>
+      <c r="AE14" s="123"/>
+      <c r="AF14" s="123" t="s">
         <v>98</v>
       </c>
-      <c r="AG14" s="121"/>
-      <c r="AH14" s="121"/>
-      <c r="AI14" s="121"/>
-      <c r="AJ14" s="121" t="s">
+      <c r="AG14" s="123"/>
+      <c r="AH14" s="123"/>
+      <c r="AI14" s="123"/>
+      <c r="AJ14" s="123" t="s">
         <v>99</v>
       </c>
-      <c r="AK14" s="121"/>
-      <c r="AL14" s="121"/>
+      <c r="AK14" s="123"/>
+      <c r="AL14" s="123"/>
     </row>
     <row r="15" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="122"/>
-      <c r="B15" s="122"/>
-      <c r="C15" s="122"/>
-      <c r="D15" s="122"/>
-      <c r="E15" s="122"/>
-      <c r="F15" s="122"/>
-      <c r="G15" s="122"/>
-      <c r="H15" s="119">
+      <c r="A15" s="124"/>
+      <c r="B15" s="124"/>
+      <c r="C15" s="124"/>
+      <c r="D15" s="124"/>
+      <c r="E15" s="124"/>
+      <c r="F15" s="124"/>
+      <c r="G15" s="124"/>
+      <c r="H15" s="121">
         <v>125</v>
       </c>
-      <c r="I15" s="119"/>
-      <c r="J15" s="119"/>
-      <c r="K15" s="119"/>
-      <c r="L15" s="120"/>
-      <c r="M15" s="120"/>
-      <c r="N15" s="120"/>
-      <c r="O15" s="120"/>
-      <c r="P15" s="120"/>
-      <c r="Q15" s="120"/>
-      <c r="R15" s="120"/>
-      <c r="S15" s="120"/>
-      <c r="T15" s="120"/>
-      <c r="U15" s="120"/>
-      <c r="V15" s="120"/>
-      <c r="W15" s="120"/>
-      <c r="X15" s="119">
+      <c r="I15" s="121"/>
+      <c r="J15" s="121"/>
+      <c r="K15" s="121"/>
+      <c r="L15" s="122"/>
+      <c r="M15" s="122"/>
+      <c r="N15" s="122"/>
+      <c r="O15" s="122"/>
+      <c r="P15" s="122"/>
+      <c r="Q15" s="122"/>
+      <c r="R15" s="122"/>
+      <c r="S15" s="122"/>
+      <c r="T15" s="122"/>
+      <c r="U15" s="122"/>
+      <c r="V15" s="122"/>
+      <c r="W15" s="122"/>
+      <c r="X15" s="121">
         <v>2000</v>
       </c>
-      <c r="Y15" s="119"/>
-      <c r="Z15" s="119"/>
-      <c r="AA15" s="119"/>
-      <c r="AB15" s="120"/>
-      <c r="AC15" s="120"/>
-      <c r="AD15" s="120"/>
-      <c r="AE15" s="120"/>
-      <c r="AF15" s="120"/>
-      <c r="AG15" s="120"/>
-      <c r="AH15" s="120"/>
-      <c r="AI15" s="120"/>
-      <c r="AJ15" s="120"/>
-      <c r="AK15" s="120"/>
-      <c r="AL15" s="120"/>
+      <c r="Y15" s="121"/>
+      <c r="Z15" s="121"/>
+      <c r="AA15" s="121"/>
+      <c r="AB15" s="122"/>
+      <c r="AC15" s="122"/>
+      <c r="AD15" s="122"/>
+      <c r="AE15" s="122"/>
+      <c r="AF15" s="122"/>
+      <c r="AG15" s="122"/>
+      <c r="AH15" s="122"/>
+      <c r="AI15" s="122"/>
+      <c r="AJ15" s="122"/>
+      <c r="AK15" s="122"/>
+      <c r="AL15" s="122"/>
     </row>
     <row r="16" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="122"/>
-      <c r="B16" s="122"/>
-      <c r="C16" s="122"/>
-      <c r="D16" s="122"/>
-      <c r="E16" s="122"/>
-      <c r="F16" s="122"/>
-      <c r="G16" s="122"/>
-      <c r="H16" s="119">
+      <c r="A16" s="124"/>
+      <c r="B16" s="124"/>
+      <c r="C16" s="124"/>
+      <c r="D16" s="124"/>
+      <c r="E16" s="124"/>
+      <c r="F16" s="124"/>
+      <c r="G16" s="124"/>
+      <c r="H16" s="121">
         <v>500</v>
       </c>
-      <c r="I16" s="119"/>
-      <c r="J16" s="119"/>
-      <c r="K16" s="119"/>
-      <c r="L16" s="120"/>
-      <c r="M16" s="120"/>
-      <c r="N16" s="120"/>
-      <c r="O16" s="120"/>
-      <c r="P16" s="120"/>
-      <c r="Q16" s="120"/>
-      <c r="R16" s="120"/>
-      <c r="S16" s="120"/>
-      <c r="T16" s="120"/>
-      <c r="U16" s="120"/>
-      <c r="V16" s="120"/>
-      <c r="W16" s="120"/>
-      <c r="X16" s="119">
+      <c r="I16" s="121"/>
+      <c r="J16" s="121"/>
+      <c r="K16" s="121"/>
+      <c r="L16" s="122"/>
+      <c r="M16" s="122"/>
+      <c r="N16" s="122"/>
+      <c r="O16" s="122"/>
+      <c r="P16" s="122"/>
+      <c r="Q16" s="122"/>
+      <c r="R16" s="122"/>
+      <c r="S16" s="122"/>
+      <c r="T16" s="122"/>
+      <c r="U16" s="122"/>
+      <c r="V16" s="122"/>
+      <c r="W16" s="122"/>
+      <c r="X16" s="121">
         <v>5000</v>
       </c>
-      <c r="Y16" s="119"/>
-      <c r="Z16" s="119"/>
-      <c r="AA16" s="119"/>
-      <c r="AB16" s="120"/>
-      <c r="AC16" s="120"/>
-      <c r="AD16" s="120"/>
-      <c r="AE16" s="120"/>
-      <c r="AF16" s="120"/>
-      <c r="AG16" s="120"/>
-      <c r="AH16" s="120"/>
-      <c r="AI16" s="120"/>
-      <c r="AJ16" s="120"/>
-      <c r="AK16" s="120"/>
-      <c r="AL16" s="120"/>
+      <c r="Y16" s="121"/>
+      <c r="Z16" s="121"/>
+      <c r="AA16" s="121"/>
+      <c r="AB16" s="122"/>
+      <c r="AC16" s="122"/>
+      <c r="AD16" s="122"/>
+      <c r="AE16" s="122"/>
+      <c r="AF16" s="122"/>
+      <c r="AG16" s="122"/>
+      <c r="AH16" s="122"/>
+      <c r="AI16" s="122"/>
+      <c r="AJ16" s="122"/>
+      <c r="AK16" s="122"/>
+      <c r="AL16" s="122"/>
     </row>
     <row r="17" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="122"/>
-      <c r="B17" s="122"/>
-      <c r="C17" s="122"/>
-      <c r="D17" s="122"/>
-      <c r="E17" s="122"/>
-      <c r="F17" s="122"/>
-      <c r="G17" s="122"/>
-      <c r="H17" s="119">
+      <c r="A17" s="124"/>
+      <c r="B17" s="124"/>
+      <c r="C17" s="124"/>
+      <c r="D17" s="124"/>
+      <c r="E17" s="124"/>
+      <c r="F17" s="124"/>
+      <c r="G17" s="124"/>
+      <c r="H17" s="121">
         <v>1000</v>
       </c>
-      <c r="I17" s="119"/>
-      <c r="J17" s="119"/>
-      <c r="K17" s="119"/>
-      <c r="L17" s="120"/>
-      <c r="M17" s="120"/>
-      <c r="N17" s="120"/>
-      <c r="O17" s="120"/>
-      <c r="P17" s="120"/>
-      <c r="Q17" s="120"/>
-      <c r="R17" s="120"/>
-      <c r="S17" s="120"/>
-      <c r="T17" s="120"/>
-      <c r="U17" s="120"/>
-      <c r="V17" s="120"/>
-      <c r="W17" s="120"/>
-      <c r="X17" s="119">
+      <c r="I17" s="121"/>
+      <c r="J17" s="121"/>
+      <c r="K17" s="121"/>
+      <c r="L17" s="122"/>
+      <c r="M17" s="122"/>
+      <c r="N17" s="122"/>
+      <c r="O17" s="122"/>
+      <c r="P17" s="122"/>
+      <c r="Q17" s="122"/>
+      <c r="R17" s="122"/>
+      <c r="S17" s="122"/>
+      <c r="T17" s="122"/>
+      <c r="U17" s="122"/>
+      <c r="V17" s="122"/>
+      <c r="W17" s="122"/>
+      <c r="X17" s="121">
         <v>7000</v>
       </c>
-      <c r="Y17" s="119"/>
-      <c r="Z17" s="119"/>
-      <c r="AA17" s="119"/>
-      <c r="AB17" s="120"/>
-      <c r="AC17" s="120"/>
-      <c r="AD17" s="120"/>
-      <c r="AE17" s="120"/>
-      <c r="AF17" s="120"/>
-      <c r="AG17" s="120"/>
-      <c r="AH17" s="120"/>
-      <c r="AI17" s="120"/>
-      <c r="AJ17" s="120"/>
-      <c r="AK17" s="120"/>
-      <c r="AL17" s="120"/>
+      <c r="Y17" s="121"/>
+      <c r="Z17" s="121"/>
+      <c r="AA17" s="121"/>
+      <c r="AB17" s="122"/>
+      <c r="AC17" s="122"/>
+      <c r="AD17" s="122"/>
+      <c r="AE17" s="122"/>
+      <c r="AF17" s="122"/>
+      <c r="AG17" s="122"/>
+      <c r="AH17" s="122"/>
+      <c r="AI17" s="122"/>
+      <c r="AJ17" s="122"/>
+      <c r="AK17" s="122"/>
+      <c r="AL17" s="122"/>
     </row>
     <row r="18" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="44"/>
@@ -7608,32 +7615,32 @@
       <c r="J1" s="54"/>
       <c r="K1" s="54"/>
       <c r="L1" s="54"/>
-      <c r="M1" s="150"/>
-      <c r="N1" s="150"/>
-      <c r="O1" s="150"/>
-      <c r="P1" s="150"/>
-      <c r="Q1" s="150"/>
-      <c r="R1" s="150"/>
-      <c r="S1" s="150"/>
-      <c r="T1" s="150"/>
-      <c r="U1" s="150"/>
-      <c r="V1" s="150"/>
-      <c r="W1" s="150"/>
-      <c r="X1" s="150"/>
-      <c r="Y1" s="150"/>
-      <c r="Z1" s="150"/>
-      <c r="AA1" s="150"/>
-      <c r="AB1" s="150"/>
-      <c r="AC1" s="150"/>
-      <c r="AD1" s="150"/>
-      <c r="AE1" s="150"/>
-      <c r="AF1" s="150"/>
-      <c r="AG1" s="150"/>
-      <c r="AH1" s="150"/>
-      <c r="AI1" s="150"/>
-      <c r="AJ1" s="150"/>
-      <c r="AK1" s="150"/>
-      <c r="AL1" s="150"/>
+      <c r="M1" s="152"/>
+      <c r="N1" s="152"/>
+      <c r="O1" s="152"/>
+      <c r="P1" s="152"/>
+      <c r="Q1" s="152"/>
+      <c r="R1" s="152"/>
+      <c r="S1" s="152"/>
+      <c r="T1" s="152"/>
+      <c r="U1" s="152"/>
+      <c r="V1" s="152"/>
+      <c r="W1" s="152"/>
+      <c r="X1" s="152"/>
+      <c r="Y1" s="152"/>
+      <c r="Z1" s="152"/>
+      <c r="AA1" s="152"/>
+      <c r="AB1" s="152"/>
+      <c r="AC1" s="152"/>
+      <c r="AD1" s="152"/>
+      <c r="AE1" s="152"/>
+      <c r="AF1" s="152"/>
+      <c r="AG1" s="152"/>
+      <c r="AH1" s="152"/>
+      <c r="AI1" s="152"/>
+      <c r="AJ1" s="152"/>
+      <c r="AK1" s="152"/>
+      <c r="AL1" s="152"/>
     </row>
     <row r="2" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="55" t="s">
@@ -7675,26 +7682,26 @@
       <c r="AL2" s="56"/>
     </row>
     <row r="3" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="157"/>
-      <c r="B3" s="157"/>
-      <c r="C3" s="157"/>
-      <c r="D3" s="157"/>
-      <c r="E3" s="157"/>
-      <c r="F3" s="157"/>
-      <c r="G3" s="157"/>
-      <c r="H3" s="157"/>
-      <c r="I3" s="157"/>
-      <c r="J3" s="157"/>
-      <c r="K3" s="157"/>
-      <c r="L3" s="157"/>
-      <c r="M3" s="157"/>
-      <c r="N3" s="157"/>
-      <c r="O3" s="157"/>
-      <c r="P3" s="157"/>
-      <c r="Q3" s="157"/>
-      <c r="R3" s="157"/>
-      <c r="S3" s="157"/>
-      <c r="T3" s="157"/>
+      <c r="A3" s="159"/>
+      <c r="B3" s="159"/>
+      <c r="C3" s="159"/>
+      <c r="D3" s="159"/>
+      <c r="E3" s="159"/>
+      <c r="F3" s="159"/>
+      <c r="G3" s="159"/>
+      <c r="H3" s="159"/>
+      <c r="I3" s="159"/>
+      <c r="J3" s="159"/>
+      <c r="K3" s="159"/>
+      <c r="L3" s="159"/>
+      <c r="M3" s="159"/>
+      <c r="N3" s="159"/>
+      <c r="O3" s="159"/>
+      <c r="P3" s="159"/>
+      <c r="Q3" s="159"/>
+      <c r="R3" s="159"/>
+      <c r="S3" s="159"/>
+      <c r="T3" s="159"/>
       <c r="U3" s="56"/>
       <c r="V3" s="56"/>
       <c r="W3" s="56"/>
@@ -7839,10 +7846,10 @@
         <v>166</v>
       </c>
       <c r="E7" s="52"/>
-      <c r="F7" s="151">
+      <c r="F7" s="153">
         <v>3</v>
       </c>
-      <c r="G7" s="151"/>
+      <c r="G7" s="153"/>
       <c r="H7" s="78" t="s">
         <v>208</v>
       </c>
@@ -7851,12 +7858,12 @@
       <c r="K7" s="64" t="s">
         <v>183</v>
       </c>
-      <c r="L7" s="158">
+      <c r="L7" s="160">
         <v>5</v>
       </c>
-      <c r="M7" s="158"/>
-      <c r="N7" s="158"/>
-      <c r="O7" s="158"/>
+      <c r="M7" s="160"/>
+      <c r="N7" s="160"/>
+      <c r="O7" s="160"/>
       <c r="P7" s="70" t="s">
         <v>184</v>
       </c>
@@ -8971,572 +8978,572 @@
       <c r="AL36" s="56"/>
     </row>
     <row r="37" spans="1:38" ht="15.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="152" t="s">
+      <c r="A37" s="154" t="s">
         <v>171</v>
       </c>
-      <c r="B37" s="152"/>
-      <c r="C37" s="153"/>
+      <c r="B37" s="154"/>
+      <c r="C37" s="155"/>
       <c r="D37" s="77"/>
-      <c r="E37" s="138" t="s">
+      <c r="E37" s="140" t="s">
         <v>18</v>
       </c>
-      <c r="F37" s="139"/>
-      <c r="G37" s="139"/>
-      <c r="H37" s="140"/>
-      <c r="I37" s="154" t="s">
+      <c r="F37" s="141"/>
+      <c r="G37" s="141"/>
+      <c r="H37" s="142"/>
+      <c r="I37" s="156" t="s">
         <v>172</v>
       </c>
-      <c r="J37" s="155"/>
-      <c r="K37" s="156"/>
-      <c r="L37" s="138" t="s">
+      <c r="J37" s="157"/>
+      <c r="K37" s="158"/>
+      <c r="L37" s="140" t="s">
         <v>173</v>
       </c>
-      <c r="M37" s="139"/>
-      <c r="N37" s="139"/>
-      <c r="O37" s="140"/>
-      <c r="P37" s="138" t="s">
+      <c r="M37" s="141"/>
+      <c r="N37" s="141"/>
+      <c r="O37" s="142"/>
+      <c r="P37" s="140" t="s">
         <v>174</v>
       </c>
-      <c r="Q37" s="139"/>
-      <c r="R37" s="139"/>
-      <c r="S37" s="140"/>
-      <c r="T37" s="138" t="s">
+      <c r="Q37" s="141"/>
+      <c r="R37" s="141"/>
+      <c r="S37" s="142"/>
+      <c r="T37" s="140" t="s">
         <v>175</v>
       </c>
-      <c r="U37" s="139"/>
-      <c r="V37" s="139"/>
-      <c r="W37" s="140"/>
-      <c r="X37" s="138" t="s">
+      <c r="U37" s="141"/>
+      <c r="V37" s="141"/>
+      <c r="W37" s="142"/>
+      <c r="X37" s="140" t="s">
         <v>176</v>
       </c>
-      <c r="Y37" s="139"/>
-      <c r="Z37" s="139"/>
-      <c r="AA37" s="140"/>
-      <c r="AB37" s="138" t="s">
+      <c r="Y37" s="141"/>
+      <c r="Z37" s="141"/>
+      <c r="AA37" s="142"/>
+      <c r="AB37" s="140" t="s">
         <v>177</v>
       </c>
-      <c r="AC37" s="139"/>
-      <c r="AD37" s="139"/>
-      <c r="AE37" s="140"/>
-      <c r="AF37" s="138" t="s">
+      <c r="AC37" s="141"/>
+      <c r="AD37" s="141"/>
+      <c r="AE37" s="142"/>
+      <c r="AF37" s="140" t="s">
         <v>178</v>
       </c>
-      <c r="AG37" s="139"/>
-      <c r="AH37" s="139"/>
-      <c r="AI37" s="140"/>
-      <c r="AJ37" s="138" t="s">
+      <c r="AG37" s="141"/>
+      <c r="AH37" s="141"/>
+      <c r="AI37" s="142"/>
+      <c r="AJ37" s="140" t="s">
         <v>179</v>
       </c>
-      <c r="AK37" s="139"/>
-      <c r="AL37" s="140"/>
+      <c r="AK37" s="141"/>
+      <c r="AL37" s="142"/>
     </row>
     <row r="38" spans="1:38" ht="15.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="127" t="s">
+      <c r="A38" s="129" t="s">
         <v>180</v>
       </c>
-      <c r="B38" s="128"/>
-      <c r="C38" s="128"/>
-      <c r="D38" s="129"/>
-      <c r="E38" s="136" t="s">
+      <c r="B38" s="130"/>
+      <c r="C38" s="130"/>
+      <c r="D38" s="131"/>
+      <c r="E38" s="138" t="s">
         <v>9</v>
       </c>
-      <c r="F38" s="137"/>
-      <c r="G38" s="137"/>
-      <c r="H38" s="137"/>
-      <c r="I38" s="141"/>
-      <c r="J38" s="142"/>
-      <c r="K38" s="143"/>
-      <c r="L38" s="138"/>
-      <c r="M38" s="139"/>
-      <c r="N38" s="139"/>
-      <c r="O38" s="140"/>
-      <c r="P38" s="138"/>
-      <c r="Q38" s="139"/>
-      <c r="R38" s="139"/>
-      <c r="S38" s="140"/>
-      <c r="T38" s="138"/>
-      <c r="U38" s="139"/>
-      <c r="V38" s="139"/>
-      <c r="W38" s="140"/>
-      <c r="X38" s="138"/>
-      <c r="Y38" s="139"/>
-      <c r="Z38" s="139"/>
-      <c r="AA38" s="140"/>
-      <c r="AB38" s="138"/>
-      <c r="AC38" s="139"/>
-      <c r="AD38" s="139"/>
-      <c r="AE38" s="140"/>
-      <c r="AF38" s="138"/>
-      <c r="AG38" s="139"/>
-      <c r="AH38" s="139"/>
-      <c r="AI38" s="140"/>
-      <c r="AJ38" s="138"/>
-      <c r="AK38" s="139"/>
-      <c r="AL38" s="140"/>
+      <c r="F38" s="139"/>
+      <c r="G38" s="139"/>
+      <c r="H38" s="139"/>
+      <c r="I38" s="143"/>
+      <c r="J38" s="144"/>
+      <c r="K38" s="145"/>
+      <c r="L38" s="140"/>
+      <c r="M38" s="141"/>
+      <c r="N38" s="141"/>
+      <c r="O38" s="142"/>
+      <c r="P38" s="140"/>
+      <c r="Q38" s="141"/>
+      <c r="R38" s="141"/>
+      <c r="S38" s="142"/>
+      <c r="T38" s="140"/>
+      <c r="U38" s="141"/>
+      <c r="V38" s="141"/>
+      <c r="W38" s="142"/>
+      <c r="X38" s="140"/>
+      <c r="Y38" s="141"/>
+      <c r="Z38" s="141"/>
+      <c r="AA38" s="142"/>
+      <c r="AB38" s="140"/>
+      <c r="AC38" s="141"/>
+      <c r="AD38" s="141"/>
+      <c r="AE38" s="142"/>
+      <c r="AF38" s="140"/>
+      <c r="AG38" s="141"/>
+      <c r="AH38" s="141"/>
+      <c r="AI38" s="142"/>
+      <c r="AJ38" s="140"/>
+      <c r="AK38" s="141"/>
+      <c r="AL38" s="142"/>
     </row>
     <row r="39" spans="1:38" ht="15.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="130"/>
-      <c r="B39" s="131"/>
-      <c r="C39" s="131"/>
-      <c r="D39" s="132"/>
-      <c r="E39" s="136" t="s">
+      <c r="A39" s="132"/>
+      <c r="B39" s="133"/>
+      <c r="C39" s="133"/>
+      <c r="D39" s="134"/>
+      <c r="E39" s="138" t="s">
         <v>10</v>
       </c>
-      <c r="F39" s="137"/>
-      <c r="G39" s="137"/>
-      <c r="H39" s="137"/>
-      <c r="I39" s="144"/>
-      <c r="J39" s="145"/>
-      <c r="K39" s="146"/>
-      <c r="L39" s="138"/>
-      <c r="M39" s="139"/>
-      <c r="N39" s="139"/>
-      <c r="O39" s="140"/>
-      <c r="P39" s="138"/>
-      <c r="Q39" s="139"/>
-      <c r="R39" s="139"/>
-      <c r="S39" s="140"/>
-      <c r="T39" s="138"/>
-      <c r="U39" s="139"/>
-      <c r="V39" s="139"/>
-      <c r="W39" s="140"/>
-      <c r="X39" s="138"/>
-      <c r="Y39" s="139"/>
-      <c r="Z39" s="139"/>
-      <c r="AA39" s="140"/>
-      <c r="AB39" s="138"/>
-      <c r="AC39" s="139"/>
-      <c r="AD39" s="139"/>
-      <c r="AE39" s="140"/>
-      <c r="AF39" s="138"/>
-      <c r="AG39" s="139"/>
-      <c r="AH39" s="139"/>
-      <c r="AI39" s="140"/>
-      <c r="AJ39" s="138"/>
-      <c r="AK39" s="139"/>
-      <c r="AL39" s="140"/>
+      <c r="F39" s="139"/>
+      <c r="G39" s="139"/>
+      <c r="H39" s="139"/>
+      <c r="I39" s="146"/>
+      <c r="J39" s="147"/>
+      <c r="K39" s="148"/>
+      <c r="L39" s="140"/>
+      <c r="M39" s="141"/>
+      <c r="N39" s="141"/>
+      <c r="O39" s="142"/>
+      <c r="P39" s="140"/>
+      <c r="Q39" s="141"/>
+      <c r="R39" s="141"/>
+      <c r="S39" s="142"/>
+      <c r="T39" s="140"/>
+      <c r="U39" s="141"/>
+      <c r="V39" s="141"/>
+      <c r="W39" s="142"/>
+      <c r="X39" s="140"/>
+      <c r="Y39" s="141"/>
+      <c r="Z39" s="141"/>
+      <c r="AA39" s="142"/>
+      <c r="AB39" s="140"/>
+      <c r="AC39" s="141"/>
+      <c r="AD39" s="141"/>
+      <c r="AE39" s="142"/>
+      <c r="AF39" s="140"/>
+      <c r="AG39" s="141"/>
+      <c r="AH39" s="141"/>
+      <c r="AI39" s="142"/>
+      <c r="AJ39" s="140"/>
+      <c r="AK39" s="141"/>
+      <c r="AL39" s="142"/>
     </row>
     <row r="40" spans="1:38" ht="15.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="130"/>
-      <c r="B40" s="131"/>
-      <c r="C40" s="131"/>
-      <c r="D40" s="132"/>
-      <c r="E40" s="136" t="s">
+      <c r="A40" s="132"/>
+      <c r="B40" s="133"/>
+      <c r="C40" s="133"/>
+      <c r="D40" s="134"/>
+      <c r="E40" s="138" t="s">
         <v>11</v>
       </c>
-      <c r="F40" s="137"/>
-      <c r="G40" s="137"/>
-      <c r="H40" s="137"/>
-      <c r="I40" s="144"/>
-      <c r="J40" s="145"/>
-      <c r="K40" s="146"/>
-      <c r="L40" s="138"/>
-      <c r="M40" s="139"/>
-      <c r="N40" s="139"/>
-      <c r="O40" s="140"/>
-      <c r="P40" s="138"/>
-      <c r="Q40" s="139"/>
-      <c r="R40" s="139"/>
-      <c r="S40" s="140"/>
-      <c r="T40" s="138"/>
-      <c r="U40" s="139"/>
-      <c r="V40" s="139"/>
-      <c r="W40" s="140"/>
-      <c r="X40" s="138"/>
-      <c r="Y40" s="139"/>
-      <c r="Z40" s="139"/>
-      <c r="AA40" s="140"/>
-      <c r="AB40" s="138"/>
-      <c r="AC40" s="139"/>
-      <c r="AD40" s="139"/>
-      <c r="AE40" s="140"/>
-      <c r="AF40" s="138"/>
-      <c r="AG40" s="139"/>
-      <c r="AH40" s="139"/>
-      <c r="AI40" s="140"/>
-      <c r="AJ40" s="138"/>
-      <c r="AK40" s="139"/>
-      <c r="AL40" s="140"/>
+      <c r="F40" s="139"/>
+      <c r="G40" s="139"/>
+      <c r="H40" s="139"/>
+      <c r="I40" s="146"/>
+      <c r="J40" s="147"/>
+      <c r="K40" s="148"/>
+      <c r="L40" s="140"/>
+      <c r="M40" s="141"/>
+      <c r="N40" s="141"/>
+      <c r="O40" s="142"/>
+      <c r="P40" s="140"/>
+      <c r="Q40" s="141"/>
+      <c r="R40" s="141"/>
+      <c r="S40" s="142"/>
+      <c r="T40" s="140"/>
+      <c r="U40" s="141"/>
+      <c r="V40" s="141"/>
+      <c r="W40" s="142"/>
+      <c r="X40" s="140"/>
+      <c r="Y40" s="141"/>
+      <c r="Z40" s="141"/>
+      <c r="AA40" s="142"/>
+      <c r="AB40" s="140"/>
+      <c r="AC40" s="141"/>
+      <c r="AD40" s="141"/>
+      <c r="AE40" s="142"/>
+      <c r="AF40" s="140"/>
+      <c r="AG40" s="141"/>
+      <c r="AH40" s="141"/>
+      <c r="AI40" s="142"/>
+      <c r="AJ40" s="140"/>
+      <c r="AK40" s="141"/>
+      <c r="AL40" s="142"/>
     </row>
     <row r="41" spans="1:38" ht="15.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="130"/>
-      <c r="B41" s="131"/>
-      <c r="C41" s="131"/>
-      <c r="D41" s="132"/>
-      <c r="E41" s="136" t="s">
+      <c r="A41" s="132"/>
+      <c r="B41" s="133"/>
+      <c r="C41" s="133"/>
+      <c r="D41" s="134"/>
+      <c r="E41" s="138" t="s">
         <v>12</v>
       </c>
-      <c r="F41" s="137"/>
-      <c r="G41" s="137"/>
-      <c r="H41" s="137"/>
-      <c r="I41" s="144"/>
-      <c r="J41" s="145"/>
-      <c r="K41" s="146"/>
-      <c r="L41" s="138"/>
-      <c r="M41" s="139"/>
-      <c r="N41" s="139"/>
-      <c r="O41" s="140"/>
-      <c r="P41" s="138"/>
-      <c r="Q41" s="139"/>
-      <c r="R41" s="139"/>
-      <c r="S41" s="140"/>
-      <c r="T41" s="138"/>
-      <c r="U41" s="139"/>
-      <c r="V41" s="139"/>
-      <c r="W41" s="140"/>
-      <c r="X41" s="138"/>
-      <c r="Y41" s="139"/>
-      <c r="Z41" s="139"/>
-      <c r="AA41" s="140"/>
-      <c r="AB41" s="138"/>
-      <c r="AC41" s="139"/>
-      <c r="AD41" s="139"/>
-      <c r="AE41" s="140"/>
-      <c r="AF41" s="138"/>
-      <c r="AG41" s="139"/>
-      <c r="AH41" s="139"/>
-      <c r="AI41" s="140"/>
-      <c r="AJ41" s="138"/>
-      <c r="AK41" s="139"/>
-      <c r="AL41" s="140"/>
+      <c r="F41" s="139"/>
+      <c r="G41" s="139"/>
+      <c r="H41" s="139"/>
+      <c r="I41" s="146"/>
+      <c r="J41" s="147"/>
+      <c r="K41" s="148"/>
+      <c r="L41" s="140"/>
+      <c r="M41" s="141"/>
+      <c r="N41" s="141"/>
+      <c r="O41" s="142"/>
+      <c r="P41" s="140"/>
+      <c r="Q41" s="141"/>
+      <c r="R41" s="141"/>
+      <c r="S41" s="142"/>
+      <c r="T41" s="140"/>
+      <c r="U41" s="141"/>
+      <c r="V41" s="141"/>
+      <c r="W41" s="142"/>
+      <c r="X41" s="140"/>
+      <c r="Y41" s="141"/>
+      <c r="Z41" s="141"/>
+      <c r="AA41" s="142"/>
+      <c r="AB41" s="140"/>
+      <c r="AC41" s="141"/>
+      <c r="AD41" s="141"/>
+      <c r="AE41" s="142"/>
+      <c r="AF41" s="140"/>
+      <c r="AG41" s="141"/>
+      <c r="AH41" s="141"/>
+      <c r="AI41" s="142"/>
+      <c r="AJ41" s="140"/>
+      <c r="AK41" s="141"/>
+      <c r="AL41" s="142"/>
     </row>
     <row r="42" spans="1:38" ht="15.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="130"/>
-      <c r="B42" s="131"/>
-      <c r="C42" s="131"/>
-      <c r="D42" s="132"/>
-      <c r="E42" s="136" t="s">
+      <c r="A42" s="132"/>
+      <c r="B42" s="133"/>
+      <c r="C42" s="133"/>
+      <c r="D42" s="134"/>
+      <c r="E42" s="138" t="s">
         <v>13</v>
       </c>
-      <c r="F42" s="137"/>
-      <c r="G42" s="137"/>
-      <c r="H42" s="137"/>
-      <c r="I42" s="144"/>
-      <c r="J42" s="145"/>
-      <c r="K42" s="146"/>
-      <c r="L42" s="138"/>
-      <c r="M42" s="139"/>
-      <c r="N42" s="139"/>
-      <c r="O42" s="140"/>
-      <c r="P42" s="138"/>
-      <c r="Q42" s="139"/>
-      <c r="R42" s="139"/>
-      <c r="S42" s="140"/>
-      <c r="T42" s="138"/>
-      <c r="U42" s="139"/>
-      <c r="V42" s="139"/>
-      <c r="W42" s="140"/>
-      <c r="X42" s="138"/>
-      <c r="Y42" s="139"/>
-      <c r="Z42" s="139"/>
-      <c r="AA42" s="140"/>
-      <c r="AB42" s="138"/>
-      <c r="AC42" s="139"/>
-      <c r="AD42" s="139"/>
-      <c r="AE42" s="140"/>
-      <c r="AF42" s="138"/>
-      <c r="AG42" s="139"/>
-      <c r="AH42" s="139"/>
-      <c r="AI42" s="140"/>
-      <c r="AJ42" s="138"/>
-      <c r="AK42" s="139"/>
-      <c r="AL42" s="140"/>
+      <c r="F42" s="139"/>
+      <c r="G42" s="139"/>
+      <c r="H42" s="139"/>
+      <c r="I42" s="146"/>
+      <c r="J42" s="147"/>
+      <c r="K42" s="148"/>
+      <c r="L42" s="140"/>
+      <c r="M42" s="141"/>
+      <c r="N42" s="141"/>
+      <c r="O42" s="142"/>
+      <c r="P42" s="140"/>
+      <c r="Q42" s="141"/>
+      <c r="R42" s="141"/>
+      <c r="S42" s="142"/>
+      <c r="T42" s="140"/>
+      <c r="U42" s="141"/>
+      <c r="V42" s="141"/>
+      <c r="W42" s="142"/>
+      <c r="X42" s="140"/>
+      <c r="Y42" s="141"/>
+      <c r="Z42" s="141"/>
+      <c r="AA42" s="142"/>
+      <c r="AB42" s="140"/>
+      <c r="AC42" s="141"/>
+      <c r="AD42" s="141"/>
+      <c r="AE42" s="142"/>
+      <c r="AF42" s="140"/>
+      <c r="AG42" s="141"/>
+      <c r="AH42" s="141"/>
+      <c r="AI42" s="142"/>
+      <c r="AJ42" s="140"/>
+      <c r="AK42" s="141"/>
+      <c r="AL42" s="142"/>
     </row>
     <row r="43" spans="1:38" ht="15.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="133"/>
-      <c r="B43" s="134"/>
-      <c r="C43" s="134"/>
-      <c r="D43" s="135"/>
-      <c r="E43" s="136" t="s">
+      <c r="A43" s="135"/>
+      <c r="B43" s="136"/>
+      <c r="C43" s="136"/>
+      <c r="D43" s="137"/>
+      <c r="E43" s="138" t="s">
         <v>19</v>
       </c>
-      <c r="F43" s="136"/>
-      <c r="G43" s="136"/>
-      <c r="H43" s="136"/>
-      <c r="I43" s="144"/>
-      <c r="J43" s="145"/>
-      <c r="K43" s="146"/>
-      <c r="L43" s="138"/>
-      <c r="M43" s="139"/>
-      <c r="N43" s="139"/>
-      <c r="O43" s="140"/>
-      <c r="P43" s="138"/>
-      <c r="Q43" s="139"/>
-      <c r="R43" s="139"/>
-      <c r="S43" s="140"/>
-      <c r="T43" s="138"/>
-      <c r="U43" s="139"/>
-      <c r="V43" s="139"/>
-      <c r="W43" s="140"/>
-      <c r="X43" s="138"/>
-      <c r="Y43" s="139"/>
-      <c r="Z43" s="139"/>
-      <c r="AA43" s="140"/>
-      <c r="AB43" s="138"/>
-      <c r="AC43" s="139"/>
-      <c r="AD43" s="139"/>
-      <c r="AE43" s="140"/>
-      <c r="AF43" s="138"/>
-      <c r="AG43" s="139"/>
-      <c r="AH43" s="139"/>
-      <c r="AI43" s="140"/>
-      <c r="AJ43" s="138"/>
-      <c r="AK43" s="139"/>
-      <c r="AL43" s="140"/>
+      <c r="F43" s="138"/>
+      <c r="G43" s="138"/>
+      <c r="H43" s="138"/>
+      <c r="I43" s="146"/>
+      <c r="J43" s="147"/>
+      <c r="K43" s="148"/>
+      <c r="L43" s="140"/>
+      <c r="M43" s="141"/>
+      <c r="N43" s="141"/>
+      <c r="O43" s="142"/>
+      <c r="P43" s="140"/>
+      <c r="Q43" s="141"/>
+      <c r="R43" s="141"/>
+      <c r="S43" s="142"/>
+      <c r="T43" s="140"/>
+      <c r="U43" s="141"/>
+      <c r="V43" s="141"/>
+      <c r="W43" s="142"/>
+      <c r="X43" s="140"/>
+      <c r="Y43" s="141"/>
+      <c r="Z43" s="141"/>
+      <c r="AA43" s="142"/>
+      <c r="AB43" s="140"/>
+      <c r="AC43" s="141"/>
+      <c r="AD43" s="141"/>
+      <c r="AE43" s="142"/>
+      <c r="AF43" s="140"/>
+      <c r="AG43" s="141"/>
+      <c r="AH43" s="141"/>
+      <c r="AI43" s="142"/>
+      <c r="AJ43" s="140"/>
+      <c r="AK43" s="141"/>
+      <c r="AL43" s="142"/>
     </row>
     <row r="44" spans="1:38" ht="15.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="127" t="s">
+      <c r="A44" s="129" t="s">
         <v>181</v>
       </c>
-      <c r="B44" s="128"/>
-      <c r="C44" s="128"/>
-      <c r="D44" s="129"/>
-      <c r="E44" s="136" t="s">
+      <c r="B44" s="130"/>
+      <c r="C44" s="130"/>
+      <c r="D44" s="131"/>
+      <c r="E44" s="138" t="s">
         <v>9</v>
       </c>
-      <c r="F44" s="137"/>
-      <c r="G44" s="137"/>
-      <c r="H44" s="137"/>
-      <c r="I44" s="144"/>
-      <c r="J44" s="145"/>
-      <c r="K44" s="146"/>
-      <c r="L44" s="138"/>
-      <c r="M44" s="139"/>
-      <c r="N44" s="139"/>
-      <c r="O44" s="140"/>
-      <c r="P44" s="138"/>
-      <c r="Q44" s="139"/>
-      <c r="R44" s="139"/>
-      <c r="S44" s="140"/>
-      <c r="T44" s="138"/>
-      <c r="U44" s="139"/>
-      <c r="V44" s="139"/>
-      <c r="W44" s="140"/>
-      <c r="X44" s="138"/>
-      <c r="Y44" s="139"/>
-      <c r="Z44" s="139"/>
-      <c r="AA44" s="140"/>
-      <c r="AB44" s="138"/>
-      <c r="AC44" s="139"/>
-      <c r="AD44" s="139"/>
-      <c r="AE44" s="140"/>
-      <c r="AF44" s="138"/>
-      <c r="AG44" s="139"/>
-      <c r="AH44" s="139"/>
-      <c r="AI44" s="140"/>
-      <c r="AJ44" s="138"/>
-      <c r="AK44" s="139"/>
-      <c r="AL44" s="140"/>
+      <c r="F44" s="139"/>
+      <c r="G44" s="139"/>
+      <c r="H44" s="139"/>
+      <c r="I44" s="146"/>
+      <c r="J44" s="147"/>
+      <c r="K44" s="148"/>
+      <c r="L44" s="140"/>
+      <c r="M44" s="141"/>
+      <c r="N44" s="141"/>
+      <c r="O44" s="142"/>
+      <c r="P44" s="140"/>
+      <c r="Q44" s="141"/>
+      <c r="R44" s="141"/>
+      <c r="S44" s="142"/>
+      <c r="T44" s="140"/>
+      <c r="U44" s="141"/>
+      <c r="V44" s="141"/>
+      <c r="W44" s="142"/>
+      <c r="X44" s="140"/>
+      <c r="Y44" s="141"/>
+      <c r="Z44" s="141"/>
+      <c r="AA44" s="142"/>
+      <c r="AB44" s="140"/>
+      <c r="AC44" s="141"/>
+      <c r="AD44" s="141"/>
+      <c r="AE44" s="142"/>
+      <c r="AF44" s="140"/>
+      <c r="AG44" s="141"/>
+      <c r="AH44" s="141"/>
+      <c r="AI44" s="142"/>
+      <c r="AJ44" s="140"/>
+      <c r="AK44" s="141"/>
+      <c r="AL44" s="142"/>
     </row>
     <row r="45" spans="1:38" ht="15.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="130"/>
-      <c r="B45" s="131"/>
-      <c r="C45" s="131"/>
-      <c r="D45" s="132"/>
-      <c r="E45" s="136" t="s">
+      <c r="A45" s="132"/>
+      <c r="B45" s="133"/>
+      <c r="C45" s="133"/>
+      <c r="D45" s="134"/>
+      <c r="E45" s="138" t="s">
         <v>10</v>
       </c>
-      <c r="F45" s="137"/>
-      <c r="G45" s="137"/>
-      <c r="H45" s="137"/>
-      <c r="I45" s="144"/>
-      <c r="J45" s="145"/>
-      <c r="K45" s="146"/>
-      <c r="L45" s="138"/>
-      <c r="M45" s="139"/>
-      <c r="N45" s="139"/>
-      <c r="O45" s="140"/>
-      <c r="P45" s="138"/>
-      <c r="Q45" s="139"/>
-      <c r="R45" s="139"/>
-      <c r="S45" s="140"/>
-      <c r="T45" s="138"/>
-      <c r="U45" s="139"/>
-      <c r="V45" s="139"/>
-      <c r="W45" s="140"/>
-      <c r="X45" s="138"/>
-      <c r="Y45" s="139"/>
-      <c r="Z45" s="139"/>
-      <c r="AA45" s="140"/>
-      <c r="AB45" s="138"/>
-      <c r="AC45" s="139"/>
-      <c r="AD45" s="139"/>
-      <c r="AE45" s="140"/>
-      <c r="AF45" s="138"/>
-      <c r="AG45" s="139"/>
-      <c r="AH45" s="139"/>
-      <c r="AI45" s="140"/>
-      <c r="AJ45" s="138"/>
-      <c r="AK45" s="139"/>
-      <c r="AL45" s="140"/>
+      <c r="F45" s="139"/>
+      <c r="G45" s="139"/>
+      <c r="H45" s="139"/>
+      <c r="I45" s="146"/>
+      <c r="J45" s="147"/>
+      <c r="K45" s="148"/>
+      <c r="L45" s="140"/>
+      <c r="M45" s="141"/>
+      <c r="N45" s="141"/>
+      <c r="O45" s="142"/>
+      <c r="P45" s="140"/>
+      <c r="Q45" s="141"/>
+      <c r="R45" s="141"/>
+      <c r="S45" s="142"/>
+      <c r="T45" s="140"/>
+      <c r="U45" s="141"/>
+      <c r="V45" s="141"/>
+      <c r="W45" s="142"/>
+      <c r="X45" s="140"/>
+      <c r="Y45" s="141"/>
+      <c r="Z45" s="141"/>
+      <c r="AA45" s="142"/>
+      <c r="AB45" s="140"/>
+      <c r="AC45" s="141"/>
+      <c r="AD45" s="141"/>
+      <c r="AE45" s="142"/>
+      <c r="AF45" s="140"/>
+      <c r="AG45" s="141"/>
+      <c r="AH45" s="141"/>
+      <c r="AI45" s="142"/>
+      <c r="AJ45" s="140"/>
+      <c r="AK45" s="141"/>
+      <c r="AL45" s="142"/>
     </row>
     <row r="46" spans="1:38" ht="15.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="130"/>
-      <c r="B46" s="131"/>
-      <c r="C46" s="131"/>
-      <c r="D46" s="132"/>
-      <c r="E46" s="136" t="s">
+      <c r="A46" s="132"/>
+      <c r="B46" s="133"/>
+      <c r="C46" s="133"/>
+      <c r="D46" s="134"/>
+      <c r="E46" s="138" t="s">
         <v>11</v>
       </c>
-      <c r="F46" s="137"/>
-      <c r="G46" s="137"/>
-      <c r="H46" s="137"/>
-      <c r="I46" s="144"/>
-      <c r="J46" s="145"/>
-      <c r="K46" s="146"/>
-      <c r="L46" s="138"/>
-      <c r="M46" s="139"/>
-      <c r="N46" s="139"/>
-      <c r="O46" s="140"/>
-      <c r="P46" s="138"/>
-      <c r="Q46" s="139"/>
-      <c r="R46" s="139"/>
-      <c r="S46" s="140"/>
-      <c r="T46" s="138"/>
-      <c r="U46" s="139"/>
-      <c r="V46" s="139"/>
-      <c r="W46" s="140"/>
-      <c r="X46" s="138"/>
-      <c r="Y46" s="139"/>
-      <c r="Z46" s="139"/>
-      <c r="AA46" s="140"/>
-      <c r="AB46" s="138"/>
-      <c r="AC46" s="139"/>
-      <c r="AD46" s="139"/>
-      <c r="AE46" s="140"/>
-      <c r="AF46" s="138"/>
-      <c r="AG46" s="139"/>
-      <c r="AH46" s="139"/>
-      <c r="AI46" s="140"/>
-      <c r="AJ46" s="138"/>
-      <c r="AK46" s="139"/>
-      <c r="AL46" s="140"/>
+      <c r="F46" s="139"/>
+      <c r="G46" s="139"/>
+      <c r="H46" s="139"/>
+      <c r="I46" s="146"/>
+      <c r="J46" s="147"/>
+      <c r="K46" s="148"/>
+      <c r="L46" s="140"/>
+      <c r="M46" s="141"/>
+      <c r="N46" s="141"/>
+      <c r="O46" s="142"/>
+      <c r="P46" s="140"/>
+      <c r="Q46" s="141"/>
+      <c r="R46" s="141"/>
+      <c r="S46" s="142"/>
+      <c r="T46" s="140"/>
+      <c r="U46" s="141"/>
+      <c r="V46" s="141"/>
+      <c r="W46" s="142"/>
+      <c r="X46" s="140"/>
+      <c r="Y46" s="141"/>
+      <c r="Z46" s="141"/>
+      <c r="AA46" s="142"/>
+      <c r="AB46" s="140"/>
+      <c r="AC46" s="141"/>
+      <c r="AD46" s="141"/>
+      <c r="AE46" s="142"/>
+      <c r="AF46" s="140"/>
+      <c r="AG46" s="141"/>
+      <c r="AH46" s="141"/>
+      <c r="AI46" s="142"/>
+      <c r="AJ46" s="140"/>
+      <c r="AK46" s="141"/>
+      <c r="AL46" s="142"/>
     </row>
     <row r="47" spans="1:38" ht="15.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="130"/>
-      <c r="B47" s="131"/>
-      <c r="C47" s="131"/>
-      <c r="D47" s="132"/>
-      <c r="E47" s="136" t="s">
+      <c r="A47" s="132"/>
+      <c r="B47" s="133"/>
+      <c r="C47" s="133"/>
+      <c r="D47" s="134"/>
+      <c r="E47" s="138" t="s">
         <v>12</v>
       </c>
-      <c r="F47" s="137"/>
-      <c r="G47" s="137"/>
-      <c r="H47" s="137"/>
-      <c r="I47" s="144"/>
-      <c r="J47" s="145"/>
-      <c r="K47" s="146"/>
-      <c r="L47" s="138"/>
-      <c r="M47" s="139"/>
-      <c r="N47" s="139"/>
-      <c r="O47" s="140"/>
-      <c r="P47" s="138"/>
-      <c r="Q47" s="139"/>
-      <c r="R47" s="139"/>
-      <c r="S47" s="140"/>
-      <c r="T47" s="138"/>
-      <c r="U47" s="139"/>
-      <c r="V47" s="139"/>
-      <c r="W47" s="140"/>
-      <c r="X47" s="138"/>
-      <c r="Y47" s="139"/>
-      <c r="Z47" s="139"/>
-      <c r="AA47" s="140"/>
-      <c r="AB47" s="138"/>
-      <c r="AC47" s="139"/>
-      <c r="AD47" s="139"/>
-      <c r="AE47" s="140"/>
-      <c r="AF47" s="138"/>
-      <c r="AG47" s="139"/>
-      <c r="AH47" s="139"/>
-      <c r="AI47" s="140"/>
-      <c r="AJ47" s="138"/>
-      <c r="AK47" s="139"/>
-      <c r="AL47" s="140"/>
+      <c r="F47" s="139"/>
+      <c r="G47" s="139"/>
+      <c r="H47" s="139"/>
+      <c r="I47" s="146"/>
+      <c r="J47" s="147"/>
+      <c r="K47" s="148"/>
+      <c r="L47" s="140"/>
+      <c r="M47" s="141"/>
+      <c r="N47" s="141"/>
+      <c r="O47" s="142"/>
+      <c r="P47" s="140"/>
+      <c r="Q47" s="141"/>
+      <c r="R47" s="141"/>
+      <c r="S47" s="142"/>
+      <c r="T47" s="140"/>
+      <c r="U47" s="141"/>
+      <c r="V47" s="141"/>
+      <c r="W47" s="142"/>
+      <c r="X47" s="140"/>
+      <c r="Y47" s="141"/>
+      <c r="Z47" s="141"/>
+      <c r="AA47" s="142"/>
+      <c r="AB47" s="140"/>
+      <c r="AC47" s="141"/>
+      <c r="AD47" s="141"/>
+      <c r="AE47" s="142"/>
+      <c r="AF47" s="140"/>
+      <c r="AG47" s="141"/>
+      <c r="AH47" s="141"/>
+      <c r="AI47" s="142"/>
+      <c r="AJ47" s="140"/>
+      <c r="AK47" s="141"/>
+      <c r="AL47" s="142"/>
     </row>
     <row r="48" spans="1:38" ht="15.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="130"/>
-      <c r="B48" s="131"/>
-      <c r="C48" s="131"/>
-      <c r="D48" s="132"/>
-      <c r="E48" s="136" t="s">
+      <c r="A48" s="132"/>
+      <c r="B48" s="133"/>
+      <c r="C48" s="133"/>
+      <c r="D48" s="134"/>
+      <c r="E48" s="138" t="s">
         <v>13</v>
       </c>
-      <c r="F48" s="137"/>
-      <c r="G48" s="137"/>
-      <c r="H48" s="137"/>
-      <c r="I48" s="144"/>
-      <c r="J48" s="145"/>
-      <c r="K48" s="146"/>
-      <c r="L48" s="138"/>
-      <c r="M48" s="139"/>
-      <c r="N48" s="139"/>
-      <c r="O48" s="140"/>
-      <c r="P48" s="138"/>
-      <c r="Q48" s="139"/>
-      <c r="R48" s="139"/>
-      <c r="S48" s="140"/>
-      <c r="T48" s="138"/>
-      <c r="U48" s="139"/>
-      <c r="V48" s="139"/>
-      <c r="W48" s="140"/>
-      <c r="X48" s="138"/>
-      <c r="Y48" s="139"/>
-      <c r="Z48" s="139"/>
-      <c r="AA48" s="140"/>
-      <c r="AB48" s="138"/>
-      <c r="AC48" s="139"/>
-      <c r="AD48" s="139"/>
-      <c r="AE48" s="140"/>
-      <c r="AF48" s="138"/>
-      <c r="AG48" s="139"/>
-      <c r="AH48" s="139"/>
-      <c r="AI48" s="140"/>
-      <c r="AJ48" s="138"/>
-      <c r="AK48" s="139"/>
-      <c r="AL48" s="140"/>
+      <c r="F48" s="139"/>
+      <c r="G48" s="139"/>
+      <c r="H48" s="139"/>
+      <c r="I48" s="146"/>
+      <c r="J48" s="147"/>
+      <c r="K48" s="148"/>
+      <c r="L48" s="140"/>
+      <c r="M48" s="141"/>
+      <c r="N48" s="141"/>
+      <c r="O48" s="142"/>
+      <c r="P48" s="140"/>
+      <c r="Q48" s="141"/>
+      <c r="R48" s="141"/>
+      <c r="S48" s="142"/>
+      <c r="T48" s="140"/>
+      <c r="U48" s="141"/>
+      <c r="V48" s="141"/>
+      <c r="W48" s="142"/>
+      <c r="X48" s="140"/>
+      <c r="Y48" s="141"/>
+      <c r="Z48" s="141"/>
+      <c r="AA48" s="142"/>
+      <c r="AB48" s="140"/>
+      <c r="AC48" s="141"/>
+      <c r="AD48" s="141"/>
+      <c r="AE48" s="142"/>
+      <c r="AF48" s="140"/>
+      <c r="AG48" s="141"/>
+      <c r="AH48" s="141"/>
+      <c r="AI48" s="142"/>
+      <c r="AJ48" s="140"/>
+      <c r="AK48" s="141"/>
+      <c r="AL48" s="142"/>
     </row>
     <row r="49" spans="1:38" ht="15.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="133"/>
-      <c r="B49" s="134"/>
-      <c r="C49" s="134"/>
-      <c r="D49" s="135"/>
-      <c r="E49" s="136" t="s">
+      <c r="A49" s="135"/>
+      <c r="B49" s="136"/>
+      <c r="C49" s="136"/>
+      <c r="D49" s="137"/>
+      <c r="E49" s="138" t="s">
         <v>19</v>
       </c>
-      <c r="F49" s="136"/>
-      <c r="G49" s="136"/>
-      <c r="H49" s="136"/>
-      <c r="I49" s="147"/>
-      <c r="J49" s="148"/>
-      <c r="K49" s="149"/>
-      <c r="L49" s="138"/>
-      <c r="M49" s="139"/>
-      <c r="N49" s="139"/>
-      <c r="O49" s="140"/>
-      <c r="P49" s="138"/>
-      <c r="Q49" s="139"/>
-      <c r="R49" s="139"/>
-      <c r="S49" s="140"/>
-      <c r="T49" s="138"/>
-      <c r="U49" s="139"/>
-      <c r="V49" s="139"/>
-      <c r="W49" s="140"/>
-      <c r="X49" s="138"/>
-      <c r="Y49" s="139"/>
-      <c r="Z49" s="139"/>
-      <c r="AA49" s="140"/>
-      <c r="AB49" s="138"/>
-      <c r="AC49" s="139"/>
-      <c r="AD49" s="139"/>
-      <c r="AE49" s="140"/>
-      <c r="AF49" s="138"/>
-      <c r="AG49" s="139"/>
-      <c r="AH49" s="139"/>
-      <c r="AI49" s="140"/>
-      <c r="AJ49" s="138"/>
-      <c r="AK49" s="139"/>
-      <c r="AL49" s="140"/>
+      <c r="F49" s="138"/>
+      <c r="G49" s="138"/>
+      <c r="H49" s="138"/>
+      <c r="I49" s="149"/>
+      <c r="J49" s="150"/>
+      <c r="K49" s="151"/>
+      <c r="L49" s="140"/>
+      <c r="M49" s="141"/>
+      <c r="N49" s="141"/>
+      <c r="O49" s="142"/>
+      <c r="P49" s="140"/>
+      <c r="Q49" s="141"/>
+      <c r="R49" s="141"/>
+      <c r="S49" s="142"/>
+      <c r="T49" s="140"/>
+      <c r="U49" s="141"/>
+      <c r="V49" s="141"/>
+      <c r="W49" s="142"/>
+      <c r="X49" s="140"/>
+      <c r="Y49" s="141"/>
+      <c r="Z49" s="141"/>
+      <c r="AA49" s="142"/>
+      <c r="AB49" s="140"/>
+      <c r="AC49" s="141"/>
+      <c r="AD49" s="141"/>
+      <c r="AE49" s="142"/>
+      <c r="AF49" s="140"/>
+      <c r="AG49" s="141"/>
+      <c r="AH49" s="141"/>
+      <c r="AI49" s="142"/>
+      <c r="AJ49" s="140"/>
+      <c r="AK49" s="141"/>
+      <c r="AL49" s="142"/>
     </row>
     <row r="50" spans="1:38" ht="8.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="64"/>
@@ -9979,44 +9986,44 @@
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
-      <c r="M1" s="161"/>
-      <c r="N1" s="161"/>
-      <c r="O1" s="161"/>
-      <c r="P1" s="161"/>
-      <c r="Q1" s="161"/>
-      <c r="R1" s="161"/>
-      <c r="S1" s="161"/>
-      <c r="T1" s="161"/>
-      <c r="U1" s="161"/>
-      <c r="V1" s="161"/>
-      <c r="W1" s="161"/>
-      <c r="X1" s="161"/>
-      <c r="Y1" s="161"/>
-      <c r="Z1" s="161"/>
-      <c r="AA1" s="161"/>
-      <c r="AB1" s="161"/>
-      <c r="AC1" s="161"/>
-      <c r="AD1" s="161"/>
-      <c r="AE1" s="161"/>
-      <c r="AF1" s="161"/>
-      <c r="AG1" s="161"/>
-      <c r="AH1" s="161"/>
-      <c r="AI1" s="161"/>
-      <c r="AJ1" s="161"/>
-      <c r="AK1" s="161"/>
-      <c r="AL1" s="161"/>
+      <c r="M1" s="163"/>
+      <c r="N1" s="163"/>
+      <c r="O1" s="163"/>
+      <c r="P1" s="163"/>
+      <c r="Q1" s="163"/>
+      <c r="R1" s="163"/>
+      <c r="S1" s="163"/>
+      <c r="T1" s="163"/>
+      <c r="U1" s="163"/>
+      <c r="V1" s="163"/>
+      <c r="W1" s="163"/>
+      <c r="X1" s="163"/>
+      <c r="Y1" s="163"/>
+      <c r="Z1" s="163"/>
+      <c r="AA1" s="163"/>
+      <c r="AB1" s="163"/>
+      <c r="AC1" s="163"/>
+      <c r="AD1" s="163"/>
+      <c r="AE1" s="163"/>
+      <c r="AF1" s="163"/>
+      <c r="AG1" s="163"/>
+      <c r="AH1" s="163"/>
+      <c r="AI1" s="163"/>
+      <c r="AJ1" s="163"/>
+      <c r="AK1" s="163"/>
+      <c r="AL1" s="163"/>
     </row>
     <row r="2" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="160" t="s">
+      <c r="A2" s="162" t="s">
         <v>54</v>
       </c>
-      <c r="B2" s="160"/>
-      <c r="C2" s="160"/>
-      <c r="D2" s="160"/>
-      <c r="E2" s="160"/>
-      <c r="F2" s="160"/>
-      <c r="G2" s="160"/>
-      <c r="H2" s="160"/>
+      <c r="B2" s="162"/>
+      <c r="C2" s="162"/>
+      <c r="D2" s="162"/>
+      <c r="E2" s="162"/>
+      <c r="F2" s="162"/>
+      <c r="G2" s="162"/>
+      <c r="H2" s="162"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
@@ -10049,18 +10056,18 @@
       <c r="AL2" s="1"/>
     </row>
     <row r="3" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="126"/>
-      <c r="B3" s="126"/>
-      <c r="C3" s="126"/>
-      <c r="D3" s="126"/>
-      <c r="E3" s="126"/>
-      <c r="F3" s="126"/>
-      <c r="G3" s="126"/>
-      <c r="H3" s="126"/>
-      <c r="I3" s="126"/>
-      <c r="J3" s="126"/>
-      <c r="K3" s="126"/>
-      <c r="L3" s="126"/>
+      <c r="A3" s="128"/>
+      <c r="B3" s="128"/>
+      <c r="C3" s="128"/>
+      <c r="D3" s="128"/>
+      <c r="E3" s="128"/>
+      <c r="F3" s="128"/>
+      <c r="G3" s="128"/>
+      <c r="H3" s="128"/>
+      <c r="I3" s="128"/>
+      <c r="J3" s="128"/>
+      <c r="K3" s="128"/>
+      <c r="L3" s="128"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
@@ -10133,18 +10140,18 @@
         <v>55</v>
       </c>
       <c r="B5" s="1"/>
-      <c r="C5" s="161"/>
-      <c r="D5" s="161"/>
-      <c r="E5" s="161"/>
+      <c r="C5" s="163"/>
+      <c r="D5" s="163"/>
+      <c r="E5" s="163"/>
       <c r="F5" s="1" t="s">
         <v>56</v>
       </c>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
-      <c r="I5" s="161"/>
-      <c r="J5" s="161"/>
-      <c r="K5" s="161"/>
-      <c r="L5" s="161"/>
+      <c r="I5" s="163"/>
+      <c r="J5" s="163"/>
+      <c r="K5" s="163"/>
+      <c r="L5" s="163"/>
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
@@ -10255,85 +10262,85 @@
       <c r="AL7" s="1"/>
     </row>
     <row r="8" spans="1:38" ht="21.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="162" t="s">
+      <c r="A8" s="164" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="162"/>
-      <c r="C8" s="162"/>
-      <c r="D8" s="162"/>
-      <c r="E8" s="162"/>
-      <c r="F8" s="162"/>
-      <c r="G8" s="162"/>
-      <c r="H8" s="122"/>
-      <c r="I8" s="122"/>
-      <c r="J8" s="122"/>
-      <c r="K8" s="122"/>
-      <c r="L8" s="122"/>
-      <c r="M8" s="122"/>
-      <c r="N8" s="122"/>
-      <c r="O8" s="122"/>
-      <c r="P8" s="122"/>
-      <c r="Q8" s="122"/>
-      <c r="R8" s="122"/>
-      <c r="S8" s="122"/>
-      <c r="T8" s="122"/>
-      <c r="U8" s="122"/>
-      <c r="V8" s="122"/>
-      <c r="W8" s="122"/>
-      <c r="X8" s="122"/>
-      <c r="Y8" s="122"/>
-      <c r="Z8" s="122"/>
-      <c r="AA8" s="122"/>
-      <c r="AB8" s="122"/>
-      <c r="AC8" s="122"/>
-      <c r="AD8" s="122"/>
-      <c r="AE8" s="122"/>
-      <c r="AF8" s="122"/>
-      <c r="AG8" s="122"/>
-      <c r="AH8" s="122"/>
-      <c r="AI8" s="122"/>
+      <c r="B8" s="164"/>
+      <c r="C8" s="164"/>
+      <c r="D8" s="164"/>
+      <c r="E8" s="164"/>
+      <c r="F8" s="164"/>
+      <c r="G8" s="164"/>
+      <c r="H8" s="124"/>
+      <c r="I8" s="124"/>
+      <c r="J8" s="124"/>
+      <c r="K8" s="124"/>
+      <c r="L8" s="124"/>
+      <c r="M8" s="124"/>
+      <c r="N8" s="124"/>
+      <c r="O8" s="124"/>
+      <c r="P8" s="124"/>
+      <c r="Q8" s="124"/>
+      <c r="R8" s="124"/>
+      <c r="S8" s="124"/>
+      <c r="T8" s="124"/>
+      <c r="U8" s="124"/>
+      <c r="V8" s="124"/>
+      <c r="W8" s="124"/>
+      <c r="X8" s="124"/>
+      <c r="Y8" s="124"/>
+      <c r="Z8" s="124"/>
+      <c r="AA8" s="124"/>
+      <c r="AB8" s="124"/>
+      <c r="AC8" s="124"/>
+      <c r="AD8" s="124"/>
+      <c r="AE8" s="124"/>
+      <c r="AF8" s="124"/>
+      <c r="AG8" s="124"/>
+      <c r="AH8" s="124"/>
+      <c r="AI8" s="124"/>
       <c r="AJ8" s="1"/>
       <c r="AK8" s="1"/>
       <c r="AL8" s="1"/>
     </row>
     <row r="9" spans="1:38" ht="21.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="162" t="s">
+      <c r="A9" s="164" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="162"/>
-      <c r="C9" s="162"/>
-      <c r="D9" s="162"/>
-      <c r="E9" s="162"/>
-      <c r="F9" s="162"/>
-      <c r="G9" s="162"/>
-      <c r="H9" s="120"/>
-      <c r="I9" s="120"/>
-      <c r="J9" s="120"/>
-      <c r="K9" s="120"/>
-      <c r="L9" s="120"/>
-      <c r="M9" s="120"/>
-      <c r="N9" s="120"/>
-      <c r="O9" s="120"/>
-      <c r="P9" s="120"/>
-      <c r="Q9" s="120"/>
-      <c r="R9" s="120"/>
-      <c r="S9" s="120"/>
-      <c r="T9" s="120"/>
-      <c r="U9" s="120"/>
-      <c r="V9" s="120"/>
-      <c r="W9" s="120"/>
-      <c r="X9" s="120"/>
-      <c r="Y9" s="120"/>
-      <c r="Z9" s="120"/>
-      <c r="AA9" s="120"/>
-      <c r="AB9" s="120"/>
-      <c r="AC9" s="120"/>
-      <c r="AD9" s="120"/>
-      <c r="AE9" s="120"/>
-      <c r="AF9" s="120"/>
-      <c r="AG9" s="120"/>
-      <c r="AH9" s="120"/>
-      <c r="AI9" s="120"/>
+      <c r="B9" s="164"/>
+      <c r="C9" s="164"/>
+      <c r="D9" s="164"/>
+      <c r="E9" s="164"/>
+      <c r="F9" s="164"/>
+      <c r="G9" s="164"/>
+      <c r="H9" s="122"/>
+      <c r="I9" s="122"/>
+      <c r="J9" s="122"/>
+      <c r="K9" s="122"/>
+      <c r="L9" s="122"/>
+      <c r="M9" s="122"/>
+      <c r="N9" s="122"/>
+      <c r="O9" s="122"/>
+      <c r="P9" s="122"/>
+      <c r="Q9" s="122"/>
+      <c r="R9" s="122"/>
+      <c r="S9" s="122"/>
+      <c r="T9" s="122"/>
+      <c r="U9" s="122"/>
+      <c r="V9" s="122"/>
+      <c r="W9" s="122"/>
+      <c r="X9" s="122"/>
+      <c r="Y9" s="122"/>
+      <c r="Z9" s="122"/>
+      <c r="AA9" s="122"/>
+      <c r="AB9" s="122"/>
+      <c r="AC9" s="122"/>
+      <c r="AD9" s="122"/>
+      <c r="AE9" s="122"/>
+      <c r="AF9" s="122"/>
+      <c r="AG9" s="122"/>
+      <c r="AH9" s="122"/>
+      <c r="AI9" s="122"/>
       <c r="AJ9" s="1"/>
       <c r="AK9" s="1"/>
       <c r="AL9" s="1"/>
@@ -10802,20 +10809,20 @@
       <c r="G21" s="30"/>
       <c r="H21" s="30"/>
       <c r="I21" s="30"/>
-      <c r="J21" s="115"/>
-      <c r="K21" s="115"/>
-      <c r="L21" s="115"/>
-      <c r="M21" s="115"/>
-      <c r="N21" s="115"/>
-      <c r="O21" s="115"/>
-      <c r="P21" s="115"/>
-      <c r="Q21" s="115"/>
-      <c r="R21" s="115"/>
-      <c r="S21" s="115"/>
-      <c r="T21" s="115"/>
-      <c r="U21" s="115"/>
-      <c r="V21" s="115"/>
-      <c r="W21" s="115"/>
+      <c r="J21" s="117"/>
+      <c r="K21" s="117"/>
+      <c r="L21" s="117"/>
+      <c r="M21" s="117"/>
+      <c r="N21" s="117"/>
+      <c r="O21" s="117"/>
+      <c r="P21" s="117"/>
+      <c r="Q21" s="117"/>
+      <c r="R21" s="117"/>
+      <c r="S21" s="117"/>
+      <c r="T21" s="117"/>
+      <c r="U21" s="117"/>
+      <c r="V21" s="117"/>
+      <c r="W21" s="117"/>
       <c r="X21" s="1"/>
       <c r="Y21" s="1"/>
       <c r="Z21" s="1"/>
@@ -10860,8 +10867,8 @@
       <c r="A23" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="C23" s="125"/>
-      <c r="D23" s="125"/>
+      <c r="C23" s="127"/>
+      <c r="D23" s="127"/>
       <c r="E23" s="30" t="s">
         <v>43</v>
       </c>
@@ -10927,250 +10934,250 @@
       <c r="AK24" s="3"/>
     </row>
     <row r="25" spans="1:38" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="159" t="s">
+      <c r="A25" s="161" t="s">
         <v>8</v>
       </c>
-      <c r="B25" s="159"/>
-      <c r="C25" s="159"/>
-      <c r="D25" s="159"/>
-      <c r="E25" s="159"/>
-      <c r="F25" s="159"/>
-      <c r="G25" s="159"/>
-      <c r="H25" s="159"/>
-      <c r="I25" s="159"/>
-      <c r="J25" s="159"/>
-      <c r="K25" s="122"/>
-      <c r="L25" s="122"/>
-      <c r="M25" s="122"/>
-      <c r="N25" s="122"/>
-      <c r="O25" s="122"/>
-      <c r="P25" s="122"/>
-      <c r="Q25" s="122"/>
-      <c r="R25" s="122"/>
-      <c r="S25" s="122"/>
-      <c r="T25" s="122"/>
-      <c r="U25" s="122"/>
-      <c r="V25" s="122"/>
-      <c r="W25" s="122"/>
-      <c r="X25" s="122"/>
-      <c r="Y25" s="122"/>
-      <c r="Z25" s="122"/>
-      <c r="AA25" s="122"/>
-      <c r="AB25" s="122"/>
-      <c r="AC25" s="122"/>
-      <c r="AD25" s="122"/>
-      <c r="AE25" s="122"/>
-      <c r="AF25" s="122"/>
-      <c r="AG25" s="122"/>
-      <c r="AH25" s="122"/>
-      <c r="AI25" s="122"/>
-      <c r="AJ25" s="122"/>
-      <c r="AK25" s="122"/>
-      <c r="AL25" s="122"/>
+      <c r="B25" s="161"/>
+      <c r="C25" s="161"/>
+      <c r="D25" s="161"/>
+      <c r="E25" s="161"/>
+      <c r="F25" s="161"/>
+      <c r="G25" s="161"/>
+      <c r="H25" s="161"/>
+      <c r="I25" s="161"/>
+      <c r="J25" s="161"/>
+      <c r="K25" s="124"/>
+      <c r="L25" s="124"/>
+      <c r="M25" s="124"/>
+      <c r="N25" s="124"/>
+      <c r="O25" s="124"/>
+      <c r="P25" s="124"/>
+      <c r="Q25" s="124"/>
+      <c r="R25" s="124"/>
+      <c r="S25" s="124"/>
+      <c r="T25" s="124"/>
+      <c r="U25" s="124"/>
+      <c r="V25" s="124"/>
+      <c r="W25" s="124"/>
+      <c r="X25" s="124"/>
+      <c r="Y25" s="124"/>
+      <c r="Z25" s="124"/>
+      <c r="AA25" s="124"/>
+      <c r="AB25" s="124"/>
+      <c r="AC25" s="124"/>
+      <c r="AD25" s="124"/>
+      <c r="AE25" s="124"/>
+      <c r="AF25" s="124"/>
+      <c r="AG25" s="124"/>
+      <c r="AH25" s="124"/>
+      <c r="AI25" s="124"/>
+      <c r="AJ25" s="124"/>
+      <c r="AK25" s="124"/>
+      <c r="AL25" s="124"/>
     </row>
     <row r="26" spans="1:38" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="159"/>
-      <c r="B26" s="159"/>
-      <c r="C26" s="159"/>
-      <c r="D26" s="159"/>
-      <c r="E26" s="159"/>
-      <c r="F26" s="159"/>
-      <c r="G26" s="159"/>
-      <c r="H26" s="159"/>
-      <c r="I26" s="159"/>
-      <c r="J26" s="159"/>
-      <c r="K26" s="122"/>
-      <c r="L26" s="122"/>
-      <c r="M26" s="122"/>
-      <c r="N26" s="122"/>
-      <c r="O26" s="122"/>
-      <c r="P26" s="122"/>
-      <c r="Q26" s="122"/>
-      <c r="R26" s="122"/>
-      <c r="S26" s="122"/>
-      <c r="T26" s="122"/>
-      <c r="U26" s="122"/>
-      <c r="V26" s="122"/>
-      <c r="W26" s="122"/>
-      <c r="X26" s="122"/>
-      <c r="Y26" s="122"/>
-      <c r="Z26" s="122"/>
-      <c r="AA26" s="122"/>
-      <c r="AB26" s="122"/>
-      <c r="AC26" s="122"/>
-      <c r="AD26" s="122"/>
-      <c r="AE26" s="122"/>
-      <c r="AF26" s="122"/>
-      <c r="AG26" s="122"/>
-      <c r="AH26" s="122"/>
-      <c r="AI26" s="122"/>
-      <c r="AJ26" s="122"/>
-      <c r="AK26" s="122"/>
-      <c r="AL26" s="122"/>
+      <c r="A26" s="161"/>
+      <c r="B26" s="161"/>
+      <c r="C26" s="161"/>
+      <c r="D26" s="161"/>
+      <c r="E26" s="161"/>
+      <c r="F26" s="161"/>
+      <c r="G26" s="161"/>
+      <c r="H26" s="161"/>
+      <c r="I26" s="161"/>
+      <c r="J26" s="161"/>
+      <c r="K26" s="124"/>
+      <c r="L26" s="124"/>
+      <c r="M26" s="124"/>
+      <c r="N26" s="124"/>
+      <c r="O26" s="124"/>
+      <c r="P26" s="124"/>
+      <c r="Q26" s="124"/>
+      <c r="R26" s="124"/>
+      <c r="S26" s="124"/>
+      <c r="T26" s="124"/>
+      <c r="U26" s="124"/>
+      <c r="V26" s="124"/>
+      <c r="W26" s="124"/>
+      <c r="X26" s="124"/>
+      <c r="Y26" s="124"/>
+      <c r="Z26" s="124"/>
+      <c r="AA26" s="124"/>
+      <c r="AB26" s="124"/>
+      <c r="AC26" s="124"/>
+      <c r="AD26" s="124"/>
+      <c r="AE26" s="124"/>
+      <c r="AF26" s="124"/>
+      <c r="AG26" s="124"/>
+      <c r="AH26" s="124"/>
+      <c r="AI26" s="124"/>
+      <c r="AJ26" s="124"/>
+      <c r="AK26" s="124"/>
+      <c r="AL26" s="124"/>
     </row>
     <row r="27" spans="1:38" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="159" t="s">
+      <c r="A27" s="161" t="s">
         <v>44</v>
       </c>
-      <c r="B27" s="159"/>
-      <c r="C27" s="159"/>
-      <c r="D27" s="159"/>
-      <c r="E27" s="159"/>
-      <c r="F27" s="159"/>
-      <c r="G27" s="159"/>
-      <c r="H27" s="159"/>
-      <c r="I27" s="159"/>
-      <c r="J27" s="159"/>
-      <c r="K27" s="159"/>
-      <c r="L27" s="159"/>
-      <c r="M27" s="159"/>
-      <c r="N27" s="159"/>
-      <c r="O27" s="159"/>
-      <c r="P27" s="159"/>
-      <c r="Q27" s="159"/>
-      <c r="R27" s="159"/>
-      <c r="S27" s="159"/>
-      <c r="T27" s="159"/>
-      <c r="U27" s="159"/>
-      <c r="V27" s="159"/>
-      <c r="W27" s="159"/>
-      <c r="X27" s="159"/>
-      <c r="Y27" s="159"/>
-      <c r="Z27" s="159"/>
-      <c r="AA27" s="159"/>
-      <c r="AB27" s="159"/>
-      <c r="AC27" s="159"/>
-      <c r="AD27" s="159"/>
-      <c r="AE27" s="159"/>
-      <c r="AF27" s="159"/>
-      <c r="AG27" s="159"/>
-      <c r="AH27" s="159"/>
-      <c r="AI27" s="159"/>
-      <c r="AJ27" s="159"/>
-      <c r="AK27" s="159"/>
-      <c r="AL27" s="159"/>
+      <c r="B27" s="161"/>
+      <c r="C27" s="161"/>
+      <c r="D27" s="161"/>
+      <c r="E27" s="161"/>
+      <c r="F27" s="161"/>
+      <c r="G27" s="161"/>
+      <c r="H27" s="161"/>
+      <c r="I27" s="161"/>
+      <c r="J27" s="161"/>
+      <c r="K27" s="161"/>
+      <c r="L27" s="161"/>
+      <c r="M27" s="161"/>
+      <c r="N27" s="161"/>
+      <c r="O27" s="161"/>
+      <c r="P27" s="161"/>
+      <c r="Q27" s="161"/>
+      <c r="R27" s="161"/>
+      <c r="S27" s="161"/>
+      <c r="T27" s="161"/>
+      <c r="U27" s="161"/>
+      <c r="V27" s="161"/>
+      <c r="W27" s="161"/>
+      <c r="X27" s="161"/>
+      <c r="Y27" s="161"/>
+      <c r="Z27" s="161"/>
+      <c r="AA27" s="161"/>
+      <c r="AB27" s="161"/>
+      <c r="AC27" s="161"/>
+      <c r="AD27" s="161"/>
+      <c r="AE27" s="161"/>
+      <c r="AF27" s="161"/>
+      <c r="AG27" s="161"/>
+      <c r="AH27" s="161"/>
+      <c r="AI27" s="161"/>
+      <c r="AJ27" s="161"/>
+      <c r="AK27" s="161"/>
+      <c r="AL27" s="161"/>
     </row>
     <row r="28" spans="1:38" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="159"/>
-      <c r="B28" s="159"/>
-      <c r="C28" s="159"/>
-      <c r="D28" s="159"/>
-      <c r="E28" s="159"/>
-      <c r="F28" s="159"/>
-      <c r="G28" s="159"/>
-      <c r="H28" s="159"/>
-      <c r="I28" s="159"/>
-      <c r="J28" s="159"/>
-      <c r="K28" s="159"/>
-      <c r="L28" s="159"/>
-      <c r="M28" s="159"/>
-      <c r="N28" s="159"/>
-      <c r="O28" s="159"/>
-      <c r="P28" s="159"/>
-      <c r="Q28" s="159"/>
-      <c r="R28" s="159"/>
-      <c r="S28" s="159"/>
-      <c r="T28" s="159"/>
-      <c r="U28" s="159"/>
-      <c r="V28" s="159"/>
-      <c r="W28" s="159"/>
-      <c r="X28" s="159"/>
-      <c r="Y28" s="159"/>
-      <c r="Z28" s="159"/>
-      <c r="AA28" s="159"/>
-      <c r="AB28" s="159"/>
-      <c r="AC28" s="159"/>
-      <c r="AD28" s="159"/>
-      <c r="AE28" s="159"/>
-      <c r="AF28" s="159"/>
-      <c r="AG28" s="159"/>
-      <c r="AH28" s="159"/>
-      <c r="AI28" s="159"/>
-      <c r="AJ28" s="159"/>
-      <c r="AK28" s="159"/>
-      <c r="AL28" s="159"/>
+      <c r="A28" s="161"/>
+      <c r="B28" s="161"/>
+      <c r="C28" s="161"/>
+      <c r="D28" s="161"/>
+      <c r="E28" s="161"/>
+      <c r="F28" s="161"/>
+      <c r="G28" s="161"/>
+      <c r="H28" s="161"/>
+      <c r="I28" s="161"/>
+      <c r="J28" s="161"/>
+      <c r="K28" s="161"/>
+      <c r="L28" s="161"/>
+      <c r="M28" s="161"/>
+      <c r="N28" s="161"/>
+      <c r="O28" s="161"/>
+      <c r="P28" s="161"/>
+      <c r="Q28" s="161"/>
+      <c r="R28" s="161"/>
+      <c r="S28" s="161"/>
+      <c r="T28" s="161"/>
+      <c r="U28" s="161"/>
+      <c r="V28" s="161"/>
+      <c r="W28" s="161"/>
+      <c r="X28" s="161"/>
+      <c r="Y28" s="161"/>
+      <c r="Z28" s="161"/>
+      <c r="AA28" s="161"/>
+      <c r="AB28" s="161"/>
+      <c r="AC28" s="161"/>
+      <c r="AD28" s="161"/>
+      <c r="AE28" s="161"/>
+      <c r="AF28" s="161"/>
+      <c r="AG28" s="161"/>
+      <c r="AH28" s="161"/>
+      <c r="AI28" s="161"/>
+      <c r="AJ28" s="161"/>
+      <c r="AK28" s="161"/>
+      <c r="AL28" s="161"/>
     </row>
     <row r="29" spans="1:38" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="159" t="s">
+      <c r="A29" s="161" t="s">
         <v>45</v>
       </c>
-      <c r="B29" s="159"/>
-      <c r="C29" s="159"/>
-      <c r="D29" s="159"/>
-      <c r="E29" s="159"/>
-      <c r="F29" s="159"/>
-      <c r="G29" s="159"/>
-      <c r="H29" s="159"/>
-      <c r="I29" s="159"/>
-      <c r="J29" s="159"/>
-      <c r="K29" s="159"/>
-      <c r="L29" s="159"/>
-      <c r="M29" s="159"/>
-      <c r="N29" s="159"/>
-      <c r="O29" s="159"/>
-      <c r="P29" s="159"/>
-      <c r="Q29" s="159"/>
-      <c r="R29" s="159"/>
-      <c r="S29" s="159"/>
-      <c r="T29" s="159"/>
-      <c r="U29" s="159"/>
-      <c r="V29" s="159"/>
-      <c r="W29" s="159"/>
-      <c r="X29" s="159"/>
-      <c r="Y29" s="159"/>
-      <c r="Z29" s="159"/>
-      <c r="AA29" s="159"/>
-      <c r="AB29" s="159"/>
-      <c r="AC29" s="159"/>
-      <c r="AD29" s="159"/>
-      <c r="AE29" s="159"/>
-      <c r="AF29" s="159"/>
-      <c r="AG29" s="159"/>
-      <c r="AH29" s="159"/>
-      <c r="AI29" s="159"/>
-      <c r="AJ29" s="159"/>
-      <c r="AK29" s="159"/>
-      <c r="AL29" s="159"/>
+      <c r="B29" s="161"/>
+      <c r="C29" s="161"/>
+      <c r="D29" s="161"/>
+      <c r="E29" s="161"/>
+      <c r="F29" s="161"/>
+      <c r="G29" s="161"/>
+      <c r="H29" s="161"/>
+      <c r="I29" s="161"/>
+      <c r="J29" s="161"/>
+      <c r="K29" s="161"/>
+      <c r="L29" s="161"/>
+      <c r="M29" s="161"/>
+      <c r="N29" s="161"/>
+      <c r="O29" s="161"/>
+      <c r="P29" s="161"/>
+      <c r="Q29" s="161"/>
+      <c r="R29" s="161"/>
+      <c r="S29" s="161"/>
+      <c r="T29" s="161"/>
+      <c r="U29" s="161"/>
+      <c r="V29" s="161"/>
+      <c r="W29" s="161"/>
+      <c r="X29" s="161"/>
+      <c r="Y29" s="161"/>
+      <c r="Z29" s="161"/>
+      <c r="AA29" s="161"/>
+      <c r="AB29" s="161"/>
+      <c r="AC29" s="161"/>
+      <c r="AD29" s="161"/>
+      <c r="AE29" s="161"/>
+      <c r="AF29" s="161"/>
+      <c r="AG29" s="161"/>
+      <c r="AH29" s="161"/>
+      <c r="AI29" s="161"/>
+      <c r="AJ29" s="161"/>
+      <c r="AK29" s="161"/>
+      <c r="AL29" s="161"/>
     </row>
     <row r="30" spans="1:38" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="159"/>
-      <c r="B30" s="159"/>
-      <c r="C30" s="159"/>
-      <c r="D30" s="159"/>
-      <c r="E30" s="159"/>
-      <c r="F30" s="159"/>
-      <c r="G30" s="159"/>
-      <c r="H30" s="159"/>
-      <c r="I30" s="159"/>
-      <c r="J30" s="159"/>
-      <c r="K30" s="159"/>
-      <c r="L30" s="159"/>
-      <c r="M30" s="159"/>
-      <c r="N30" s="159"/>
-      <c r="O30" s="159"/>
-      <c r="P30" s="159"/>
-      <c r="Q30" s="159"/>
-      <c r="R30" s="159"/>
-      <c r="S30" s="159"/>
-      <c r="T30" s="159"/>
-      <c r="U30" s="159"/>
-      <c r="V30" s="159"/>
-      <c r="W30" s="159"/>
-      <c r="X30" s="159"/>
-      <c r="Y30" s="159"/>
-      <c r="Z30" s="159"/>
-      <c r="AA30" s="159"/>
-      <c r="AB30" s="159"/>
-      <c r="AC30" s="159"/>
-      <c r="AD30" s="159"/>
-      <c r="AE30" s="159"/>
-      <c r="AF30" s="159"/>
-      <c r="AG30" s="159"/>
-      <c r="AH30" s="159"/>
-      <c r="AI30" s="159"/>
-      <c r="AJ30" s="159"/>
-      <c r="AK30" s="159"/>
-      <c r="AL30" s="159"/>
+      <c r="A30" s="161"/>
+      <c r="B30" s="161"/>
+      <c r="C30" s="161"/>
+      <c r="D30" s="161"/>
+      <c r="E30" s="161"/>
+      <c r="F30" s="161"/>
+      <c r="G30" s="161"/>
+      <c r="H30" s="161"/>
+      <c r="I30" s="161"/>
+      <c r="J30" s="161"/>
+      <c r="K30" s="161"/>
+      <c r="L30" s="161"/>
+      <c r="M30" s="161"/>
+      <c r="N30" s="161"/>
+      <c r="O30" s="161"/>
+      <c r="P30" s="161"/>
+      <c r="Q30" s="161"/>
+      <c r="R30" s="161"/>
+      <c r="S30" s="161"/>
+      <c r="T30" s="161"/>
+      <c r="U30" s="161"/>
+      <c r="V30" s="161"/>
+      <c r="W30" s="161"/>
+      <c r="X30" s="161"/>
+      <c r="Y30" s="161"/>
+      <c r="Z30" s="161"/>
+      <c r="AA30" s="161"/>
+      <c r="AB30" s="161"/>
+      <c r="AC30" s="161"/>
+      <c r="AD30" s="161"/>
+      <c r="AE30" s="161"/>
+      <c r="AF30" s="161"/>
+      <c r="AG30" s="161"/>
+      <c r="AH30" s="161"/>
+      <c r="AI30" s="161"/>
+      <c r="AJ30" s="161"/>
+      <c r="AK30" s="161"/>
+      <c r="AL30" s="161"/>
     </row>
     <row r="31" spans="1:38" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="23" t="s">
@@ -12053,32 +12060,32 @@
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
-      <c r="M1" s="125"/>
-      <c r="N1" s="125"/>
-      <c r="O1" s="125"/>
-      <c r="P1" s="125"/>
-      <c r="Q1" s="125"/>
-      <c r="R1" s="125"/>
-      <c r="S1" s="125"/>
-      <c r="T1" s="125"/>
-      <c r="U1" s="125"/>
-      <c r="V1" s="125"/>
-      <c r="W1" s="125"/>
-      <c r="X1" s="125"/>
-      <c r="Y1" s="125"/>
-      <c r="Z1" s="125"/>
-      <c r="AA1" s="125"/>
-      <c r="AB1" s="125"/>
-      <c r="AC1" s="125"/>
-      <c r="AD1" s="125"/>
-      <c r="AE1" s="125"/>
-      <c r="AF1" s="125"/>
-      <c r="AG1" s="125"/>
-      <c r="AH1" s="125"/>
-      <c r="AI1" s="125"/>
-      <c r="AJ1" s="125"/>
-      <c r="AK1" s="125"/>
-      <c r="AL1" s="125"/>
+      <c r="M1" s="127"/>
+      <c r="N1" s="127"/>
+      <c r="O1" s="127"/>
+      <c r="P1" s="127"/>
+      <c r="Q1" s="127"/>
+      <c r="R1" s="127"/>
+      <c r="S1" s="127"/>
+      <c r="T1" s="127"/>
+      <c r="U1" s="127"/>
+      <c r="V1" s="127"/>
+      <c r="W1" s="127"/>
+      <c r="X1" s="127"/>
+      <c r="Y1" s="127"/>
+      <c r="Z1" s="127"/>
+      <c r="AA1" s="127"/>
+      <c r="AB1" s="127"/>
+      <c r="AC1" s="127"/>
+      <c r="AD1" s="127"/>
+      <c r="AE1" s="127"/>
+      <c r="AF1" s="127"/>
+      <c r="AG1" s="127"/>
+      <c r="AH1" s="127"/>
+      <c r="AI1" s="127"/>
+      <c r="AJ1" s="127"/>
+      <c r="AK1" s="127"/>
+      <c r="AL1" s="127"/>
     </row>
     <row r="2" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
@@ -12114,17 +12121,17 @@
       <c r="AF2" s="1"/>
     </row>
     <row r="3" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="115"/>
-      <c r="B3" s="115"/>
-      <c r="C3" s="115"/>
-      <c r="D3" s="115"/>
-      <c r="E3" s="115"/>
-      <c r="F3" s="115"/>
-      <c r="G3" s="115"/>
-      <c r="H3" s="115"/>
-      <c r="I3" s="115"/>
-      <c r="J3" s="115"/>
-      <c r="K3" s="115"/>
+      <c r="A3" s="117"/>
+      <c r="B3" s="117"/>
+      <c r="C3" s="117"/>
+      <c r="D3" s="117"/>
+      <c r="E3" s="117"/>
+      <c r="F3" s="117"/>
+      <c r="G3" s="117"/>
+      <c r="H3" s="117"/>
+      <c r="I3" s="117"/>
+      <c r="J3" s="117"/>
+      <c r="K3" s="117"/>
       <c r="L3" s="17"/>
       <c r="M3" s="17"/>
       <c r="N3" s="1"/>
@@ -12137,11 +12144,11 @@
       <c r="S3" s="1"/>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
-      <c r="V3" s="178"/>
-      <c r="W3" s="178"/>
-      <c r="X3" s="178"/>
-      <c r="Y3" s="178"/>
-      <c r="Z3" s="178"/>
+      <c r="V3" s="180"/>
+      <c r="W3" s="180"/>
+      <c r="X3" s="180"/>
+      <c r="Y3" s="180"/>
+      <c r="Z3" s="180"/>
       <c r="AA3" s="1"/>
       <c r="AB3" s="1"/>
       <c r="AC3" s="1"/>
@@ -12287,268 +12294,268 @@
       <c r="AL7" s="11"/>
     </row>
     <row r="8" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="167" t="s">
+      <c r="A8" s="169" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="167"/>
-      <c r="C8" s="167"/>
-      <c r="D8" s="167"/>
-      <c r="E8" s="167"/>
-      <c r="F8" s="167"/>
-      <c r="G8" s="167"/>
-      <c r="H8" s="167"/>
-      <c r="I8" s="167"/>
-      <c r="J8" s="166" t="s">
+      <c r="B8" s="169"/>
+      <c r="C8" s="169"/>
+      <c r="D8" s="169"/>
+      <c r="E8" s="169"/>
+      <c r="F8" s="169"/>
+      <c r="G8" s="169"/>
+      <c r="H8" s="169"/>
+      <c r="I8" s="169"/>
+      <c r="J8" s="168" t="s">
         <v>18</v>
       </c>
-      <c r="K8" s="166"/>
-      <c r="L8" s="166"/>
-      <c r="M8" s="166"/>
-      <c r="N8" s="166"/>
-      <c r="O8" s="166"/>
-      <c r="P8" s="166"/>
-      <c r="Q8" s="166"/>
-      <c r="R8" s="166"/>
-      <c r="S8" s="166"/>
-      <c r="T8" s="166"/>
-      <c r="U8" s="166"/>
-      <c r="V8" s="166"/>
-      <c r="W8" s="166"/>
-      <c r="X8" s="166"/>
-      <c r="Y8" s="166"/>
-      <c r="Z8" s="166"/>
-      <c r="AA8" s="166"/>
-      <c r="AB8" s="166"/>
-      <c r="AC8" s="166"/>
-      <c r="AD8" s="166"/>
-      <c r="AE8" s="166"/>
-      <c r="AF8" s="166"/>
-      <c r="AG8" s="166"/>
-      <c r="AH8" s="166"/>
-      <c r="AI8" s="168" t="s">
+      <c r="K8" s="168"/>
+      <c r="L8" s="168"/>
+      <c r="M8" s="168"/>
+      <c r="N8" s="168"/>
+      <c r="O8" s="168"/>
+      <c r="P8" s="168"/>
+      <c r="Q8" s="168"/>
+      <c r="R8" s="168"/>
+      <c r="S8" s="168"/>
+      <c r="T8" s="168"/>
+      <c r="U8" s="168"/>
+      <c r="V8" s="168"/>
+      <c r="W8" s="168"/>
+      <c r="X8" s="168"/>
+      <c r="Y8" s="168"/>
+      <c r="Z8" s="168"/>
+      <c r="AA8" s="168"/>
+      <c r="AB8" s="168"/>
+      <c r="AC8" s="168"/>
+      <c r="AD8" s="168"/>
+      <c r="AE8" s="168"/>
+      <c r="AF8" s="168"/>
+      <c r="AG8" s="168"/>
+      <c r="AH8" s="168"/>
+      <c r="AI8" s="170" t="s">
         <v>19</v>
       </c>
-      <c r="AJ8" s="169"/>
-      <c r="AK8" s="169"/>
-      <c r="AL8" s="170"/>
+      <c r="AJ8" s="171"/>
+      <c r="AK8" s="171"/>
+      <c r="AL8" s="172"/>
     </row>
     <row r="9" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="167"/>
-      <c r="B9" s="167"/>
-      <c r="C9" s="167"/>
-      <c r="D9" s="167"/>
-      <c r="E9" s="167"/>
-      <c r="F9" s="167"/>
-      <c r="G9" s="167"/>
-      <c r="H9" s="167"/>
-      <c r="I9" s="167"/>
-      <c r="J9" s="166" t="s">
+      <c r="A9" s="169"/>
+      <c r="B9" s="169"/>
+      <c r="C9" s="169"/>
+      <c r="D9" s="169"/>
+      <c r="E9" s="169"/>
+      <c r="F9" s="169"/>
+      <c r="G9" s="169"/>
+      <c r="H9" s="169"/>
+      <c r="I9" s="169"/>
+      <c r="J9" s="168" t="s">
         <v>28</v>
       </c>
-      <c r="K9" s="166"/>
-      <c r="L9" s="166"/>
-      <c r="M9" s="166"/>
-      <c r="N9" s="166"/>
-      <c r="O9" s="166" t="s">
+      <c r="K9" s="168"/>
+      <c r="L9" s="168"/>
+      <c r="M9" s="168"/>
+      <c r="N9" s="168"/>
+      <c r="O9" s="168" t="s">
         <v>29</v>
       </c>
-      <c r="P9" s="166"/>
-      <c r="Q9" s="166"/>
-      <c r="R9" s="166"/>
-      <c r="S9" s="166"/>
-      <c r="T9" s="166" t="s">
+      <c r="P9" s="168"/>
+      <c r="Q9" s="168"/>
+      <c r="R9" s="168"/>
+      <c r="S9" s="168"/>
+      <c r="T9" s="168" t="s">
         <v>30</v>
       </c>
-      <c r="U9" s="166"/>
-      <c r="V9" s="166"/>
-      <c r="W9" s="166"/>
-      <c r="X9" s="166"/>
-      <c r="Y9" s="166" t="s">
+      <c r="U9" s="168"/>
+      <c r="V9" s="168"/>
+      <c r="W9" s="168"/>
+      <c r="X9" s="168"/>
+      <c r="Y9" s="168" t="s">
         <v>31</v>
       </c>
-      <c r="Z9" s="166"/>
-      <c r="AA9" s="166"/>
-      <c r="AB9" s="166"/>
-      <c r="AC9" s="166"/>
-      <c r="AD9" s="166" t="s">
+      <c r="Z9" s="168"/>
+      <c r="AA9" s="168"/>
+      <c r="AB9" s="168"/>
+      <c r="AC9" s="168"/>
+      <c r="AD9" s="168" t="s">
         <v>32</v>
       </c>
-      <c r="AE9" s="166"/>
-      <c r="AF9" s="166"/>
-      <c r="AG9" s="166"/>
-      <c r="AH9" s="166"/>
-      <c r="AI9" s="171"/>
-      <c r="AJ9" s="172"/>
-      <c r="AK9" s="172"/>
-      <c r="AL9" s="173"/>
+      <c r="AE9" s="168"/>
+      <c r="AF9" s="168"/>
+      <c r="AG9" s="168"/>
+      <c r="AH9" s="168"/>
+      <c r="AI9" s="173"/>
+      <c r="AJ9" s="174"/>
+      <c r="AK9" s="174"/>
+      <c r="AL9" s="175"/>
     </row>
     <row r="10" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="122"/>
-      <c r="B10" s="122"/>
-      <c r="C10" s="122"/>
-      <c r="D10" s="163" t="s">
+      <c r="A10" s="124"/>
+      <c r="B10" s="124"/>
+      <c r="C10" s="124"/>
+      <c r="D10" s="165" t="s">
         <v>25</v>
       </c>
-      <c r="E10" s="164"/>
-      <c r="F10" s="164"/>
-      <c r="G10" s="164"/>
-      <c r="H10" s="164"/>
-      <c r="I10" s="165"/>
-      <c r="J10" s="166"/>
-      <c r="K10" s="166"/>
-      <c r="L10" s="166"/>
-      <c r="M10" s="166"/>
-      <c r="N10" s="166"/>
-      <c r="O10" s="166"/>
-      <c r="P10" s="166"/>
-      <c r="Q10" s="166"/>
-      <c r="R10" s="166"/>
-      <c r="S10" s="166"/>
-      <c r="T10" s="166"/>
-      <c r="U10" s="166"/>
-      <c r="V10" s="166"/>
-      <c r="W10" s="166"/>
-      <c r="X10" s="166"/>
-      <c r="Y10" s="166"/>
-      <c r="Z10" s="166"/>
-      <c r="AA10" s="166"/>
-      <c r="AB10" s="166"/>
-      <c r="AC10" s="166"/>
-      <c r="AD10" s="166"/>
-      <c r="AE10" s="166"/>
-      <c r="AF10" s="166"/>
-      <c r="AG10" s="166"/>
-      <c r="AH10" s="166"/>
-      <c r="AI10" s="163"/>
-      <c r="AJ10" s="164"/>
-      <c r="AK10" s="164"/>
-      <c r="AL10" s="165"/>
+      <c r="E10" s="166"/>
+      <c r="F10" s="166"/>
+      <c r="G10" s="166"/>
+      <c r="H10" s="166"/>
+      <c r="I10" s="167"/>
+      <c r="J10" s="168"/>
+      <c r="K10" s="168"/>
+      <c r="L10" s="168"/>
+      <c r="M10" s="168"/>
+      <c r="N10" s="168"/>
+      <c r="O10" s="168"/>
+      <c r="P10" s="168"/>
+      <c r="Q10" s="168"/>
+      <c r="R10" s="168"/>
+      <c r="S10" s="168"/>
+      <c r="T10" s="168"/>
+      <c r="U10" s="168"/>
+      <c r="V10" s="168"/>
+      <c r="W10" s="168"/>
+      <c r="X10" s="168"/>
+      <c r="Y10" s="168"/>
+      <c r="Z10" s="168"/>
+      <c r="AA10" s="168"/>
+      <c r="AB10" s="168"/>
+      <c r="AC10" s="168"/>
+      <c r="AD10" s="168"/>
+      <c r="AE10" s="168"/>
+      <c r="AF10" s="168"/>
+      <c r="AG10" s="168"/>
+      <c r="AH10" s="168"/>
+      <c r="AI10" s="165"/>
+      <c r="AJ10" s="166"/>
+      <c r="AK10" s="166"/>
+      <c r="AL10" s="167"/>
     </row>
     <row r="11" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="122"/>
-      <c r="B11" s="122"/>
-      <c r="C11" s="122"/>
-      <c r="D11" s="174" t="s">
+      <c r="A11" s="124"/>
+      <c r="B11" s="124"/>
+      <c r="C11" s="124"/>
+      <c r="D11" s="176" t="s">
         <v>196</v>
       </c>
-      <c r="E11" s="164"/>
-      <c r="F11" s="164"/>
-      <c r="G11" s="164"/>
-      <c r="H11" s="164"/>
-      <c r="I11" s="165"/>
-      <c r="J11" s="166"/>
-      <c r="K11" s="166"/>
-      <c r="L11" s="166"/>
-      <c r="M11" s="166"/>
-      <c r="N11" s="166"/>
-      <c r="O11" s="166"/>
-      <c r="P11" s="166"/>
-      <c r="Q11" s="166"/>
-      <c r="R11" s="166"/>
-      <c r="S11" s="166"/>
-      <c r="T11" s="166"/>
-      <c r="U11" s="166"/>
-      <c r="V11" s="166"/>
-      <c r="W11" s="166"/>
-      <c r="X11" s="166"/>
-      <c r="Y11" s="166"/>
-      <c r="Z11" s="166"/>
-      <c r="AA11" s="166"/>
-      <c r="AB11" s="166"/>
-      <c r="AC11" s="166"/>
-      <c r="AD11" s="166"/>
-      <c r="AE11" s="166"/>
-      <c r="AF11" s="166"/>
-      <c r="AG11" s="166"/>
-      <c r="AH11" s="166"/>
-      <c r="AI11" s="163"/>
-      <c r="AJ11" s="164"/>
-      <c r="AK11" s="164"/>
-      <c r="AL11" s="165"/>
+      <c r="E11" s="166"/>
+      <c r="F11" s="166"/>
+      <c r="G11" s="166"/>
+      <c r="H11" s="166"/>
+      <c r="I11" s="167"/>
+      <c r="J11" s="168"/>
+      <c r="K11" s="168"/>
+      <c r="L11" s="168"/>
+      <c r="M11" s="168"/>
+      <c r="N11" s="168"/>
+      <c r="O11" s="168"/>
+      <c r="P11" s="168"/>
+      <c r="Q11" s="168"/>
+      <c r="R11" s="168"/>
+      <c r="S11" s="168"/>
+      <c r="T11" s="168"/>
+      <c r="U11" s="168"/>
+      <c r="V11" s="168"/>
+      <c r="W11" s="168"/>
+      <c r="X11" s="168"/>
+      <c r="Y11" s="168"/>
+      <c r="Z11" s="168"/>
+      <c r="AA11" s="168"/>
+      <c r="AB11" s="168"/>
+      <c r="AC11" s="168"/>
+      <c r="AD11" s="168"/>
+      <c r="AE11" s="168"/>
+      <c r="AF11" s="168"/>
+      <c r="AG11" s="168"/>
+      <c r="AH11" s="168"/>
+      <c r="AI11" s="165"/>
+      <c r="AJ11" s="166"/>
+      <c r="AK11" s="166"/>
+      <c r="AL11" s="167"/>
     </row>
     <row r="12" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="122"/>
-      <c r="B12" s="122"/>
-      <c r="C12" s="122"/>
-      <c r="D12" s="163" t="s">
+      <c r="A12" s="124"/>
+      <c r="B12" s="124"/>
+      <c r="C12" s="124"/>
+      <c r="D12" s="165" t="s">
         <v>25</v>
       </c>
-      <c r="E12" s="164"/>
-      <c r="F12" s="164"/>
-      <c r="G12" s="164"/>
-      <c r="H12" s="164"/>
-      <c r="I12" s="165"/>
-      <c r="J12" s="166"/>
-      <c r="K12" s="166"/>
-      <c r="L12" s="166"/>
-      <c r="M12" s="166"/>
-      <c r="N12" s="166"/>
-      <c r="O12" s="166"/>
-      <c r="P12" s="166"/>
-      <c r="Q12" s="166"/>
-      <c r="R12" s="166"/>
-      <c r="S12" s="166"/>
-      <c r="T12" s="166"/>
-      <c r="U12" s="166"/>
-      <c r="V12" s="166"/>
-      <c r="W12" s="166"/>
-      <c r="X12" s="166"/>
-      <c r="Y12" s="166"/>
-      <c r="Z12" s="166"/>
-      <c r="AA12" s="166"/>
-      <c r="AB12" s="166"/>
-      <c r="AC12" s="166"/>
-      <c r="AD12" s="166"/>
-      <c r="AE12" s="166"/>
-      <c r="AF12" s="166"/>
-      <c r="AG12" s="166"/>
-      <c r="AH12" s="166"/>
-      <c r="AI12" s="163"/>
-      <c r="AJ12" s="164"/>
-      <c r="AK12" s="164"/>
-      <c r="AL12" s="165"/>
+      <c r="E12" s="166"/>
+      <c r="F12" s="166"/>
+      <c r="G12" s="166"/>
+      <c r="H12" s="166"/>
+      <c r="I12" s="167"/>
+      <c r="J12" s="168"/>
+      <c r="K12" s="168"/>
+      <c r="L12" s="168"/>
+      <c r="M12" s="168"/>
+      <c r="N12" s="168"/>
+      <c r="O12" s="168"/>
+      <c r="P12" s="168"/>
+      <c r="Q12" s="168"/>
+      <c r="R12" s="168"/>
+      <c r="S12" s="168"/>
+      <c r="T12" s="168"/>
+      <c r="U12" s="168"/>
+      <c r="V12" s="168"/>
+      <c r="W12" s="168"/>
+      <c r="X12" s="168"/>
+      <c r="Y12" s="168"/>
+      <c r="Z12" s="168"/>
+      <c r="AA12" s="168"/>
+      <c r="AB12" s="168"/>
+      <c r="AC12" s="168"/>
+      <c r="AD12" s="168"/>
+      <c r="AE12" s="168"/>
+      <c r="AF12" s="168"/>
+      <c r="AG12" s="168"/>
+      <c r="AH12" s="168"/>
+      <c r="AI12" s="165"/>
+      <c r="AJ12" s="166"/>
+      <c r="AK12" s="166"/>
+      <c r="AL12" s="167"/>
     </row>
     <row r="13" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="122"/>
-      <c r="B13" s="122"/>
-      <c r="C13" s="122"/>
-      <c r="D13" s="163" t="s">
+      <c r="A13" s="124"/>
+      <c r="B13" s="124"/>
+      <c r="C13" s="124"/>
+      <c r="D13" s="165" t="s">
         <v>26</v>
       </c>
-      <c r="E13" s="164"/>
-      <c r="F13" s="164"/>
-      <c r="G13" s="164"/>
-      <c r="H13" s="164"/>
-      <c r="I13" s="165"/>
-      <c r="J13" s="166"/>
-      <c r="K13" s="166"/>
-      <c r="L13" s="166"/>
-      <c r="M13" s="166"/>
-      <c r="N13" s="166"/>
-      <c r="O13" s="166"/>
-      <c r="P13" s="166"/>
-      <c r="Q13" s="166"/>
-      <c r="R13" s="166"/>
-      <c r="S13" s="166"/>
-      <c r="T13" s="166"/>
-      <c r="U13" s="166"/>
-      <c r="V13" s="166"/>
-      <c r="W13" s="166"/>
-      <c r="X13" s="166"/>
-      <c r="Y13" s="166"/>
-      <c r="Z13" s="166"/>
-      <c r="AA13" s="166"/>
-      <c r="AB13" s="166"/>
-      <c r="AC13" s="166"/>
-      <c r="AD13" s="166"/>
-      <c r="AE13" s="166"/>
-      <c r="AF13" s="166"/>
-      <c r="AG13" s="166"/>
-      <c r="AH13" s="166"/>
-      <c r="AI13" s="163"/>
-      <c r="AJ13" s="164"/>
-      <c r="AK13" s="164"/>
-      <c r="AL13" s="165"/>
+      <c r="E13" s="166"/>
+      <c r="F13" s="166"/>
+      <c r="G13" s="166"/>
+      <c r="H13" s="166"/>
+      <c r="I13" s="167"/>
+      <c r="J13" s="168"/>
+      <c r="K13" s="168"/>
+      <c r="L13" s="168"/>
+      <c r="M13" s="168"/>
+      <c r="N13" s="168"/>
+      <c r="O13" s="168"/>
+      <c r="P13" s="168"/>
+      <c r="Q13" s="168"/>
+      <c r="R13" s="168"/>
+      <c r="S13" s="168"/>
+      <c r="T13" s="168"/>
+      <c r="U13" s="168"/>
+      <c r="V13" s="168"/>
+      <c r="W13" s="168"/>
+      <c r="X13" s="168"/>
+      <c r="Y13" s="168"/>
+      <c r="Z13" s="168"/>
+      <c r="AA13" s="168"/>
+      <c r="AB13" s="168"/>
+      <c r="AC13" s="168"/>
+      <c r="AD13" s="168"/>
+      <c r="AE13" s="168"/>
+      <c r="AF13" s="168"/>
+      <c r="AG13" s="168"/>
+      <c r="AH13" s="168"/>
+      <c r="AI13" s="165"/>
+      <c r="AJ13" s="166"/>
+      <c r="AK13" s="166"/>
+      <c r="AL13" s="167"/>
     </row>
     <row r="14" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="19"/>
@@ -13078,17 +13085,17 @@
       <c r="AL27" s="37"/>
     </row>
     <row r="28" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="115"/>
-      <c r="B28" s="115"/>
-      <c r="C28" s="115"/>
-      <c r="D28" s="115"/>
-      <c r="E28" s="115"/>
-      <c r="F28" s="115"/>
-      <c r="G28" s="115"/>
-      <c r="H28" s="115"/>
-      <c r="I28" s="115"/>
-      <c r="J28" s="115"/>
-      <c r="K28" s="115"/>
+      <c r="A28" s="117"/>
+      <c r="B28" s="117"/>
+      <c r="C28" s="117"/>
+      <c r="D28" s="117"/>
+      <c r="E28" s="117"/>
+      <c r="F28" s="117"/>
+      <c r="G28" s="117"/>
+      <c r="H28" s="117"/>
+      <c r="I28" s="117"/>
+      <c r="J28" s="117"/>
+      <c r="K28" s="117"/>
       <c r="L28" s="2"/>
       <c r="M28" s="37"/>
       <c r="N28" s="75" t="s">
@@ -13309,352 +13316,352 @@
       <c r="AL33" s="37"/>
     </row>
     <row r="34" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A34" s="175" t="s">
+      <c r="A34" s="177" t="s">
         <v>89</v>
       </c>
-      <c r="B34" s="176"/>
-      <c r="C34" s="176"/>
-      <c r="D34" s="176"/>
-      <c r="E34" s="176"/>
-      <c r="F34" s="176"/>
-      <c r="G34" s="176"/>
-      <c r="H34" s="176"/>
-      <c r="I34" s="176"/>
-      <c r="J34" s="176"/>
-      <c r="K34" s="176"/>
-      <c r="L34" s="176"/>
-      <c r="M34" s="162" t="s">
+      <c r="B34" s="178"/>
+      <c r="C34" s="178"/>
+      <c r="D34" s="178"/>
+      <c r="E34" s="178"/>
+      <c r="F34" s="178"/>
+      <c r="G34" s="178"/>
+      <c r="H34" s="178"/>
+      <c r="I34" s="178"/>
+      <c r="J34" s="178"/>
+      <c r="K34" s="178"/>
+      <c r="L34" s="178"/>
+      <c r="M34" s="164" t="s">
         <v>18</v>
       </c>
-      <c r="N34" s="162"/>
-      <c r="O34" s="162"/>
-      <c r="P34" s="162"/>
-      <c r="Q34" s="162"/>
-      <c r="R34" s="162"/>
-      <c r="S34" s="162"/>
-      <c r="T34" s="162"/>
-      <c r="U34" s="162"/>
-      <c r="V34" s="162"/>
-      <c r="W34" s="162"/>
-      <c r="X34" s="162"/>
-      <c r="Y34" s="162"/>
-      <c r="Z34" s="162"/>
-      <c r="AA34" s="162"/>
-      <c r="AB34" s="162"/>
-      <c r="AC34" s="162"/>
-      <c r="AD34" s="162"/>
-      <c r="AE34" s="162"/>
-      <c r="AF34" s="162"/>
-      <c r="AG34" s="162" t="s">
+      <c r="N34" s="164"/>
+      <c r="O34" s="164"/>
+      <c r="P34" s="164"/>
+      <c r="Q34" s="164"/>
+      <c r="R34" s="164"/>
+      <c r="S34" s="164"/>
+      <c r="T34" s="164"/>
+      <c r="U34" s="164"/>
+      <c r="V34" s="164"/>
+      <c r="W34" s="164"/>
+      <c r="X34" s="164"/>
+      <c r="Y34" s="164"/>
+      <c r="Z34" s="164"/>
+      <c r="AA34" s="164"/>
+      <c r="AB34" s="164"/>
+      <c r="AC34" s="164"/>
+      <c r="AD34" s="164"/>
+      <c r="AE34" s="164"/>
+      <c r="AF34" s="164"/>
+      <c r="AG34" s="164" t="s">
         <v>19</v>
       </c>
-      <c r="AH34" s="162"/>
-      <c r="AI34" s="162"/>
-      <c r="AJ34" s="162"/>
-      <c r="AK34" s="162"/>
-      <c r="AL34" s="162"/>
+      <c r="AH34" s="164"/>
+      <c r="AI34" s="164"/>
+      <c r="AJ34" s="164"/>
+      <c r="AK34" s="164"/>
+      <c r="AL34" s="164"/>
     </row>
     <row r="35" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A35" s="176"/>
-      <c r="B35" s="176"/>
-      <c r="C35" s="176"/>
-      <c r="D35" s="176"/>
-      <c r="E35" s="176"/>
-      <c r="F35" s="176"/>
-      <c r="G35" s="176"/>
-      <c r="H35" s="176"/>
-      <c r="I35" s="176"/>
-      <c r="J35" s="176"/>
-      <c r="K35" s="176"/>
-      <c r="L35" s="176"/>
-      <c r="M35" s="162" t="s">
+      <c r="A35" s="178"/>
+      <c r="B35" s="178"/>
+      <c r="C35" s="178"/>
+      <c r="D35" s="178"/>
+      <c r="E35" s="178"/>
+      <c r="F35" s="178"/>
+      <c r="G35" s="178"/>
+      <c r="H35" s="178"/>
+      <c r="I35" s="178"/>
+      <c r="J35" s="178"/>
+      <c r="K35" s="178"/>
+      <c r="L35" s="178"/>
+      <c r="M35" s="164" t="s">
         <v>28</v>
       </c>
-      <c r="N35" s="162"/>
-      <c r="O35" s="162"/>
-      <c r="P35" s="162"/>
-      <c r="Q35" s="162" t="s">
+      <c r="N35" s="164"/>
+      <c r="O35" s="164"/>
+      <c r="P35" s="164"/>
+      <c r="Q35" s="164" t="s">
         <v>29</v>
       </c>
-      <c r="R35" s="162"/>
-      <c r="S35" s="162"/>
-      <c r="T35" s="162"/>
-      <c r="U35" s="162" t="s">
+      <c r="R35" s="164"/>
+      <c r="S35" s="164"/>
+      <c r="T35" s="164"/>
+      <c r="U35" s="164" t="s">
         <v>30</v>
       </c>
-      <c r="V35" s="162"/>
-      <c r="W35" s="162"/>
-      <c r="X35" s="162"/>
-      <c r="Y35" s="162" t="s">
+      <c r="V35" s="164"/>
+      <c r="W35" s="164"/>
+      <c r="X35" s="164"/>
+      <c r="Y35" s="164" t="s">
         <v>31</v>
       </c>
-      <c r="Z35" s="162"/>
-      <c r="AA35" s="162"/>
-      <c r="AB35" s="162"/>
-      <c r="AC35" s="162" t="s">
+      <c r="Z35" s="164"/>
+      <c r="AA35" s="164"/>
+      <c r="AB35" s="164"/>
+      <c r="AC35" s="164" t="s">
         <v>32</v>
       </c>
-      <c r="AD35" s="162"/>
-      <c r="AE35" s="162"/>
-      <c r="AF35" s="162"/>
-      <c r="AG35" s="162"/>
-      <c r="AH35" s="162"/>
-      <c r="AI35" s="162"/>
-      <c r="AJ35" s="162"/>
-      <c r="AK35" s="162"/>
-      <c r="AL35" s="162"/>
+      <c r="AD35" s="164"/>
+      <c r="AE35" s="164"/>
+      <c r="AF35" s="164"/>
+      <c r="AG35" s="164"/>
+      <c r="AH35" s="164"/>
+      <c r="AI35" s="164"/>
+      <c r="AJ35" s="164"/>
+      <c r="AK35" s="164"/>
+      <c r="AL35" s="164"/>
     </row>
     <row r="36" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A36" s="122"/>
-      <c r="B36" s="122"/>
-      <c r="C36" s="122"/>
-      <c r="D36" s="122"/>
-      <c r="E36" s="122"/>
-      <c r="F36" s="177" t="s">
+      <c r="A36" s="124"/>
+      <c r="B36" s="124"/>
+      <c r="C36" s="124"/>
+      <c r="D36" s="124"/>
+      <c r="E36" s="124"/>
+      <c r="F36" s="179" t="s">
         <v>90</v>
       </c>
-      <c r="G36" s="120"/>
-      <c r="H36" s="120"/>
-      <c r="I36" s="120"/>
-      <c r="J36" s="120"/>
-      <c r="K36" s="120"/>
-      <c r="L36" s="120"/>
-      <c r="M36" s="122"/>
-      <c r="N36" s="122"/>
-      <c r="O36" s="122"/>
-      <c r="P36" s="122"/>
-      <c r="Q36" s="122"/>
-      <c r="R36" s="122"/>
-      <c r="S36" s="122"/>
-      <c r="T36" s="122"/>
-      <c r="U36" s="122"/>
-      <c r="V36" s="122"/>
-      <c r="W36" s="122"/>
-      <c r="X36" s="122"/>
-      <c r="Y36" s="122"/>
-      <c r="Z36" s="122"/>
-      <c r="AA36" s="122"/>
-      <c r="AB36" s="122"/>
-      <c r="AC36" s="122"/>
-      <c r="AD36" s="122"/>
-      <c r="AE36" s="122"/>
-      <c r="AF36" s="122"/>
-      <c r="AG36" s="122"/>
-      <c r="AH36" s="122"/>
-      <c r="AI36" s="122"/>
-      <c r="AJ36" s="122"/>
-      <c r="AK36" s="122"/>
-      <c r="AL36" s="122"/>
+      <c r="G36" s="122"/>
+      <c r="H36" s="122"/>
+      <c r="I36" s="122"/>
+      <c r="J36" s="122"/>
+      <c r="K36" s="122"/>
+      <c r="L36" s="122"/>
+      <c r="M36" s="124"/>
+      <c r="N36" s="124"/>
+      <c r="O36" s="124"/>
+      <c r="P36" s="124"/>
+      <c r="Q36" s="124"/>
+      <c r="R36" s="124"/>
+      <c r="S36" s="124"/>
+      <c r="T36" s="124"/>
+      <c r="U36" s="124"/>
+      <c r="V36" s="124"/>
+      <c r="W36" s="124"/>
+      <c r="X36" s="124"/>
+      <c r="Y36" s="124"/>
+      <c r="Z36" s="124"/>
+      <c r="AA36" s="124"/>
+      <c r="AB36" s="124"/>
+      <c r="AC36" s="124"/>
+      <c r="AD36" s="124"/>
+      <c r="AE36" s="124"/>
+      <c r="AF36" s="124"/>
+      <c r="AG36" s="124"/>
+      <c r="AH36" s="124"/>
+      <c r="AI36" s="124"/>
+      <c r="AJ36" s="124"/>
+      <c r="AK36" s="124"/>
+      <c r="AL36" s="124"/>
     </row>
     <row r="37" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A37" s="122"/>
-      <c r="B37" s="122"/>
-      <c r="C37" s="122"/>
-      <c r="D37" s="122"/>
-      <c r="E37" s="122"/>
-      <c r="F37" s="177" t="s">
+      <c r="A37" s="124"/>
+      <c r="B37" s="124"/>
+      <c r="C37" s="124"/>
+      <c r="D37" s="124"/>
+      <c r="E37" s="124"/>
+      <c r="F37" s="179" t="s">
         <v>91</v>
       </c>
-      <c r="G37" s="120"/>
-      <c r="H37" s="120"/>
-      <c r="I37" s="120"/>
-      <c r="J37" s="120"/>
-      <c r="K37" s="120"/>
-      <c r="L37" s="120"/>
-      <c r="M37" s="122"/>
-      <c r="N37" s="122"/>
-      <c r="O37" s="122"/>
-      <c r="P37" s="122"/>
-      <c r="Q37" s="122"/>
-      <c r="R37" s="122"/>
-      <c r="S37" s="122"/>
-      <c r="T37" s="122"/>
-      <c r="U37" s="122"/>
-      <c r="V37" s="122"/>
-      <c r="W37" s="122"/>
-      <c r="X37" s="122"/>
-      <c r="Y37" s="122"/>
-      <c r="Z37" s="122"/>
-      <c r="AA37" s="122"/>
-      <c r="AB37" s="122"/>
-      <c r="AC37" s="122"/>
-      <c r="AD37" s="122"/>
-      <c r="AE37" s="122"/>
-      <c r="AF37" s="122"/>
-      <c r="AG37" s="122"/>
-      <c r="AH37" s="122"/>
-      <c r="AI37" s="122"/>
-      <c r="AJ37" s="122"/>
-      <c r="AK37" s="122"/>
-      <c r="AL37" s="122"/>
+      <c r="G37" s="122"/>
+      <c r="H37" s="122"/>
+      <c r="I37" s="122"/>
+      <c r="J37" s="122"/>
+      <c r="K37" s="122"/>
+      <c r="L37" s="122"/>
+      <c r="M37" s="124"/>
+      <c r="N37" s="124"/>
+      <c r="O37" s="124"/>
+      <c r="P37" s="124"/>
+      <c r="Q37" s="124"/>
+      <c r="R37" s="124"/>
+      <c r="S37" s="124"/>
+      <c r="T37" s="124"/>
+      <c r="U37" s="124"/>
+      <c r="V37" s="124"/>
+      <c r="W37" s="124"/>
+      <c r="X37" s="124"/>
+      <c r="Y37" s="124"/>
+      <c r="Z37" s="124"/>
+      <c r="AA37" s="124"/>
+      <c r="AB37" s="124"/>
+      <c r="AC37" s="124"/>
+      <c r="AD37" s="124"/>
+      <c r="AE37" s="124"/>
+      <c r="AF37" s="124"/>
+      <c r="AG37" s="124"/>
+      <c r="AH37" s="124"/>
+      <c r="AI37" s="124"/>
+      <c r="AJ37" s="124"/>
+      <c r="AK37" s="124"/>
+      <c r="AL37" s="124"/>
     </row>
     <row r="38" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A38" s="122"/>
-      <c r="B38" s="122"/>
-      <c r="C38" s="122"/>
-      <c r="D38" s="122"/>
-      <c r="E38" s="122"/>
-      <c r="F38" s="177" t="s">
+      <c r="A38" s="124"/>
+      <c r="B38" s="124"/>
+      <c r="C38" s="124"/>
+      <c r="D38" s="124"/>
+      <c r="E38" s="124"/>
+      <c r="F38" s="179" t="s">
         <v>90</v>
       </c>
-      <c r="G38" s="120"/>
-      <c r="H38" s="120"/>
-      <c r="I38" s="120"/>
-      <c r="J38" s="120"/>
-      <c r="K38" s="120"/>
-      <c r="L38" s="120"/>
-      <c r="M38" s="122"/>
-      <c r="N38" s="122"/>
-      <c r="O38" s="122"/>
-      <c r="P38" s="122"/>
-      <c r="Q38" s="122"/>
-      <c r="R38" s="122"/>
-      <c r="S38" s="122"/>
-      <c r="T38" s="122"/>
-      <c r="U38" s="122"/>
-      <c r="V38" s="122"/>
-      <c r="W38" s="122"/>
-      <c r="X38" s="122"/>
-      <c r="Y38" s="122"/>
-      <c r="Z38" s="122"/>
-      <c r="AA38" s="122"/>
-      <c r="AB38" s="122"/>
-      <c r="AC38" s="122"/>
-      <c r="AD38" s="122"/>
-      <c r="AE38" s="122"/>
-      <c r="AF38" s="122"/>
-      <c r="AG38" s="122"/>
-      <c r="AH38" s="122"/>
-      <c r="AI38" s="122"/>
-      <c r="AJ38" s="122"/>
-      <c r="AK38" s="122"/>
-      <c r="AL38" s="122"/>
+      <c r="G38" s="122"/>
+      <c r="H38" s="122"/>
+      <c r="I38" s="122"/>
+      <c r="J38" s="122"/>
+      <c r="K38" s="122"/>
+      <c r="L38" s="122"/>
+      <c r="M38" s="124"/>
+      <c r="N38" s="124"/>
+      <c r="O38" s="124"/>
+      <c r="P38" s="124"/>
+      <c r="Q38" s="124"/>
+      <c r="R38" s="124"/>
+      <c r="S38" s="124"/>
+      <c r="T38" s="124"/>
+      <c r="U38" s="124"/>
+      <c r="V38" s="124"/>
+      <c r="W38" s="124"/>
+      <c r="X38" s="124"/>
+      <c r="Y38" s="124"/>
+      <c r="Z38" s="124"/>
+      <c r="AA38" s="124"/>
+      <c r="AB38" s="124"/>
+      <c r="AC38" s="124"/>
+      <c r="AD38" s="124"/>
+      <c r="AE38" s="124"/>
+      <c r="AF38" s="124"/>
+      <c r="AG38" s="124"/>
+      <c r="AH38" s="124"/>
+      <c r="AI38" s="124"/>
+      <c r="AJ38" s="124"/>
+      <c r="AK38" s="124"/>
+      <c r="AL38" s="124"/>
     </row>
     <row r="39" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A39" s="122"/>
-      <c r="B39" s="122"/>
-      <c r="C39" s="122"/>
-      <c r="D39" s="122"/>
-      <c r="E39" s="122"/>
-      <c r="F39" s="177" t="s">
+      <c r="A39" s="124"/>
+      <c r="B39" s="124"/>
+      <c r="C39" s="124"/>
+      <c r="D39" s="124"/>
+      <c r="E39" s="124"/>
+      <c r="F39" s="179" t="s">
         <v>91</v>
       </c>
-      <c r="G39" s="120"/>
-      <c r="H39" s="120"/>
-      <c r="I39" s="120"/>
-      <c r="J39" s="120"/>
-      <c r="K39" s="120"/>
-      <c r="L39" s="120"/>
-      <c r="M39" s="122"/>
-      <c r="N39" s="122"/>
-      <c r="O39" s="122"/>
-      <c r="P39" s="122"/>
-      <c r="Q39" s="122"/>
-      <c r="R39" s="122"/>
-      <c r="S39" s="122"/>
-      <c r="T39" s="122"/>
-      <c r="U39" s="122"/>
-      <c r="V39" s="122"/>
-      <c r="W39" s="122"/>
-      <c r="X39" s="122"/>
-      <c r="Y39" s="122"/>
-      <c r="Z39" s="122"/>
-      <c r="AA39" s="122"/>
-      <c r="AB39" s="122"/>
-      <c r="AC39" s="122"/>
-      <c r="AD39" s="122"/>
-      <c r="AE39" s="122"/>
-      <c r="AF39" s="122"/>
-      <c r="AG39" s="122"/>
-      <c r="AH39" s="122"/>
-      <c r="AI39" s="122"/>
-      <c r="AJ39" s="122"/>
-      <c r="AK39" s="122"/>
-      <c r="AL39" s="122"/>
+      <c r="G39" s="122"/>
+      <c r="H39" s="122"/>
+      <c r="I39" s="122"/>
+      <c r="J39" s="122"/>
+      <c r="K39" s="122"/>
+      <c r="L39" s="122"/>
+      <c r="M39" s="124"/>
+      <c r="N39" s="124"/>
+      <c r="O39" s="124"/>
+      <c r="P39" s="124"/>
+      <c r="Q39" s="124"/>
+      <c r="R39" s="124"/>
+      <c r="S39" s="124"/>
+      <c r="T39" s="124"/>
+      <c r="U39" s="124"/>
+      <c r="V39" s="124"/>
+      <c r="W39" s="124"/>
+      <c r="X39" s="124"/>
+      <c r="Y39" s="124"/>
+      <c r="Z39" s="124"/>
+      <c r="AA39" s="124"/>
+      <c r="AB39" s="124"/>
+      <c r="AC39" s="124"/>
+      <c r="AD39" s="124"/>
+      <c r="AE39" s="124"/>
+      <c r="AF39" s="124"/>
+      <c r="AG39" s="124"/>
+      <c r="AH39" s="124"/>
+      <c r="AI39" s="124"/>
+      <c r="AJ39" s="124"/>
+      <c r="AK39" s="124"/>
+      <c r="AL39" s="124"/>
     </row>
     <row r="40" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A40" s="122"/>
-      <c r="B40" s="122"/>
-      <c r="C40" s="122"/>
-      <c r="D40" s="122"/>
-      <c r="E40" s="122"/>
-      <c r="F40" s="177" t="s">
+      <c r="A40" s="124"/>
+      <c r="B40" s="124"/>
+      <c r="C40" s="124"/>
+      <c r="D40" s="124"/>
+      <c r="E40" s="124"/>
+      <c r="F40" s="179" t="s">
         <v>90</v>
       </c>
-      <c r="G40" s="120"/>
-      <c r="H40" s="120"/>
-      <c r="I40" s="120"/>
-      <c r="J40" s="120"/>
-      <c r="K40" s="120"/>
-      <c r="L40" s="120"/>
-      <c r="M40" s="122"/>
-      <c r="N40" s="122"/>
-      <c r="O40" s="122"/>
-      <c r="P40" s="122"/>
-      <c r="Q40" s="122"/>
-      <c r="R40" s="122"/>
-      <c r="S40" s="122"/>
-      <c r="T40" s="122"/>
-      <c r="U40" s="122"/>
-      <c r="V40" s="122"/>
-      <c r="W40" s="122"/>
-      <c r="X40" s="122"/>
-      <c r="Y40" s="122"/>
-      <c r="Z40" s="122"/>
-      <c r="AA40" s="122"/>
-      <c r="AB40" s="122"/>
-      <c r="AC40" s="122"/>
-      <c r="AD40" s="122"/>
-      <c r="AE40" s="122"/>
-      <c r="AF40" s="122"/>
-      <c r="AG40" s="122"/>
-      <c r="AH40" s="122"/>
-      <c r="AI40" s="122"/>
-      <c r="AJ40" s="122"/>
-      <c r="AK40" s="122"/>
-      <c r="AL40" s="122"/>
+      <c r="G40" s="122"/>
+      <c r="H40" s="122"/>
+      <c r="I40" s="122"/>
+      <c r="J40" s="122"/>
+      <c r="K40" s="122"/>
+      <c r="L40" s="122"/>
+      <c r="M40" s="124"/>
+      <c r="N40" s="124"/>
+      <c r="O40" s="124"/>
+      <c r="P40" s="124"/>
+      <c r="Q40" s="124"/>
+      <c r="R40" s="124"/>
+      <c r="S40" s="124"/>
+      <c r="T40" s="124"/>
+      <c r="U40" s="124"/>
+      <c r="V40" s="124"/>
+      <c r="W40" s="124"/>
+      <c r="X40" s="124"/>
+      <c r="Y40" s="124"/>
+      <c r="Z40" s="124"/>
+      <c r="AA40" s="124"/>
+      <c r="AB40" s="124"/>
+      <c r="AC40" s="124"/>
+      <c r="AD40" s="124"/>
+      <c r="AE40" s="124"/>
+      <c r="AF40" s="124"/>
+      <c r="AG40" s="124"/>
+      <c r="AH40" s="124"/>
+      <c r="AI40" s="124"/>
+      <c r="AJ40" s="124"/>
+      <c r="AK40" s="124"/>
+      <c r="AL40" s="124"/>
     </row>
     <row r="41" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A41" s="122"/>
-      <c r="B41" s="122"/>
-      <c r="C41" s="122"/>
-      <c r="D41" s="122"/>
-      <c r="E41" s="122"/>
-      <c r="F41" s="177" t="s">
+      <c r="A41" s="124"/>
+      <c r="B41" s="124"/>
+      <c r="C41" s="124"/>
+      <c r="D41" s="124"/>
+      <c r="E41" s="124"/>
+      <c r="F41" s="179" t="s">
         <v>91</v>
       </c>
-      <c r="G41" s="120"/>
-      <c r="H41" s="120"/>
-      <c r="I41" s="120"/>
-      <c r="J41" s="120"/>
-      <c r="K41" s="120"/>
-      <c r="L41" s="120"/>
-      <c r="M41" s="122"/>
-      <c r="N41" s="122"/>
-      <c r="O41" s="122"/>
-      <c r="P41" s="122"/>
-      <c r="Q41" s="122"/>
-      <c r="R41" s="122"/>
-      <c r="S41" s="122"/>
-      <c r="T41" s="122"/>
-      <c r="U41" s="122"/>
-      <c r="V41" s="122"/>
-      <c r="W41" s="122"/>
-      <c r="X41" s="122"/>
-      <c r="Y41" s="122"/>
-      <c r="Z41" s="122"/>
-      <c r="AA41" s="122"/>
-      <c r="AB41" s="122"/>
-      <c r="AC41" s="122"/>
-      <c r="AD41" s="122"/>
-      <c r="AE41" s="122"/>
-      <c r="AF41" s="122"/>
-      <c r="AG41" s="122"/>
-      <c r="AH41" s="122"/>
-      <c r="AI41" s="122"/>
-      <c r="AJ41" s="122"/>
-      <c r="AK41" s="122"/>
-      <c r="AL41" s="122"/>
+      <c r="G41" s="122"/>
+      <c r="H41" s="122"/>
+      <c r="I41" s="122"/>
+      <c r="J41" s="122"/>
+      <c r="K41" s="122"/>
+      <c r="L41" s="122"/>
+      <c r="M41" s="124"/>
+      <c r="N41" s="124"/>
+      <c r="O41" s="124"/>
+      <c r="P41" s="124"/>
+      <c r="Q41" s="124"/>
+      <c r="R41" s="124"/>
+      <c r="S41" s="124"/>
+      <c r="T41" s="124"/>
+      <c r="U41" s="124"/>
+      <c r="V41" s="124"/>
+      <c r="W41" s="124"/>
+      <c r="X41" s="124"/>
+      <c r="Y41" s="124"/>
+      <c r="Z41" s="124"/>
+      <c r="AA41" s="124"/>
+      <c r="AB41" s="124"/>
+      <c r="AC41" s="124"/>
+      <c r="AD41" s="124"/>
+      <c r="AE41" s="124"/>
+      <c r="AF41" s="124"/>
+      <c r="AG41" s="124"/>
+      <c r="AH41" s="124"/>
+      <c r="AI41" s="124"/>
+      <c r="AJ41" s="124"/>
+      <c r="AK41" s="124"/>
+      <c r="AL41" s="124"/>
     </row>
     <row r="42" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A42" s="50" t="s">
@@ -13873,32 +13880,32 @@
       <c r="J1" s="85"/>
       <c r="K1" s="85"/>
       <c r="L1" s="85"/>
-      <c r="M1" s="189"/>
-      <c r="N1" s="189"/>
-      <c r="O1" s="189"/>
-      <c r="P1" s="189"/>
-      <c r="Q1" s="189"/>
-      <c r="R1" s="189"/>
-      <c r="S1" s="189"/>
-      <c r="T1" s="189"/>
-      <c r="U1" s="189"/>
-      <c r="V1" s="189"/>
-      <c r="W1" s="189"/>
-      <c r="X1" s="189"/>
-      <c r="Y1" s="189"/>
-      <c r="Z1" s="189"/>
-      <c r="AA1" s="189"/>
-      <c r="AB1" s="189"/>
-      <c r="AC1" s="189"/>
-      <c r="AD1" s="189"/>
-      <c r="AE1" s="189"/>
-      <c r="AF1" s="189"/>
-      <c r="AG1" s="189"/>
-      <c r="AH1" s="189"/>
-      <c r="AI1" s="189"/>
-      <c r="AJ1" s="189"/>
-      <c r="AK1" s="189"/>
-      <c r="AL1" s="189"/>
+      <c r="M1" s="193"/>
+      <c r="N1" s="193"/>
+      <c r="O1" s="193"/>
+      <c r="P1" s="193"/>
+      <c r="Q1" s="193"/>
+      <c r="R1" s="193"/>
+      <c r="S1" s="193"/>
+      <c r="T1" s="193"/>
+      <c r="U1" s="193"/>
+      <c r="V1" s="193"/>
+      <c r="W1" s="193"/>
+      <c r="X1" s="193"/>
+      <c r="Y1" s="193"/>
+      <c r="Z1" s="193"/>
+      <c r="AA1" s="193"/>
+      <c r="AB1" s="193"/>
+      <c r="AC1" s="193"/>
+      <c r="AD1" s="193"/>
+      <c r="AE1" s="193"/>
+      <c r="AF1" s="193"/>
+      <c r="AG1" s="193"/>
+      <c r="AH1" s="193"/>
+      <c r="AI1" s="193"/>
+      <c r="AJ1" s="193"/>
+      <c r="AK1" s="193"/>
+      <c r="AL1" s="193"/>
     </row>
     <row r="2" spans="1:38" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="86" t="s">
@@ -13943,46 +13950,46 @@
       <c r="AL2" s="89"/>
     </row>
     <row r="3" spans="1:38" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="179" t="s">
+      <c r="A3" s="190" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="179"/>
-      <c r="C3" s="180"/>
+      <c r="B3" s="190"/>
+      <c r="C3" s="191"/>
       <c r="D3" s="181"/>
       <c r="E3" s="181"/>
       <c r="F3" s="181"/>
       <c r="G3" s="181"/>
       <c r="H3" s="181"/>
       <c r="I3" s="182"/>
-      <c r="J3" s="188"/>
-      <c r="K3" s="188"/>
-      <c r="L3" s="188"/>
-      <c r="M3" s="188"/>
-      <c r="N3" s="188"/>
-      <c r="O3" s="188"/>
-      <c r="P3" s="188"/>
-      <c r="Q3" s="188"/>
-      <c r="R3" s="188"/>
-      <c r="S3" s="188"/>
-      <c r="T3" s="188"/>
-      <c r="U3" s="188"/>
-      <c r="V3" s="188"/>
-      <c r="W3" s="188"/>
-      <c r="X3" s="188"/>
-      <c r="Y3" s="188"/>
-      <c r="Z3" s="188"/>
-      <c r="AA3" s="188"/>
-      <c r="AB3" s="188"/>
-      <c r="AC3" s="188"/>
-      <c r="AD3" s="188"/>
-      <c r="AE3" s="188"/>
-      <c r="AF3" s="188"/>
-      <c r="AG3" s="188"/>
-      <c r="AH3" s="188"/>
-      <c r="AI3" s="188"/>
-      <c r="AJ3" s="188"/>
-      <c r="AK3" s="188"/>
-      <c r="AL3" s="188"/>
+      <c r="J3" s="192"/>
+      <c r="K3" s="192"/>
+      <c r="L3" s="192"/>
+      <c r="M3" s="192"/>
+      <c r="N3" s="192"/>
+      <c r="O3" s="192"/>
+      <c r="P3" s="192"/>
+      <c r="Q3" s="192"/>
+      <c r="R3" s="192"/>
+      <c r="S3" s="192"/>
+      <c r="T3" s="192"/>
+      <c r="U3" s="192"/>
+      <c r="V3" s="192"/>
+      <c r="W3" s="192"/>
+      <c r="X3" s="192"/>
+      <c r="Y3" s="192"/>
+      <c r="Z3" s="192"/>
+      <c r="AA3" s="192"/>
+      <c r="AB3" s="192"/>
+      <c r="AC3" s="192"/>
+      <c r="AD3" s="192"/>
+      <c r="AE3" s="192"/>
+      <c r="AF3" s="192"/>
+      <c r="AG3" s="192"/>
+      <c r="AH3" s="192"/>
+      <c r="AI3" s="192"/>
+      <c r="AJ3" s="192"/>
+      <c r="AK3" s="192"/>
+      <c r="AL3" s="192"/>
     </row>
     <row r="4" spans="1:38" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="183" t="s">
@@ -13996,15 +14003,15 @@
       <c r="G4" s="184"/>
       <c r="H4" s="184"/>
       <c r="I4" s="185"/>
-      <c r="J4" s="190" t="s">
+      <c r="J4" s="188" t="s">
         <v>214</v>
       </c>
-      <c r="K4" s="191"/>
-      <c r="L4" s="191"/>
-      <c r="M4" s="191"/>
-      <c r="N4" s="191"/>
-      <c r="O4" s="191"/>
-      <c r="P4" s="191"/>
+      <c r="K4" s="189"/>
+      <c r="L4" s="189"/>
+      <c r="M4" s="189"/>
+      <c r="N4" s="189"/>
+      <c r="O4" s="189"/>
+      <c r="P4" s="189"/>
       <c r="Q4" s="91"/>
       <c r="R4" s="184" t="s">
         <v>215</v>
@@ -14015,15 +14022,15 @@
       <c r="V4" s="184"/>
       <c r="W4" s="184"/>
       <c r="X4" s="185"/>
-      <c r="Y4" s="190" t="s">
+      <c r="Y4" s="188" t="s">
         <v>216</v>
       </c>
-      <c r="Z4" s="191"/>
-      <c r="AA4" s="191"/>
-      <c r="AB4" s="191"/>
-      <c r="AC4" s="191"/>
-      <c r="AD4" s="191"/>
-      <c r="AE4" s="191"/>
+      <c r="Z4" s="189"/>
+      <c r="AA4" s="189"/>
+      <c r="AB4" s="189"/>
+      <c r="AC4" s="189"/>
+      <c r="AD4" s="189"/>
+      <c r="AE4" s="189"/>
       <c r="AF4" s="91"/>
       <c r="AG4" s="184" t="s">
         <v>215</v>
@@ -14557,46 +14564,46 @@
       <c r="AL17" s="89"/>
     </row>
     <row r="18" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A18" s="179" t="s">
+      <c r="A18" s="190" t="s">
         <v>8</v>
       </c>
-      <c r="B18" s="179"/>
-      <c r="C18" s="180"/>
+      <c r="B18" s="190"/>
+      <c r="C18" s="191"/>
       <c r="D18" s="181"/>
       <c r="E18" s="181"/>
       <c r="F18" s="181"/>
       <c r="G18" s="181"/>
       <c r="H18" s="181"/>
       <c r="I18" s="182"/>
-      <c r="J18" s="188"/>
-      <c r="K18" s="188"/>
-      <c r="L18" s="188"/>
-      <c r="M18" s="188"/>
-      <c r="N18" s="188"/>
-      <c r="O18" s="188"/>
-      <c r="P18" s="188"/>
-      <c r="Q18" s="188"/>
-      <c r="R18" s="188"/>
-      <c r="S18" s="188"/>
-      <c r="T18" s="188"/>
-      <c r="U18" s="188"/>
-      <c r="V18" s="188"/>
-      <c r="W18" s="188"/>
-      <c r="X18" s="188"/>
-      <c r="Y18" s="188"/>
-      <c r="Z18" s="188"/>
-      <c r="AA18" s="188"/>
-      <c r="AB18" s="188"/>
-      <c r="AC18" s="188"/>
-      <c r="AD18" s="188"/>
-      <c r="AE18" s="188"/>
-      <c r="AF18" s="188"/>
-      <c r="AG18" s="188"/>
-      <c r="AH18" s="188"/>
-      <c r="AI18" s="188"/>
-      <c r="AJ18" s="188"/>
-      <c r="AK18" s="188"/>
-      <c r="AL18" s="188"/>
+      <c r="J18" s="192"/>
+      <c r="K18" s="192"/>
+      <c r="L18" s="192"/>
+      <c r="M18" s="192"/>
+      <c r="N18" s="192"/>
+      <c r="O18" s="192"/>
+      <c r="P18" s="192"/>
+      <c r="Q18" s="192"/>
+      <c r="R18" s="192"/>
+      <c r="S18" s="192"/>
+      <c r="T18" s="192"/>
+      <c r="U18" s="192"/>
+      <c r="V18" s="192"/>
+      <c r="W18" s="192"/>
+      <c r="X18" s="192"/>
+      <c r="Y18" s="192"/>
+      <c r="Z18" s="192"/>
+      <c r="AA18" s="192"/>
+      <c r="AB18" s="192"/>
+      <c r="AC18" s="192"/>
+      <c r="AD18" s="192"/>
+      <c r="AE18" s="192"/>
+      <c r="AF18" s="192"/>
+      <c r="AG18" s="192"/>
+      <c r="AH18" s="192"/>
+      <c r="AI18" s="192"/>
+      <c r="AJ18" s="192"/>
+      <c r="AK18" s="192"/>
+      <c r="AL18" s="192"/>
     </row>
     <row r="19" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A19" s="183" t="s">
@@ -14610,15 +14617,15 @@
       <c r="G19" s="184"/>
       <c r="H19" s="184"/>
       <c r="I19" s="185"/>
-      <c r="J19" s="190" t="s">
+      <c r="J19" s="188" t="s">
         <v>214</v>
       </c>
-      <c r="K19" s="191"/>
-      <c r="L19" s="191"/>
-      <c r="M19" s="191"/>
-      <c r="N19" s="191"/>
-      <c r="O19" s="191"/>
-      <c r="P19" s="191"/>
+      <c r="K19" s="189"/>
+      <c r="L19" s="189"/>
+      <c r="M19" s="189"/>
+      <c r="N19" s="189"/>
+      <c r="O19" s="189"/>
+      <c r="P19" s="189"/>
       <c r="Q19" s="91"/>
       <c r="R19" s="184" t="s">
         <v>215</v>
@@ -14629,15 +14636,15 @@
       <c r="V19" s="184"/>
       <c r="W19" s="184"/>
       <c r="X19" s="185"/>
-      <c r="Y19" s="190" t="s">
+      <c r="Y19" s="188" t="s">
         <v>216</v>
       </c>
-      <c r="Z19" s="191"/>
-      <c r="AA19" s="191"/>
-      <c r="AB19" s="191"/>
-      <c r="AC19" s="191"/>
-      <c r="AD19" s="191"/>
-      <c r="AE19" s="191"/>
+      <c r="Z19" s="189"/>
+      <c r="AA19" s="189"/>
+      <c r="AB19" s="189"/>
+      <c r="AC19" s="189"/>
+      <c r="AD19" s="189"/>
+      <c r="AE19" s="189"/>
       <c r="AF19" s="91"/>
       <c r="AG19" s="184" t="s">
         <v>215</v>
@@ -15471,6 +15478,9 @@
     <mergeCell ref="A30:I30"/>
     <mergeCell ref="J30:X30"/>
     <mergeCell ref="Y30:AL30"/>
+    <mergeCell ref="A29:I29"/>
+    <mergeCell ref="J29:X29"/>
+    <mergeCell ref="Y29:AL29"/>
     <mergeCell ref="A26:I26"/>
     <mergeCell ref="J26:X26"/>
     <mergeCell ref="Y26:AL26"/>
@@ -15491,6 +15501,7 @@
     <mergeCell ref="A23:I23"/>
     <mergeCell ref="J23:X23"/>
     <mergeCell ref="Y23:AL23"/>
+    <mergeCell ref="A25:I25"/>
     <mergeCell ref="Y4:AE4"/>
     <mergeCell ref="AG4:AL4"/>
     <mergeCell ref="A19:I19"/>
@@ -15505,9 +15516,6 @@
     <mergeCell ref="A12:I12"/>
     <mergeCell ref="J12:X12"/>
     <mergeCell ref="Y12:AL12"/>
-    <mergeCell ref="A29:I29"/>
-    <mergeCell ref="J29:X29"/>
-    <mergeCell ref="Y29:AL29"/>
     <mergeCell ref="A13:I13"/>
     <mergeCell ref="J13:X13"/>
     <mergeCell ref="Y13:AL13"/>
@@ -15516,7 +15524,7 @@
     <mergeCell ref="Y15:AL15"/>
     <mergeCell ref="J16:X16"/>
     <mergeCell ref="Y16:AL16"/>
-    <mergeCell ref="A25:I25"/>
+    <mergeCell ref="Y14:AL14"/>
     <mergeCell ref="Y5:AL5"/>
     <mergeCell ref="A6:I6"/>
     <mergeCell ref="J6:X6"/>
@@ -15524,7 +15532,6 @@
     <mergeCell ref="A7:I7"/>
     <mergeCell ref="J7:X7"/>
     <mergeCell ref="Y7:AL7"/>
-    <mergeCell ref="Y14:AL14"/>
     <mergeCell ref="A18:C18"/>
     <mergeCell ref="D18:I18"/>
     <mergeCell ref="J18:AL18"/>
@@ -15569,7 +15576,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D1F3C76-7811-48C0-97A4-A377101F88AD}">
-  <dimension ref="A1:AL28"/>
+  <dimension ref="A1:AL31"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="7" width="2.33203125" customWidth="1"/>
@@ -15593,32 +15600,32 @@
       <c r="J1" s="85"/>
       <c r="K1" s="85"/>
       <c r="L1" s="85"/>
-      <c r="M1" s="189"/>
-      <c r="N1" s="189"/>
-      <c r="O1" s="189"/>
-      <c r="P1" s="189"/>
-      <c r="Q1" s="189"/>
-      <c r="R1" s="189"/>
-      <c r="S1" s="189"/>
-      <c r="T1" s="189"/>
-      <c r="U1" s="189"/>
-      <c r="V1" s="189"/>
-      <c r="W1" s="189"/>
-      <c r="X1" s="189"/>
-      <c r="Y1" s="189"/>
-      <c r="Z1" s="189"/>
-      <c r="AA1" s="189"/>
-      <c r="AB1" s="189"/>
-      <c r="AC1" s="189"/>
-      <c r="AD1" s="189"/>
-      <c r="AE1" s="189"/>
-      <c r="AF1" s="189"/>
-      <c r="AG1" s="189"/>
-      <c r="AH1" s="189"/>
-      <c r="AI1" s="189"/>
-      <c r="AJ1" s="189"/>
-      <c r="AK1" s="189"/>
-      <c r="AL1" s="189"/>
+      <c r="M1" s="193"/>
+      <c r="N1" s="193"/>
+      <c r="O1" s="193"/>
+      <c r="P1" s="193"/>
+      <c r="Q1" s="193"/>
+      <c r="R1" s="193"/>
+      <c r="S1" s="193"/>
+      <c r="T1" s="193"/>
+      <c r="U1" s="193"/>
+      <c r="V1" s="193"/>
+      <c r="W1" s="193"/>
+      <c r="X1" s="193"/>
+      <c r="Y1" s="193"/>
+      <c r="Z1" s="193"/>
+      <c r="AA1" s="193"/>
+      <c r="AB1" s="193"/>
+      <c r="AC1" s="193"/>
+      <c r="AD1" s="193"/>
+      <c r="AE1" s="193"/>
+      <c r="AF1" s="193"/>
+      <c r="AG1" s="193"/>
+      <c r="AH1" s="193"/>
+      <c r="AI1" s="193"/>
+      <c r="AJ1" s="193"/>
+      <c r="AK1" s="193"/>
+      <c r="AL1" s="193"/>
     </row>
     <row r="2" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="86" t="s">
@@ -15663,216 +15670,221 @@
       <c r="AL2" s="89"/>
     </row>
     <row r="3" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="179" t="s">
+      <c r="A3" s="83" t="s">
+        <v>82</v>
+      </c>
+      <c r="B3" s="87"/>
+      <c r="C3" s="87"/>
+      <c r="D3" s="87"/>
+      <c r="E3" s="65" t="s">
+        <v>83</v>
+      </c>
+      <c r="F3" s="87"/>
+      <c r="G3" s="87"/>
+      <c r="H3" s="88"/>
+      <c r="I3" s="88"/>
+      <c r="J3" s="88"/>
+      <c r="K3" s="88"/>
+      <c r="L3" s="97"/>
+      <c r="M3" s="89"/>
+      <c r="N3" s="89"/>
+      <c r="O3" s="89"/>
+      <c r="P3" s="89"/>
+      <c r="Q3" s="89"/>
+      <c r="R3" s="89"/>
+      <c r="S3" s="89"/>
+      <c r="T3" s="89"/>
+      <c r="U3" s="90"/>
+      <c r="V3" s="89"/>
+      <c r="W3" s="89"/>
+      <c r="X3" s="89"/>
+      <c r="Y3" s="89"/>
+      <c r="Z3" s="89"/>
+      <c r="AA3" s="89"/>
+      <c r="AB3" s="89"/>
+      <c r="AC3" s="89"/>
+      <c r="AD3" s="89"/>
+      <c r="AE3" s="89"/>
+      <c r="AF3" s="89"/>
+      <c r="AG3" s="89"/>
+      <c r="AH3" s="89"/>
+      <c r="AI3" s="89"/>
+      <c r="AJ3" s="89"/>
+      <c r="AK3" s="89"/>
+    </row>
+    <row r="4" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="83" t="s">
+        <v>84</v>
+      </c>
+      <c r="B4" s="87"/>
+      <c r="C4" s="87"/>
+      <c r="D4" s="87"/>
+      <c r="E4" s="87"/>
+      <c r="F4" s="87"/>
+      <c r="G4" s="87"/>
+      <c r="H4" s="87"/>
+      <c r="I4" s="88"/>
+      <c r="J4" s="88"/>
+      <c r="K4" s="88"/>
+      <c r="L4" s="88"/>
+      <c r="M4" s="89"/>
+      <c r="N4" s="89"/>
+      <c r="O4" s="89"/>
+      <c r="P4" s="89"/>
+      <c r="Q4" s="89"/>
+      <c r="R4" s="89"/>
+      <c r="S4" s="89"/>
+      <c r="T4" s="89"/>
+      <c r="U4" s="89"/>
+      <c r="V4" s="90"/>
+      <c r="W4" s="89"/>
+      <c r="X4" s="89"/>
+      <c r="Y4" s="89"/>
+      <c r="Z4" s="89"/>
+      <c r="AA4" s="89"/>
+      <c r="AB4" s="89"/>
+      <c r="AC4" s="89"/>
+      <c r="AD4" s="89"/>
+      <c r="AE4" s="89"/>
+      <c r="AF4" s="89"/>
+      <c r="AG4" s="89"/>
+      <c r="AH4" s="89"/>
+      <c r="AI4" s="89"/>
+      <c r="AJ4" s="89"/>
+      <c r="AK4" s="89"/>
+      <c r="AL4" s="89"/>
+    </row>
+    <row r="5" spans="1:38" ht="8.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="98"/>
+      <c r="B5" s="87"/>
+      <c r="C5" s="87"/>
+      <c r="D5" s="87"/>
+      <c r="E5" s="87"/>
+      <c r="F5" s="87"/>
+      <c r="G5" s="87"/>
+      <c r="H5" s="87"/>
+      <c r="I5" s="88"/>
+      <c r="J5" s="88"/>
+      <c r="K5" s="88"/>
+      <c r="L5" s="88"/>
+      <c r="M5" s="89"/>
+      <c r="N5" s="89"/>
+      <c r="O5" s="89"/>
+      <c r="P5" s="89"/>
+      <c r="Q5" s="89"/>
+      <c r="R5" s="89"/>
+      <c r="S5" s="89"/>
+      <c r="T5" s="89"/>
+      <c r="U5" s="89"/>
+      <c r="V5" s="90"/>
+      <c r="W5" s="89"/>
+      <c r="X5" s="89"/>
+      <c r="Y5" s="89"/>
+      <c r="Z5" s="89"/>
+      <c r="AA5" s="89"/>
+      <c r="AB5" s="89"/>
+      <c r="AC5" s="89"/>
+      <c r="AD5" s="89"/>
+      <c r="AE5" s="89"/>
+      <c r="AF5" s="89"/>
+      <c r="AG5" s="89"/>
+      <c r="AH5" s="89"/>
+      <c r="AI5" s="89"/>
+      <c r="AJ5" s="89"/>
+      <c r="AK5" s="89"/>
+      <c r="AL5" s="89"/>
+    </row>
+    <row r="6" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="190" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="179"/>
-      <c r="C3" s="180"/>
-      <c r="D3" s="181"/>
-      <c r="E3" s="181"/>
-      <c r="F3" s="181"/>
-      <c r="G3" s="181"/>
-      <c r="H3" s="181"/>
-      <c r="I3" s="182"/>
-      <c r="J3" s="188"/>
-      <c r="K3" s="188"/>
-      <c r="L3" s="188"/>
-      <c r="M3" s="188"/>
-      <c r="N3" s="188"/>
-      <c r="O3" s="188"/>
-      <c r="P3" s="188"/>
-      <c r="Q3" s="188"/>
-      <c r="R3" s="188"/>
-      <c r="S3" s="188"/>
-      <c r="T3" s="188"/>
-      <c r="U3" s="188"/>
-      <c r="V3" s="188"/>
-      <c r="W3" s="188"/>
-      <c r="X3" s="188"/>
-      <c r="Y3" s="188"/>
-      <c r="Z3" s="188"/>
-      <c r="AA3" s="188"/>
-      <c r="AB3" s="188"/>
-      <c r="AC3" s="188"/>
-      <c r="AD3" s="188"/>
-      <c r="AE3" s="188"/>
-      <c r="AF3" s="188"/>
-      <c r="AG3" s="188"/>
-      <c r="AH3" s="188"/>
-      <c r="AI3" s="188"/>
-      <c r="AJ3" s="188"/>
-      <c r="AK3" s="188"/>
-      <c r="AL3" s="188"/>
-    </row>
-    <row r="4" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="183" t="s">
+      <c r="B6" s="190"/>
+      <c r="C6" s="191"/>
+      <c r="D6" s="181"/>
+      <c r="E6" s="181"/>
+      <c r="F6" s="181"/>
+      <c r="G6" s="181"/>
+      <c r="H6" s="181"/>
+      <c r="I6" s="182"/>
+      <c r="J6" s="192"/>
+      <c r="K6" s="192"/>
+      <c r="L6" s="192"/>
+      <c r="M6" s="192"/>
+      <c r="N6" s="192"/>
+      <c r="O6" s="192"/>
+      <c r="P6" s="192"/>
+      <c r="Q6" s="192"/>
+      <c r="R6" s="192"/>
+      <c r="S6" s="192"/>
+      <c r="T6" s="192"/>
+      <c r="U6" s="192"/>
+      <c r="V6" s="192"/>
+      <c r="W6" s="192"/>
+      <c r="X6" s="192"/>
+      <c r="Y6" s="192"/>
+      <c r="Z6" s="192"/>
+      <c r="AA6" s="192"/>
+      <c r="AB6" s="192"/>
+      <c r="AC6" s="192"/>
+      <c r="AD6" s="192"/>
+      <c r="AE6" s="192"/>
+      <c r="AF6" s="192"/>
+      <c r="AG6" s="192"/>
+      <c r="AH6" s="192"/>
+      <c r="AI6" s="192"/>
+      <c r="AJ6" s="192"/>
+      <c r="AK6" s="192"/>
+      <c r="AL6" s="192"/>
+    </row>
+    <row r="7" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="183" t="s">
         <v>213</v>
       </c>
-      <c r="B4" s="184"/>
-      <c r="C4" s="184"/>
-      <c r="D4" s="184"/>
-      <c r="E4" s="184"/>
-      <c r="F4" s="184"/>
-      <c r="G4" s="184"/>
-      <c r="H4" s="184"/>
-      <c r="I4" s="185"/>
-      <c r="J4" s="190" t="s">
+      <c r="B7" s="184"/>
+      <c r="C7" s="184"/>
+      <c r="D7" s="184"/>
+      <c r="E7" s="184"/>
+      <c r="F7" s="184"/>
+      <c r="G7" s="184"/>
+      <c r="H7" s="184"/>
+      <c r="I7" s="185"/>
+      <c r="J7" s="188" t="s">
         <v>214</v>
       </c>
-      <c r="K4" s="191"/>
-      <c r="L4" s="191"/>
-      <c r="M4" s="191"/>
-      <c r="N4" s="191"/>
-      <c r="O4" s="191"/>
-      <c r="P4" s="191"/>
-      <c r="Q4" s="91"/>
-      <c r="R4" s="184" t="s">
+      <c r="K7" s="189"/>
+      <c r="L7" s="189"/>
+      <c r="M7" s="189"/>
+      <c r="N7" s="189"/>
+      <c r="O7" s="189"/>
+      <c r="P7" s="189"/>
+      <c r="Q7" s="91"/>
+      <c r="R7" s="184" t="s">
         <v>215</v>
       </c>
-      <c r="S4" s="184"/>
-      <c r="T4" s="184"/>
-      <c r="U4" s="184"/>
-      <c r="V4" s="184"/>
-      <c r="W4" s="184"/>
-      <c r="X4" s="185"/>
-      <c r="Y4" s="190" t="s">
+      <c r="S7" s="184"/>
+      <c r="T7" s="184"/>
+      <c r="U7" s="184"/>
+      <c r="V7" s="184"/>
+      <c r="W7" s="184"/>
+      <c r="X7" s="185"/>
+      <c r="Y7" s="188" t="s">
         <v>216</v>
       </c>
-      <c r="Z4" s="191"/>
-      <c r="AA4" s="191"/>
-      <c r="AB4" s="191"/>
-      <c r="AC4" s="191"/>
-      <c r="AD4" s="191"/>
-      <c r="AE4" s="191"/>
-      <c r="AF4" s="91"/>
-      <c r="AG4" s="184" t="s">
+      <c r="Z7" s="189"/>
+      <c r="AA7" s="189"/>
+      <c r="AB7" s="189"/>
+      <c r="AC7" s="189"/>
+      <c r="AD7" s="189"/>
+      <c r="AE7" s="189"/>
+      <c r="AF7" s="91"/>
+      <c r="AG7" s="184" t="s">
         <v>215</v>
       </c>
-      <c r="AH4" s="184"/>
-      <c r="AI4" s="184"/>
-      <c r="AJ4" s="184"/>
-      <c r="AK4" s="184"/>
-      <c r="AL4" s="185"/>
-    </row>
-    <row r="5" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="186"/>
-      <c r="B5" s="186"/>
-      <c r="C5" s="186"/>
-      <c r="D5" s="186"/>
-      <c r="E5" s="186"/>
-      <c r="F5" s="186"/>
-      <c r="G5" s="186"/>
-      <c r="H5" s="186"/>
-      <c r="I5" s="186"/>
-      <c r="J5" s="187"/>
-      <c r="K5" s="187"/>
-      <c r="L5" s="187"/>
-      <c r="M5" s="187"/>
-      <c r="N5" s="187"/>
-      <c r="O5" s="187"/>
-      <c r="P5" s="187"/>
-      <c r="Q5" s="187"/>
-      <c r="R5" s="187"/>
-      <c r="S5" s="187"/>
-      <c r="T5" s="187"/>
-      <c r="U5" s="187"/>
-      <c r="V5" s="187"/>
-      <c r="W5" s="187"/>
-      <c r="X5" s="187"/>
-      <c r="Y5" s="187"/>
-      <c r="Z5" s="187"/>
-      <c r="AA5" s="187"/>
-      <c r="AB5" s="187"/>
-      <c r="AC5" s="187"/>
-      <c r="AD5" s="187"/>
-      <c r="AE5" s="187"/>
-      <c r="AF5" s="187"/>
-      <c r="AG5" s="187"/>
-      <c r="AH5" s="187"/>
-      <c r="AI5" s="187"/>
-      <c r="AJ5" s="187"/>
-      <c r="AK5" s="187"/>
-      <c r="AL5" s="187"/>
-    </row>
-    <row r="6" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="186"/>
-      <c r="B6" s="186"/>
-      <c r="C6" s="186"/>
-      <c r="D6" s="186"/>
-      <c r="E6" s="186"/>
-      <c r="F6" s="186"/>
-      <c r="G6" s="186"/>
-      <c r="H6" s="186"/>
-      <c r="I6" s="186"/>
-      <c r="J6" s="187"/>
-      <c r="K6" s="187"/>
-      <c r="L6" s="187"/>
-      <c r="M6" s="187"/>
-      <c r="N6" s="187"/>
-      <c r="O6" s="187"/>
-      <c r="P6" s="187"/>
-      <c r="Q6" s="187"/>
-      <c r="R6" s="187"/>
-      <c r="S6" s="187"/>
-      <c r="T6" s="187"/>
-      <c r="U6" s="187"/>
-      <c r="V6" s="187"/>
-      <c r="W6" s="187"/>
-      <c r="X6" s="187"/>
-      <c r="Y6" s="187"/>
-      <c r="Z6" s="187"/>
-      <c r="AA6" s="187"/>
-      <c r="AB6" s="187"/>
-      <c r="AC6" s="187"/>
-      <c r="AD6" s="187"/>
-      <c r="AE6" s="187"/>
-      <c r="AF6" s="187"/>
-      <c r="AG6" s="187"/>
-      <c r="AH6" s="187"/>
-      <c r="AI6" s="187"/>
-      <c r="AJ6" s="187"/>
-      <c r="AK6" s="187"/>
-      <c r="AL6" s="187"/>
-    </row>
-    <row r="7" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="186"/>
-      <c r="B7" s="186"/>
-      <c r="C7" s="186"/>
-      <c r="D7" s="186"/>
-      <c r="E7" s="186"/>
-      <c r="F7" s="186"/>
-      <c r="G7" s="186"/>
-      <c r="H7" s="186"/>
-      <c r="I7" s="186"/>
-      <c r="J7" s="187"/>
-      <c r="K7" s="187"/>
-      <c r="L7" s="187"/>
-      <c r="M7" s="187"/>
-      <c r="N7" s="187"/>
-      <c r="O7" s="187"/>
-      <c r="P7" s="187"/>
-      <c r="Q7" s="187"/>
-      <c r="R7" s="187"/>
-      <c r="S7" s="187"/>
-      <c r="T7" s="187"/>
-      <c r="U7" s="187"/>
-      <c r="V7" s="187"/>
-      <c r="W7" s="187"/>
-      <c r="X7" s="187"/>
-      <c r="Y7" s="187"/>
-      <c r="Z7" s="187"/>
-      <c r="AA7" s="187"/>
-      <c r="AB7" s="187"/>
-      <c r="AC7" s="187"/>
-      <c r="AD7" s="187"/>
-      <c r="AE7" s="187"/>
-      <c r="AF7" s="187"/>
-      <c r="AG7" s="187"/>
-      <c r="AH7" s="187"/>
-      <c r="AI7" s="187"/>
-      <c r="AJ7" s="187"/>
-      <c r="AK7" s="187"/>
-      <c r="AL7" s="187"/>
+      <c r="AH7" s="184"/>
+      <c r="AI7" s="184"/>
+      <c r="AJ7" s="184"/>
+      <c r="AK7" s="184"/>
+      <c r="AL7" s="185"/>
     </row>
     <row r="8" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="186"/>
@@ -16235,215 +16247,210 @@
       <c r="AL16" s="187"/>
     </row>
     <row r="17" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="92" t="s">
+      <c r="A17" s="186"/>
+      <c r="B17" s="186"/>
+      <c r="C17" s="186"/>
+      <c r="D17" s="186"/>
+      <c r="E17" s="186"/>
+      <c r="F17" s="186"/>
+      <c r="G17" s="186"/>
+      <c r="H17" s="186"/>
+      <c r="I17" s="186"/>
+      <c r="J17" s="187"/>
+      <c r="K17" s="187"/>
+      <c r="L17" s="187"/>
+      <c r="M17" s="187"/>
+      <c r="N17" s="187"/>
+      <c r="O17" s="187"/>
+      <c r="P17" s="187"/>
+      <c r="Q17" s="187"/>
+      <c r="R17" s="187"/>
+      <c r="S17" s="187"/>
+      <c r="T17" s="187"/>
+      <c r="U17" s="187"/>
+      <c r="V17" s="187"/>
+      <c r="W17" s="187"/>
+      <c r="X17" s="187"/>
+      <c r="Y17" s="187"/>
+      <c r="Z17" s="187"/>
+      <c r="AA17" s="187"/>
+      <c r="AB17" s="187"/>
+      <c r="AC17" s="187"/>
+      <c r="AD17" s="187"/>
+      <c r="AE17" s="187"/>
+      <c r="AF17" s="187"/>
+      <c r="AG17" s="187"/>
+      <c r="AH17" s="187"/>
+      <c r="AI17" s="187"/>
+      <c r="AJ17" s="187"/>
+      <c r="AK17" s="187"/>
+      <c r="AL17" s="187"/>
+    </row>
+    <row r="18" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="186"/>
+      <c r="B18" s="186"/>
+      <c r="C18" s="186"/>
+      <c r="D18" s="186"/>
+      <c r="E18" s="186"/>
+      <c r="F18" s="186"/>
+      <c r="G18" s="186"/>
+      <c r="H18" s="186"/>
+      <c r="I18" s="186"/>
+      <c r="J18" s="187"/>
+      <c r="K18" s="187"/>
+      <c r="L18" s="187"/>
+      <c r="M18" s="187"/>
+      <c r="N18" s="187"/>
+      <c r="O18" s="187"/>
+      <c r="P18" s="187"/>
+      <c r="Q18" s="187"/>
+      <c r="R18" s="187"/>
+      <c r="S18" s="187"/>
+      <c r="T18" s="187"/>
+      <c r="U18" s="187"/>
+      <c r="V18" s="187"/>
+      <c r="W18" s="187"/>
+      <c r="X18" s="187"/>
+      <c r="Y18" s="187"/>
+      <c r="Z18" s="187"/>
+      <c r="AA18" s="187"/>
+      <c r="AB18" s="187"/>
+      <c r="AC18" s="187"/>
+      <c r="AD18" s="187"/>
+      <c r="AE18" s="187"/>
+      <c r="AF18" s="187"/>
+      <c r="AG18" s="187"/>
+      <c r="AH18" s="187"/>
+      <c r="AI18" s="187"/>
+      <c r="AJ18" s="187"/>
+      <c r="AK18" s="187"/>
+      <c r="AL18" s="187"/>
+    </row>
+    <row r="19" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="186"/>
+      <c r="B19" s="186"/>
+      <c r="C19" s="186"/>
+      <c r="D19" s="186"/>
+      <c r="E19" s="186"/>
+      <c r="F19" s="186"/>
+      <c r="G19" s="186"/>
+      <c r="H19" s="186"/>
+      <c r="I19" s="186"/>
+      <c r="J19" s="187"/>
+      <c r="K19" s="187"/>
+      <c r="L19" s="187"/>
+      <c r="M19" s="187"/>
+      <c r="N19" s="187"/>
+      <c r="O19" s="187"/>
+      <c r="P19" s="187"/>
+      <c r="Q19" s="187"/>
+      <c r="R19" s="187"/>
+      <c r="S19" s="187"/>
+      <c r="T19" s="187"/>
+      <c r="U19" s="187"/>
+      <c r="V19" s="187"/>
+      <c r="W19" s="187"/>
+      <c r="X19" s="187"/>
+      <c r="Y19" s="187"/>
+      <c r="Z19" s="187"/>
+      <c r="AA19" s="187"/>
+      <c r="AB19" s="187"/>
+      <c r="AC19" s="187"/>
+      <c r="AD19" s="187"/>
+      <c r="AE19" s="187"/>
+      <c r="AF19" s="187"/>
+      <c r="AG19" s="187"/>
+      <c r="AH19" s="187"/>
+      <c r="AI19" s="187"/>
+      <c r="AJ19" s="187"/>
+      <c r="AK19" s="187"/>
+      <c r="AL19" s="187"/>
+    </row>
+    <row r="20" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="92" t="s">
         <v>217</v>
       </c>
-      <c r="B17" s="53"/>
-      <c r="C17" s="53"/>
-      <c r="D17" s="53"/>
-      <c r="E17" s="53"/>
-      <c r="F17" s="53"/>
-      <c r="G17" s="53"/>
-      <c r="H17" s="53"/>
-      <c r="I17" s="53"/>
-      <c r="J17" s="53"/>
-      <c r="K17" s="53"/>
-      <c r="L17" s="53"/>
-      <c r="M17" s="53"/>
-      <c r="N17" s="53"/>
-      <c r="O17" s="53"/>
-      <c r="P17" s="53"/>
-      <c r="Q17" s="53"/>
-      <c r="R17" s="53"/>
-      <c r="S17" s="53"/>
-      <c r="T17" s="53"/>
-      <c r="U17" s="53"/>
-      <c r="V17" s="53"/>
-      <c r="W17" s="53"/>
-      <c r="X17" s="53"/>
-      <c r="Y17" s="53"/>
-      <c r="Z17" s="53"/>
-      <c r="AA17" s="53"/>
-      <c r="AB17" s="53"/>
-      <c r="AC17" s="53"/>
-      <c r="AD17" s="53"/>
-      <c r="AE17" s="53"/>
-      <c r="AF17" s="53"/>
-      <c r="AG17" s="53"/>
-      <c r="AH17" s="53"/>
-      <c r="AI17" s="53"/>
-      <c r="AJ17" s="53"/>
-      <c r="AK17" s="53"/>
-      <c r="AL17" s="96"/>
-    </row>
-    <row r="18" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="53"/>
-      <c r="B18" s="53"/>
-      <c r="C18" s="53"/>
-      <c r="D18" s="53"/>
-      <c r="E18" s="53"/>
-      <c r="F18" s="53"/>
-      <c r="G18" s="53"/>
-      <c r="H18" s="53"/>
-      <c r="I18" s="53"/>
-      <c r="J18" s="53"/>
-      <c r="K18" s="53"/>
-      <c r="L18" s="53"/>
-      <c r="M18" s="53"/>
-      <c r="N18" s="53"/>
-      <c r="O18" s="53"/>
-      <c r="P18" s="53"/>
-      <c r="Q18" s="53"/>
-      <c r="R18" s="53"/>
-      <c r="S18" s="53"/>
-      <c r="T18" s="53"/>
-      <c r="U18" s="53"/>
-      <c r="V18" s="53"/>
-      <c r="W18" s="53"/>
-      <c r="X18" s="53"/>
-      <c r="Y18" s="53"/>
-      <c r="Z18" s="53"/>
-      <c r="AA18" s="53"/>
-      <c r="AB18" s="53"/>
-      <c r="AC18" s="53"/>
-      <c r="AD18" s="53"/>
-      <c r="AE18" s="53"/>
-      <c r="AF18" s="53"/>
-      <c r="AG18" s="53"/>
-      <c r="AH18" s="53"/>
-      <c r="AI18" s="53"/>
-      <c r="AJ18" s="53"/>
-      <c r="AK18" s="53"/>
-      <c r="AL18" s="96"/>
-    </row>
-    <row r="19" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="93" t="s">
+      <c r="B20" s="53"/>
+      <c r="C20" s="53"/>
+      <c r="D20" s="53"/>
+      <c r="E20" s="53"/>
+      <c r="F20" s="53"/>
+      <c r="G20" s="53"/>
+      <c r="H20" s="53"/>
+      <c r="I20" s="53"/>
+      <c r="J20" s="53"/>
+      <c r="K20" s="53"/>
+      <c r="L20" s="53"/>
+      <c r="M20" s="53"/>
+      <c r="N20" s="53"/>
+      <c r="O20" s="53"/>
+      <c r="P20" s="53"/>
+      <c r="Q20" s="53"/>
+      <c r="R20" s="53"/>
+      <c r="S20" s="53"/>
+      <c r="T20" s="53"/>
+      <c r="U20" s="53"/>
+      <c r="V20" s="53"/>
+      <c r="W20" s="53"/>
+      <c r="X20" s="53"/>
+      <c r="Y20" s="53"/>
+      <c r="Z20" s="53"/>
+      <c r="AA20" s="53"/>
+      <c r="AB20" s="53"/>
+      <c r="AC20" s="53"/>
+      <c r="AD20" s="53"/>
+      <c r="AE20" s="53"/>
+      <c r="AF20" s="53"/>
+      <c r="AG20" s="53"/>
+      <c r="AH20" s="53"/>
+      <c r="AI20" s="53"/>
+      <c r="AJ20" s="53"/>
+      <c r="AK20" s="53"/>
+      <c r="AL20" s="96"/>
+    </row>
+    <row r="21" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="53"/>
+      <c r="B21" s="53"/>
+      <c r="C21" s="53"/>
+      <c r="D21" s="53"/>
+      <c r="E21" s="53"/>
+      <c r="F21" s="53"/>
+      <c r="G21" s="53"/>
+      <c r="H21" s="53"/>
+      <c r="I21" s="53"/>
+      <c r="J21" s="53"/>
+      <c r="K21" s="53"/>
+      <c r="L21" s="53"/>
+      <c r="M21" s="53"/>
+      <c r="N21" s="53"/>
+      <c r="O21" s="53"/>
+      <c r="P21" s="53"/>
+      <c r="Q21" s="53"/>
+      <c r="R21" s="53"/>
+      <c r="S21" s="53"/>
+      <c r="T21" s="53"/>
+      <c r="U21" s="53"/>
+      <c r="V21" s="53"/>
+      <c r="W21" s="53"/>
+      <c r="X21" s="53"/>
+      <c r="Y21" s="53"/>
+      <c r="Z21" s="53"/>
+      <c r="AA21" s="53"/>
+      <c r="AB21" s="53"/>
+      <c r="AC21" s="53"/>
+      <c r="AD21" s="53"/>
+      <c r="AE21" s="53"/>
+      <c r="AF21" s="53"/>
+      <c r="AG21" s="53"/>
+      <c r="AH21" s="53"/>
+      <c r="AI21" s="53"/>
+      <c r="AJ21" s="53"/>
+      <c r="AK21" s="53"/>
+      <c r="AL21" s="96"/>
+    </row>
+    <row r="22" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="93" t="s">
         <v>218</v>
-      </c>
-      <c r="B19" s="94"/>
-      <c r="C19" s="94"/>
-      <c r="D19" s="94"/>
-      <c r="E19" s="93"/>
-      <c r="F19" s="93"/>
-      <c r="G19" s="93"/>
-      <c r="H19" s="93"/>
-      <c r="I19" s="93"/>
-      <c r="J19" s="93"/>
-      <c r="K19" s="93"/>
-      <c r="L19" s="93"/>
-      <c r="M19" s="93"/>
-      <c r="N19" s="93"/>
-      <c r="O19" s="93"/>
-      <c r="P19" s="93"/>
-      <c r="Q19" s="93"/>
-      <c r="R19" s="93"/>
-      <c r="S19" s="93"/>
-      <c r="T19" s="93"/>
-      <c r="U19" s="93"/>
-      <c r="V19" s="93"/>
-      <c r="W19" s="93"/>
-      <c r="X19" s="93"/>
-      <c r="Y19" s="93"/>
-      <c r="Z19" s="93"/>
-      <c r="AA19" s="93"/>
-      <c r="AB19" s="93"/>
-      <c r="AC19" s="93"/>
-      <c r="AD19" s="93"/>
-      <c r="AE19" s="93"/>
-      <c r="AF19" s="93"/>
-      <c r="AG19" s="94"/>
-      <c r="AH19" s="94"/>
-      <c r="AI19" s="94"/>
-      <c r="AJ19" s="92"/>
-      <c r="AK19" s="92"/>
-      <c r="AL19" s="96"/>
-    </row>
-    <row r="20" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="95" t="s">
-        <v>37</v>
-      </c>
-      <c r="B20" s="94"/>
-      <c r="C20" s="94"/>
-      <c r="D20" s="94"/>
-      <c r="E20" s="93"/>
-      <c r="F20" s="93"/>
-      <c r="G20" s="93"/>
-      <c r="H20" s="93"/>
-      <c r="I20" s="93"/>
-      <c r="J20" s="93"/>
-      <c r="K20" s="93"/>
-      <c r="L20" s="93"/>
-      <c r="M20" s="93"/>
-      <c r="N20" s="93"/>
-      <c r="O20" s="93"/>
-      <c r="P20" s="93"/>
-      <c r="Q20" s="93"/>
-      <c r="R20" s="93"/>
-      <c r="S20" s="93"/>
-      <c r="T20" s="93"/>
-      <c r="U20" s="93"/>
-      <c r="V20" s="93"/>
-      <c r="W20" s="93"/>
-      <c r="X20" s="93"/>
-      <c r="Y20" s="93"/>
-      <c r="Z20" s="93"/>
-      <c r="AA20" s="93"/>
-      <c r="AB20" s="93"/>
-      <c r="AC20" s="93"/>
-      <c r="AD20" s="93"/>
-      <c r="AE20" s="93"/>
-      <c r="AF20" s="93"/>
-      <c r="AG20" s="94"/>
-      <c r="AH20" s="94"/>
-      <c r="AI20" s="94"/>
-      <c r="AJ20" s="92"/>
-      <c r="AK20" s="92"/>
-      <c r="AL20" s="96"/>
-    </row>
-    <row r="21" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="93" t="s">
-        <v>219</v>
-      </c>
-      <c r="B21" s="94"/>
-      <c r="C21" s="94"/>
-      <c r="D21" s="94"/>
-      <c r="E21" s="93"/>
-      <c r="F21" s="93"/>
-      <c r="G21" s="93"/>
-      <c r="H21" s="93"/>
-      <c r="I21" s="93"/>
-      <c r="J21" s="93"/>
-      <c r="K21" s="93"/>
-      <c r="L21" s="93"/>
-      <c r="M21" s="93"/>
-      <c r="N21" s="93"/>
-      <c r="O21" s="93"/>
-      <c r="P21" s="93"/>
-      <c r="Q21" s="93"/>
-      <c r="R21" s="93"/>
-      <c r="S21" s="93"/>
-      <c r="T21" s="93"/>
-      <c r="U21" s="93"/>
-      <c r="V21" s="93"/>
-      <c r="W21" s="93"/>
-      <c r="X21" s="93"/>
-      <c r="Y21" s="93"/>
-      <c r="Z21" s="93"/>
-      <c r="AA21" s="93"/>
-      <c r="AB21" s="93"/>
-      <c r="AC21" s="93"/>
-      <c r="AD21" s="93"/>
-      <c r="AE21" s="93"/>
-      <c r="AF21" s="93"/>
-      <c r="AG21" s="94"/>
-      <c r="AH21" s="94"/>
-      <c r="AI21" s="94"/>
-      <c r="AJ21" s="92"/>
-      <c r="AK21" s="92"/>
-    </row>
-    <row r="22" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="95" t="s">
-        <v>37</v>
       </c>
       <c r="B22" s="94"/>
       <c r="C22" s="94"/>
@@ -16481,147 +16488,287 @@
       <c r="AI22" s="94"/>
       <c r="AJ22" s="92"/>
       <c r="AK22" s="92"/>
+      <c r="AL22" s="96"/>
     </row>
     <row r="23" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="53"/>
-      <c r="B23" s="53"/>
-      <c r="C23" s="53"/>
-      <c r="D23" s="53"/>
-      <c r="E23" s="53"/>
-      <c r="F23" s="53"/>
-      <c r="G23" s="53"/>
-      <c r="H23" s="53"/>
-      <c r="I23" s="53"/>
-      <c r="J23" s="53"/>
-      <c r="K23" s="53"/>
-      <c r="L23" s="53"/>
-      <c r="M23" s="53"/>
-      <c r="N23" s="53"/>
-      <c r="O23" s="53"/>
-      <c r="P23" s="53"/>
-      <c r="Q23" s="53"/>
-      <c r="R23" s="53"/>
-      <c r="S23" s="53"/>
-      <c r="T23" s="53"/>
-      <c r="U23" s="53"/>
-      <c r="V23" s="53"/>
-      <c r="W23" s="53"/>
-      <c r="X23" s="53"/>
-      <c r="Y23" s="53"/>
-      <c r="Z23" s="53"/>
-      <c r="AA23" s="53"/>
-      <c r="AB23" s="53"/>
-      <c r="AC23" s="53"/>
-      <c r="AD23" s="53"/>
-      <c r="AE23" s="53"/>
-      <c r="AF23" s="53"/>
-      <c r="AG23" s="53"/>
-      <c r="AH23" s="53"/>
-      <c r="AI23" s="53"/>
-      <c r="AJ23" s="53"/>
-      <c r="AK23" s="53"/>
+      <c r="A23" s="95" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="94"/>
+      <c r="C23" s="94"/>
+      <c r="D23" s="94"/>
+      <c r="E23" s="93"/>
+      <c r="F23" s="93"/>
+      <c r="G23" s="93"/>
+      <c r="H23" s="93"/>
+      <c r="I23" s="93"/>
+      <c r="J23" s="93"/>
+      <c r="K23" s="93"/>
+      <c r="L23" s="93"/>
+      <c r="M23" s="93"/>
+      <c r="N23" s="93"/>
+      <c r="O23" s="93"/>
+      <c r="P23" s="93"/>
+      <c r="Q23" s="93"/>
+      <c r="R23" s="93"/>
+      <c r="S23" s="93"/>
+      <c r="T23" s="93"/>
+      <c r="U23" s="93"/>
+      <c r="V23" s="93"/>
+      <c r="W23" s="93"/>
+      <c r="X23" s="93"/>
+      <c r="Y23" s="93"/>
+      <c r="Z23" s="93"/>
+      <c r="AA23" s="93"/>
+      <c r="AB23" s="93"/>
+      <c r="AC23" s="93"/>
+      <c r="AD23" s="93"/>
+      <c r="AE23" s="93"/>
+      <c r="AF23" s="93"/>
+      <c r="AG23" s="94"/>
+      <c r="AH23" s="94"/>
+      <c r="AI23" s="94"/>
+      <c r="AJ23" s="92"/>
+      <c r="AK23" s="92"/>
+      <c r="AL23" s="96"/>
     </row>
     <row r="24" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="53" t="s">
+      <c r="A24" s="93" t="s">
+        <v>219</v>
+      </c>
+      <c r="B24" s="94"/>
+      <c r="C24" s="94"/>
+      <c r="D24" s="94"/>
+      <c r="E24" s="93"/>
+      <c r="F24" s="93"/>
+      <c r="G24" s="93"/>
+      <c r="H24" s="93"/>
+      <c r="I24" s="93"/>
+      <c r="J24" s="93"/>
+      <c r="K24" s="93"/>
+      <c r="L24" s="93"/>
+      <c r="M24" s="93"/>
+      <c r="N24" s="93"/>
+      <c r="O24" s="93"/>
+      <c r="P24" s="93"/>
+      <c r="Q24" s="93"/>
+      <c r="R24" s="93"/>
+      <c r="S24" s="93"/>
+      <c r="T24" s="93"/>
+      <c r="U24" s="93"/>
+      <c r="V24" s="93"/>
+      <c r="W24" s="93"/>
+      <c r="X24" s="93"/>
+      <c r="Y24" s="93"/>
+      <c r="Z24" s="93"/>
+      <c r="AA24" s="93"/>
+      <c r="AB24" s="93"/>
+      <c r="AC24" s="93"/>
+      <c r="AD24" s="93"/>
+      <c r="AE24" s="93"/>
+      <c r="AF24" s="93"/>
+      <c r="AG24" s="94"/>
+      <c r="AH24" s="94"/>
+      <c r="AI24" s="94"/>
+      <c r="AJ24" s="92"/>
+      <c r="AK24" s="92"/>
+    </row>
+    <row r="25" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="95" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="94"/>
+      <c r="C25" s="94"/>
+      <c r="D25" s="94"/>
+      <c r="E25" s="93"/>
+      <c r="F25" s="93"/>
+      <c r="G25" s="93"/>
+      <c r="H25" s="93"/>
+      <c r="I25" s="93"/>
+      <c r="J25" s="93"/>
+      <c r="K25" s="93"/>
+      <c r="L25" s="93"/>
+      <c r="M25" s="93"/>
+      <c r="N25" s="93"/>
+      <c r="O25" s="93"/>
+      <c r="P25" s="93"/>
+      <c r="Q25" s="93"/>
+      <c r="R25" s="93"/>
+      <c r="S25" s="93"/>
+      <c r="T25" s="93"/>
+      <c r="U25" s="93"/>
+      <c r="V25" s="93"/>
+      <c r="W25" s="93"/>
+      <c r="X25" s="93"/>
+      <c r="Y25" s="93"/>
+      <c r="Z25" s="93"/>
+      <c r="AA25" s="93"/>
+      <c r="AB25" s="93"/>
+      <c r="AC25" s="93"/>
+      <c r="AD25" s="93"/>
+      <c r="AE25" s="93"/>
+      <c r="AF25" s="93"/>
+      <c r="AG25" s="94"/>
+      <c r="AH25" s="94"/>
+      <c r="AI25" s="94"/>
+      <c r="AJ25" s="92"/>
+      <c r="AK25" s="92"/>
+    </row>
+    <row r="26" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="53"/>
+      <c r="B26" s="53"/>
+      <c r="C26" s="53"/>
+      <c r="D26" s="53"/>
+      <c r="E26" s="53"/>
+      <c r="F26" s="53"/>
+      <c r="G26" s="53"/>
+      <c r="H26" s="53"/>
+      <c r="I26" s="53"/>
+      <c r="J26" s="53"/>
+      <c r="K26" s="53"/>
+      <c r="L26" s="53"/>
+      <c r="M26" s="53"/>
+      <c r="N26" s="53"/>
+      <c r="O26" s="53"/>
+      <c r="P26" s="53"/>
+      <c r="Q26" s="53"/>
+      <c r="R26" s="53"/>
+      <c r="S26" s="53"/>
+      <c r="T26" s="53"/>
+      <c r="U26" s="53"/>
+      <c r="V26" s="53"/>
+      <c r="W26" s="53"/>
+      <c r="X26" s="53"/>
+      <c r="Y26" s="53"/>
+      <c r="Z26" s="53"/>
+      <c r="AA26" s="53"/>
+      <c r="AB26" s="53"/>
+      <c r="AC26" s="53"/>
+      <c r="AD26" s="53"/>
+      <c r="AE26" s="53"/>
+      <c r="AF26" s="53"/>
+      <c r="AG26" s="53"/>
+      <c r="AH26" s="53"/>
+      <c r="AI26" s="53"/>
+      <c r="AJ26" s="53"/>
+      <c r="AK26" s="53"/>
+    </row>
+    <row r="27" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="53" t="s">
         <v>92</v>
       </c>
-      <c r="B24" s="53"/>
-      <c r="C24" s="53"/>
-      <c r="D24" s="53"/>
-      <c r="E24" s="53"/>
-      <c r="F24" s="53"/>
-      <c r="G24" s="53"/>
-      <c r="H24" s="53"/>
-      <c r="I24" s="53"/>
-      <c r="J24" s="53"/>
-      <c r="K24" s="53"/>
-      <c r="L24" s="53"/>
-      <c r="M24" s="53"/>
-      <c r="N24" s="53"/>
-      <c r="O24" s="53"/>
-      <c r="P24" s="53"/>
-      <c r="Q24" s="53"/>
-      <c r="R24" s="53"/>
-      <c r="S24" s="53"/>
-      <c r="T24" s="53"/>
-      <c r="U24" s="53"/>
-      <c r="V24" s="53"/>
-      <c r="W24" s="53"/>
-      <c r="X24" s="53"/>
-      <c r="Y24" s="53"/>
-      <c r="Z24" s="53"/>
-      <c r="AA24" s="53"/>
-      <c r="AB24" s="53"/>
-      <c r="AC24" s="53"/>
-      <c r="AD24" s="53"/>
-      <c r="AE24" s="53"/>
-      <c r="AF24" s="53"/>
-      <c r="AG24" s="53"/>
-      <c r="AH24" s="53"/>
-      <c r="AI24" s="53"/>
-      <c r="AJ24" s="53"/>
-      <c r="AK24" s="53"/>
-    </row>
-    <row r="25" spans="1:38" ht="13.95" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="1:38" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="7"/>
-      <c r="B26" s="12"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="12"/>
-      <c r="H26" s="12"/>
-      <c r="I26" s="12"/>
-      <c r="J26" s="12"/>
-      <c r="K26" s="12"/>
-      <c r="L26" s="12"/>
-      <c r="M26" s="12"/>
-      <c r="N26" s="12"/>
-    </row>
-    <row r="27" spans="1:38" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="7"/>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
-      <c r="G27" s="4"/>
-      <c r="H27" s="4"/>
-      <c r="I27" s="4"/>
-      <c r="J27" s="4"/>
-      <c r="K27" s="4"/>
-      <c r="L27" s="4"/>
-      <c r="M27" s="4"/>
-      <c r="N27" s="4"/>
-    </row>
-    <row r="28" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A28" s="7"/>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="4"/>
-      <c r="I28" s="4"/>
-      <c r="J28" s="4"/>
-      <c r="K28" s="4"/>
-      <c r="L28" s="4"/>
-      <c r="M28" s="4"/>
-      <c r="N28" s="4"/>
+      <c r="B27" s="53"/>
+      <c r="C27" s="53"/>
+      <c r="D27" s="53"/>
+      <c r="E27" s="53"/>
+      <c r="F27" s="53"/>
+      <c r="G27" s="53"/>
+      <c r="H27" s="53"/>
+      <c r="I27" s="53"/>
+      <c r="J27" s="53"/>
+      <c r="K27" s="53"/>
+      <c r="L27" s="53"/>
+      <c r="M27" s="53"/>
+      <c r="N27" s="53"/>
+      <c r="O27" s="53"/>
+      <c r="P27" s="53"/>
+      <c r="Q27" s="53"/>
+      <c r="R27" s="53"/>
+      <c r="S27" s="53"/>
+      <c r="T27" s="53"/>
+      <c r="U27" s="53"/>
+      <c r="V27" s="53"/>
+      <c r="W27" s="53"/>
+      <c r="X27" s="53"/>
+      <c r="Y27" s="53"/>
+      <c r="Z27" s="53"/>
+      <c r="AA27" s="53"/>
+      <c r="AB27" s="53"/>
+      <c r="AC27" s="53"/>
+      <c r="AD27" s="53"/>
+      <c r="AE27" s="53"/>
+      <c r="AF27" s="53"/>
+      <c r="AG27" s="53"/>
+      <c r="AH27" s="53"/>
+      <c r="AI27" s="53"/>
+      <c r="AJ27" s="53"/>
+      <c r="AK27" s="53"/>
+    </row>
+    <row r="28" spans="1:38" ht="13.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:38" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="7"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="12"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="12"/>
+      <c r="G29" s="12"/>
+      <c r="H29" s="12"/>
+      <c r="I29" s="12"/>
+      <c r="J29" s="12"/>
+      <c r="K29" s="12"/>
+      <c r="L29" s="12"/>
+      <c r="M29" s="12"/>
+      <c r="N29" s="12"/>
+    </row>
+    <row r="30" spans="1:38" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="7"/>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+      <c r="K30" s="4"/>
+      <c r="L30" s="4"/>
+      <c r="M30" s="4"/>
+      <c r="N30" s="4"/>
+    </row>
+    <row r="31" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A31" s="7"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="4"/>
+      <c r="K31" s="4"/>
+      <c r="L31" s="4"/>
+      <c r="M31" s="4"/>
+      <c r="N31" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="45">
-    <mergeCell ref="A16:I16"/>
-    <mergeCell ref="J16:X16"/>
-    <mergeCell ref="Y16:AL16"/>
+    <mergeCell ref="A19:I19"/>
+    <mergeCell ref="J19:X19"/>
+    <mergeCell ref="Y19:AL19"/>
+    <mergeCell ref="A17:I17"/>
+    <mergeCell ref="J17:X17"/>
+    <mergeCell ref="Y17:AL17"/>
+    <mergeCell ref="A18:I18"/>
+    <mergeCell ref="J18:X18"/>
+    <mergeCell ref="Y18:AL18"/>
+    <mergeCell ref="A13:I13"/>
+    <mergeCell ref="J13:X13"/>
+    <mergeCell ref="Y13:AL13"/>
     <mergeCell ref="A14:I14"/>
     <mergeCell ref="J14:X14"/>
     <mergeCell ref="Y14:AL14"/>
     <mergeCell ref="A15:I15"/>
     <mergeCell ref="J15:X15"/>
     <mergeCell ref="Y15:AL15"/>
+    <mergeCell ref="A16:I16"/>
+    <mergeCell ref="J16:X16"/>
+    <mergeCell ref="Y16:AL16"/>
+    <mergeCell ref="A9:I9"/>
+    <mergeCell ref="J9:X9"/>
+    <mergeCell ref="Y9:AL9"/>
     <mergeCell ref="A10:I10"/>
     <mergeCell ref="J10:X10"/>
     <mergeCell ref="Y10:AL10"/>
@@ -16631,33 +16778,18 @@
     <mergeCell ref="A12:I12"/>
     <mergeCell ref="J12:X12"/>
     <mergeCell ref="Y12:AL12"/>
-    <mergeCell ref="A13:I13"/>
-    <mergeCell ref="J13:X13"/>
-    <mergeCell ref="Y13:AL13"/>
-    <mergeCell ref="A6:I6"/>
-    <mergeCell ref="J6:X6"/>
-    <mergeCell ref="Y6:AL6"/>
-    <mergeCell ref="A7:I7"/>
-    <mergeCell ref="J7:X7"/>
-    <mergeCell ref="Y7:AL7"/>
     <mergeCell ref="A8:I8"/>
     <mergeCell ref="J8:X8"/>
     <mergeCell ref="Y8:AL8"/>
-    <mergeCell ref="A9:I9"/>
-    <mergeCell ref="J9:X9"/>
-    <mergeCell ref="Y9:AL9"/>
     <mergeCell ref="M1:AL1"/>
-    <mergeCell ref="A4:I4"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="D3:I3"/>
-    <mergeCell ref="J3:AL3"/>
-    <mergeCell ref="J4:P4"/>
-    <mergeCell ref="R4:X4"/>
-    <mergeCell ref="Y4:AE4"/>
-    <mergeCell ref="AG4:AL4"/>
-    <mergeCell ref="A5:I5"/>
-    <mergeCell ref="J5:X5"/>
-    <mergeCell ref="Y5:AL5"/>
+    <mergeCell ref="A7:I7"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:I6"/>
+    <mergeCell ref="J6:AL6"/>
+    <mergeCell ref="J7:P7"/>
+    <mergeCell ref="R7:X7"/>
+    <mergeCell ref="Y7:AE7"/>
+    <mergeCell ref="AG7:AL7"/>
   </mergeCells>
   <phoneticPr fontId="22" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.82677165354330717" bottom="0.98425196850393704" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -16700,32 +16832,32 @@
       <c r="J1" s="54"/>
       <c r="K1" s="54"/>
       <c r="L1" s="54"/>
-      <c r="M1" s="150"/>
-      <c r="N1" s="150"/>
-      <c r="O1" s="150"/>
-      <c r="P1" s="150"/>
-      <c r="Q1" s="150"/>
-      <c r="R1" s="150"/>
-      <c r="S1" s="150"/>
-      <c r="T1" s="150"/>
-      <c r="U1" s="150"/>
-      <c r="V1" s="150"/>
-      <c r="W1" s="150"/>
-      <c r="X1" s="150"/>
-      <c r="Y1" s="150"/>
-      <c r="Z1" s="150"/>
-      <c r="AA1" s="150"/>
-      <c r="AB1" s="150"/>
-      <c r="AC1" s="150"/>
-      <c r="AD1" s="150"/>
-      <c r="AE1" s="150"/>
-      <c r="AF1" s="150"/>
-      <c r="AG1" s="150"/>
-      <c r="AH1" s="150"/>
-      <c r="AI1" s="150"/>
-      <c r="AJ1" s="150"/>
-      <c r="AK1" s="150"/>
-      <c r="AL1" s="150"/>
+      <c r="M1" s="152"/>
+      <c r="N1" s="152"/>
+      <c r="O1" s="152"/>
+      <c r="P1" s="152"/>
+      <c r="Q1" s="152"/>
+      <c r="R1" s="152"/>
+      <c r="S1" s="152"/>
+      <c r="T1" s="152"/>
+      <c r="U1" s="152"/>
+      <c r="V1" s="152"/>
+      <c r="W1" s="152"/>
+      <c r="X1" s="152"/>
+      <c r="Y1" s="152"/>
+      <c r="Z1" s="152"/>
+      <c r="AA1" s="152"/>
+      <c r="AB1" s="152"/>
+      <c r="AC1" s="152"/>
+      <c r="AD1" s="152"/>
+      <c r="AE1" s="152"/>
+      <c r="AF1" s="152"/>
+      <c r="AG1" s="152"/>
+      <c r="AH1" s="152"/>
+      <c r="AI1" s="152"/>
+      <c r="AJ1" s="152"/>
+      <c r="AK1" s="152"/>
+      <c r="AL1" s="152"/>
     </row>
     <row r="2" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="80" t="s">
@@ -16780,23 +16912,23 @@
       <c r="F3" s="53"/>
       <c r="G3" s="53"/>
       <c r="H3" s="53"/>
-      <c r="I3" s="150"/>
-      <c r="J3" s="150"/>
-      <c r="K3" s="150"/>
-      <c r="L3" s="150"/>
-      <c r="M3" s="150"/>
-      <c r="N3" s="150"/>
-      <c r="O3" s="150"/>
-      <c r="P3" s="150"/>
-      <c r="Q3" s="150"/>
-      <c r="R3" s="150"/>
-      <c r="S3" s="150"/>
-      <c r="T3" s="150"/>
-      <c r="U3" s="150"/>
-      <c r="V3" s="150"/>
-      <c r="W3" s="150"/>
-      <c r="X3" s="150"/>
-      <c r="Y3" s="150"/>
+      <c r="I3" s="152"/>
+      <c r="J3" s="152"/>
+      <c r="K3" s="152"/>
+      <c r="L3" s="152"/>
+      <c r="M3" s="152"/>
+      <c r="N3" s="152"/>
+      <c r="O3" s="152"/>
+      <c r="P3" s="152"/>
+      <c r="Q3" s="152"/>
+      <c r="R3" s="152"/>
+      <c r="S3" s="152"/>
+      <c r="T3" s="152"/>
+      <c r="U3" s="152"/>
+      <c r="V3" s="152"/>
+      <c r="W3" s="152"/>
+      <c r="X3" s="152"/>
+      <c r="Y3" s="152"/>
       <c r="Z3" s="53"/>
       <c r="AA3" s="53"/>
       <c r="AB3" s="81"/>
@@ -16938,220 +17070,220 @@
       <c r="AL6" s="84"/>
     </row>
     <row r="7" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="198" t="s">
+      <c r="A7" s="200" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="199"/>
-      <c r="C7" s="199"/>
-      <c r="D7" s="200"/>
-      <c r="E7" s="204" t="s">
+      <c r="B7" s="201"/>
+      <c r="C7" s="201"/>
+      <c r="D7" s="202"/>
+      <c r="E7" s="206" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="205"/>
-      <c r="G7" s="205"/>
-      <c r="H7" s="205"/>
-      <c r="I7" s="205"/>
-      <c r="J7" s="205"/>
-      <c r="K7" s="205"/>
-      <c r="L7" s="205"/>
-      <c r="M7" s="205"/>
-      <c r="N7" s="205"/>
-      <c r="O7" s="205"/>
-      <c r="P7" s="205"/>
-      <c r="Q7" s="205"/>
-      <c r="R7" s="205"/>
-      <c r="S7" s="205"/>
-      <c r="T7" s="205"/>
-      <c r="U7" s="205"/>
-      <c r="V7" s="205"/>
-      <c r="W7" s="205"/>
-      <c r="X7" s="205"/>
-      <c r="Y7" s="205"/>
-      <c r="Z7" s="205"/>
-      <c r="AA7" s="205"/>
-      <c r="AB7" s="205"/>
-      <c r="AC7" s="205"/>
-      <c r="AD7" s="205"/>
-      <c r="AE7" s="205"/>
-      <c r="AF7" s="205"/>
-      <c r="AG7" s="205"/>
-      <c r="AH7" s="206"/>
-      <c r="AI7" s="198" t="s">
+      <c r="F7" s="207"/>
+      <c r="G7" s="207"/>
+      <c r="H7" s="207"/>
+      <c r="I7" s="207"/>
+      <c r="J7" s="207"/>
+      <c r="K7" s="207"/>
+      <c r="L7" s="207"/>
+      <c r="M7" s="207"/>
+      <c r="N7" s="207"/>
+      <c r="O7" s="207"/>
+      <c r="P7" s="207"/>
+      <c r="Q7" s="207"/>
+      <c r="R7" s="207"/>
+      <c r="S7" s="207"/>
+      <c r="T7" s="207"/>
+      <c r="U7" s="207"/>
+      <c r="V7" s="207"/>
+      <c r="W7" s="207"/>
+      <c r="X7" s="207"/>
+      <c r="Y7" s="207"/>
+      <c r="Z7" s="207"/>
+      <c r="AA7" s="207"/>
+      <c r="AB7" s="207"/>
+      <c r="AC7" s="207"/>
+      <c r="AD7" s="207"/>
+      <c r="AE7" s="207"/>
+      <c r="AF7" s="207"/>
+      <c r="AG7" s="207"/>
+      <c r="AH7" s="208"/>
+      <c r="AI7" s="200" t="s">
         <v>19</v>
       </c>
-      <c r="AJ7" s="199"/>
-      <c r="AK7" s="199"/>
-      <c r="AL7" s="200"/>
+      <c r="AJ7" s="201"/>
+      <c r="AK7" s="201"/>
+      <c r="AL7" s="202"/>
     </row>
     <row r="8" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="201"/>
-      <c r="B8" s="202"/>
-      <c r="C8" s="202"/>
-      <c r="D8" s="203"/>
-      <c r="E8" s="192" t="s">
+      <c r="A8" s="203"/>
+      <c r="B8" s="204"/>
+      <c r="C8" s="204"/>
+      <c r="D8" s="205"/>
+      <c r="E8" s="194" t="s">
         <v>199</v>
       </c>
-      <c r="F8" s="193"/>
-      <c r="G8" s="193"/>
-      <c r="H8" s="193"/>
-      <c r="I8" s="193"/>
-      <c r="J8" s="194"/>
-      <c r="K8" s="192" t="s">
+      <c r="F8" s="195"/>
+      <c r="G8" s="195"/>
+      <c r="H8" s="195"/>
+      <c r="I8" s="195"/>
+      <c r="J8" s="196"/>
+      <c r="K8" s="194" t="s">
         <v>201</v>
       </c>
-      <c r="L8" s="193"/>
-      <c r="M8" s="193"/>
-      <c r="N8" s="193"/>
-      <c r="O8" s="193"/>
-      <c r="P8" s="194"/>
-      <c r="Q8" s="192" t="s">
+      <c r="L8" s="195"/>
+      <c r="M8" s="195"/>
+      <c r="N8" s="195"/>
+      <c r="O8" s="195"/>
+      <c r="P8" s="196"/>
+      <c r="Q8" s="194" t="s">
         <v>202</v>
       </c>
-      <c r="R8" s="193"/>
-      <c r="S8" s="193"/>
-      <c r="T8" s="193"/>
-      <c r="U8" s="193"/>
-      <c r="V8" s="194"/>
-      <c r="W8" s="192" t="s">
+      <c r="R8" s="195"/>
+      <c r="S8" s="195"/>
+      <c r="T8" s="195"/>
+      <c r="U8" s="195"/>
+      <c r="V8" s="196"/>
+      <c r="W8" s="194" t="s">
         <v>203</v>
       </c>
-      <c r="X8" s="193"/>
-      <c r="Y8" s="193"/>
-      <c r="Z8" s="193"/>
-      <c r="AA8" s="193"/>
-      <c r="AB8" s="194"/>
-      <c r="AC8" s="192" t="s">
+      <c r="X8" s="195"/>
+      <c r="Y8" s="195"/>
+      <c r="Z8" s="195"/>
+      <c r="AA8" s="195"/>
+      <c r="AB8" s="196"/>
+      <c r="AC8" s="194" t="s">
         <v>200</v>
       </c>
-      <c r="AD8" s="193"/>
-      <c r="AE8" s="193"/>
-      <c r="AF8" s="193"/>
-      <c r="AG8" s="193"/>
-      <c r="AH8" s="194"/>
-      <c r="AI8" s="201"/>
-      <c r="AJ8" s="202"/>
-      <c r="AK8" s="202"/>
-      <c r="AL8" s="203"/>
+      <c r="AD8" s="195"/>
+      <c r="AE8" s="195"/>
+      <c r="AF8" s="195"/>
+      <c r="AG8" s="195"/>
+      <c r="AH8" s="196"/>
+      <c r="AI8" s="203"/>
+      <c r="AJ8" s="204"/>
+      <c r="AK8" s="204"/>
+      <c r="AL8" s="205"/>
     </row>
     <row r="9" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="195"/>
-      <c r="B9" s="196"/>
-      <c r="C9" s="196"/>
-      <c r="D9" s="197"/>
-      <c r="E9" s="192"/>
-      <c r="F9" s="193"/>
-      <c r="G9" s="193"/>
-      <c r="H9" s="193"/>
-      <c r="I9" s="193"/>
-      <c r="J9" s="194"/>
-      <c r="K9" s="192"/>
-      <c r="L9" s="193"/>
-      <c r="M9" s="193"/>
-      <c r="N9" s="193"/>
-      <c r="O9" s="193"/>
-      <c r="P9" s="194"/>
-      <c r="Q9" s="192"/>
-      <c r="R9" s="193"/>
-      <c r="S9" s="193"/>
-      <c r="T9" s="193"/>
-      <c r="U9" s="193"/>
-      <c r="V9" s="194"/>
-      <c r="W9" s="192"/>
-      <c r="X9" s="193"/>
-      <c r="Y9" s="193"/>
-      <c r="Z9" s="193"/>
-      <c r="AA9" s="193"/>
-      <c r="AB9" s="194"/>
-      <c r="AC9" s="192"/>
-      <c r="AD9" s="193"/>
-      <c r="AE9" s="193"/>
-      <c r="AF9" s="193"/>
-      <c r="AG9" s="193"/>
-      <c r="AH9" s="194"/>
-      <c r="AI9" s="192"/>
-      <c r="AJ9" s="193"/>
-      <c r="AK9" s="193"/>
-      <c r="AL9" s="194"/>
+      <c r="A9" s="197"/>
+      <c r="B9" s="198"/>
+      <c r="C9" s="198"/>
+      <c r="D9" s="199"/>
+      <c r="E9" s="194"/>
+      <c r="F9" s="195"/>
+      <c r="G9" s="195"/>
+      <c r="H9" s="195"/>
+      <c r="I9" s="195"/>
+      <c r="J9" s="196"/>
+      <c r="K9" s="194"/>
+      <c r="L9" s="195"/>
+      <c r="M9" s="195"/>
+      <c r="N9" s="195"/>
+      <c r="O9" s="195"/>
+      <c r="P9" s="196"/>
+      <c r="Q9" s="194"/>
+      <c r="R9" s="195"/>
+      <c r="S9" s="195"/>
+      <c r="T9" s="195"/>
+      <c r="U9" s="195"/>
+      <c r="V9" s="196"/>
+      <c r="W9" s="194"/>
+      <c r="X9" s="195"/>
+      <c r="Y9" s="195"/>
+      <c r="Z9" s="195"/>
+      <c r="AA9" s="195"/>
+      <c r="AB9" s="196"/>
+      <c r="AC9" s="194"/>
+      <c r="AD9" s="195"/>
+      <c r="AE9" s="195"/>
+      <c r="AF9" s="195"/>
+      <c r="AG9" s="195"/>
+      <c r="AH9" s="196"/>
+      <c r="AI9" s="194"/>
+      <c r="AJ9" s="195"/>
+      <c r="AK9" s="195"/>
+      <c r="AL9" s="196"/>
     </row>
     <row r="10" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="188"/>
-      <c r="B10" s="188"/>
-      <c r="C10" s="188"/>
-      <c r="D10" s="188"/>
-      <c r="E10" s="137"/>
-      <c r="F10" s="137"/>
-      <c r="G10" s="137"/>
-      <c r="H10" s="137"/>
-      <c r="I10" s="137"/>
-      <c r="J10" s="137"/>
-      <c r="K10" s="137"/>
-      <c r="L10" s="137"/>
-      <c r="M10" s="137"/>
-      <c r="N10" s="137"/>
-      <c r="O10" s="137"/>
-      <c r="P10" s="137"/>
-      <c r="Q10" s="137"/>
-      <c r="R10" s="137"/>
-      <c r="S10" s="137"/>
-      <c r="T10" s="137"/>
-      <c r="U10" s="137"/>
-      <c r="V10" s="137"/>
-      <c r="W10" s="137"/>
-      <c r="X10" s="137"/>
-      <c r="Y10" s="137"/>
-      <c r="Z10" s="137"/>
-      <c r="AA10" s="137"/>
-      <c r="AB10" s="137"/>
-      <c r="AC10" s="137"/>
-      <c r="AD10" s="137"/>
-      <c r="AE10" s="137"/>
-      <c r="AF10" s="137"/>
-      <c r="AG10" s="137"/>
-      <c r="AH10" s="137"/>
-      <c r="AI10" s="137"/>
-      <c r="AJ10" s="137"/>
-      <c r="AK10" s="137"/>
-      <c r="AL10" s="137"/>
+      <c r="A10" s="192"/>
+      <c r="B10" s="192"/>
+      <c r="C10" s="192"/>
+      <c r="D10" s="192"/>
+      <c r="E10" s="139"/>
+      <c r="F10" s="139"/>
+      <c r="G10" s="139"/>
+      <c r="H10" s="139"/>
+      <c r="I10" s="139"/>
+      <c r="J10" s="139"/>
+      <c r="K10" s="139"/>
+      <c r="L10" s="139"/>
+      <c r="M10" s="139"/>
+      <c r="N10" s="139"/>
+      <c r="O10" s="139"/>
+      <c r="P10" s="139"/>
+      <c r="Q10" s="139"/>
+      <c r="R10" s="139"/>
+      <c r="S10" s="139"/>
+      <c r="T10" s="139"/>
+      <c r="U10" s="139"/>
+      <c r="V10" s="139"/>
+      <c r="W10" s="139"/>
+      <c r="X10" s="139"/>
+      <c r="Y10" s="139"/>
+      <c r="Z10" s="139"/>
+      <c r="AA10" s="139"/>
+      <c r="AB10" s="139"/>
+      <c r="AC10" s="139"/>
+      <c r="AD10" s="139"/>
+      <c r="AE10" s="139"/>
+      <c r="AF10" s="139"/>
+      <c r="AG10" s="139"/>
+      <c r="AH10" s="139"/>
+      <c r="AI10" s="139"/>
+      <c r="AJ10" s="139"/>
+      <c r="AK10" s="139"/>
+      <c r="AL10" s="139"/>
     </row>
     <row r="11" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="188"/>
-      <c r="B11" s="188"/>
-      <c r="C11" s="188"/>
-      <c r="D11" s="188"/>
-      <c r="E11" s="137"/>
-      <c r="F11" s="137"/>
-      <c r="G11" s="137"/>
-      <c r="H11" s="137"/>
-      <c r="I11" s="137"/>
-      <c r="J11" s="137"/>
-      <c r="K11" s="137"/>
-      <c r="L11" s="137"/>
-      <c r="M11" s="137"/>
-      <c r="N11" s="137"/>
-      <c r="O11" s="137"/>
-      <c r="P11" s="137"/>
-      <c r="Q11" s="137"/>
-      <c r="R11" s="137"/>
-      <c r="S11" s="137"/>
-      <c r="T11" s="137"/>
-      <c r="U11" s="137"/>
-      <c r="V11" s="137"/>
-      <c r="W11" s="137"/>
-      <c r="X11" s="137"/>
-      <c r="Y11" s="137"/>
-      <c r="Z11" s="137"/>
-      <c r="AA11" s="137"/>
-      <c r="AB11" s="137"/>
-      <c r="AC11" s="137"/>
-      <c r="AD11" s="137"/>
-      <c r="AE11" s="137"/>
-      <c r="AF11" s="137"/>
-      <c r="AG11" s="137"/>
-      <c r="AH11" s="137"/>
-      <c r="AI11" s="137"/>
-      <c r="AJ11" s="137"/>
-      <c r="AK11" s="137"/>
-      <c r="AL11" s="137"/>
+      <c r="A11" s="192"/>
+      <c r="B11" s="192"/>
+      <c r="C11" s="192"/>
+      <c r="D11" s="192"/>
+      <c r="E11" s="139"/>
+      <c r="F11" s="139"/>
+      <c r="G11" s="139"/>
+      <c r="H11" s="139"/>
+      <c r="I11" s="139"/>
+      <c r="J11" s="139"/>
+      <c r="K11" s="139"/>
+      <c r="L11" s="139"/>
+      <c r="M11" s="139"/>
+      <c r="N11" s="139"/>
+      <c r="O11" s="139"/>
+      <c r="P11" s="139"/>
+      <c r="Q11" s="139"/>
+      <c r="R11" s="139"/>
+      <c r="S11" s="139"/>
+      <c r="T11" s="139"/>
+      <c r="U11" s="139"/>
+      <c r="V11" s="139"/>
+      <c r="W11" s="139"/>
+      <c r="X11" s="139"/>
+      <c r="Y11" s="139"/>
+      <c r="Z11" s="139"/>
+      <c r="AA11" s="139"/>
+      <c r="AB11" s="139"/>
+      <c r="AC11" s="139"/>
+      <c r="AD11" s="139"/>
+      <c r="AE11" s="139"/>
+      <c r="AF11" s="139"/>
+      <c r="AG11" s="139"/>
+      <c r="AH11" s="139"/>
+      <c r="AI11" s="139"/>
+      <c r="AJ11" s="139"/>
+      <c r="AK11" s="139"/>
+      <c r="AL11" s="139"/>
     </row>
     <row r="12" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
@@ -17514,32 +17646,32 @@
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
-      <c r="M1" s="125"/>
-      <c r="N1" s="125"/>
-      <c r="O1" s="125"/>
-      <c r="P1" s="125"/>
-      <c r="Q1" s="125"/>
-      <c r="R1" s="125"/>
-      <c r="S1" s="125"/>
-      <c r="T1" s="125"/>
-      <c r="U1" s="125"/>
-      <c r="V1" s="125"/>
-      <c r="W1" s="125"/>
-      <c r="X1" s="125"/>
-      <c r="Y1" s="125"/>
-      <c r="Z1" s="125"/>
-      <c r="AA1" s="125"/>
-      <c r="AB1" s="125"/>
-      <c r="AC1" s="125"/>
-      <c r="AD1" s="125"/>
-      <c r="AE1" s="125"/>
-      <c r="AF1" s="125"/>
-      <c r="AG1" s="125"/>
-      <c r="AH1" s="125"/>
-      <c r="AI1" s="125"/>
-      <c r="AJ1" s="125"/>
-      <c r="AK1" s="125"/>
-      <c r="AL1" s="125"/>
+      <c r="M1" s="127"/>
+      <c r="N1" s="127"/>
+      <c r="O1" s="127"/>
+      <c r="P1" s="127"/>
+      <c r="Q1" s="127"/>
+      <c r="R1" s="127"/>
+      <c r="S1" s="127"/>
+      <c r="T1" s="127"/>
+      <c r="U1" s="127"/>
+      <c r="V1" s="127"/>
+      <c r="W1" s="127"/>
+      <c r="X1" s="127"/>
+      <c r="Y1" s="127"/>
+      <c r="Z1" s="127"/>
+      <c r="AA1" s="127"/>
+      <c r="AB1" s="127"/>
+      <c r="AC1" s="127"/>
+      <c r="AD1" s="127"/>
+      <c r="AE1" s="127"/>
+      <c r="AF1" s="127"/>
+      <c r="AG1" s="127"/>
+      <c r="AH1" s="127"/>
+      <c r="AI1" s="127"/>
+      <c r="AJ1" s="127"/>
+      <c r="AK1" s="127"/>
+      <c r="AL1" s="127"/>
     </row>
     <row r="2" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
@@ -17575,21 +17707,21 @@
       <c r="AF2" s="1"/>
     </row>
     <row r="3" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="126"/>
-      <c r="B3" s="126"/>
-      <c r="C3" s="126"/>
-      <c r="D3" s="126"/>
-      <c r="E3" s="126"/>
-      <c r="F3" s="126"/>
-      <c r="G3" s="126"/>
-      <c r="H3" s="126"/>
-      <c r="I3" s="126"/>
-      <c r="J3" s="126"/>
-      <c r="K3" s="126"/>
-      <c r="L3" s="126"/>
-      <c r="M3" s="126"/>
-      <c r="N3" s="126"/>
-      <c r="O3" s="126"/>
+      <c r="A3" s="128"/>
+      <c r="B3" s="128"/>
+      <c r="C3" s="128"/>
+      <c r="D3" s="128"/>
+      <c r="E3" s="128"/>
+      <c r="F3" s="128"/>
+      <c r="G3" s="128"/>
+      <c r="H3" s="128"/>
+      <c r="I3" s="128"/>
+      <c r="J3" s="128"/>
+      <c r="K3" s="128"/>
+      <c r="L3" s="128"/>
+      <c r="M3" s="128"/>
+      <c r="N3" s="128"/>
+      <c r="O3" s="128"/>
       <c r="P3" s="1"/>
       <c r="Q3" s="1"/>
       <c r="R3" s="1"/>
@@ -17727,352 +17859,352 @@
       <c r="AL6" s="13"/>
     </row>
     <row r="7" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="162" t="s">
+      <c r="A7" s="164" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="162"/>
-      <c r="C7" s="162"/>
-      <c r="D7" s="162"/>
-      <c r="E7" s="162"/>
-      <c r="F7" s="162"/>
-      <c r="G7" s="162"/>
-      <c r="H7" s="162"/>
-      <c r="I7" s="162"/>
-      <c r="J7" s="162"/>
-      <c r="K7" s="162"/>
-      <c r="L7" s="162"/>
-      <c r="M7" s="162"/>
-      <c r="N7" s="162"/>
-      <c r="O7" s="162"/>
-      <c r="P7" s="162" t="s">
+      <c r="B7" s="164"/>
+      <c r="C7" s="164"/>
+      <c r="D7" s="164"/>
+      <c r="E7" s="164"/>
+      <c r="F7" s="164"/>
+      <c r="G7" s="164"/>
+      <c r="H7" s="164"/>
+      <c r="I7" s="164"/>
+      <c r="J7" s="164"/>
+      <c r="K7" s="164"/>
+      <c r="L7" s="164"/>
+      <c r="M7" s="164"/>
+      <c r="N7" s="164"/>
+      <c r="O7" s="164"/>
+      <c r="P7" s="164" t="s">
         <v>18</v>
       </c>
-      <c r="Q7" s="162"/>
-      <c r="R7" s="162"/>
-      <c r="S7" s="162"/>
-      <c r="T7" s="162"/>
-      <c r="U7" s="162"/>
-      <c r="V7" s="162"/>
-      <c r="W7" s="162"/>
-      <c r="X7" s="162"/>
-      <c r="Y7" s="162"/>
-      <c r="Z7" s="162"/>
-      <c r="AA7" s="162"/>
-      <c r="AB7" s="162"/>
-      <c r="AC7" s="162"/>
-      <c r="AD7" s="162"/>
-      <c r="AE7" s="162"/>
-      <c r="AF7" s="162"/>
-      <c r="AG7" s="162"/>
-      <c r="AH7" s="162"/>
-      <c r="AI7" s="162"/>
-      <c r="AJ7" s="162" t="s">
+      <c r="Q7" s="164"/>
+      <c r="R7" s="164"/>
+      <c r="S7" s="164"/>
+      <c r="T7" s="164"/>
+      <c r="U7" s="164"/>
+      <c r="V7" s="164"/>
+      <c r="W7" s="164"/>
+      <c r="X7" s="164"/>
+      <c r="Y7" s="164"/>
+      <c r="Z7" s="164"/>
+      <c r="AA7" s="164"/>
+      <c r="AB7" s="164"/>
+      <c r="AC7" s="164"/>
+      <c r="AD7" s="164"/>
+      <c r="AE7" s="164"/>
+      <c r="AF7" s="164"/>
+      <c r="AG7" s="164"/>
+      <c r="AH7" s="164"/>
+      <c r="AI7" s="164"/>
+      <c r="AJ7" s="164" t="s">
         <v>19</v>
       </c>
-      <c r="AK7" s="162"/>
-      <c r="AL7" s="162"/>
+      <c r="AK7" s="164"/>
+      <c r="AL7" s="164"/>
     </row>
     <row r="8" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="162"/>
-      <c r="B8" s="162"/>
-      <c r="C8" s="162"/>
-      <c r="D8" s="162"/>
-      <c r="E8" s="162"/>
-      <c r="F8" s="162"/>
-      <c r="G8" s="162"/>
-      <c r="H8" s="162"/>
-      <c r="I8" s="162"/>
-      <c r="J8" s="162"/>
-      <c r="K8" s="162"/>
-      <c r="L8" s="162"/>
-      <c r="M8" s="162"/>
-      <c r="N8" s="162"/>
-      <c r="O8" s="162"/>
-      <c r="P8" s="162" t="s">
+      <c r="A8" s="164"/>
+      <c r="B8" s="164"/>
+      <c r="C8" s="164"/>
+      <c r="D8" s="164"/>
+      <c r="E8" s="164"/>
+      <c r="F8" s="164"/>
+      <c r="G8" s="164"/>
+      <c r="H8" s="164"/>
+      <c r="I8" s="164"/>
+      <c r="J8" s="164"/>
+      <c r="K8" s="164"/>
+      <c r="L8" s="164"/>
+      <c r="M8" s="164"/>
+      <c r="N8" s="164"/>
+      <c r="O8" s="164"/>
+      <c r="P8" s="164" t="s">
         <v>73</v>
       </c>
-      <c r="Q8" s="162"/>
-      <c r="R8" s="162"/>
-      <c r="S8" s="162"/>
-      <c r="T8" s="162" t="s">
+      <c r="Q8" s="164"/>
+      <c r="R8" s="164"/>
+      <c r="S8" s="164"/>
+      <c r="T8" s="164" t="s">
         <v>29</v>
       </c>
-      <c r="U8" s="162"/>
-      <c r="V8" s="162"/>
-      <c r="W8" s="162"/>
-      <c r="X8" s="162" t="s">
+      <c r="U8" s="164"/>
+      <c r="V8" s="164"/>
+      <c r="W8" s="164"/>
+      <c r="X8" s="164" t="s">
         <v>30</v>
       </c>
-      <c r="Y8" s="162"/>
-      <c r="Z8" s="162"/>
-      <c r="AA8" s="162"/>
-      <c r="AB8" s="162" t="s">
+      <c r="Y8" s="164"/>
+      <c r="Z8" s="164"/>
+      <c r="AA8" s="164"/>
+      <c r="AB8" s="164" t="s">
         <v>31</v>
       </c>
-      <c r="AC8" s="162"/>
-      <c r="AD8" s="162"/>
-      <c r="AE8" s="162"/>
-      <c r="AF8" s="162" t="s">
+      <c r="AC8" s="164"/>
+      <c r="AD8" s="164"/>
+      <c r="AE8" s="164"/>
+      <c r="AF8" s="164" t="s">
         <v>32</v>
       </c>
-      <c r="AG8" s="162"/>
-      <c r="AH8" s="162"/>
-      <c r="AI8" s="162"/>
-      <c r="AJ8" s="162"/>
-      <c r="AK8" s="162"/>
-      <c r="AL8" s="162"/>
+      <c r="AG8" s="164"/>
+      <c r="AH8" s="164"/>
+      <c r="AI8" s="164"/>
+      <c r="AJ8" s="164"/>
+      <c r="AK8" s="164"/>
+      <c r="AL8" s="164"/>
     </row>
     <row r="9" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="122"/>
-      <c r="B9" s="122"/>
-      <c r="C9" s="122"/>
-      <c r="D9" s="122"/>
-      <c r="E9" s="122"/>
-      <c r="F9" s="162" t="s">
+      <c r="A9" s="124"/>
+      <c r="B9" s="124"/>
+      <c r="C9" s="124"/>
+      <c r="D9" s="124"/>
+      <c r="E9" s="124"/>
+      <c r="F9" s="164" t="s">
         <v>74</v>
       </c>
-      <c r="G9" s="162"/>
-      <c r="H9" s="162"/>
-      <c r="I9" s="162"/>
-      <c r="J9" s="162"/>
-      <c r="K9" s="162"/>
-      <c r="L9" s="162"/>
-      <c r="M9" s="162"/>
-      <c r="N9" s="162"/>
-      <c r="O9" s="162"/>
-      <c r="P9" s="162"/>
-      <c r="Q9" s="162"/>
-      <c r="R9" s="162"/>
-      <c r="S9" s="162"/>
-      <c r="T9" s="162"/>
-      <c r="U9" s="162"/>
-      <c r="V9" s="162"/>
-      <c r="W9" s="162"/>
-      <c r="X9" s="162"/>
-      <c r="Y9" s="162"/>
-      <c r="Z9" s="162"/>
-      <c r="AA9" s="162"/>
-      <c r="AB9" s="162"/>
-      <c r="AC9" s="162"/>
-      <c r="AD9" s="162"/>
-      <c r="AE9" s="162"/>
-      <c r="AF9" s="162"/>
-      <c r="AG9" s="162"/>
-      <c r="AH9" s="162"/>
-      <c r="AI9" s="162"/>
-      <c r="AJ9" s="162"/>
-      <c r="AK9" s="162"/>
-      <c r="AL9" s="162"/>
+      <c r="G9" s="164"/>
+      <c r="H9" s="164"/>
+      <c r="I9" s="164"/>
+      <c r="J9" s="164"/>
+      <c r="K9" s="164"/>
+      <c r="L9" s="164"/>
+      <c r="M9" s="164"/>
+      <c r="N9" s="164"/>
+      <c r="O9" s="164"/>
+      <c r="P9" s="164"/>
+      <c r="Q9" s="164"/>
+      <c r="R9" s="164"/>
+      <c r="S9" s="164"/>
+      <c r="T9" s="164"/>
+      <c r="U9" s="164"/>
+      <c r="V9" s="164"/>
+      <c r="W9" s="164"/>
+      <c r="X9" s="164"/>
+      <c r="Y9" s="164"/>
+      <c r="Z9" s="164"/>
+      <c r="AA9" s="164"/>
+      <c r="AB9" s="164"/>
+      <c r="AC9" s="164"/>
+      <c r="AD9" s="164"/>
+      <c r="AE9" s="164"/>
+      <c r="AF9" s="164"/>
+      <c r="AG9" s="164"/>
+      <c r="AH9" s="164"/>
+      <c r="AI9" s="164"/>
+      <c r="AJ9" s="164"/>
+      <c r="AK9" s="164"/>
+      <c r="AL9" s="164"/>
     </row>
     <row r="10" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="122"/>
-      <c r="B10" s="122"/>
-      <c r="C10" s="122"/>
-      <c r="D10" s="122"/>
-      <c r="E10" s="122"/>
-      <c r="F10" s="162" t="s">
+      <c r="A10" s="124"/>
+      <c r="B10" s="124"/>
+      <c r="C10" s="124"/>
+      <c r="D10" s="124"/>
+      <c r="E10" s="124"/>
+      <c r="F10" s="164" t="s">
         <v>75</v>
       </c>
-      <c r="G10" s="162"/>
-      <c r="H10" s="162"/>
-      <c r="I10" s="162"/>
-      <c r="J10" s="162"/>
-      <c r="K10" s="162"/>
-      <c r="L10" s="162"/>
-      <c r="M10" s="162"/>
-      <c r="N10" s="162"/>
-      <c r="O10" s="162"/>
-      <c r="P10" s="162"/>
-      <c r="Q10" s="162"/>
-      <c r="R10" s="162"/>
-      <c r="S10" s="162"/>
-      <c r="T10" s="162"/>
-      <c r="U10" s="162"/>
-      <c r="V10" s="162"/>
-      <c r="W10" s="162"/>
-      <c r="X10" s="162"/>
-      <c r="Y10" s="162"/>
-      <c r="Z10" s="162"/>
-      <c r="AA10" s="162"/>
-      <c r="AB10" s="162"/>
-      <c r="AC10" s="162"/>
-      <c r="AD10" s="162"/>
-      <c r="AE10" s="162"/>
-      <c r="AF10" s="162"/>
-      <c r="AG10" s="162"/>
-      <c r="AH10" s="162"/>
-      <c r="AI10" s="162"/>
-      <c r="AJ10" s="162"/>
-      <c r="AK10" s="162"/>
-      <c r="AL10" s="162"/>
+      <c r="G10" s="164"/>
+      <c r="H10" s="164"/>
+      <c r="I10" s="164"/>
+      <c r="J10" s="164"/>
+      <c r="K10" s="164"/>
+      <c r="L10" s="164"/>
+      <c r="M10" s="164"/>
+      <c r="N10" s="164"/>
+      <c r="O10" s="164"/>
+      <c r="P10" s="164"/>
+      <c r="Q10" s="164"/>
+      <c r="R10" s="164"/>
+      <c r="S10" s="164"/>
+      <c r="T10" s="164"/>
+      <c r="U10" s="164"/>
+      <c r="V10" s="164"/>
+      <c r="W10" s="164"/>
+      <c r="X10" s="164"/>
+      <c r="Y10" s="164"/>
+      <c r="Z10" s="164"/>
+      <c r="AA10" s="164"/>
+      <c r="AB10" s="164"/>
+      <c r="AC10" s="164"/>
+      <c r="AD10" s="164"/>
+      <c r="AE10" s="164"/>
+      <c r="AF10" s="164"/>
+      <c r="AG10" s="164"/>
+      <c r="AH10" s="164"/>
+      <c r="AI10" s="164"/>
+      <c r="AJ10" s="164"/>
+      <c r="AK10" s="164"/>
+      <c r="AL10" s="164"/>
     </row>
     <row r="11" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="122"/>
-      <c r="B11" s="122"/>
-      <c r="C11" s="122"/>
-      <c r="D11" s="122"/>
-      <c r="E11" s="122"/>
-      <c r="F11" s="162" t="s">
+      <c r="A11" s="124"/>
+      <c r="B11" s="124"/>
+      <c r="C11" s="124"/>
+      <c r="D11" s="124"/>
+      <c r="E11" s="124"/>
+      <c r="F11" s="164" t="s">
         <v>74</v>
       </c>
-      <c r="G11" s="162"/>
-      <c r="H11" s="162"/>
-      <c r="I11" s="162"/>
-      <c r="J11" s="162"/>
-      <c r="K11" s="162"/>
-      <c r="L11" s="162"/>
-      <c r="M11" s="162"/>
-      <c r="N11" s="162"/>
-      <c r="O11" s="162"/>
-      <c r="P11" s="162"/>
-      <c r="Q11" s="162"/>
-      <c r="R11" s="162"/>
-      <c r="S11" s="162"/>
-      <c r="T11" s="162"/>
-      <c r="U11" s="162"/>
-      <c r="V11" s="162"/>
-      <c r="W11" s="162"/>
-      <c r="X11" s="162"/>
-      <c r="Y11" s="162"/>
-      <c r="Z11" s="162"/>
-      <c r="AA11" s="162"/>
-      <c r="AB11" s="162"/>
-      <c r="AC11" s="162"/>
-      <c r="AD11" s="162"/>
-      <c r="AE11" s="162"/>
-      <c r="AF11" s="162"/>
-      <c r="AG11" s="162"/>
-      <c r="AH11" s="162"/>
-      <c r="AI11" s="162"/>
-      <c r="AJ11" s="162"/>
-      <c r="AK11" s="162"/>
-      <c r="AL11" s="162"/>
+      <c r="G11" s="164"/>
+      <c r="H11" s="164"/>
+      <c r="I11" s="164"/>
+      <c r="J11" s="164"/>
+      <c r="K11" s="164"/>
+      <c r="L11" s="164"/>
+      <c r="M11" s="164"/>
+      <c r="N11" s="164"/>
+      <c r="O11" s="164"/>
+      <c r="P11" s="164"/>
+      <c r="Q11" s="164"/>
+      <c r="R11" s="164"/>
+      <c r="S11" s="164"/>
+      <c r="T11" s="164"/>
+      <c r="U11" s="164"/>
+      <c r="V11" s="164"/>
+      <c r="W11" s="164"/>
+      <c r="X11" s="164"/>
+      <c r="Y11" s="164"/>
+      <c r="Z11" s="164"/>
+      <c r="AA11" s="164"/>
+      <c r="AB11" s="164"/>
+      <c r="AC11" s="164"/>
+      <c r="AD11" s="164"/>
+      <c r="AE11" s="164"/>
+      <c r="AF11" s="164"/>
+      <c r="AG11" s="164"/>
+      <c r="AH11" s="164"/>
+      <c r="AI11" s="164"/>
+      <c r="AJ11" s="164"/>
+      <c r="AK11" s="164"/>
+      <c r="AL11" s="164"/>
     </row>
     <row r="12" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="122"/>
-      <c r="B12" s="122"/>
-      <c r="C12" s="122"/>
-      <c r="D12" s="122"/>
-      <c r="E12" s="122"/>
-      <c r="F12" s="162" t="s">
+      <c r="A12" s="124"/>
+      <c r="B12" s="124"/>
+      <c r="C12" s="124"/>
+      <c r="D12" s="124"/>
+      <c r="E12" s="124"/>
+      <c r="F12" s="164" t="s">
         <v>75</v>
       </c>
-      <c r="G12" s="162"/>
-      <c r="H12" s="162"/>
-      <c r="I12" s="162"/>
-      <c r="J12" s="162"/>
-      <c r="K12" s="162"/>
-      <c r="L12" s="162"/>
-      <c r="M12" s="162"/>
-      <c r="N12" s="162"/>
-      <c r="O12" s="162"/>
-      <c r="P12" s="162"/>
-      <c r="Q12" s="162"/>
-      <c r="R12" s="162"/>
-      <c r="S12" s="162"/>
-      <c r="T12" s="162"/>
-      <c r="U12" s="162"/>
-      <c r="V12" s="162"/>
-      <c r="W12" s="162"/>
-      <c r="X12" s="162"/>
-      <c r="Y12" s="162"/>
-      <c r="Z12" s="162"/>
-      <c r="AA12" s="162"/>
-      <c r="AB12" s="162"/>
-      <c r="AC12" s="162"/>
-      <c r="AD12" s="162"/>
-      <c r="AE12" s="162"/>
-      <c r="AF12" s="162"/>
-      <c r="AG12" s="162"/>
-      <c r="AH12" s="162"/>
-      <c r="AI12" s="162"/>
-      <c r="AJ12" s="162"/>
-      <c r="AK12" s="162"/>
-      <c r="AL12" s="162"/>
+      <c r="G12" s="164"/>
+      <c r="H12" s="164"/>
+      <c r="I12" s="164"/>
+      <c r="J12" s="164"/>
+      <c r="K12" s="164"/>
+      <c r="L12" s="164"/>
+      <c r="M12" s="164"/>
+      <c r="N12" s="164"/>
+      <c r="O12" s="164"/>
+      <c r="P12" s="164"/>
+      <c r="Q12" s="164"/>
+      <c r="R12" s="164"/>
+      <c r="S12" s="164"/>
+      <c r="T12" s="164"/>
+      <c r="U12" s="164"/>
+      <c r="V12" s="164"/>
+      <c r="W12" s="164"/>
+      <c r="X12" s="164"/>
+      <c r="Y12" s="164"/>
+      <c r="Z12" s="164"/>
+      <c r="AA12" s="164"/>
+      <c r="AB12" s="164"/>
+      <c r="AC12" s="164"/>
+      <c r="AD12" s="164"/>
+      <c r="AE12" s="164"/>
+      <c r="AF12" s="164"/>
+      <c r="AG12" s="164"/>
+      <c r="AH12" s="164"/>
+      <c r="AI12" s="164"/>
+      <c r="AJ12" s="164"/>
+      <c r="AK12" s="164"/>
+      <c r="AL12" s="164"/>
     </row>
     <row r="13" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="122"/>
-      <c r="B13" s="122"/>
-      <c r="C13" s="122"/>
-      <c r="D13" s="122"/>
-      <c r="E13" s="122"/>
-      <c r="F13" s="162" t="s">
+      <c r="A13" s="124"/>
+      <c r="B13" s="124"/>
+      <c r="C13" s="124"/>
+      <c r="D13" s="124"/>
+      <c r="E13" s="124"/>
+      <c r="F13" s="164" t="s">
         <v>74</v>
       </c>
-      <c r="G13" s="162"/>
-      <c r="H13" s="162"/>
-      <c r="I13" s="162"/>
-      <c r="J13" s="162"/>
-      <c r="K13" s="162"/>
-      <c r="L13" s="162"/>
-      <c r="M13" s="162"/>
-      <c r="N13" s="162"/>
-      <c r="O13" s="162"/>
-      <c r="P13" s="162"/>
-      <c r="Q13" s="162"/>
-      <c r="R13" s="162"/>
-      <c r="S13" s="162"/>
-      <c r="T13" s="162"/>
-      <c r="U13" s="162"/>
-      <c r="V13" s="162"/>
-      <c r="W13" s="162"/>
-      <c r="X13" s="162"/>
-      <c r="Y13" s="162"/>
-      <c r="Z13" s="162"/>
-      <c r="AA13" s="162"/>
-      <c r="AB13" s="162"/>
-      <c r="AC13" s="162"/>
-      <c r="AD13" s="162"/>
-      <c r="AE13" s="162"/>
-      <c r="AF13" s="162"/>
-      <c r="AG13" s="162"/>
-      <c r="AH13" s="162"/>
-      <c r="AI13" s="162"/>
-      <c r="AJ13" s="162"/>
-      <c r="AK13" s="162"/>
-      <c r="AL13" s="162"/>
+      <c r="G13" s="164"/>
+      <c r="H13" s="164"/>
+      <c r="I13" s="164"/>
+      <c r="J13" s="164"/>
+      <c r="K13" s="164"/>
+      <c r="L13" s="164"/>
+      <c r="M13" s="164"/>
+      <c r="N13" s="164"/>
+      <c r="O13" s="164"/>
+      <c r="P13" s="164"/>
+      <c r="Q13" s="164"/>
+      <c r="R13" s="164"/>
+      <c r="S13" s="164"/>
+      <c r="T13" s="164"/>
+      <c r="U13" s="164"/>
+      <c r="V13" s="164"/>
+      <c r="W13" s="164"/>
+      <c r="X13" s="164"/>
+      <c r="Y13" s="164"/>
+      <c r="Z13" s="164"/>
+      <c r="AA13" s="164"/>
+      <c r="AB13" s="164"/>
+      <c r="AC13" s="164"/>
+      <c r="AD13" s="164"/>
+      <c r="AE13" s="164"/>
+      <c r="AF13" s="164"/>
+      <c r="AG13" s="164"/>
+      <c r="AH13" s="164"/>
+      <c r="AI13" s="164"/>
+      <c r="AJ13" s="164"/>
+      <c r="AK13" s="164"/>
+      <c r="AL13" s="164"/>
     </row>
     <row r="14" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="122"/>
-      <c r="B14" s="122"/>
-      <c r="C14" s="122"/>
-      <c r="D14" s="122"/>
-      <c r="E14" s="122"/>
-      <c r="F14" s="162" t="s">
+      <c r="A14" s="124"/>
+      <c r="B14" s="124"/>
+      <c r="C14" s="124"/>
+      <c r="D14" s="124"/>
+      <c r="E14" s="124"/>
+      <c r="F14" s="164" t="s">
         <v>75</v>
       </c>
-      <c r="G14" s="162"/>
-      <c r="H14" s="162"/>
-      <c r="I14" s="162"/>
-      <c r="J14" s="162"/>
-      <c r="K14" s="162"/>
-      <c r="L14" s="162"/>
-      <c r="M14" s="162"/>
-      <c r="N14" s="162"/>
-      <c r="O14" s="162"/>
-      <c r="P14" s="162"/>
-      <c r="Q14" s="162"/>
-      <c r="R14" s="162"/>
-      <c r="S14" s="162"/>
-      <c r="T14" s="162"/>
-      <c r="U14" s="162"/>
-      <c r="V14" s="162"/>
-      <c r="W14" s="162"/>
-      <c r="X14" s="162"/>
-      <c r="Y14" s="162"/>
-      <c r="Z14" s="162"/>
-      <c r="AA14" s="162"/>
-      <c r="AB14" s="162"/>
-      <c r="AC14" s="162"/>
-      <c r="AD14" s="162"/>
-      <c r="AE14" s="162"/>
-      <c r="AF14" s="162"/>
-      <c r="AG14" s="162"/>
-      <c r="AH14" s="162"/>
-      <c r="AI14" s="162"/>
-      <c r="AJ14" s="162"/>
-      <c r="AK14" s="162"/>
-      <c r="AL14" s="162"/>
+      <c r="G14" s="164"/>
+      <c r="H14" s="164"/>
+      <c r="I14" s="164"/>
+      <c r="J14" s="164"/>
+      <c r="K14" s="164"/>
+      <c r="L14" s="164"/>
+      <c r="M14" s="164"/>
+      <c r="N14" s="164"/>
+      <c r="O14" s="164"/>
+      <c r="P14" s="164"/>
+      <c r="Q14" s="164"/>
+      <c r="R14" s="164"/>
+      <c r="S14" s="164"/>
+      <c r="T14" s="164"/>
+      <c r="U14" s="164"/>
+      <c r="V14" s="164"/>
+      <c r="W14" s="164"/>
+      <c r="X14" s="164"/>
+      <c r="Y14" s="164"/>
+      <c r="Z14" s="164"/>
+      <c r="AA14" s="164"/>
+      <c r="AB14" s="164"/>
+      <c r="AC14" s="164"/>
+      <c r="AD14" s="164"/>
+      <c r="AE14" s="164"/>
+      <c r="AF14" s="164"/>
+      <c r="AG14" s="164"/>
+      <c r="AH14" s="164"/>
+      <c r="AI14" s="164"/>
+      <c r="AJ14" s="164"/>
+      <c r="AK14" s="164"/>
+      <c r="AL14" s="164"/>
     </row>
     <row r="15" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="39" t="s">

--- a/wwwroot/ExcelModel/Jako_PHY_sheet.xlsx
+++ b/wwwroot/ExcelModel/Jako_PHY_sheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\source\NX-lims Softlines Command System\wwwroot\ExcelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F7F7BA9-4AC9-4187-ABBF-61936586AEED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB544363-23E5-42FF-BB88-50BF2AD97844}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Weight" sheetId="3" r:id="rId1"/>
@@ -31,7 +31,7 @@
     <definedName name="ReportNumber" localSheetId="10">'Hydroatatic Test'!$M$1</definedName>
     <definedName name="ReportNumber" localSheetId="1">'Pilling Resistance'!$M$1</definedName>
     <definedName name="ReportNumber" localSheetId="6">'Seam Bursting-G'!$M$1</definedName>
-    <definedName name="ReportNumber" localSheetId="5">'Seam Slippage&amp;Breakage-G'!#REF!</definedName>
+    <definedName name="ReportNumber" localSheetId="5">'Seam Slippage&amp;Breakage-G'!$M$1</definedName>
     <definedName name="ReportNumber" localSheetId="4">'Seam Slippage&amp;Tensile'!$M$1</definedName>
     <definedName name="ReportNumber" localSheetId="2">'Stretch&amp;Recovery of Elastic'!$M$1</definedName>
     <definedName name="ReportNumber" localSheetId="8">'Tear Strength'!$M$1</definedName>
@@ -1205,7 +1205,7 @@
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="58" x14ac:knownFonts="1">
+  <fonts count="59" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1650,6 +1650,15 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -2324,9 +2333,6 @@
     <xf numFmtId="0" fontId="38" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -2458,6 +2464,9 @@
     </xf>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -3652,56 +3661,56 @@
       <c r="AL5"/>
     </row>
     <row r="6" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A6" s="211" t="s">
+      <c r="A6" s="210" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="212"/>
-      <c r="C6" s="212"/>
-      <c r="D6" s="212"/>
-      <c r="E6" s="212"/>
-      <c r="F6" s="213"/>
-      <c r="G6" s="217" t="s">
+      <c r="B6" s="211"/>
+      <c r="C6" s="211"/>
+      <c r="D6" s="211"/>
+      <c r="E6" s="211"/>
+      <c r="F6" s="212"/>
+      <c r="G6" s="216" t="s">
         <v>118</v>
       </c>
-      <c r="H6" s="218"/>
-      <c r="I6" s="218"/>
-      <c r="J6" s="218"/>
-      <c r="K6" s="218"/>
-      <c r="L6" s="218"/>
-      <c r="M6" s="218"/>
-      <c r="N6" s="218"/>
-      <c r="O6" s="218"/>
-      <c r="P6" s="218"/>
-      <c r="Q6" s="218"/>
-      <c r="R6" s="218"/>
-      <c r="S6" s="218"/>
-      <c r="T6" s="218"/>
-      <c r="U6" s="218"/>
-      <c r="V6" s="218"/>
-      <c r="W6" s="218"/>
-      <c r="X6" s="218"/>
-      <c r="Y6" s="218"/>
-      <c r="Z6" s="218"/>
-      <c r="AA6" s="218"/>
-      <c r="AB6" s="218"/>
-      <c r="AC6" s="218"/>
-      <c r="AD6" s="218"/>
-      <c r="AE6" s="218"/>
-      <c r="AF6" s="218"/>
-      <c r="AG6" s="218"/>
-      <c r="AH6" s="218"/>
-      <c r="AI6" s="218"/>
-      <c r="AJ6" s="218"/>
-      <c r="AK6" s="218"/>
-      <c r="AL6" s="219"/>
+      <c r="H6" s="217"/>
+      <c r="I6" s="217"/>
+      <c r="J6" s="217"/>
+      <c r="K6" s="217"/>
+      <c r="L6" s="217"/>
+      <c r="M6" s="217"/>
+      <c r="N6" s="217"/>
+      <c r="O6" s="217"/>
+      <c r="P6" s="217"/>
+      <c r="Q6" s="217"/>
+      <c r="R6" s="217"/>
+      <c r="S6" s="217"/>
+      <c r="T6" s="217"/>
+      <c r="U6" s="217"/>
+      <c r="V6" s="217"/>
+      <c r="W6" s="217"/>
+      <c r="X6" s="217"/>
+      <c r="Y6" s="217"/>
+      <c r="Z6" s="217"/>
+      <c r="AA6" s="217"/>
+      <c r="AB6" s="217"/>
+      <c r="AC6" s="217"/>
+      <c r="AD6" s="217"/>
+      <c r="AE6" s="217"/>
+      <c r="AF6" s="217"/>
+      <c r="AG6" s="217"/>
+      <c r="AH6" s="217"/>
+      <c r="AI6" s="217"/>
+      <c r="AJ6" s="217"/>
+      <c r="AK6" s="217"/>
+      <c r="AL6" s="218"/>
     </row>
     <row r="7" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A7" s="214"/>
-      <c r="B7" s="215"/>
-      <c r="C7" s="215"/>
-      <c r="D7" s="215"/>
-      <c r="E7" s="215"/>
-      <c r="F7" s="216"/>
+      <c r="A7" s="213"/>
+      <c r="B7" s="214"/>
+      <c r="C7" s="214"/>
+      <c r="D7" s="214"/>
+      <c r="E7" s="214"/>
+      <c r="F7" s="215"/>
       <c r="G7" s="122" t="s">
         <v>204</v>
       </c>
@@ -3742,12 +3751,12 @@
       <c r="AL7" s="126"/>
     </row>
     <row r="8" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A8" s="210"/>
-      <c r="B8" s="210"/>
-      <c r="C8" s="210"/>
-      <c r="D8" s="210"/>
-      <c r="E8" s="210"/>
-      <c r="F8" s="210"/>
+      <c r="A8" s="209"/>
+      <c r="B8" s="209"/>
+      <c r="C8" s="209"/>
+      <c r="D8" s="209"/>
+      <c r="E8" s="209"/>
+      <c r="F8" s="209"/>
       <c r="G8" s="126"/>
       <c r="H8" s="126"/>
       <c r="I8" s="126"/>
@@ -3782,12 +3791,12 @@
       <c r="AL8" s="126"/>
     </row>
     <row r="9" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A9" s="210"/>
-      <c r="B9" s="210"/>
-      <c r="C9" s="210"/>
-      <c r="D9" s="210"/>
-      <c r="E9" s="210"/>
-      <c r="F9" s="210"/>
+      <c r="A9" s="209"/>
+      <c r="B9" s="209"/>
+      <c r="C9" s="209"/>
+      <c r="D9" s="209"/>
+      <c r="E9" s="209"/>
+      <c r="F9" s="209"/>
       <c r="G9" s="126"/>
       <c r="H9" s="126"/>
       <c r="I9" s="126"/>
@@ -3822,12 +3831,12 @@
       <c r="AL9" s="126"/>
     </row>
     <row r="10" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="210"/>
-      <c r="B10" s="210"/>
-      <c r="C10" s="210"/>
-      <c r="D10" s="210"/>
-      <c r="E10" s="210"/>
-      <c r="F10" s="210"/>
+      <c r="A10" s="209"/>
+      <c r="B10" s="209"/>
+      <c r="C10" s="209"/>
+      <c r="D10" s="209"/>
+      <c r="E10" s="209"/>
+      <c r="F10" s="209"/>
       <c r="G10" s="126"/>
       <c r="H10" s="126"/>
       <c r="I10" s="126"/>
@@ -3904,56 +3913,56 @@
       <c r="AL11"/>
     </row>
     <row r="12" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="211" t="s">
+      <c r="A12" s="210" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="212"/>
-      <c r="C12" s="212"/>
-      <c r="D12" s="212"/>
-      <c r="E12" s="212"/>
-      <c r="F12" s="213"/>
-      <c r="G12" s="217" t="s">
+      <c r="B12" s="211"/>
+      <c r="C12" s="211"/>
+      <c r="D12" s="211"/>
+      <c r="E12" s="211"/>
+      <c r="F12" s="212"/>
+      <c r="G12" s="216" t="s">
         <v>118</v>
       </c>
-      <c r="H12" s="218"/>
-      <c r="I12" s="218"/>
-      <c r="J12" s="218"/>
-      <c r="K12" s="218"/>
-      <c r="L12" s="218"/>
-      <c r="M12" s="218"/>
-      <c r="N12" s="218"/>
-      <c r="O12" s="218"/>
-      <c r="P12" s="218"/>
-      <c r="Q12" s="218"/>
-      <c r="R12" s="218"/>
-      <c r="S12" s="218"/>
-      <c r="T12" s="218"/>
-      <c r="U12" s="218"/>
-      <c r="V12" s="218"/>
-      <c r="W12" s="218"/>
-      <c r="X12" s="218"/>
-      <c r="Y12" s="218"/>
-      <c r="Z12" s="218"/>
-      <c r="AA12" s="218"/>
-      <c r="AB12" s="218"/>
-      <c r="AC12" s="218"/>
-      <c r="AD12" s="218"/>
-      <c r="AE12" s="218"/>
-      <c r="AF12" s="218"/>
-      <c r="AG12" s="218"/>
-      <c r="AH12" s="218"/>
-      <c r="AI12" s="218"/>
-      <c r="AJ12" s="218"/>
-      <c r="AK12" s="218"/>
-      <c r="AL12" s="219"/>
+      <c r="H12" s="217"/>
+      <c r="I12" s="217"/>
+      <c r="J12" s="217"/>
+      <c r="K12" s="217"/>
+      <c r="L12" s="217"/>
+      <c r="M12" s="217"/>
+      <c r="N12" s="217"/>
+      <c r="O12" s="217"/>
+      <c r="P12" s="217"/>
+      <c r="Q12" s="217"/>
+      <c r="R12" s="217"/>
+      <c r="S12" s="217"/>
+      <c r="T12" s="217"/>
+      <c r="U12" s="217"/>
+      <c r="V12" s="217"/>
+      <c r="W12" s="217"/>
+      <c r="X12" s="217"/>
+      <c r="Y12" s="217"/>
+      <c r="Z12" s="217"/>
+      <c r="AA12" s="217"/>
+      <c r="AB12" s="217"/>
+      <c r="AC12" s="217"/>
+      <c r="AD12" s="217"/>
+      <c r="AE12" s="217"/>
+      <c r="AF12" s="217"/>
+      <c r="AG12" s="217"/>
+      <c r="AH12" s="217"/>
+      <c r="AI12" s="217"/>
+      <c r="AJ12" s="217"/>
+      <c r="AK12" s="217"/>
+      <c r="AL12" s="218"/>
     </row>
     <row r="13" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="214"/>
-      <c r="B13" s="215"/>
-      <c r="C13" s="215"/>
-      <c r="D13" s="215"/>
-      <c r="E13" s="215"/>
-      <c r="F13" s="216"/>
+      <c r="A13" s="213"/>
+      <c r="B13" s="214"/>
+      <c r="C13" s="214"/>
+      <c r="D13" s="214"/>
+      <c r="E13" s="214"/>
+      <c r="F13" s="215"/>
       <c r="G13" s="122" t="s">
         <v>204</v>
       </c>
@@ -3994,12 +4003,12 @@
       <c r="AL13" s="126"/>
     </row>
     <row r="14" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A14" s="210"/>
-      <c r="B14" s="210"/>
-      <c r="C14" s="210"/>
-      <c r="D14" s="210"/>
-      <c r="E14" s="210"/>
-      <c r="F14" s="210"/>
+      <c r="A14" s="209"/>
+      <c r="B14" s="209"/>
+      <c r="C14" s="209"/>
+      <c r="D14" s="209"/>
+      <c r="E14" s="209"/>
+      <c r="F14" s="209"/>
       <c r="G14" s="126"/>
       <c r="H14" s="126"/>
       <c r="I14" s="126"/>
@@ -4034,12 +4043,12 @@
       <c r="AL14" s="126"/>
     </row>
     <row r="15" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A15" s="210"/>
-      <c r="B15" s="210"/>
-      <c r="C15" s="210"/>
-      <c r="D15" s="210"/>
-      <c r="E15" s="210"/>
-      <c r="F15" s="210"/>
+      <c r="A15" s="209"/>
+      <c r="B15" s="209"/>
+      <c r="C15" s="209"/>
+      <c r="D15" s="209"/>
+      <c r="E15" s="209"/>
+      <c r="F15" s="209"/>
       <c r="G15" s="126"/>
       <c r="H15" s="126"/>
       <c r="I15" s="126"/>
@@ -4074,12 +4083,12 @@
       <c r="AL15" s="126"/>
     </row>
     <row r="16" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A16" s="210"/>
-      <c r="B16" s="210"/>
-      <c r="C16" s="210"/>
-      <c r="D16" s="210"/>
-      <c r="E16" s="210"/>
-      <c r="F16" s="210"/>
+      <c r="A16" s="209"/>
+      <c r="B16" s="209"/>
+      <c r="C16" s="209"/>
+      <c r="D16" s="209"/>
+      <c r="E16" s="209"/>
+      <c r="F16" s="209"/>
       <c r="G16" s="126"/>
       <c r="H16" s="126"/>
       <c r="I16" s="126"/>
@@ -4169,29 +4178,29 @@
       <c r="I19" s="72" t="s">
         <v>160</v>
       </c>
-      <c r="AJ19" s="208">
+      <c r="AJ19" s="207">
         <v>40</v>
       </c>
-      <c r="AK19" s="208"/>
-      <c r="AL19" s="208"/>
+      <c r="AK19" s="207"/>
+      <c r="AL19" s="207"/>
     </row>
     <row r="20" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A20" s="53" t="s">
         <v>161</v>
       </c>
-      <c r="P20" s="208" t="s">
+      <c r="P20" s="207" t="s">
         <v>162</v>
       </c>
-      <c r="Q20" s="208"/>
-      <c r="R20" s="208"/>
-      <c r="S20" s="208"/>
-      <c r="T20" s="208"/>
-      <c r="U20" s="208"/>
-      <c r="V20" s="208"/>
-      <c r="W20" s="208"/>
-      <c r="X20" s="208"/>
-      <c r="Y20" s="208"/>
-      <c r="Z20" s="208"/>
+      <c r="Q20" s="207"/>
+      <c r="R20" s="207"/>
+      <c r="S20" s="207"/>
+      <c r="T20" s="207"/>
+      <c r="U20" s="207"/>
+      <c r="V20" s="207"/>
+      <c r="W20" s="207"/>
+      <c r="X20" s="207"/>
+      <c r="Y20" s="207"/>
+      <c r="Z20" s="207"/>
       <c r="AA20" s="66" t="s">
         <v>163</v>
       </c>
@@ -4216,16 +4225,16 @@
       <c r="O21" s="57"/>
       <c r="P21" s="57"/>
       <c r="Q21" s="57"/>
-      <c r="S21" s="209" t="s">
+      <c r="S21" s="208" t="s">
         <v>222</v>
       </c>
-      <c r="T21" s="209"/>
-      <c r="U21" s="209"/>
-      <c r="V21" s="209"/>
-      <c r="W21" s="209"/>
-      <c r="X21" s="209"/>
-      <c r="Y21" s="209"/>
-      <c r="Z21" s="209"/>
+      <c r="T21" s="208"/>
+      <c r="U21" s="208"/>
+      <c r="V21" s="208"/>
+      <c r="W21" s="208"/>
+      <c r="X21" s="208"/>
+      <c r="Y21" s="208"/>
+      <c r="Z21" s="208"/>
       <c r="AA21" s="53" t="s">
         <v>165</v>
       </c>
@@ -5135,9 +5144,9 @@
       <c r="A7" s="55" t="s">
         <v>143</v>
       </c>
-      <c r="E7" s="225"/>
-      <c r="F7" s="225"/>
-      <c r="G7" s="225"/>
+      <c r="E7" s="224"/>
+      <c r="F7" s="224"/>
+      <c r="G7" s="224"/>
       <c r="H7" s="63" t="s">
         <v>144</v>
       </c>
@@ -5266,11 +5275,11 @@
       <c r="AL9" s="148"/>
     </row>
     <row r="10" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="220"/>
-      <c r="B10" s="221"/>
-      <c r="C10" s="221"/>
-      <c r="D10" s="221"/>
-      <c r="E10" s="222"/>
+      <c r="A10" s="219"/>
+      <c r="B10" s="220"/>
+      <c r="C10" s="220"/>
+      <c r="D10" s="220"/>
+      <c r="E10" s="221"/>
       <c r="F10" s="133" t="s">
         <v>148</v>
       </c>
@@ -5308,11 +5317,11 @@
       <c r="AL10" s="134"/>
     </row>
     <row r="11" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="223"/>
-      <c r="B11" s="192"/>
-      <c r="C11" s="192"/>
-      <c r="D11" s="192"/>
-      <c r="E11" s="224"/>
+      <c r="A11" s="222"/>
+      <c r="B11" s="191"/>
+      <c r="C11" s="191"/>
+      <c r="D11" s="191"/>
+      <c r="E11" s="223"/>
       <c r="F11" s="133" t="s">
         <v>149</v>
       </c>
@@ -5350,11 +5359,11 @@
       <c r="AL11" s="134"/>
     </row>
     <row r="12" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="220"/>
-      <c r="B12" s="221"/>
-      <c r="C12" s="221"/>
-      <c r="D12" s="221"/>
-      <c r="E12" s="222"/>
+      <c r="A12" s="219"/>
+      <c r="B12" s="220"/>
+      <c r="C12" s="220"/>
+      <c r="D12" s="220"/>
+      <c r="E12" s="221"/>
       <c r="F12" s="133" t="s">
         <v>148</v>
       </c>
@@ -5392,11 +5401,11 @@
       <c r="AL12" s="134"/>
     </row>
     <row r="13" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="223"/>
-      <c r="B13" s="192"/>
-      <c r="C13" s="192"/>
-      <c r="D13" s="192"/>
-      <c r="E13" s="224"/>
+      <c r="A13" s="222"/>
+      <c r="B13" s="191"/>
+      <c r="C13" s="191"/>
+      <c r="D13" s="191"/>
+      <c r="E13" s="223"/>
       <c r="F13" s="133" t="s">
         <v>149</v>
       </c>
@@ -13877,32 +13886,32 @@
       <c r="J1" s="85"/>
       <c r="K1" s="85"/>
       <c r="L1" s="85"/>
-      <c r="M1" s="192"/>
-      <c r="N1" s="192"/>
-      <c r="O1" s="192"/>
-      <c r="P1" s="192"/>
-      <c r="Q1" s="192"/>
-      <c r="R1" s="192"/>
-      <c r="S1" s="192"/>
-      <c r="T1" s="192"/>
-      <c r="U1" s="192"/>
-      <c r="V1" s="192"/>
-      <c r="W1" s="192"/>
-      <c r="X1" s="192"/>
-      <c r="Y1" s="192"/>
-      <c r="Z1" s="192"/>
-      <c r="AA1" s="192"/>
-      <c r="AB1" s="192"/>
-      <c r="AC1" s="192"/>
-      <c r="AD1" s="192"/>
-      <c r="AE1" s="192"/>
-      <c r="AF1" s="192"/>
-      <c r="AG1" s="192"/>
-      <c r="AH1" s="192"/>
-      <c r="AI1" s="192"/>
-      <c r="AJ1" s="192"/>
-      <c r="AK1" s="192"/>
-      <c r="AL1" s="192"/>
+      <c r="M1" s="191"/>
+      <c r="N1" s="191"/>
+      <c r="O1" s="191"/>
+      <c r="P1" s="191"/>
+      <c r="Q1" s="191"/>
+      <c r="R1" s="191"/>
+      <c r="S1" s="191"/>
+      <c r="T1" s="191"/>
+      <c r="U1" s="191"/>
+      <c r="V1" s="191"/>
+      <c r="W1" s="191"/>
+      <c r="X1" s="191"/>
+      <c r="Y1" s="191"/>
+      <c r="Z1" s="191"/>
+      <c r="AA1" s="191"/>
+      <c r="AB1" s="191"/>
+      <c r="AC1" s="191"/>
+      <c r="AD1" s="191"/>
+      <c r="AE1" s="191"/>
+      <c r="AF1" s="191"/>
+      <c r="AG1" s="191"/>
+      <c r="AH1" s="191"/>
+      <c r="AI1" s="191"/>
+      <c r="AJ1" s="191"/>
+      <c r="AK1" s="191"/>
+      <c r="AL1" s="191"/>
     </row>
     <row r="2" spans="1:38" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="86" t="s">
@@ -13947,96 +13956,96 @@
       <c r="AL2" s="89"/>
     </row>
     <row r="3" spans="1:38" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="187" t="s">
+      <c r="A3" s="186" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="187"/>
-      <c r="C3" s="188"/>
-      <c r="D3" s="189"/>
-      <c r="E3" s="189"/>
-      <c r="F3" s="189"/>
-      <c r="G3" s="189"/>
-      <c r="H3" s="189"/>
-      <c r="I3" s="190"/>
-      <c r="J3" s="191"/>
-      <c r="K3" s="191"/>
-      <c r="L3" s="191"/>
-      <c r="M3" s="191"/>
-      <c r="N3" s="191"/>
-      <c r="O3" s="191"/>
-      <c r="P3" s="191"/>
-      <c r="Q3" s="191"/>
-      <c r="R3" s="191"/>
-      <c r="S3" s="191"/>
-      <c r="T3" s="191"/>
-      <c r="U3" s="191"/>
-      <c r="V3" s="191"/>
-      <c r="W3" s="191"/>
-      <c r="X3" s="191"/>
-      <c r="Y3" s="191"/>
-      <c r="Z3" s="191"/>
-      <c r="AA3" s="191"/>
-      <c r="AB3" s="191"/>
-      <c r="AC3" s="191"/>
-      <c r="AD3" s="191"/>
-      <c r="AE3" s="191"/>
-      <c r="AF3" s="191"/>
-      <c r="AG3" s="191"/>
-      <c r="AH3" s="191"/>
-      <c r="AI3" s="191"/>
-      <c r="AJ3" s="191"/>
-      <c r="AK3" s="191"/>
-      <c r="AL3" s="191"/>
+      <c r="B3" s="186"/>
+      <c r="C3" s="187"/>
+      <c r="D3" s="188"/>
+      <c r="E3" s="188"/>
+      <c r="F3" s="188"/>
+      <c r="G3" s="188"/>
+      <c r="H3" s="188"/>
+      <c r="I3" s="189"/>
+      <c r="J3" s="190"/>
+      <c r="K3" s="190"/>
+      <c r="L3" s="190"/>
+      <c r="M3" s="190"/>
+      <c r="N3" s="190"/>
+      <c r="O3" s="190"/>
+      <c r="P3" s="190"/>
+      <c r="Q3" s="190"/>
+      <c r="R3" s="190"/>
+      <c r="S3" s="190"/>
+      <c r="T3" s="190"/>
+      <c r="U3" s="190"/>
+      <c r="V3" s="190"/>
+      <c r="W3" s="190"/>
+      <c r="X3" s="190"/>
+      <c r="Y3" s="190"/>
+      <c r="Z3" s="190"/>
+      <c r="AA3" s="190"/>
+      <c r="AB3" s="190"/>
+      <c r="AC3" s="190"/>
+      <c r="AD3" s="190"/>
+      <c r="AE3" s="190"/>
+      <c r="AF3" s="190"/>
+      <c r="AG3" s="190"/>
+      <c r="AH3" s="190"/>
+      <c r="AI3" s="190"/>
+      <c r="AJ3" s="190"/>
+      <c r="AK3" s="190"/>
+      <c r="AL3" s="190"/>
     </row>
     <row r="4" spans="1:38" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="186" t="s">
+      <c r="A4" s="185" t="s">
         <v>213</v>
       </c>
-      <c r="B4" s="184"/>
-      <c r="C4" s="184"/>
-      <c r="D4" s="184"/>
-      <c r="E4" s="184"/>
-      <c r="F4" s="184"/>
-      <c r="G4" s="184"/>
-      <c r="H4" s="184"/>
-      <c r="I4" s="185"/>
-      <c r="J4" s="182" t="s">
+      <c r="B4" s="183"/>
+      <c r="C4" s="183"/>
+      <c r="D4" s="183"/>
+      <c r="E4" s="183"/>
+      <c r="F4" s="183"/>
+      <c r="G4" s="183"/>
+      <c r="H4" s="183"/>
+      <c r="I4" s="184"/>
+      <c r="J4" s="181" t="s">
         <v>214</v>
       </c>
-      <c r="K4" s="183"/>
-      <c r="L4" s="183"/>
-      <c r="M4" s="183"/>
-      <c r="N4" s="183"/>
-      <c r="O4" s="183"/>
-      <c r="P4" s="183"/>
+      <c r="K4" s="182"/>
+      <c r="L4" s="182"/>
+      <c r="M4" s="182"/>
+      <c r="N4" s="182"/>
+      <c r="O4" s="182"/>
+      <c r="P4" s="182"/>
       <c r="Q4" s="91"/>
-      <c r="R4" s="184" t="s">
+      <c r="R4" s="183" t="s">
         <v>215</v>
       </c>
-      <c r="S4" s="184"/>
-      <c r="T4" s="184"/>
-      <c r="U4" s="184"/>
-      <c r="V4" s="184"/>
-      <c r="W4" s="184"/>
-      <c r="X4" s="185"/>
-      <c r="Y4" s="182" t="s">
+      <c r="S4" s="183"/>
+      <c r="T4" s="183"/>
+      <c r="U4" s="183"/>
+      <c r="V4" s="183"/>
+      <c r="W4" s="183"/>
+      <c r="X4" s="184"/>
+      <c r="Y4" s="181" t="s">
         <v>216</v>
       </c>
-      <c r="Z4" s="183"/>
-      <c r="AA4" s="183"/>
-      <c r="AB4" s="183"/>
-      <c r="AC4" s="183"/>
-      <c r="AD4" s="183"/>
-      <c r="AE4" s="183"/>
+      <c r="Z4" s="182"/>
+      <c r="AA4" s="182"/>
+      <c r="AB4" s="182"/>
+      <c r="AC4" s="182"/>
+      <c r="AD4" s="182"/>
+      <c r="AE4" s="182"/>
       <c r="AF4" s="91"/>
-      <c r="AG4" s="184" t="s">
+      <c r="AG4" s="183" t="s">
         <v>215</v>
       </c>
-      <c r="AH4" s="184"/>
-      <c r="AI4" s="184"/>
-      <c r="AJ4" s="184"/>
-      <c r="AK4" s="184"/>
-      <c r="AL4" s="185"/>
+      <c r="AH4" s="183"/>
+      <c r="AI4" s="183"/>
+      <c r="AJ4" s="183"/>
+      <c r="AK4" s="183"/>
+      <c r="AL4" s="184"/>
     </row>
     <row r="5" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A5" s="180"/>
@@ -14048,35 +14057,35 @@
       <c r="G5" s="180"/>
       <c r="H5" s="180"/>
       <c r="I5" s="180"/>
-      <c r="J5" s="181"/>
-      <c r="K5" s="181"/>
-      <c r="L5" s="181"/>
-      <c r="M5" s="181"/>
-      <c r="N5" s="181"/>
-      <c r="O5" s="181"/>
-      <c r="P5" s="181"/>
-      <c r="Q5" s="181"/>
-      <c r="R5" s="181"/>
-      <c r="S5" s="181"/>
-      <c r="T5" s="181"/>
-      <c r="U5" s="181"/>
-      <c r="V5" s="181"/>
-      <c r="W5" s="181"/>
-      <c r="X5" s="181"/>
-      <c r="Y5" s="181"/>
-      <c r="Z5" s="181"/>
-      <c r="AA5" s="181"/>
-      <c r="AB5" s="181"/>
-      <c r="AC5" s="181"/>
-      <c r="AD5" s="181"/>
-      <c r="AE5" s="181"/>
-      <c r="AF5" s="181"/>
-      <c r="AG5" s="181"/>
-      <c r="AH5" s="181"/>
-      <c r="AI5" s="181"/>
-      <c r="AJ5" s="181"/>
-      <c r="AK5" s="181"/>
-      <c r="AL5" s="181"/>
+      <c r="J5" s="225"/>
+      <c r="K5" s="225"/>
+      <c r="L5" s="225"/>
+      <c r="M5" s="225"/>
+      <c r="N5" s="225"/>
+      <c r="O5" s="225"/>
+      <c r="P5" s="225"/>
+      <c r="Q5" s="225"/>
+      <c r="R5" s="225"/>
+      <c r="S5" s="225"/>
+      <c r="T5" s="225"/>
+      <c r="U5" s="225"/>
+      <c r="V5" s="225"/>
+      <c r="W5" s="225"/>
+      <c r="X5" s="225"/>
+      <c r="Y5" s="225"/>
+      <c r="Z5" s="225"/>
+      <c r="AA5" s="225"/>
+      <c r="AB5" s="225"/>
+      <c r="AC5" s="225"/>
+      <c r="AD5" s="225"/>
+      <c r="AE5" s="225"/>
+      <c r="AF5" s="225"/>
+      <c r="AG5" s="225"/>
+      <c r="AH5" s="225"/>
+      <c r="AI5" s="225"/>
+      <c r="AJ5" s="225"/>
+      <c r="AK5" s="225"/>
+      <c r="AL5" s="225"/>
     </row>
     <row r="6" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A6" s="180"/>
@@ -14088,35 +14097,35 @@
       <c r="G6" s="180"/>
       <c r="H6" s="180"/>
       <c r="I6" s="180"/>
-      <c r="J6" s="181"/>
-      <c r="K6" s="181"/>
-      <c r="L6" s="181"/>
-      <c r="M6" s="181"/>
-      <c r="N6" s="181"/>
-      <c r="O6" s="181"/>
-      <c r="P6" s="181"/>
-      <c r="Q6" s="181"/>
-      <c r="R6" s="181"/>
-      <c r="S6" s="181"/>
-      <c r="T6" s="181"/>
-      <c r="U6" s="181"/>
-      <c r="V6" s="181"/>
-      <c r="W6" s="181"/>
-      <c r="X6" s="181"/>
-      <c r="Y6" s="181"/>
-      <c r="Z6" s="181"/>
-      <c r="AA6" s="181"/>
-      <c r="AB6" s="181"/>
-      <c r="AC6" s="181"/>
-      <c r="AD6" s="181"/>
-      <c r="AE6" s="181"/>
-      <c r="AF6" s="181"/>
-      <c r="AG6" s="181"/>
-      <c r="AH6" s="181"/>
-      <c r="AI6" s="181"/>
-      <c r="AJ6" s="181"/>
-      <c r="AK6" s="181"/>
-      <c r="AL6" s="181"/>
+      <c r="J6" s="225"/>
+      <c r="K6" s="225"/>
+      <c r="L6" s="225"/>
+      <c r="M6" s="225"/>
+      <c r="N6" s="225"/>
+      <c r="O6" s="225"/>
+      <c r="P6" s="225"/>
+      <c r="Q6" s="225"/>
+      <c r="R6" s="225"/>
+      <c r="S6" s="225"/>
+      <c r="T6" s="225"/>
+      <c r="U6" s="225"/>
+      <c r="V6" s="225"/>
+      <c r="W6" s="225"/>
+      <c r="X6" s="225"/>
+      <c r="Y6" s="225"/>
+      <c r="Z6" s="225"/>
+      <c r="AA6" s="225"/>
+      <c r="AB6" s="225"/>
+      <c r="AC6" s="225"/>
+      <c r="AD6" s="225"/>
+      <c r="AE6" s="225"/>
+      <c r="AF6" s="225"/>
+      <c r="AG6" s="225"/>
+      <c r="AH6" s="225"/>
+      <c r="AI6" s="225"/>
+      <c r="AJ6" s="225"/>
+      <c r="AK6" s="225"/>
+      <c r="AL6" s="225"/>
     </row>
     <row r="7" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A7" s="180"/>
@@ -14128,35 +14137,35 @@
       <c r="G7" s="180"/>
       <c r="H7" s="180"/>
       <c r="I7" s="180"/>
-      <c r="J7" s="181"/>
-      <c r="K7" s="181"/>
-      <c r="L7" s="181"/>
-      <c r="M7" s="181"/>
-      <c r="N7" s="181"/>
-      <c r="O7" s="181"/>
-      <c r="P7" s="181"/>
-      <c r="Q7" s="181"/>
-      <c r="R7" s="181"/>
-      <c r="S7" s="181"/>
-      <c r="T7" s="181"/>
-      <c r="U7" s="181"/>
-      <c r="V7" s="181"/>
-      <c r="W7" s="181"/>
-      <c r="X7" s="181"/>
-      <c r="Y7" s="181"/>
-      <c r="Z7" s="181"/>
-      <c r="AA7" s="181"/>
-      <c r="AB7" s="181"/>
-      <c r="AC7" s="181"/>
-      <c r="AD7" s="181"/>
-      <c r="AE7" s="181"/>
-      <c r="AF7" s="181"/>
-      <c r="AG7" s="181"/>
-      <c r="AH7" s="181"/>
-      <c r="AI7" s="181"/>
-      <c r="AJ7" s="181"/>
-      <c r="AK7" s="181"/>
-      <c r="AL7" s="181"/>
+      <c r="J7" s="225"/>
+      <c r="K7" s="225"/>
+      <c r="L7" s="225"/>
+      <c r="M7" s="225"/>
+      <c r="N7" s="225"/>
+      <c r="O7" s="225"/>
+      <c r="P7" s="225"/>
+      <c r="Q7" s="225"/>
+      <c r="R7" s="225"/>
+      <c r="S7" s="225"/>
+      <c r="T7" s="225"/>
+      <c r="U7" s="225"/>
+      <c r="V7" s="225"/>
+      <c r="W7" s="225"/>
+      <c r="X7" s="225"/>
+      <c r="Y7" s="225"/>
+      <c r="Z7" s="225"/>
+      <c r="AA7" s="225"/>
+      <c r="AB7" s="225"/>
+      <c r="AC7" s="225"/>
+      <c r="AD7" s="225"/>
+      <c r="AE7" s="225"/>
+      <c r="AF7" s="225"/>
+      <c r="AG7" s="225"/>
+      <c r="AH7" s="225"/>
+      <c r="AI7" s="225"/>
+      <c r="AJ7" s="225"/>
+      <c r="AK7" s="225"/>
+      <c r="AL7" s="225"/>
     </row>
     <row r="8" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A8" s="180"/>
@@ -14168,35 +14177,35 @@
       <c r="G8" s="180"/>
       <c r="H8" s="180"/>
       <c r="I8" s="180"/>
-      <c r="J8" s="181"/>
-      <c r="K8" s="181"/>
-      <c r="L8" s="181"/>
-      <c r="M8" s="181"/>
-      <c r="N8" s="181"/>
-      <c r="O8" s="181"/>
-      <c r="P8" s="181"/>
-      <c r="Q8" s="181"/>
-      <c r="R8" s="181"/>
-      <c r="S8" s="181"/>
-      <c r="T8" s="181"/>
-      <c r="U8" s="181"/>
-      <c r="V8" s="181"/>
-      <c r="W8" s="181"/>
-      <c r="X8" s="181"/>
-      <c r="Y8" s="181"/>
-      <c r="Z8" s="181"/>
-      <c r="AA8" s="181"/>
-      <c r="AB8" s="181"/>
-      <c r="AC8" s="181"/>
-      <c r="AD8" s="181"/>
-      <c r="AE8" s="181"/>
-      <c r="AF8" s="181"/>
-      <c r="AG8" s="181"/>
-      <c r="AH8" s="181"/>
-      <c r="AI8" s="181"/>
-      <c r="AJ8" s="181"/>
-      <c r="AK8" s="181"/>
-      <c r="AL8" s="181"/>
+      <c r="J8" s="225"/>
+      <c r="K8" s="225"/>
+      <c r="L8" s="225"/>
+      <c r="M8" s="225"/>
+      <c r="N8" s="225"/>
+      <c r="O8" s="225"/>
+      <c r="P8" s="225"/>
+      <c r="Q8" s="225"/>
+      <c r="R8" s="225"/>
+      <c r="S8" s="225"/>
+      <c r="T8" s="225"/>
+      <c r="U8" s="225"/>
+      <c r="V8" s="225"/>
+      <c r="W8" s="225"/>
+      <c r="X8" s="225"/>
+      <c r="Y8" s="225"/>
+      <c r="Z8" s="225"/>
+      <c r="AA8" s="225"/>
+      <c r="AB8" s="225"/>
+      <c r="AC8" s="225"/>
+      <c r="AD8" s="225"/>
+      <c r="AE8" s="225"/>
+      <c r="AF8" s="225"/>
+      <c r="AG8" s="225"/>
+      <c r="AH8" s="225"/>
+      <c r="AI8" s="225"/>
+      <c r="AJ8" s="225"/>
+      <c r="AK8" s="225"/>
+      <c r="AL8" s="225"/>
     </row>
     <row r="9" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A9" s="180"/>
@@ -14208,35 +14217,35 @@
       <c r="G9" s="180"/>
       <c r="H9" s="180"/>
       <c r="I9" s="180"/>
-      <c r="J9" s="181"/>
-      <c r="K9" s="181"/>
-      <c r="L9" s="181"/>
-      <c r="M9" s="181"/>
-      <c r="N9" s="181"/>
-      <c r="O9" s="181"/>
-      <c r="P9" s="181"/>
-      <c r="Q9" s="181"/>
-      <c r="R9" s="181"/>
-      <c r="S9" s="181"/>
-      <c r="T9" s="181"/>
-      <c r="U9" s="181"/>
-      <c r="V9" s="181"/>
-      <c r="W9" s="181"/>
-      <c r="X9" s="181"/>
-      <c r="Y9" s="181"/>
-      <c r="Z9" s="181"/>
-      <c r="AA9" s="181"/>
-      <c r="AB9" s="181"/>
-      <c r="AC9" s="181"/>
-      <c r="AD9" s="181"/>
-      <c r="AE9" s="181"/>
-      <c r="AF9" s="181"/>
-      <c r="AG9" s="181"/>
-      <c r="AH9" s="181"/>
-      <c r="AI9" s="181"/>
-      <c r="AJ9" s="181"/>
-      <c r="AK9" s="181"/>
-      <c r="AL9" s="181"/>
+      <c r="J9" s="225"/>
+      <c r="K9" s="225"/>
+      <c r="L9" s="225"/>
+      <c r="M9" s="225"/>
+      <c r="N9" s="225"/>
+      <c r="O9" s="225"/>
+      <c r="P9" s="225"/>
+      <c r="Q9" s="225"/>
+      <c r="R9" s="225"/>
+      <c r="S9" s="225"/>
+      <c r="T9" s="225"/>
+      <c r="U9" s="225"/>
+      <c r="V9" s="225"/>
+      <c r="W9" s="225"/>
+      <c r="X9" s="225"/>
+      <c r="Y9" s="225"/>
+      <c r="Z9" s="225"/>
+      <c r="AA9" s="225"/>
+      <c r="AB9" s="225"/>
+      <c r="AC9" s="225"/>
+      <c r="AD9" s="225"/>
+      <c r="AE9" s="225"/>
+      <c r="AF9" s="225"/>
+      <c r="AG9" s="225"/>
+      <c r="AH9" s="225"/>
+      <c r="AI9" s="225"/>
+      <c r="AJ9" s="225"/>
+      <c r="AK9" s="225"/>
+      <c r="AL9" s="225"/>
     </row>
     <row r="10" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A10" s="180"/>
@@ -14248,35 +14257,35 @@
       <c r="G10" s="180"/>
       <c r="H10" s="180"/>
       <c r="I10" s="180"/>
-      <c r="J10" s="181"/>
-      <c r="K10" s="181"/>
-      <c r="L10" s="181"/>
-      <c r="M10" s="181"/>
-      <c r="N10" s="181"/>
-      <c r="O10" s="181"/>
-      <c r="P10" s="181"/>
-      <c r="Q10" s="181"/>
-      <c r="R10" s="181"/>
-      <c r="S10" s="181"/>
-      <c r="T10" s="181"/>
-      <c r="U10" s="181"/>
-      <c r="V10" s="181"/>
-      <c r="W10" s="181"/>
-      <c r="X10" s="181"/>
-      <c r="Y10" s="181"/>
-      <c r="Z10" s="181"/>
-      <c r="AA10" s="181"/>
-      <c r="AB10" s="181"/>
-      <c r="AC10" s="181"/>
-      <c r="AD10" s="181"/>
-      <c r="AE10" s="181"/>
-      <c r="AF10" s="181"/>
-      <c r="AG10" s="181"/>
-      <c r="AH10" s="181"/>
-      <c r="AI10" s="181"/>
-      <c r="AJ10" s="181"/>
-      <c r="AK10" s="181"/>
-      <c r="AL10" s="181"/>
+      <c r="J10" s="225"/>
+      <c r="K10" s="225"/>
+      <c r="L10" s="225"/>
+      <c r="M10" s="225"/>
+      <c r="N10" s="225"/>
+      <c r="O10" s="225"/>
+      <c r="P10" s="225"/>
+      <c r="Q10" s="225"/>
+      <c r="R10" s="225"/>
+      <c r="S10" s="225"/>
+      <c r="T10" s="225"/>
+      <c r="U10" s="225"/>
+      <c r="V10" s="225"/>
+      <c r="W10" s="225"/>
+      <c r="X10" s="225"/>
+      <c r="Y10" s="225"/>
+      <c r="Z10" s="225"/>
+      <c r="AA10" s="225"/>
+      <c r="AB10" s="225"/>
+      <c r="AC10" s="225"/>
+      <c r="AD10" s="225"/>
+      <c r="AE10" s="225"/>
+      <c r="AF10" s="225"/>
+      <c r="AG10" s="225"/>
+      <c r="AH10" s="225"/>
+      <c r="AI10" s="225"/>
+      <c r="AJ10" s="225"/>
+      <c r="AK10" s="225"/>
+      <c r="AL10" s="225"/>
     </row>
     <row r="11" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A11" s="180"/>
@@ -14288,35 +14297,35 @@
       <c r="G11" s="180"/>
       <c r="H11" s="180"/>
       <c r="I11" s="180"/>
-      <c r="J11" s="181"/>
-      <c r="K11" s="181"/>
-      <c r="L11" s="181"/>
-      <c r="M11" s="181"/>
-      <c r="N11" s="181"/>
-      <c r="O11" s="181"/>
-      <c r="P11" s="181"/>
-      <c r="Q11" s="181"/>
-      <c r="R11" s="181"/>
-      <c r="S11" s="181"/>
-      <c r="T11" s="181"/>
-      <c r="U11" s="181"/>
-      <c r="V11" s="181"/>
-      <c r="W11" s="181"/>
-      <c r="X11" s="181"/>
-      <c r="Y11" s="181"/>
-      <c r="Z11" s="181"/>
-      <c r="AA11" s="181"/>
-      <c r="AB11" s="181"/>
-      <c r="AC11" s="181"/>
-      <c r="AD11" s="181"/>
-      <c r="AE11" s="181"/>
-      <c r="AF11" s="181"/>
-      <c r="AG11" s="181"/>
-      <c r="AH11" s="181"/>
-      <c r="AI11" s="181"/>
-      <c r="AJ11" s="181"/>
-      <c r="AK11" s="181"/>
-      <c r="AL11" s="181"/>
+      <c r="J11" s="225"/>
+      <c r="K11" s="225"/>
+      <c r="L11" s="225"/>
+      <c r="M11" s="225"/>
+      <c r="N11" s="225"/>
+      <c r="O11" s="225"/>
+      <c r="P11" s="225"/>
+      <c r="Q11" s="225"/>
+      <c r="R11" s="225"/>
+      <c r="S11" s="225"/>
+      <c r="T11" s="225"/>
+      <c r="U11" s="225"/>
+      <c r="V11" s="225"/>
+      <c r="W11" s="225"/>
+      <c r="X11" s="225"/>
+      <c r="Y11" s="225"/>
+      <c r="Z11" s="225"/>
+      <c r="AA11" s="225"/>
+      <c r="AB11" s="225"/>
+      <c r="AC11" s="225"/>
+      <c r="AD11" s="225"/>
+      <c r="AE11" s="225"/>
+      <c r="AF11" s="225"/>
+      <c r="AG11" s="225"/>
+      <c r="AH11" s="225"/>
+      <c r="AI11" s="225"/>
+      <c r="AJ11" s="225"/>
+      <c r="AK11" s="225"/>
+      <c r="AL11" s="225"/>
     </row>
     <row r="12" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A12" s="180"/>
@@ -14328,35 +14337,35 @@
       <c r="G12" s="180"/>
       <c r="H12" s="180"/>
       <c r="I12" s="180"/>
-      <c r="J12" s="181"/>
-      <c r="K12" s="181"/>
-      <c r="L12" s="181"/>
-      <c r="M12" s="181"/>
-      <c r="N12" s="181"/>
-      <c r="O12" s="181"/>
-      <c r="P12" s="181"/>
-      <c r="Q12" s="181"/>
-      <c r="R12" s="181"/>
-      <c r="S12" s="181"/>
-      <c r="T12" s="181"/>
-      <c r="U12" s="181"/>
-      <c r="V12" s="181"/>
-      <c r="W12" s="181"/>
-      <c r="X12" s="181"/>
-      <c r="Y12" s="181"/>
-      <c r="Z12" s="181"/>
-      <c r="AA12" s="181"/>
-      <c r="AB12" s="181"/>
-      <c r="AC12" s="181"/>
-      <c r="AD12" s="181"/>
-      <c r="AE12" s="181"/>
-      <c r="AF12" s="181"/>
-      <c r="AG12" s="181"/>
-      <c r="AH12" s="181"/>
-      <c r="AI12" s="181"/>
-      <c r="AJ12" s="181"/>
-      <c r="AK12" s="181"/>
-      <c r="AL12" s="181"/>
+      <c r="J12" s="225"/>
+      <c r="K12" s="225"/>
+      <c r="L12" s="225"/>
+      <c r="M12" s="225"/>
+      <c r="N12" s="225"/>
+      <c r="O12" s="225"/>
+      <c r="P12" s="225"/>
+      <c r="Q12" s="225"/>
+      <c r="R12" s="225"/>
+      <c r="S12" s="225"/>
+      <c r="T12" s="225"/>
+      <c r="U12" s="225"/>
+      <c r="V12" s="225"/>
+      <c r="W12" s="225"/>
+      <c r="X12" s="225"/>
+      <c r="Y12" s="225"/>
+      <c r="Z12" s="225"/>
+      <c r="AA12" s="225"/>
+      <c r="AB12" s="225"/>
+      <c r="AC12" s="225"/>
+      <c r="AD12" s="225"/>
+      <c r="AE12" s="225"/>
+      <c r="AF12" s="225"/>
+      <c r="AG12" s="225"/>
+      <c r="AH12" s="225"/>
+      <c r="AI12" s="225"/>
+      <c r="AJ12" s="225"/>
+      <c r="AK12" s="225"/>
+      <c r="AL12" s="225"/>
     </row>
     <row r="13" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A13" s="180"/>
@@ -14368,35 +14377,35 @@
       <c r="G13" s="180"/>
       <c r="H13" s="180"/>
       <c r="I13" s="180"/>
-      <c r="J13" s="181"/>
-      <c r="K13" s="181"/>
-      <c r="L13" s="181"/>
-      <c r="M13" s="181"/>
-      <c r="N13" s="181"/>
-      <c r="O13" s="181"/>
-      <c r="P13" s="181"/>
-      <c r="Q13" s="181"/>
-      <c r="R13" s="181"/>
-      <c r="S13" s="181"/>
-      <c r="T13" s="181"/>
-      <c r="U13" s="181"/>
-      <c r="V13" s="181"/>
-      <c r="W13" s="181"/>
-      <c r="X13" s="181"/>
-      <c r="Y13" s="181"/>
-      <c r="Z13" s="181"/>
-      <c r="AA13" s="181"/>
-      <c r="AB13" s="181"/>
-      <c r="AC13" s="181"/>
-      <c r="AD13" s="181"/>
-      <c r="AE13" s="181"/>
-      <c r="AF13" s="181"/>
-      <c r="AG13" s="181"/>
-      <c r="AH13" s="181"/>
-      <c r="AI13" s="181"/>
-      <c r="AJ13" s="181"/>
-      <c r="AK13" s="181"/>
-      <c r="AL13" s="181"/>
+      <c r="J13" s="225"/>
+      <c r="K13" s="225"/>
+      <c r="L13" s="225"/>
+      <c r="M13" s="225"/>
+      <c r="N13" s="225"/>
+      <c r="O13" s="225"/>
+      <c r="P13" s="225"/>
+      <c r="Q13" s="225"/>
+      <c r="R13" s="225"/>
+      <c r="S13" s="225"/>
+      <c r="T13" s="225"/>
+      <c r="U13" s="225"/>
+      <c r="V13" s="225"/>
+      <c r="W13" s="225"/>
+      <c r="X13" s="225"/>
+      <c r="Y13" s="225"/>
+      <c r="Z13" s="225"/>
+      <c r="AA13" s="225"/>
+      <c r="AB13" s="225"/>
+      <c r="AC13" s="225"/>
+      <c r="AD13" s="225"/>
+      <c r="AE13" s="225"/>
+      <c r="AF13" s="225"/>
+      <c r="AG13" s="225"/>
+      <c r="AH13" s="225"/>
+      <c r="AI13" s="225"/>
+      <c r="AJ13" s="225"/>
+      <c r="AK13" s="225"/>
+      <c r="AL13" s="225"/>
     </row>
     <row r="14" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A14" s="180"/>
@@ -14408,35 +14417,35 @@
       <c r="G14" s="180"/>
       <c r="H14" s="180"/>
       <c r="I14" s="180"/>
-      <c r="J14" s="181"/>
-      <c r="K14" s="181"/>
-      <c r="L14" s="181"/>
-      <c r="M14" s="181"/>
-      <c r="N14" s="181"/>
-      <c r="O14" s="181"/>
-      <c r="P14" s="181"/>
-      <c r="Q14" s="181"/>
-      <c r="R14" s="181"/>
-      <c r="S14" s="181"/>
-      <c r="T14" s="181"/>
-      <c r="U14" s="181"/>
-      <c r="V14" s="181"/>
-      <c r="W14" s="181"/>
-      <c r="X14" s="181"/>
-      <c r="Y14" s="181"/>
-      <c r="Z14" s="181"/>
-      <c r="AA14" s="181"/>
-      <c r="AB14" s="181"/>
-      <c r="AC14" s="181"/>
-      <c r="AD14" s="181"/>
-      <c r="AE14" s="181"/>
-      <c r="AF14" s="181"/>
-      <c r="AG14" s="181"/>
-      <c r="AH14" s="181"/>
-      <c r="AI14" s="181"/>
-      <c r="AJ14" s="181"/>
-      <c r="AK14" s="181"/>
-      <c r="AL14" s="181"/>
+      <c r="J14" s="225"/>
+      <c r="K14" s="225"/>
+      <c r="L14" s="225"/>
+      <c r="M14" s="225"/>
+      <c r="N14" s="225"/>
+      <c r="O14" s="225"/>
+      <c r="P14" s="225"/>
+      <c r="Q14" s="225"/>
+      <c r="R14" s="225"/>
+      <c r="S14" s="225"/>
+      <c r="T14" s="225"/>
+      <c r="U14" s="225"/>
+      <c r="V14" s="225"/>
+      <c r="W14" s="225"/>
+      <c r="X14" s="225"/>
+      <c r="Y14" s="225"/>
+      <c r="Z14" s="225"/>
+      <c r="AA14" s="225"/>
+      <c r="AB14" s="225"/>
+      <c r="AC14" s="225"/>
+      <c r="AD14" s="225"/>
+      <c r="AE14" s="225"/>
+      <c r="AF14" s="225"/>
+      <c r="AG14" s="225"/>
+      <c r="AH14" s="225"/>
+      <c r="AI14" s="225"/>
+      <c r="AJ14" s="225"/>
+      <c r="AK14" s="225"/>
+      <c r="AL14" s="225"/>
     </row>
     <row r="15" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A15" s="180"/>
@@ -14448,35 +14457,35 @@
       <c r="G15" s="180"/>
       <c r="H15" s="180"/>
       <c r="I15" s="180"/>
-      <c r="J15" s="181"/>
-      <c r="K15" s="181"/>
-      <c r="L15" s="181"/>
-      <c r="M15" s="181"/>
-      <c r="N15" s="181"/>
-      <c r="O15" s="181"/>
-      <c r="P15" s="181"/>
-      <c r="Q15" s="181"/>
-      <c r="R15" s="181"/>
-      <c r="S15" s="181"/>
-      <c r="T15" s="181"/>
-      <c r="U15" s="181"/>
-      <c r="V15" s="181"/>
-      <c r="W15" s="181"/>
-      <c r="X15" s="181"/>
-      <c r="Y15" s="181"/>
-      <c r="Z15" s="181"/>
-      <c r="AA15" s="181"/>
-      <c r="AB15" s="181"/>
-      <c r="AC15" s="181"/>
-      <c r="AD15" s="181"/>
-      <c r="AE15" s="181"/>
-      <c r="AF15" s="181"/>
-      <c r="AG15" s="181"/>
-      <c r="AH15" s="181"/>
-      <c r="AI15" s="181"/>
-      <c r="AJ15" s="181"/>
-      <c r="AK15" s="181"/>
-      <c r="AL15" s="181"/>
+      <c r="J15" s="225"/>
+      <c r="K15" s="225"/>
+      <c r="L15" s="225"/>
+      <c r="M15" s="225"/>
+      <c r="N15" s="225"/>
+      <c r="O15" s="225"/>
+      <c r="P15" s="225"/>
+      <c r="Q15" s="225"/>
+      <c r="R15" s="225"/>
+      <c r="S15" s="225"/>
+      <c r="T15" s="225"/>
+      <c r="U15" s="225"/>
+      <c r="V15" s="225"/>
+      <c r="W15" s="225"/>
+      <c r="X15" s="225"/>
+      <c r="Y15" s="225"/>
+      <c r="Z15" s="225"/>
+      <c r="AA15" s="225"/>
+      <c r="AB15" s="225"/>
+      <c r="AC15" s="225"/>
+      <c r="AD15" s="225"/>
+      <c r="AE15" s="225"/>
+      <c r="AF15" s="225"/>
+      <c r="AG15" s="225"/>
+      <c r="AH15" s="225"/>
+      <c r="AI15" s="225"/>
+      <c r="AJ15" s="225"/>
+      <c r="AK15" s="225"/>
+      <c r="AL15" s="225"/>
     </row>
     <row r="16" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A16" s="180"/>
@@ -14488,35 +14497,35 @@
       <c r="G16" s="180"/>
       <c r="H16" s="180"/>
       <c r="I16" s="180"/>
-      <c r="J16" s="181"/>
-      <c r="K16" s="181"/>
-      <c r="L16" s="181"/>
-      <c r="M16" s="181"/>
-      <c r="N16" s="181"/>
-      <c r="O16" s="181"/>
-      <c r="P16" s="181"/>
-      <c r="Q16" s="181"/>
-      <c r="R16" s="181"/>
-      <c r="S16" s="181"/>
-      <c r="T16" s="181"/>
-      <c r="U16" s="181"/>
-      <c r="V16" s="181"/>
-      <c r="W16" s="181"/>
-      <c r="X16" s="181"/>
-      <c r="Y16" s="181"/>
-      <c r="Z16" s="181"/>
-      <c r="AA16" s="181"/>
-      <c r="AB16" s="181"/>
-      <c r="AC16" s="181"/>
-      <c r="AD16" s="181"/>
-      <c r="AE16" s="181"/>
-      <c r="AF16" s="181"/>
-      <c r="AG16" s="181"/>
-      <c r="AH16" s="181"/>
-      <c r="AI16" s="181"/>
-      <c r="AJ16" s="181"/>
-      <c r="AK16" s="181"/>
-      <c r="AL16" s="181"/>
+      <c r="J16" s="225"/>
+      <c r="K16" s="225"/>
+      <c r="L16" s="225"/>
+      <c r="M16" s="225"/>
+      <c r="N16" s="225"/>
+      <c r="O16" s="225"/>
+      <c r="P16" s="225"/>
+      <c r="Q16" s="225"/>
+      <c r="R16" s="225"/>
+      <c r="S16" s="225"/>
+      <c r="T16" s="225"/>
+      <c r="U16" s="225"/>
+      <c r="V16" s="225"/>
+      <c r="W16" s="225"/>
+      <c r="X16" s="225"/>
+      <c r="Y16" s="225"/>
+      <c r="Z16" s="225"/>
+      <c r="AA16" s="225"/>
+      <c r="AB16" s="225"/>
+      <c r="AC16" s="225"/>
+      <c r="AD16" s="225"/>
+      <c r="AE16" s="225"/>
+      <c r="AF16" s="225"/>
+      <c r="AG16" s="225"/>
+      <c r="AH16" s="225"/>
+      <c r="AI16" s="225"/>
+      <c r="AJ16" s="225"/>
+      <c r="AK16" s="225"/>
+      <c r="AL16" s="225"/>
     </row>
     <row r="17" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A17" s="86" t="s">
@@ -14561,96 +14570,96 @@
       <c r="AL17" s="89"/>
     </row>
     <row r="18" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A18" s="187" t="s">
+      <c r="A18" s="186" t="s">
         <v>8</v>
       </c>
-      <c r="B18" s="187"/>
-      <c r="C18" s="188"/>
-      <c r="D18" s="189"/>
-      <c r="E18" s="189"/>
-      <c r="F18" s="189"/>
-      <c r="G18" s="189"/>
-      <c r="H18" s="189"/>
-      <c r="I18" s="190"/>
-      <c r="J18" s="191"/>
-      <c r="K18" s="191"/>
-      <c r="L18" s="191"/>
-      <c r="M18" s="191"/>
-      <c r="N18" s="191"/>
-      <c r="O18" s="191"/>
-      <c r="P18" s="191"/>
-      <c r="Q18" s="191"/>
-      <c r="R18" s="191"/>
-      <c r="S18" s="191"/>
-      <c r="T18" s="191"/>
-      <c r="U18" s="191"/>
-      <c r="V18" s="191"/>
-      <c r="W18" s="191"/>
-      <c r="X18" s="191"/>
-      <c r="Y18" s="191"/>
-      <c r="Z18" s="191"/>
-      <c r="AA18" s="191"/>
-      <c r="AB18" s="191"/>
-      <c r="AC18" s="191"/>
-      <c r="AD18" s="191"/>
-      <c r="AE18" s="191"/>
-      <c r="AF18" s="191"/>
-      <c r="AG18" s="191"/>
-      <c r="AH18" s="191"/>
-      <c r="AI18" s="191"/>
-      <c r="AJ18" s="191"/>
-      <c r="AK18" s="191"/>
-      <c r="AL18" s="191"/>
+      <c r="B18" s="186"/>
+      <c r="C18" s="187"/>
+      <c r="D18" s="188"/>
+      <c r="E18" s="188"/>
+      <c r="F18" s="188"/>
+      <c r="G18" s="188"/>
+      <c r="H18" s="188"/>
+      <c r="I18" s="189"/>
+      <c r="J18" s="190"/>
+      <c r="K18" s="190"/>
+      <c r="L18" s="190"/>
+      <c r="M18" s="190"/>
+      <c r="N18" s="190"/>
+      <c r="O18" s="190"/>
+      <c r="P18" s="190"/>
+      <c r="Q18" s="190"/>
+      <c r="R18" s="190"/>
+      <c r="S18" s="190"/>
+      <c r="T18" s="190"/>
+      <c r="U18" s="190"/>
+      <c r="V18" s="190"/>
+      <c r="W18" s="190"/>
+      <c r="X18" s="190"/>
+      <c r="Y18" s="190"/>
+      <c r="Z18" s="190"/>
+      <c r="AA18" s="190"/>
+      <c r="AB18" s="190"/>
+      <c r="AC18" s="190"/>
+      <c r="AD18" s="190"/>
+      <c r="AE18" s="190"/>
+      <c r="AF18" s="190"/>
+      <c r="AG18" s="190"/>
+      <c r="AH18" s="190"/>
+      <c r="AI18" s="190"/>
+      <c r="AJ18" s="190"/>
+      <c r="AK18" s="190"/>
+      <c r="AL18" s="190"/>
     </row>
     <row r="19" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A19" s="186" t="s">
+      <c r="A19" s="185" t="s">
         <v>213</v>
       </c>
-      <c r="B19" s="184"/>
-      <c r="C19" s="184"/>
-      <c r="D19" s="184"/>
-      <c r="E19" s="184"/>
-      <c r="F19" s="184"/>
-      <c r="G19" s="184"/>
-      <c r="H19" s="184"/>
-      <c r="I19" s="185"/>
-      <c r="J19" s="182" t="s">
+      <c r="B19" s="183"/>
+      <c r="C19" s="183"/>
+      <c r="D19" s="183"/>
+      <c r="E19" s="183"/>
+      <c r="F19" s="183"/>
+      <c r="G19" s="183"/>
+      <c r="H19" s="183"/>
+      <c r="I19" s="184"/>
+      <c r="J19" s="181" t="s">
         <v>214</v>
       </c>
-      <c r="K19" s="183"/>
-      <c r="L19" s="183"/>
-      <c r="M19" s="183"/>
-      <c r="N19" s="183"/>
-      <c r="O19" s="183"/>
-      <c r="P19" s="183"/>
+      <c r="K19" s="182"/>
+      <c r="L19" s="182"/>
+      <c r="M19" s="182"/>
+      <c r="N19" s="182"/>
+      <c r="O19" s="182"/>
+      <c r="P19" s="182"/>
       <c r="Q19" s="91"/>
-      <c r="R19" s="184" t="s">
+      <c r="R19" s="183" t="s">
         <v>215</v>
       </c>
-      <c r="S19" s="184"/>
-      <c r="T19" s="184"/>
-      <c r="U19" s="184"/>
-      <c r="V19" s="184"/>
-      <c r="W19" s="184"/>
-      <c r="X19" s="185"/>
-      <c r="Y19" s="182" t="s">
+      <c r="S19" s="183"/>
+      <c r="T19" s="183"/>
+      <c r="U19" s="183"/>
+      <c r="V19" s="183"/>
+      <c r="W19" s="183"/>
+      <c r="X19" s="184"/>
+      <c r="Y19" s="181" t="s">
         <v>216</v>
       </c>
-      <c r="Z19" s="183"/>
-      <c r="AA19" s="183"/>
-      <c r="AB19" s="183"/>
-      <c r="AC19" s="183"/>
-      <c r="AD19" s="183"/>
-      <c r="AE19" s="183"/>
+      <c r="Z19" s="182"/>
+      <c r="AA19" s="182"/>
+      <c r="AB19" s="182"/>
+      <c r="AC19" s="182"/>
+      <c r="AD19" s="182"/>
+      <c r="AE19" s="182"/>
       <c r="AF19" s="91"/>
-      <c r="AG19" s="184" t="s">
+      <c r="AG19" s="183" t="s">
         <v>215</v>
       </c>
-      <c r="AH19" s="184"/>
-      <c r="AI19" s="184"/>
-      <c r="AJ19" s="184"/>
-      <c r="AK19" s="184"/>
-      <c r="AL19" s="185"/>
+      <c r="AH19" s="183"/>
+      <c r="AI19" s="183"/>
+      <c r="AJ19" s="183"/>
+      <c r="AK19" s="183"/>
+      <c r="AL19" s="184"/>
     </row>
     <row r="20" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A20" s="180"/>
@@ -14662,35 +14671,35 @@
       <c r="G20" s="180"/>
       <c r="H20" s="180"/>
       <c r="I20" s="180"/>
-      <c r="J20" s="181"/>
-      <c r="K20" s="181"/>
-      <c r="L20" s="181"/>
-      <c r="M20" s="181"/>
-      <c r="N20" s="181"/>
-      <c r="O20" s="181"/>
-      <c r="P20" s="181"/>
-      <c r="Q20" s="181"/>
-      <c r="R20" s="181"/>
-      <c r="S20" s="181"/>
-      <c r="T20" s="181"/>
-      <c r="U20" s="181"/>
-      <c r="V20" s="181"/>
-      <c r="W20" s="181"/>
-      <c r="X20" s="181"/>
-      <c r="Y20" s="181"/>
-      <c r="Z20" s="181"/>
-      <c r="AA20" s="181"/>
-      <c r="AB20" s="181"/>
-      <c r="AC20" s="181"/>
-      <c r="AD20" s="181"/>
-      <c r="AE20" s="181"/>
-      <c r="AF20" s="181"/>
-      <c r="AG20" s="181"/>
-      <c r="AH20" s="181"/>
-      <c r="AI20" s="181"/>
-      <c r="AJ20" s="181"/>
-      <c r="AK20" s="181"/>
-      <c r="AL20" s="181"/>
+      <c r="J20" s="225"/>
+      <c r="K20" s="225"/>
+      <c r="L20" s="225"/>
+      <c r="M20" s="225"/>
+      <c r="N20" s="225"/>
+      <c r="O20" s="225"/>
+      <c r="P20" s="225"/>
+      <c r="Q20" s="225"/>
+      <c r="R20" s="225"/>
+      <c r="S20" s="225"/>
+      <c r="T20" s="225"/>
+      <c r="U20" s="225"/>
+      <c r="V20" s="225"/>
+      <c r="W20" s="225"/>
+      <c r="X20" s="225"/>
+      <c r="Y20" s="225"/>
+      <c r="Z20" s="225"/>
+      <c r="AA20" s="225"/>
+      <c r="AB20" s="225"/>
+      <c r="AC20" s="225"/>
+      <c r="AD20" s="225"/>
+      <c r="AE20" s="225"/>
+      <c r="AF20" s="225"/>
+      <c r="AG20" s="225"/>
+      <c r="AH20" s="225"/>
+      <c r="AI20" s="225"/>
+      <c r="AJ20" s="225"/>
+      <c r="AK20" s="225"/>
+      <c r="AL20" s="225"/>
     </row>
     <row r="21" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A21" s="180"/>
@@ -14702,35 +14711,35 @@
       <c r="G21" s="180"/>
       <c r="H21" s="180"/>
       <c r="I21" s="180"/>
-      <c r="J21" s="181"/>
-      <c r="K21" s="181"/>
-      <c r="L21" s="181"/>
-      <c r="M21" s="181"/>
-      <c r="N21" s="181"/>
-      <c r="O21" s="181"/>
-      <c r="P21" s="181"/>
-      <c r="Q21" s="181"/>
-      <c r="R21" s="181"/>
-      <c r="S21" s="181"/>
-      <c r="T21" s="181"/>
-      <c r="U21" s="181"/>
-      <c r="V21" s="181"/>
-      <c r="W21" s="181"/>
-      <c r="X21" s="181"/>
-      <c r="Y21" s="181"/>
-      <c r="Z21" s="181"/>
-      <c r="AA21" s="181"/>
-      <c r="AB21" s="181"/>
-      <c r="AC21" s="181"/>
-      <c r="AD21" s="181"/>
-      <c r="AE21" s="181"/>
-      <c r="AF21" s="181"/>
-      <c r="AG21" s="181"/>
-      <c r="AH21" s="181"/>
-      <c r="AI21" s="181"/>
-      <c r="AJ21" s="181"/>
-      <c r="AK21" s="181"/>
-      <c r="AL21" s="181"/>
+      <c r="J21" s="225"/>
+      <c r="K21" s="225"/>
+      <c r="L21" s="225"/>
+      <c r="M21" s="225"/>
+      <c r="N21" s="225"/>
+      <c r="O21" s="225"/>
+      <c r="P21" s="225"/>
+      <c r="Q21" s="225"/>
+      <c r="R21" s="225"/>
+      <c r="S21" s="225"/>
+      <c r="T21" s="225"/>
+      <c r="U21" s="225"/>
+      <c r="V21" s="225"/>
+      <c r="W21" s="225"/>
+      <c r="X21" s="225"/>
+      <c r="Y21" s="225"/>
+      <c r="Z21" s="225"/>
+      <c r="AA21" s="225"/>
+      <c r="AB21" s="225"/>
+      <c r="AC21" s="225"/>
+      <c r="AD21" s="225"/>
+      <c r="AE21" s="225"/>
+      <c r="AF21" s="225"/>
+      <c r="AG21" s="225"/>
+      <c r="AH21" s="225"/>
+      <c r="AI21" s="225"/>
+      <c r="AJ21" s="225"/>
+      <c r="AK21" s="225"/>
+      <c r="AL21" s="225"/>
     </row>
     <row r="22" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A22" s="180"/>
@@ -14742,35 +14751,35 @@
       <c r="G22" s="180"/>
       <c r="H22" s="180"/>
       <c r="I22" s="180"/>
-      <c r="J22" s="181"/>
-      <c r="K22" s="181"/>
-      <c r="L22" s="181"/>
-      <c r="M22" s="181"/>
-      <c r="N22" s="181"/>
-      <c r="O22" s="181"/>
-      <c r="P22" s="181"/>
-      <c r="Q22" s="181"/>
-      <c r="R22" s="181"/>
-      <c r="S22" s="181"/>
-      <c r="T22" s="181"/>
-      <c r="U22" s="181"/>
-      <c r="V22" s="181"/>
-      <c r="W22" s="181"/>
-      <c r="X22" s="181"/>
-      <c r="Y22" s="181"/>
-      <c r="Z22" s="181"/>
-      <c r="AA22" s="181"/>
-      <c r="AB22" s="181"/>
-      <c r="AC22" s="181"/>
-      <c r="AD22" s="181"/>
-      <c r="AE22" s="181"/>
-      <c r="AF22" s="181"/>
-      <c r="AG22" s="181"/>
-      <c r="AH22" s="181"/>
-      <c r="AI22" s="181"/>
-      <c r="AJ22" s="181"/>
-      <c r="AK22" s="181"/>
-      <c r="AL22" s="181"/>
+      <c r="J22" s="225"/>
+      <c r="K22" s="225"/>
+      <c r="L22" s="225"/>
+      <c r="M22" s="225"/>
+      <c r="N22" s="225"/>
+      <c r="O22" s="225"/>
+      <c r="P22" s="225"/>
+      <c r="Q22" s="225"/>
+      <c r="R22" s="225"/>
+      <c r="S22" s="225"/>
+      <c r="T22" s="225"/>
+      <c r="U22" s="225"/>
+      <c r="V22" s="225"/>
+      <c r="W22" s="225"/>
+      <c r="X22" s="225"/>
+      <c r="Y22" s="225"/>
+      <c r="Z22" s="225"/>
+      <c r="AA22" s="225"/>
+      <c r="AB22" s="225"/>
+      <c r="AC22" s="225"/>
+      <c r="AD22" s="225"/>
+      <c r="AE22" s="225"/>
+      <c r="AF22" s="225"/>
+      <c r="AG22" s="225"/>
+      <c r="AH22" s="225"/>
+      <c r="AI22" s="225"/>
+      <c r="AJ22" s="225"/>
+      <c r="AK22" s="225"/>
+      <c r="AL22" s="225"/>
     </row>
     <row r="23" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A23" s="180"/>
@@ -14782,35 +14791,35 @@
       <c r="G23" s="180"/>
       <c r="H23" s="180"/>
       <c r="I23" s="180"/>
-      <c r="J23" s="181"/>
-      <c r="K23" s="181"/>
-      <c r="L23" s="181"/>
-      <c r="M23" s="181"/>
-      <c r="N23" s="181"/>
-      <c r="O23" s="181"/>
-      <c r="P23" s="181"/>
-      <c r="Q23" s="181"/>
-      <c r="R23" s="181"/>
-      <c r="S23" s="181"/>
-      <c r="T23" s="181"/>
-      <c r="U23" s="181"/>
-      <c r="V23" s="181"/>
-      <c r="W23" s="181"/>
-      <c r="X23" s="181"/>
-      <c r="Y23" s="181"/>
-      <c r="Z23" s="181"/>
-      <c r="AA23" s="181"/>
-      <c r="AB23" s="181"/>
-      <c r="AC23" s="181"/>
-      <c r="AD23" s="181"/>
-      <c r="AE23" s="181"/>
-      <c r="AF23" s="181"/>
-      <c r="AG23" s="181"/>
-      <c r="AH23" s="181"/>
-      <c r="AI23" s="181"/>
-      <c r="AJ23" s="181"/>
-      <c r="AK23" s="181"/>
-      <c r="AL23" s="181"/>
+      <c r="J23" s="225"/>
+      <c r="K23" s="225"/>
+      <c r="L23" s="225"/>
+      <c r="M23" s="225"/>
+      <c r="N23" s="225"/>
+      <c r="O23" s="225"/>
+      <c r="P23" s="225"/>
+      <c r="Q23" s="225"/>
+      <c r="R23" s="225"/>
+      <c r="S23" s="225"/>
+      <c r="T23" s="225"/>
+      <c r="U23" s="225"/>
+      <c r="V23" s="225"/>
+      <c r="W23" s="225"/>
+      <c r="X23" s="225"/>
+      <c r="Y23" s="225"/>
+      <c r="Z23" s="225"/>
+      <c r="AA23" s="225"/>
+      <c r="AB23" s="225"/>
+      <c r="AC23" s="225"/>
+      <c r="AD23" s="225"/>
+      <c r="AE23" s="225"/>
+      <c r="AF23" s="225"/>
+      <c r="AG23" s="225"/>
+      <c r="AH23" s="225"/>
+      <c r="AI23" s="225"/>
+      <c r="AJ23" s="225"/>
+      <c r="AK23" s="225"/>
+      <c r="AL23" s="225"/>
     </row>
     <row r="24" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A24" s="180"/>
@@ -14822,35 +14831,35 @@
       <c r="G24" s="180"/>
       <c r="H24" s="180"/>
       <c r="I24" s="180"/>
-      <c r="J24" s="181"/>
-      <c r="K24" s="181"/>
-      <c r="L24" s="181"/>
-      <c r="M24" s="181"/>
-      <c r="N24" s="181"/>
-      <c r="O24" s="181"/>
-      <c r="P24" s="181"/>
-      <c r="Q24" s="181"/>
-      <c r="R24" s="181"/>
-      <c r="S24" s="181"/>
-      <c r="T24" s="181"/>
-      <c r="U24" s="181"/>
-      <c r="V24" s="181"/>
-      <c r="W24" s="181"/>
-      <c r="X24" s="181"/>
-      <c r="Y24" s="181"/>
-      <c r="Z24" s="181"/>
-      <c r="AA24" s="181"/>
-      <c r="AB24" s="181"/>
-      <c r="AC24" s="181"/>
-      <c r="AD24" s="181"/>
-      <c r="AE24" s="181"/>
-      <c r="AF24" s="181"/>
-      <c r="AG24" s="181"/>
-      <c r="AH24" s="181"/>
-      <c r="AI24" s="181"/>
-      <c r="AJ24" s="181"/>
-      <c r="AK24" s="181"/>
-      <c r="AL24" s="181"/>
+      <c r="J24" s="225"/>
+      <c r="K24" s="225"/>
+      <c r="L24" s="225"/>
+      <c r="M24" s="225"/>
+      <c r="N24" s="225"/>
+      <c r="O24" s="225"/>
+      <c r="P24" s="225"/>
+      <c r="Q24" s="225"/>
+      <c r="R24" s="225"/>
+      <c r="S24" s="225"/>
+      <c r="T24" s="225"/>
+      <c r="U24" s="225"/>
+      <c r="V24" s="225"/>
+      <c r="W24" s="225"/>
+      <c r="X24" s="225"/>
+      <c r="Y24" s="225"/>
+      <c r="Z24" s="225"/>
+      <c r="AA24" s="225"/>
+      <c r="AB24" s="225"/>
+      <c r="AC24" s="225"/>
+      <c r="AD24" s="225"/>
+      <c r="AE24" s="225"/>
+      <c r="AF24" s="225"/>
+      <c r="AG24" s="225"/>
+      <c r="AH24" s="225"/>
+      <c r="AI24" s="225"/>
+      <c r="AJ24" s="225"/>
+      <c r="AK24" s="225"/>
+      <c r="AL24" s="225"/>
     </row>
     <row r="25" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A25" s="180"/>
@@ -14862,35 +14871,35 @@
       <c r="G25" s="180"/>
       <c r="H25" s="180"/>
       <c r="I25" s="180"/>
-      <c r="J25" s="181"/>
-      <c r="K25" s="181"/>
-      <c r="L25" s="181"/>
-      <c r="M25" s="181"/>
-      <c r="N25" s="181"/>
-      <c r="O25" s="181"/>
-      <c r="P25" s="181"/>
-      <c r="Q25" s="181"/>
-      <c r="R25" s="181"/>
-      <c r="S25" s="181"/>
-      <c r="T25" s="181"/>
-      <c r="U25" s="181"/>
-      <c r="V25" s="181"/>
-      <c r="W25" s="181"/>
-      <c r="X25" s="181"/>
-      <c r="Y25" s="181"/>
-      <c r="Z25" s="181"/>
-      <c r="AA25" s="181"/>
-      <c r="AB25" s="181"/>
-      <c r="AC25" s="181"/>
-      <c r="AD25" s="181"/>
-      <c r="AE25" s="181"/>
-      <c r="AF25" s="181"/>
-      <c r="AG25" s="181"/>
-      <c r="AH25" s="181"/>
-      <c r="AI25" s="181"/>
-      <c r="AJ25" s="181"/>
-      <c r="AK25" s="181"/>
-      <c r="AL25" s="181"/>
+      <c r="J25" s="225"/>
+      <c r="K25" s="225"/>
+      <c r="L25" s="225"/>
+      <c r="M25" s="225"/>
+      <c r="N25" s="225"/>
+      <c r="O25" s="225"/>
+      <c r="P25" s="225"/>
+      <c r="Q25" s="225"/>
+      <c r="R25" s="225"/>
+      <c r="S25" s="225"/>
+      <c r="T25" s="225"/>
+      <c r="U25" s="225"/>
+      <c r="V25" s="225"/>
+      <c r="W25" s="225"/>
+      <c r="X25" s="225"/>
+      <c r="Y25" s="225"/>
+      <c r="Z25" s="225"/>
+      <c r="AA25" s="225"/>
+      <c r="AB25" s="225"/>
+      <c r="AC25" s="225"/>
+      <c r="AD25" s="225"/>
+      <c r="AE25" s="225"/>
+      <c r="AF25" s="225"/>
+      <c r="AG25" s="225"/>
+      <c r="AH25" s="225"/>
+      <c r="AI25" s="225"/>
+      <c r="AJ25" s="225"/>
+      <c r="AK25" s="225"/>
+      <c r="AL25" s="225"/>
     </row>
     <row r="26" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A26" s="180"/>
@@ -14902,35 +14911,35 @@
       <c r="G26" s="180"/>
       <c r="H26" s="180"/>
       <c r="I26" s="180"/>
-      <c r="J26" s="181"/>
-      <c r="K26" s="181"/>
-      <c r="L26" s="181"/>
-      <c r="M26" s="181"/>
-      <c r="N26" s="181"/>
-      <c r="O26" s="181"/>
-      <c r="P26" s="181"/>
-      <c r="Q26" s="181"/>
-      <c r="R26" s="181"/>
-      <c r="S26" s="181"/>
-      <c r="T26" s="181"/>
-      <c r="U26" s="181"/>
-      <c r="V26" s="181"/>
-      <c r="W26" s="181"/>
-      <c r="X26" s="181"/>
-      <c r="Y26" s="181"/>
-      <c r="Z26" s="181"/>
-      <c r="AA26" s="181"/>
-      <c r="AB26" s="181"/>
-      <c r="AC26" s="181"/>
-      <c r="AD26" s="181"/>
-      <c r="AE26" s="181"/>
-      <c r="AF26" s="181"/>
-      <c r="AG26" s="181"/>
-      <c r="AH26" s="181"/>
-      <c r="AI26" s="181"/>
-      <c r="AJ26" s="181"/>
-      <c r="AK26" s="181"/>
-      <c r="AL26" s="181"/>
+      <c r="J26" s="225"/>
+      <c r="K26" s="225"/>
+      <c r="L26" s="225"/>
+      <c r="M26" s="225"/>
+      <c r="N26" s="225"/>
+      <c r="O26" s="225"/>
+      <c r="P26" s="225"/>
+      <c r="Q26" s="225"/>
+      <c r="R26" s="225"/>
+      <c r="S26" s="225"/>
+      <c r="T26" s="225"/>
+      <c r="U26" s="225"/>
+      <c r="V26" s="225"/>
+      <c r="W26" s="225"/>
+      <c r="X26" s="225"/>
+      <c r="Y26" s="225"/>
+      <c r="Z26" s="225"/>
+      <c r="AA26" s="225"/>
+      <c r="AB26" s="225"/>
+      <c r="AC26" s="225"/>
+      <c r="AD26" s="225"/>
+      <c r="AE26" s="225"/>
+      <c r="AF26" s="225"/>
+      <c r="AG26" s="225"/>
+      <c r="AH26" s="225"/>
+      <c r="AI26" s="225"/>
+      <c r="AJ26" s="225"/>
+      <c r="AK26" s="225"/>
+      <c r="AL26" s="225"/>
     </row>
     <row r="27" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A27" s="180"/>
@@ -14942,35 +14951,35 @@
       <c r="G27" s="180"/>
       <c r="H27" s="180"/>
       <c r="I27" s="180"/>
-      <c r="J27" s="181"/>
-      <c r="K27" s="181"/>
-      <c r="L27" s="181"/>
-      <c r="M27" s="181"/>
-      <c r="N27" s="181"/>
-      <c r="O27" s="181"/>
-      <c r="P27" s="181"/>
-      <c r="Q27" s="181"/>
-      <c r="R27" s="181"/>
-      <c r="S27" s="181"/>
-      <c r="T27" s="181"/>
-      <c r="U27" s="181"/>
-      <c r="V27" s="181"/>
-      <c r="W27" s="181"/>
-      <c r="X27" s="181"/>
-      <c r="Y27" s="181"/>
-      <c r="Z27" s="181"/>
-      <c r="AA27" s="181"/>
-      <c r="AB27" s="181"/>
-      <c r="AC27" s="181"/>
-      <c r="AD27" s="181"/>
-      <c r="AE27" s="181"/>
-      <c r="AF27" s="181"/>
-      <c r="AG27" s="181"/>
-      <c r="AH27" s="181"/>
-      <c r="AI27" s="181"/>
-      <c r="AJ27" s="181"/>
-      <c r="AK27" s="181"/>
-      <c r="AL27" s="181"/>
+      <c r="J27" s="225"/>
+      <c r="K27" s="225"/>
+      <c r="L27" s="225"/>
+      <c r="M27" s="225"/>
+      <c r="N27" s="225"/>
+      <c r="O27" s="225"/>
+      <c r="P27" s="225"/>
+      <c r="Q27" s="225"/>
+      <c r="R27" s="225"/>
+      <c r="S27" s="225"/>
+      <c r="T27" s="225"/>
+      <c r="U27" s="225"/>
+      <c r="V27" s="225"/>
+      <c r="W27" s="225"/>
+      <c r="X27" s="225"/>
+      <c r="Y27" s="225"/>
+      <c r="Z27" s="225"/>
+      <c r="AA27" s="225"/>
+      <c r="AB27" s="225"/>
+      <c r="AC27" s="225"/>
+      <c r="AD27" s="225"/>
+      <c r="AE27" s="225"/>
+      <c r="AF27" s="225"/>
+      <c r="AG27" s="225"/>
+      <c r="AH27" s="225"/>
+      <c r="AI27" s="225"/>
+      <c r="AJ27" s="225"/>
+      <c r="AK27" s="225"/>
+      <c r="AL27" s="225"/>
     </row>
     <row r="28" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A28" s="180"/>
@@ -14982,35 +14991,35 @@
       <c r="G28" s="180"/>
       <c r="H28" s="180"/>
       <c r="I28" s="180"/>
-      <c r="J28" s="181"/>
-      <c r="K28" s="181"/>
-      <c r="L28" s="181"/>
-      <c r="M28" s="181"/>
-      <c r="N28" s="181"/>
-      <c r="O28" s="181"/>
-      <c r="P28" s="181"/>
-      <c r="Q28" s="181"/>
-      <c r="R28" s="181"/>
-      <c r="S28" s="181"/>
-      <c r="T28" s="181"/>
-      <c r="U28" s="181"/>
-      <c r="V28" s="181"/>
-      <c r="W28" s="181"/>
-      <c r="X28" s="181"/>
-      <c r="Y28" s="181"/>
-      <c r="Z28" s="181"/>
-      <c r="AA28" s="181"/>
-      <c r="AB28" s="181"/>
-      <c r="AC28" s="181"/>
-      <c r="AD28" s="181"/>
-      <c r="AE28" s="181"/>
-      <c r="AF28" s="181"/>
-      <c r="AG28" s="181"/>
-      <c r="AH28" s="181"/>
-      <c r="AI28" s="181"/>
-      <c r="AJ28" s="181"/>
-      <c r="AK28" s="181"/>
-      <c r="AL28" s="181"/>
+      <c r="J28" s="225"/>
+      <c r="K28" s="225"/>
+      <c r="L28" s="225"/>
+      <c r="M28" s="225"/>
+      <c r="N28" s="225"/>
+      <c r="O28" s="225"/>
+      <c r="P28" s="225"/>
+      <c r="Q28" s="225"/>
+      <c r="R28" s="225"/>
+      <c r="S28" s="225"/>
+      <c r="T28" s="225"/>
+      <c r="U28" s="225"/>
+      <c r="V28" s="225"/>
+      <c r="W28" s="225"/>
+      <c r="X28" s="225"/>
+      <c r="Y28" s="225"/>
+      <c r="Z28" s="225"/>
+      <c r="AA28" s="225"/>
+      <c r="AB28" s="225"/>
+      <c r="AC28" s="225"/>
+      <c r="AD28" s="225"/>
+      <c r="AE28" s="225"/>
+      <c r="AF28" s="225"/>
+      <c r="AG28" s="225"/>
+      <c r="AH28" s="225"/>
+      <c r="AI28" s="225"/>
+      <c r="AJ28" s="225"/>
+      <c r="AK28" s="225"/>
+      <c r="AL28" s="225"/>
     </row>
     <row r="29" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A29" s="180"/>
@@ -15022,35 +15031,35 @@
       <c r="G29" s="180"/>
       <c r="H29" s="180"/>
       <c r="I29" s="180"/>
-      <c r="J29" s="181"/>
-      <c r="K29" s="181"/>
-      <c r="L29" s="181"/>
-      <c r="M29" s="181"/>
-      <c r="N29" s="181"/>
-      <c r="O29" s="181"/>
-      <c r="P29" s="181"/>
-      <c r="Q29" s="181"/>
-      <c r="R29" s="181"/>
-      <c r="S29" s="181"/>
-      <c r="T29" s="181"/>
-      <c r="U29" s="181"/>
-      <c r="V29" s="181"/>
-      <c r="W29" s="181"/>
-      <c r="X29" s="181"/>
-      <c r="Y29" s="181"/>
-      <c r="Z29" s="181"/>
-      <c r="AA29" s="181"/>
-      <c r="AB29" s="181"/>
-      <c r="AC29" s="181"/>
-      <c r="AD29" s="181"/>
-      <c r="AE29" s="181"/>
-      <c r="AF29" s="181"/>
-      <c r="AG29" s="181"/>
-      <c r="AH29" s="181"/>
-      <c r="AI29" s="181"/>
-      <c r="AJ29" s="181"/>
-      <c r="AK29" s="181"/>
-      <c r="AL29" s="181"/>
+      <c r="J29" s="225"/>
+      <c r="K29" s="225"/>
+      <c r="L29" s="225"/>
+      <c r="M29" s="225"/>
+      <c r="N29" s="225"/>
+      <c r="O29" s="225"/>
+      <c r="P29" s="225"/>
+      <c r="Q29" s="225"/>
+      <c r="R29" s="225"/>
+      <c r="S29" s="225"/>
+      <c r="T29" s="225"/>
+      <c r="U29" s="225"/>
+      <c r="V29" s="225"/>
+      <c r="W29" s="225"/>
+      <c r="X29" s="225"/>
+      <c r="Y29" s="225"/>
+      <c r="Z29" s="225"/>
+      <c r="AA29" s="225"/>
+      <c r="AB29" s="225"/>
+      <c r="AC29" s="225"/>
+      <c r="AD29" s="225"/>
+      <c r="AE29" s="225"/>
+      <c r="AF29" s="225"/>
+      <c r="AG29" s="225"/>
+      <c r="AH29" s="225"/>
+      <c r="AI29" s="225"/>
+      <c r="AJ29" s="225"/>
+      <c r="AK29" s="225"/>
+      <c r="AL29" s="225"/>
     </row>
     <row r="30" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A30" s="180"/>
@@ -15062,35 +15071,35 @@
       <c r="G30" s="180"/>
       <c r="H30" s="180"/>
       <c r="I30" s="180"/>
-      <c r="J30" s="181"/>
-      <c r="K30" s="181"/>
-      <c r="L30" s="181"/>
-      <c r="M30" s="181"/>
-      <c r="N30" s="181"/>
-      <c r="O30" s="181"/>
-      <c r="P30" s="181"/>
-      <c r="Q30" s="181"/>
-      <c r="R30" s="181"/>
-      <c r="S30" s="181"/>
-      <c r="T30" s="181"/>
-      <c r="U30" s="181"/>
-      <c r="V30" s="181"/>
-      <c r="W30" s="181"/>
-      <c r="X30" s="181"/>
-      <c r="Y30" s="181"/>
-      <c r="Z30" s="181"/>
-      <c r="AA30" s="181"/>
-      <c r="AB30" s="181"/>
-      <c r="AC30" s="181"/>
-      <c r="AD30" s="181"/>
-      <c r="AE30" s="181"/>
-      <c r="AF30" s="181"/>
-      <c r="AG30" s="181"/>
-      <c r="AH30" s="181"/>
-      <c r="AI30" s="181"/>
-      <c r="AJ30" s="181"/>
-      <c r="AK30" s="181"/>
-      <c r="AL30" s="181"/>
+      <c r="J30" s="225"/>
+      <c r="K30" s="225"/>
+      <c r="L30" s="225"/>
+      <c r="M30" s="225"/>
+      <c r="N30" s="225"/>
+      <c r="O30" s="225"/>
+      <c r="P30" s="225"/>
+      <c r="Q30" s="225"/>
+      <c r="R30" s="225"/>
+      <c r="S30" s="225"/>
+      <c r="T30" s="225"/>
+      <c r="U30" s="225"/>
+      <c r="V30" s="225"/>
+      <c r="W30" s="225"/>
+      <c r="X30" s="225"/>
+      <c r="Y30" s="225"/>
+      <c r="Z30" s="225"/>
+      <c r="AA30" s="225"/>
+      <c r="AB30" s="225"/>
+      <c r="AC30" s="225"/>
+      <c r="AD30" s="225"/>
+      <c r="AE30" s="225"/>
+      <c r="AF30" s="225"/>
+      <c r="AG30" s="225"/>
+      <c r="AH30" s="225"/>
+      <c r="AI30" s="225"/>
+      <c r="AJ30" s="225"/>
+      <c r="AK30" s="225"/>
+      <c r="AL30" s="225"/>
     </row>
     <row r="31" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A31" s="180"/>
@@ -15102,35 +15111,35 @@
       <c r="G31" s="180"/>
       <c r="H31" s="180"/>
       <c r="I31" s="180"/>
-      <c r="J31" s="181"/>
-      <c r="K31" s="181"/>
-      <c r="L31" s="181"/>
-      <c r="M31" s="181"/>
-      <c r="N31" s="181"/>
-      <c r="O31" s="181"/>
-      <c r="P31" s="181"/>
-      <c r="Q31" s="181"/>
-      <c r="R31" s="181"/>
-      <c r="S31" s="181"/>
-      <c r="T31" s="181"/>
-      <c r="U31" s="181"/>
-      <c r="V31" s="181"/>
-      <c r="W31" s="181"/>
-      <c r="X31" s="181"/>
-      <c r="Y31" s="181"/>
-      <c r="Z31" s="181"/>
-      <c r="AA31" s="181"/>
-      <c r="AB31" s="181"/>
-      <c r="AC31" s="181"/>
-      <c r="AD31" s="181"/>
-      <c r="AE31" s="181"/>
-      <c r="AF31" s="181"/>
-      <c r="AG31" s="181"/>
-      <c r="AH31" s="181"/>
-      <c r="AI31" s="181"/>
-      <c r="AJ31" s="181"/>
-      <c r="AK31" s="181"/>
-      <c r="AL31" s="181"/>
+      <c r="J31" s="225"/>
+      <c r="K31" s="225"/>
+      <c r="L31" s="225"/>
+      <c r="M31" s="225"/>
+      <c r="N31" s="225"/>
+      <c r="O31" s="225"/>
+      <c r="P31" s="225"/>
+      <c r="Q31" s="225"/>
+      <c r="R31" s="225"/>
+      <c r="S31" s="225"/>
+      <c r="T31" s="225"/>
+      <c r="U31" s="225"/>
+      <c r="V31" s="225"/>
+      <c r="W31" s="225"/>
+      <c r="X31" s="225"/>
+      <c r="Y31" s="225"/>
+      <c r="Z31" s="225"/>
+      <c r="AA31" s="225"/>
+      <c r="AB31" s="225"/>
+      <c r="AC31" s="225"/>
+      <c r="AD31" s="225"/>
+      <c r="AE31" s="225"/>
+      <c r="AF31" s="225"/>
+      <c r="AG31" s="225"/>
+      <c r="AH31" s="225"/>
+      <c r="AI31" s="225"/>
+      <c r="AJ31" s="225"/>
+      <c r="AK31" s="225"/>
+      <c r="AL31" s="225"/>
     </row>
     <row r="32" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A32" s="92" t="s">
@@ -15597,32 +15606,32 @@
       <c r="J1" s="85"/>
       <c r="K1" s="85"/>
       <c r="L1" s="85"/>
-      <c r="M1" s="192"/>
-      <c r="N1" s="192"/>
-      <c r="O1" s="192"/>
-      <c r="P1" s="192"/>
-      <c r="Q1" s="192"/>
-      <c r="R1" s="192"/>
-      <c r="S1" s="192"/>
-      <c r="T1" s="192"/>
-      <c r="U1" s="192"/>
-      <c r="V1" s="192"/>
-      <c r="W1" s="192"/>
-      <c r="X1" s="192"/>
-      <c r="Y1" s="192"/>
-      <c r="Z1" s="192"/>
-      <c r="AA1" s="192"/>
-      <c r="AB1" s="192"/>
-      <c r="AC1" s="192"/>
-      <c r="AD1" s="192"/>
-      <c r="AE1" s="192"/>
-      <c r="AF1" s="192"/>
-      <c r="AG1" s="192"/>
-      <c r="AH1" s="192"/>
-      <c r="AI1" s="192"/>
-      <c r="AJ1" s="192"/>
-      <c r="AK1" s="192"/>
-      <c r="AL1" s="192"/>
+      <c r="M1" s="191"/>
+      <c r="N1" s="191"/>
+      <c r="O1" s="191"/>
+      <c r="P1" s="191"/>
+      <c r="Q1" s="191"/>
+      <c r="R1" s="191"/>
+      <c r="S1" s="191"/>
+      <c r="T1" s="191"/>
+      <c r="U1" s="191"/>
+      <c r="V1" s="191"/>
+      <c r="W1" s="191"/>
+      <c r="X1" s="191"/>
+      <c r="Y1" s="191"/>
+      <c r="Z1" s="191"/>
+      <c r="AA1" s="191"/>
+      <c r="AB1" s="191"/>
+      <c r="AC1" s="191"/>
+      <c r="AD1" s="191"/>
+      <c r="AE1" s="191"/>
+      <c r="AF1" s="191"/>
+      <c r="AG1" s="191"/>
+      <c r="AH1" s="191"/>
+      <c r="AI1" s="191"/>
+      <c r="AJ1" s="191"/>
+      <c r="AK1" s="191"/>
+      <c r="AL1" s="191"/>
     </row>
     <row r="2" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="86" t="s">
@@ -15752,96 +15761,96 @@
       <c r="AL4" s="89"/>
     </row>
     <row r="5" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="187" t="s">
+      <c r="A5" s="186" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="187"/>
-      <c r="C5" s="188"/>
-      <c r="D5" s="189"/>
-      <c r="E5" s="189"/>
-      <c r="F5" s="189"/>
-      <c r="G5" s="189"/>
-      <c r="H5" s="189"/>
-      <c r="I5" s="190"/>
-      <c r="J5" s="191"/>
-      <c r="K5" s="191"/>
-      <c r="L5" s="191"/>
-      <c r="M5" s="191"/>
-      <c r="N5" s="191"/>
-      <c r="O5" s="191"/>
-      <c r="P5" s="191"/>
-      <c r="Q5" s="191"/>
-      <c r="R5" s="191"/>
-      <c r="S5" s="191"/>
-      <c r="T5" s="191"/>
-      <c r="U5" s="191"/>
-      <c r="V5" s="191"/>
-      <c r="W5" s="191"/>
-      <c r="X5" s="191"/>
-      <c r="Y5" s="191"/>
-      <c r="Z5" s="191"/>
-      <c r="AA5" s="191"/>
-      <c r="AB5" s="191"/>
-      <c r="AC5" s="191"/>
-      <c r="AD5" s="191"/>
-      <c r="AE5" s="191"/>
-      <c r="AF5" s="191"/>
-      <c r="AG5" s="191"/>
-      <c r="AH5" s="191"/>
-      <c r="AI5" s="191"/>
-      <c r="AJ5" s="191"/>
-      <c r="AK5" s="191"/>
-      <c r="AL5" s="191"/>
+      <c r="B5" s="186"/>
+      <c r="C5" s="187"/>
+      <c r="D5" s="188"/>
+      <c r="E5" s="188"/>
+      <c r="F5" s="188"/>
+      <c r="G5" s="188"/>
+      <c r="H5" s="188"/>
+      <c r="I5" s="189"/>
+      <c r="J5" s="190"/>
+      <c r="K5" s="190"/>
+      <c r="L5" s="190"/>
+      <c r="M5" s="190"/>
+      <c r="N5" s="190"/>
+      <c r="O5" s="190"/>
+      <c r="P5" s="190"/>
+      <c r="Q5" s="190"/>
+      <c r="R5" s="190"/>
+      <c r="S5" s="190"/>
+      <c r="T5" s="190"/>
+      <c r="U5" s="190"/>
+      <c r="V5" s="190"/>
+      <c r="W5" s="190"/>
+      <c r="X5" s="190"/>
+      <c r="Y5" s="190"/>
+      <c r="Z5" s="190"/>
+      <c r="AA5" s="190"/>
+      <c r="AB5" s="190"/>
+      <c r="AC5" s="190"/>
+      <c r="AD5" s="190"/>
+      <c r="AE5" s="190"/>
+      <c r="AF5" s="190"/>
+      <c r="AG5" s="190"/>
+      <c r="AH5" s="190"/>
+      <c r="AI5" s="190"/>
+      <c r="AJ5" s="190"/>
+      <c r="AK5" s="190"/>
+      <c r="AL5" s="190"/>
     </row>
     <row r="6" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="186" t="s">
+      <c r="A6" s="185" t="s">
         <v>213</v>
       </c>
-      <c r="B6" s="184"/>
-      <c r="C6" s="184"/>
-      <c r="D6" s="184"/>
-      <c r="E6" s="184"/>
-      <c r="F6" s="184"/>
-      <c r="G6" s="184"/>
-      <c r="H6" s="184"/>
-      <c r="I6" s="185"/>
-      <c r="J6" s="182" t="s">
+      <c r="B6" s="183"/>
+      <c r="C6" s="183"/>
+      <c r="D6" s="183"/>
+      <c r="E6" s="183"/>
+      <c r="F6" s="183"/>
+      <c r="G6" s="183"/>
+      <c r="H6" s="183"/>
+      <c r="I6" s="184"/>
+      <c r="J6" s="181" t="s">
         <v>214</v>
       </c>
-      <c r="K6" s="183"/>
-      <c r="L6" s="183"/>
-      <c r="M6" s="183"/>
-      <c r="N6" s="183"/>
-      <c r="O6" s="183"/>
-      <c r="P6" s="183"/>
+      <c r="K6" s="182"/>
+      <c r="L6" s="182"/>
+      <c r="M6" s="182"/>
+      <c r="N6" s="182"/>
+      <c r="O6" s="182"/>
+      <c r="P6" s="182"/>
       <c r="Q6" s="91"/>
-      <c r="R6" s="184" t="s">
+      <c r="R6" s="183" t="s">
         <v>215</v>
       </c>
-      <c r="S6" s="184"/>
-      <c r="T6" s="184"/>
-      <c r="U6" s="184"/>
-      <c r="V6" s="184"/>
-      <c r="W6" s="184"/>
-      <c r="X6" s="185"/>
-      <c r="Y6" s="182" t="s">
+      <c r="S6" s="183"/>
+      <c r="T6" s="183"/>
+      <c r="U6" s="183"/>
+      <c r="V6" s="183"/>
+      <c r="W6" s="183"/>
+      <c r="X6" s="184"/>
+      <c r="Y6" s="181" t="s">
         <v>216</v>
       </c>
-      <c r="Z6" s="183"/>
-      <c r="AA6" s="183"/>
-      <c r="AB6" s="183"/>
-      <c r="AC6" s="183"/>
-      <c r="AD6" s="183"/>
-      <c r="AE6" s="183"/>
+      <c r="Z6" s="182"/>
+      <c r="AA6" s="182"/>
+      <c r="AB6" s="182"/>
+      <c r="AC6" s="182"/>
+      <c r="AD6" s="182"/>
+      <c r="AE6" s="182"/>
       <c r="AF6" s="91"/>
-      <c r="AG6" s="184" t="s">
+      <c r="AG6" s="183" t="s">
         <v>215</v>
       </c>
-      <c r="AH6" s="184"/>
-      <c r="AI6" s="184"/>
-      <c r="AJ6" s="184"/>
-      <c r="AK6" s="184"/>
-      <c r="AL6" s="185"/>
+      <c r="AH6" s="183"/>
+      <c r="AI6" s="183"/>
+      <c r="AJ6" s="183"/>
+      <c r="AK6" s="183"/>
+      <c r="AL6" s="184"/>
     </row>
     <row r="7" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="180"/>
@@ -15853,35 +15862,35 @@
       <c r="G7" s="180"/>
       <c r="H7" s="180"/>
       <c r="I7" s="180"/>
-      <c r="J7" s="181"/>
-      <c r="K7" s="181"/>
-      <c r="L7" s="181"/>
-      <c r="M7" s="181"/>
-      <c r="N7" s="181"/>
-      <c r="O7" s="181"/>
-      <c r="P7" s="181"/>
-      <c r="Q7" s="181"/>
-      <c r="R7" s="181"/>
-      <c r="S7" s="181"/>
-      <c r="T7" s="181"/>
-      <c r="U7" s="181"/>
-      <c r="V7" s="181"/>
-      <c r="W7" s="181"/>
-      <c r="X7" s="181"/>
-      <c r="Y7" s="181"/>
-      <c r="Z7" s="181"/>
-      <c r="AA7" s="181"/>
-      <c r="AB7" s="181"/>
-      <c r="AC7" s="181"/>
-      <c r="AD7" s="181"/>
-      <c r="AE7" s="181"/>
-      <c r="AF7" s="181"/>
-      <c r="AG7" s="181"/>
-      <c r="AH7" s="181"/>
-      <c r="AI7" s="181"/>
-      <c r="AJ7" s="181"/>
-      <c r="AK7" s="181"/>
-      <c r="AL7" s="181"/>
+      <c r="J7" s="225"/>
+      <c r="K7" s="225"/>
+      <c r="L7" s="225"/>
+      <c r="M7" s="225"/>
+      <c r="N7" s="225"/>
+      <c r="O7" s="225"/>
+      <c r="P7" s="225"/>
+      <c r="Q7" s="225"/>
+      <c r="R7" s="225"/>
+      <c r="S7" s="225"/>
+      <c r="T7" s="225"/>
+      <c r="U7" s="225"/>
+      <c r="V7" s="225"/>
+      <c r="W7" s="225"/>
+      <c r="X7" s="225"/>
+      <c r="Y7" s="225"/>
+      <c r="Z7" s="225"/>
+      <c r="AA7" s="225"/>
+      <c r="AB7" s="225"/>
+      <c r="AC7" s="225"/>
+      <c r="AD7" s="225"/>
+      <c r="AE7" s="225"/>
+      <c r="AF7" s="225"/>
+      <c r="AG7" s="225"/>
+      <c r="AH7" s="225"/>
+      <c r="AI7" s="225"/>
+      <c r="AJ7" s="225"/>
+      <c r="AK7" s="225"/>
+      <c r="AL7" s="225"/>
     </row>
     <row r="8" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="180"/>
@@ -15893,35 +15902,35 @@
       <c r="G8" s="180"/>
       <c r="H8" s="180"/>
       <c r="I8" s="180"/>
-      <c r="J8" s="181"/>
-      <c r="K8" s="181"/>
-      <c r="L8" s="181"/>
-      <c r="M8" s="181"/>
-      <c r="N8" s="181"/>
-      <c r="O8" s="181"/>
-      <c r="P8" s="181"/>
-      <c r="Q8" s="181"/>
-      <c r="R8" s="181"/>
-      <c r="S8" s="181"/>
-      <c r="T8" s="181"/>
-      <c r="U8" s="181"/>
-      <c r="V8" s="181"/>
-      <c r="W8" s="181"/>
-      <c r="X8" s="181"/>
-      <c r="Y8" s="181"/>
-      <c r="Z8" s="181"/>
-      <c r="AA8" s="181"/>
-      <c r="AB8" s="181"/>
-      <c r="AC8" s="181"/>
-      <c r="AD8" s="181"/>
-      <c r="AE8" s="181"/>
-      <c r="AF8" s="181"/>
-      <c r="AG8" s="181"/>
-      <c r="AH8" s="181"/>
-      <c r="AI8" s="181"/>
-      <c r="AJ8" s="181"/>
-      <c r="AK8" s="181"/>
-      <c r="AL8" s="181"/>
+      <c r="J8" s="225"/>
+      <c r="K8" s="225"/>
+      <c r="L8" s="225"/>
+      <c r="M8" s="225"/>
+      <c r="N8" s="225"/>
+      <c r="O8" s="225"/>
+      <c r="P8" s="225"/>
+      <c r="Q8" s="225"/>
+      <c r="R8" s="225"/>
+      <c r="S8" s="225"/>
+      <c r="T8" s="225"/>
+      <c r="U8" s="225"/>
+      <c r="V8" s="225"/>
+      <c r="W8" s="225"/>
+      <c r="X8" s="225"/>
+      <c r="Y8" s="225"/>
+      <c r="Z8" s="225"/>
+      <c r="AA8" s="225"/>
+      <c r="AB8" s="225"/>
+      <c r="AC8" s="225"/>
+      <c r="AD8" s="225"/>
+      <c r="AE8" s="225"/>
+      <c r="AF8" s="225"/>
+      <c r="AG8" s="225"/>
+      <c r="AH8" s="225"/>
+      <c r="AI8" s="225"/>
+      <c r="AJ8" s="225"/>
+      <c r="AK8" s="225"/>
+      <c r="AL8" s="225"/>
     </row>
     <row r="9" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="180"/>
@@ -15933,35 +15942,35 @@
       <c r="G9" s="180"/>
       <c r="H9" s="180"/>
       <c r="I9" s="180"/>
-      <c r="J9" s="181"/>
-      <c r="K9" s="181"/>
-      <c r="L9" s="181"/>
-      <c r="M9" s="181"/>
-      <c r="N9" s="181"/>
-      <c r="O9" s="181"/>
-      <c r="P9" s="181"/>
-      <c r="Q9" s="181"/>
-      <c r="R9" s="181"/>
-      <c r="S9" s="181"/>
-      <c r="T9" s="181"/>
-      <c r="U9" s="181"/>
-      <c r="V9" s="181"/>
-      <c r="W9" s="181"/>
-      <c r="X9" s="181"/>
-      <c r="Y9" s="181"/>
-      <c r="Z9" s="181"/>
-      <c r="AA9" s="181"/>
-      <c r="AB9" s="181"/>
-      <c r="AC9" s="181"/>
-      <c r="AD9" s="181"/>
-      <c r="AE9" s="181"/>
-      <c r="AF9" s="181"/>
-      <c r="AG9" s="181"/>
-      <c r="AH9" s="181"/>
-      <c r="AI9" s="181"/>
-      <c r="AJ9" s="181"/>
-      <c r="AK9" s="181"/>
-      <c r="AL9" s="181"/>
+      <c r="J9" s="225"/>
+      <c r="K9" s="225"/>
+      <c r="L9" s="225"/>
+      <c r="M9" s="225"/>
+      <c r="N9" s="225"/>
+      <c r="O9" s="225"/>
+      <c r="P9" s="225"/>
+      <c r="Q9" s="225"/>
+      <c r="R9" s="225"/>
+      <c r="S9" s="225"/>
+      <c r="T9" s="225"/>
+      <c r="U9" s="225"/>
+      <c r="V9" s="225"/>
+      <c r="W9" s="225"/>
+      <c r="X9" s="225"/>
+      <c r="Y9" s="225"/>
+      <c r="Z9" s="225"/>
+      <c r="AA9" s="225"/>
+      <c r="AB9" s="225"/>
+      <c r="AC9" s="225"/>
+      <c r="AD9" s="225"/>
+      <c r="AE9" s="225"/>
+      <c r="AF9" s="225"/>
+      <c r="AG9" s="225"/>
+      <c r="AH9" s="225"/>
+      <c r="AI9" s="225"/>
+      <c r="AJ9" s="225"/>
+      <c r="AK9" s="225"/>
+      <c r="AL9" s="225"/>
     </row>
     <row r="10" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="180"/>
@@ -15973,35 +15982,35 @@
       <c r="G10" s="180"/>
       <c r="H10" s="180"/>
       <c r="I10" s="180"/>
-      <c r="J10" s="181"/>
-      <c r="K10" s="181"/>
-      <c r="L10" s="181"/>
-      <c r="M10" s="181"/>
-      <c r="N10" s="181"/>
-      <c r="O10" s="181"/>
-      <c r="P10" s="181"/>
-      <c r="Q10" s="181"/>
-      <c r="R10" s="181"/>
-      <c r="S10" s="181"/>
-      <c r="T10" s="181"/>
-      <c r="U10" s="181"/>
-      <c r="V10" s="181"/>
-      <c r="W10" s="181"/>
-      <c r="X10" s="181"/>
-      <c r="Y10" s="181"/>
-      <c r="Z10" s="181"/>
-      <c r="AA10" s="181"/>
-      <c r="AB10" s="181"/>
-      <c r="AC10" s="181"/>
-      <c r="AD10" s="181"/>
-      <c r="AE10" s="181"/>
-      <c r="AF10" s="181"/>
-      <c r="AG10" s="181"/>
-      <c r="AH10" s="181"/>
-      <c r="AI10" s="181"/>
-      <c r="AJ10" s="181"/>
-      <c r="AK10" s="181"/>
-      <c r="AL10" s="181"/>
+      <c r="J10" s="225"/>
+      <c r="K10" s="225"/>
+      <c r="L10" s="225"/>
+      <c r="M10" s="225"/>
+      <c r="N10" s="225"/>
+      <c r="O10" s="225"/>
+      <c r="P10" s="225"/>
+      <c r="Q10" s="225"/>
+      <c r="R10" s="225"/>
+      <c r="S10" s="225"/>
+      <c r="T10" s="225"/>
+      <c r="U10" s="225"/>
+      <c r="V10" s="225"/>
+      <c r="W10" s="225"/>
+      <c r="X10" s="225"/>
+      <c r="Y10" s="225"/>
+      <c r="Z10" s="225"/>
+      <c r="AA10" s="225"/>
+      <c r="AB10" s="225"/>
+      <c r="AC10" s="225"/>
+      <c r="AD10" s="225"/>
+      <c r="AE10" s="225"/>
+      <c r="AF10" s="225"/>
+      <c r="AG10" s="225"/>
+      <c r="AH10" s="225"/>
+      <c r="AI10" s="225"/>
+      <c r="AJ10" s="225"/>
+      <c r="AK10" s="225"/>
+      <c r="AL10" s="225"/>
     </row>
     <row r="11" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="180"/>
@@ -16013,35 +16022,35 @@
       <c r="G11" s="180"/>
       <c r="H11" s="180"/>
       <c r="I11" s="180"/>
-      <c r="J11" s="181"/>
-      <c r="K11" s="181"/>
-      <c r="L11" s="181"/>
-      <c r="M11" s="181"/>
-      <c r="N11" s="181"/>
-      <c r="O11" s="181"/>
-      <c r="P11" s="181"/>
-      <c r="Q11" s="181"/>
-      <c r="R11" s="181"/>
-      <c r="S11" s="181"/>
-      <c r="T11" s="181"/>
-      <c r="U11" s="181"/>
-      <c r="V11" s="181"/>
-      <c r="W11" s="181"/>
-      <c r="X11" s="181"/>
-      <c r="Y11" s="181"/>
-      <c r="Z11" s="181"/>
-      <c r="AA11" s="181"/>
-      <c r="AB11" s="181"/>
-      <c r="AC11" s="181"/>
-      <c r="AD11" s="181"/>
-      <c r="AE11" s="181"/>
-      <c r="AF11" s="181"/>
-      <c r="AG11" s="181"/>
-      <c r="AH11" s="181"/>
-      <c r="AI11" s="181"/>
-      <c r="AJ11" s="181"/>
-      <c r="AK11" s="181"/>
-      <c r="AL11" s="181"/>
+      <c r="J11" s="225"/>
+      <c r="K11" s="225"/>
+      <c r="L11" s="225"/>
+      <c r="M11" s="225"/>
+      <c r="N11" s="225"/>
+      <c r="O11" s="225"/>
+      <c r="P11" s="225"/>
+      <c r="Q11" s="225"/>
+      <c r="R11" s="225"/>
+      <c r="S11" s="225"/>
+      <c r="T11" s="225"/>
+      <c r="U11" s="225"/>
+      <c r="V11" s="225"/>
+      <c r="W11" s="225"/>
+      <c r="X11" s="225"/>
+      <c r="Y11" s="225"/>
+      <c r="Z11" s="225"/>
+      <c r="AA11" s="225"/>
+      <c r="AB11" s="225"/>
+      <c r="AC11" s="225"/>
+      <c r="AD11" s="225"/>
+      <c r="AE11" s="225"/>
+      <c r="AF11" s="225"/>
+      <c r="AG11" s="225"/>
+      <c r="AH11" s="225"/>
+      <c r="AI11" s="225"/>
+      <c r="AJ11" s="225"/>
+      <c r="AK11" s="225"/>
+      <c r="AL11" s="225"/>
     </row>
     <row r="12" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="180"/>
@@ -16053,35 +16062,35 @@
       <c r="G12" s="180"/>
       <c r="H12" s="180"/>
       <c r="I12" s="180"/>
-      <c r="J12" s="181"/>
-      <c r="K12" s="181"/>
-      <c r="L12" s="181"/>
-      <c r="M12" s="181"/>
-      <c r="N12" s="181"/>
-      <c r="O12" s="181"/>
-      <c r="P12" s="181"/>
-      <c r="Q12" s="181"/>
-      <c r="R12" s="181"/>
-      <c r="S12" s="181"/>
-      <c r="T12" s="181"/>
-      <c r="U12" s="181"/>
-      <c r="V12" s="181"/>
-      <c r="W12" s="181"/>
-      <c r="X12" s="181"/>
-      <c r="Y12" s="181"/>
-      <c r="Z12" s="181"/>
-      <c r="AA12" s="181"/>
-      <c r="AB12" s="181"/>
-      <c r="AC12" s="181"/>
-      <c r="AD12" s="181"/>
-      <c r="AE12" s="181"/>
-      <c r="AF12" s="181"/>
-      <c r="AG12" s="181"/>
-      <c r="AH12" s="181"/>
-      <c r="AI12" s="181"/>
-      <c r="AJ12" s="181"/>
-      <c r="AK12" s="181"/>
-      <c r="AL12" s="181"/>
+      <c r="J12" s="225"/>
+      <c r="K12" s="225"/>
+      <c r="L12" s="225"/>
+      <c r="M12" s="225"/>
+      <c r="N12" s="225"/>
+      <c r="O12" s="225"/>
+      <c r="P12" s="225"/>
+      <c r="Q12" s="225"/>
+      <c r="R12" s="225"/>
+      <c r="S12" s="225"/>
+      <c r="T12" s="225"/>
+      <c r="U12" s="225"/>
+      <c r="V12" s="225"/>
+      <c r="W12" s="225"/>
+      <c r="X12" s="225"/>
+      <c r="Y12" s="225"/>
+      <c r="Z12" s="225"/>
+      <c r="AA12" s="225"/>
+      <c r="AB12" s="225"/>
+      <c r="AC12" s="225"/>
+      <c r="AD12" s="225"/>
+      <c r="AE12" s="225"/>
+      <c r="AF12" s="225"/>
+      <c r="AG12" s="225"/>
+      <c r="AH12" s="225"/>
+      <c r="AI12" s="225"/>
+      <c r="AJ12" s="225"/>
+      <c r="AK12" s="225"/>
+      <c r="AL12" s="225"/>
     </row>
     <row r="13" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="180"/>
@@ -16093,35 +16102,35 @@
       <c r="G13" s="180"/>
       <c r="H13" s="180"/>
       <c r="I13" s="180"/>
-      <c r="J13" s="181"/>
-      <c r="K13" s="181"/>
-      <c r="L13" s="181"/>
-      <c r="M13" s="181"/>
-      <c r="N13" s="181"/>
-      <c r="O13" s="181"/>
-      <c r="P13" s="181"/>
-      <c r="Q13" s="181"/>
-      <c r="R13" s="181"/>
-      <c r="S13" s="181"/>
-      <c r="T13" s="181"/>
-      <c r="U13" s="181"/>
-      <c r="V13" s="181"/>
-      <c r="W13" s="181"/>
-      <c r="X13" s="181"/>
-      <c r="Y13" s="181"/>
-      <c r="Z13" s="181"/>
-      <c r="AA13" s="181"/>
-      <c r="AB13" s="181"/>
-      <c r="AC13" s="181"/>
-      <c r="AD13" s="181"/>
-      <c r="AE13" s="181"/>
-      <c r="AF13" s="181"/>
-      <c r="AG13" s="181"/>
-      <c r="AH13" s="181"/>
-      <c r="AI13" s="181"/>
-      <c r="AJ13" s="181"/>
-      <c r="AK13" s="181"/>
-      <c r="AL13" s="181"/>
+      <c r="J13" s="225"/>
+      <c r="K13" s="225"/>
+      <c r="L13" s="225"/>
+      <c r="M13" s="225"/>
+      <c r="N13" s="225"/>
+      <c r="O13" s="225"/>
+      <c r="P13" s="225"/>
+      <c r="Q13" s="225"/>
+      <c r="R13" s="225"/>
+      <c r="S13" s="225"/>
+      <c r="T13" s="225"/>
+      <c r="U13" s="225"/>
+      <c r="V13" s="225"/>
+      <c r="W13" s="225"/>
+      <c r="X13" s="225"/>
+      <c r="Y13" s="225"/>
+      <c r="Z13" s="225"/>
+      <c r="AA13" s="225"/>
+      <c r="AB13" s="225"/>
+      <c r="AC13" s="225"/>
+      <c r="AD13" s="225"/>
+      <c r="AE13" s="225"/>
+      <c r="AF13" s="225"/>
+      <c r="AG13" s="225"/>
+      <c r="AH13" s="225"/>
+      <c r="AI13" s="225"/>
+      <c r="AJ13" s="225"/>
+      <c r="AK13" s="225"/>
+      <c r="AL13" s="225"/>
     </row>
     <row r="14" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="180"/>
@@ -16133,35 +16142,35 @@
       <c r="G14" s="180"/>
       <c r="H14" s="180"/>
       <c r="I14" s="180"/>
-      <c r="J14" s="181"/>
-      <c r="K14" s="181"/>
-      <c r="L14" s="181"/>
-      <c r="M14" s="181"/>
-      <c r="N14" s="181"/>
-      <c r="O14" s="181"/>
-      <c r="P14" s="181"/>
-      <c r="Q14" s="181"/>
-      <c r="R14" s="181"/>
-      <c r="S14" s="181"/>
-      <c r="T14" s="181"/>
-      <c r="U14" s="181"/>
-      <c r="V14" s="181"/>
-      <c r="W14" s="181"/>
-      <c r="X14" s="181"/>
-      <c r="Y14" s="181"/>
-      <c r="Z14" s="181"/>
-      <c r="AA14" s="181"/>
-      <c r="AB14" s="181"/>
-      <c r="AC14" s="181"/>
-      <c r="AD14" s="181"/>
-      <c r="AE14" s="181"/>
-      <c r="AF14" s="181"/>
-      <c r="AG14" s="181"/>
-      <c r="AH14" s="181"/>
-      <c r="AI14" s="181"/>
-      <c r="AJ14" s="181"/>
-      <c r="AK14" s="181"/>
-      <c r="AL14" s="181"/>
+      <c r="J14" s="225"/>
+      <c r="K14" s="225"/>
+      <c r="L14" s="225"/>
+      <c r="M14" s="225"/>
+      <c r="N14" s="225"/>
+      <c r="O14" s="225"/>
+      <c r="P14" s="225"/>
+      <c r="Q14" s="225"/>
+      <c r="R14" s="225"/>
+      <c r="S14" s="225"/>
+      <c r="T14" s="225"/>
+      <c r="U14" s="225"/>
+      <c r="V14" s="225"/>
+      <c r="W14" s="225"/>
+      <c r="X14" s="225"/>
+      <c r="Y14" s="225"/>
+      <c r="Z14" s="225"/>
+      <c r="AA14" s="225"/>
+      <c r="AB14" s="225"/>
+      <c r="AC14" s="225"/>
+      <c r="AD14" s="225"/>
+      <c r="AE14" s="225"/>
+      <c r="AF14" s="225"/>
+      <c r="AG14" s="225"/>
+      <c r="AH14" s="225"/>
+      <c r="AI14" s="225"/>
+      <c r="AJ14" s="225"/>
+      <c r="AK14" s="225"/>
+      <c r="AL14" s="225"/>
     </row>
     <row r="15" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="180"/>
@@ -16173,35 +16182,35 @@
       <c r="G15" s="180"/>
       <c r="H15" s="180"/>
       <c r="I15" s="180"/>
-      <c r="J15" s="181"/>
-      <c r="K15" s="181"/>
-      <c r="L15" s="181"/>
-      <c r="M15" s="181"/>
-      <c r="N15" s="181"/>
-      <c r="O15" s="181"/>
-      <c r="P15" s="181"/>
-      <c r="Q15" s="181"/>
-      <c r="R15" s="181"/>
-      <c r="S15" s="181"/>
-      <c r="T15" s="181"/>
-      <c r="U15" s="181"/>
-      <c r="V15" s="181"/>
-      <c r="W15" s="181"/>
-      <c r="X15" s="181"/>
-      <c r="Y15" s="181"/>
-      <c r="Z15" s="181"/>
-      <c r="AA15" s="181"/>
-      <c r="AB15" s="181"/>
-      <c r="AC15" s="181"/>
-      <c r="AD15" s="181"/>
-      <c r="AE15" s="181"/>
-      <c r="AF15" s="181"/>
-      <c r="AG15" s="181"/>
-      <c r="AH15" s="181"/>
-      <c r="AI15" s="181"/>
-      <c r="AJ15" s="181"/>
-      <c r="AK15" s="181"/>
-      <c r="AL15" s="181"/>
+      <c r="J15" s="225"/>
+      <c r="K15" s="225"/>
+      <c r="L15" s="225"/>
+      <c r="M15" s="225"/>
+      <c r="N15" s="225"/>
+      <c r="O15" s="225"/>
+      <c r="P15" s="225"/>
+      <c r="Q15" s="225"/>
+      <c r="R15" s="225"/>
+      <c r="S15" s="225"/>
+      <c r="T15" s="225"/>
+      <c r="U15" s="225"/>
+      <c r="V15" s="225"/>
+      <c r="W15" s="225"/>
+      <c r="X15" s="225"/>
+      <c r="Y15" s="225"/>
+      <c r="Z15" s="225"/>
+      <c r="AA15" s="225"/>
+      <c r="AB15" s="225"/>
+      <c r="AC15" s="225"/>
+      <c r="AD15" s="225"/>
+      <c r="AE15" s="225"/>
+      <c r="AF15" s="225"/>
+      <c r="AG15" s="225"/>
+      <c r="AH15" s="225"/>
+      <c r="AI15" s="225"/>
+      <c r="AJ15" s="225"/>
+      <c r="AK15" s="225"/>
+      <c r="AL15" s="225"/>
     </row>
     <row r="16" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="180"/>
@@ -16213,35 +16222,35 @@
       <c r="G16" s="180"/>
       <c r="H16" s="180"/>
       <c r="I16" s="180"/>
-      <c r="J16" s="181"/>
-      <c r="K16" s="181"/>
-      <c r="L16" s="181"/>
-      <c r="M16" s="181"/>
-      <c r="N16" s="181"/>
-      <c r="O16" s="181"/>
-      <c r="P16" s="181"/>
-      <c r="Q16" s="181"/>
-      <c r="R16" s="181"/>
-      <c r="S16" s="181"/>
-      <c r="T16" s="181"/>
-      <c r="U16" s="181"/>
-      <c r="V16" s="181"/>
-      <c r="W16" s="181"/>
-      <c r="X16" s="181"/>
-      <c r="Y16" s="181"/>
-      <c r="Z16" s="181"/>
-      <c r="AA16" s="181"/>
-      <c r="AB16" s="181"/>
-      <c r="AC16" s="181"/>
-      <c r="AD16" s="181"/>
-      <c r="AE16" s="181"/>
-      <c r="AF16" s="181"/>
-      <c r="AG16" s="181"/>
-      <c r="AH16" s="181"/>
-      <c r="AI16" s="181"/>
-      <c r="AJ16" s="181"/>
-      <c r="AK16" s="181"/>
-      <c r="AL16" s="181"/>
+      <c r="J16" s="225"/>
+      <c r="K16" s="225"/>
+      <c r="L16" s="225"/>
+      <c r="M16" s="225"/>
+      <c r="N16" s="225"/>
+      <c r="O16" s="225"/>
+      <c r="P16" s="225"/>
+      <c r="Q16" s="225"/>
+      <c r="R16" s="225"/>
+      <c r="S16" s="225"/>
+      <c r="T16" s="225"/>
+      <c r="U16" s="225"/>
+      <c r="V16" s="225"/>
+      <c r="W16" s="225"/>
+      <c r="X16" s="225"/>
+      <c r="Y16" s="225"/>
+      <c r="Z16" s="225"/>
+      <c r="AA16" s="225"/>
+      <c r="AB16" s="225"/>
+      <c r="AC16" s="225"/>
+      <c r="AD16" s="225"/>
+      <c r="AE16" s="225"/>
+      <c r="AF16" s="225"/>
+      <c r="AG16" s="225"/>
+      <c r="AH16" s="225"/>
+      <c r="AI16" s="225"/>
+      <c r="AJ16" s="225"/>
+      <c r="AK16" s="225"/>
+      <c r="AL16" s="225"/>
     </row>
     <row r="17" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="180"/>
@@ -16253,35 +16262,35 @@
       <c r="G17" s="180"/>
       <c r="H17" s="180"/>
       <c r="I17" s="180"/>
-      <c r="J17" s="181"/>
-      <c r="K17" s="181"/>
-      <c r="L17" s="181"/>
-      <c r="M17" s="181"/>
-      <c r="N17" s="181"/>
-      <c r="O17" s="181"/>
-      <c r="P17" s="181"/>
-      <c r="Q17" s="181"/>
-      <c r="R17" s="181"/>
-      <c r="S17" s="181"/>
-      <c r="T17" s="181"/>
-      <c r="U17" s="181"/>
-      <c r="V17" s="181"/>
-      <c r="W17" s="181"/>
-      <c r="X17" s="181"/>
-      <c r="Y17" s="181"/>
-      <c r="Z17" s="181"/>
-      <c r="AA17" s="181"/>
-      <c r="AB17" s="181"/>
-      <c r="AC17" s="181"/>
-      <c r="AD17" s="181"/>
-      <c r="AE17" s="181"/>
-      <c r="AF17" s="181"/>
-      <c r="AG17" s="181"/>
-      <c r="AH17" s="181"/>
-      <c r="AI17" s="181"/>
-      <c r="AJ17" s="181"/>
-      <c r="AK17" s="181"/>
-      <c r="AL17" s="181"/>
+      <c r="J17" s="225"/>
+      <c r="K17" s="225"/>
+      <c r="L17" s="225"/>
+      <c r="M17" s="225"/>
+      <c r="N17" s="225"/>
+      <c r="O17" s="225"/>
+      <c r="P17" s="225"/>
+      <c r="Q17" s="225"/>
+      <c r="R17" s="225"/>
+      <c r="S17" s="225"/>
+      <c r="T17" s="225"/>
+      <c r="U17" s="225"/>
+      <c r="V17" s="225"/>
+      <c r="W17" s="225"/>
+      <c r="X17" s="225"/>
+      <c r="Y17" s="225"/>
+      <c r="Z17" s="225"/>
+      <c r="AA17" s="225"/>
+      <c r="AB17" s="225"/>
+      <c r="AC17" s="225"/>
+      <c r="AD17" s="225"/>
+      <c r="AE17" s="225"/>
+      <c r="AF17" s="225"/>
+      <c r="AG17" s="225"/>
+      <c r="AH17" s="225"/>
+      <c r="AI17" s="225"/>
+      <c r="AJ17" s="225"/>
+      <c r="AK17" s="225"/>
+      <c r="AL17" s="225"/>
     </row>
     <row r="18" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="180"/>
@@ -16293,35 +16302,35 @@
       <c r="G18" s="180"/>
       <c r="H18" s="180"/>
       <c r="I18" s="180"/>
-      <c r="J18" s="181"/>
-      <c r="K18" s="181"/>
-      <c r="L18" s="181"/>
-      <c r="M18" s="181"/>
-      <c r="N18" s="181"/>
-      <c r="O18" s="181"/>
-      <c r="P18" s="181"/>
-      <c r="Q18" s="181"/>
-      <c r="R18" s="181"/>
-      <c r="S18" s="181"/>
-      <c r="T18" s="181"/>
-      <c r="U18" s="181"/>
-      <c r="V18" s="181"/>
-      <c r="W18" s="181"/>
-      <c r="X18" s="181"/>
-      <c r="Y18" s="181"/>
-      <c r="Z18" s="181"/>
-      <c r="AA18" s="181"/>
-      <c r="AB18" s="181"/>
-      <c r="AC18" s="181"/>
-      <c r="AD18" s="181"/>
-      <c r="AE18" s="181"/>
-      <c r="AF18" s="181"/>
-      <c r="AG18" s="181"/>
-      <c r="AH18" s="181"/>
-      <c r="AI18" s="181"/>
-      <c r="AJ18" s="181"/>
-      <c r="AK18" s="181"/>
-      <c r="AL18" s="181"/>
+      <c r="J18" s="225"/>
+      <c r="K18" s="225"/>
+      <c r="L18" s="225"/>
+      <c r="M18" s="225"/>
+      <c r="N18" s="225"/>
+      <c r="O18" s="225"/>
+      <c r="P18" s="225"/>
+      <c r="Q18" s="225"/>
+      <c r="R18" s="225"/>
+      <c r="S18" s="225"/>
+      <c r="T18" s="225"/>
+      <c r="U18" s="225"/>
+      <c r="V18" s="225"/>
+      <c r="W18" s="225"/>
+      <c r="X18" s="225"/>
+      <c r="Y18" s="225"/>
+      <c r="Z18" s="225"/>
+      <c r="AA18" s="225"/>
+      <c r="AB18" s="225"/>
+      <c r="AC18" s="225"/>
+      <c r="AD18" s="225"/>
+      <c r="AE18" s="225"/>
+      <c r="AF18" s="225"/>
+      <c r="AG18" s="225"/>
+      <c r="AH18" s="225"/>
+      <c r="AI18" s="225"/>
+      <c r="AJ18" s="225"/>
+      <c r="AK18" s="225"/>
+      <c r="AL18" s="225"/>
     </row>
     <row r="19" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="92" t="s">
@@ -17027,146 +17036,146 @@
       <c r="AL6" s="84"/>
     </row>
     <row r="7" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="199" t="s">
+      <c r="A7" s="198" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="200"/>
-      <c r="C7" s="200"/>
-      <c r="D7" s="201"/>
-      <c r="E7" s="205" t="s">
+      <c r="B7" s="199"/>
+      <c r="C7" s="199"/>
+      <c r="D7" s="200"/>
+      <c r="E7" s="204" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="206"/>
-      <c r="G7" s="206"/>
-      <c r="H7" s="206"/>
-      <c r="I7" s="206"/>
-      <c r="J7" s="206"/>
-      <c r="K7" s="206"/>
-      <c r="L7" s="206"/>
-      <c r="M7" s="206"/>
-      <c r="N7" s="206"/>
-      <c r="O7" s="206"/>
-      <c r="P7" s="206"/>
-      <c r="Q7" s="206"/>
-      <c r="R7" s="206"/>
-      <c r="S7" s="206"/>
-      <c r="T7" s="206"/>
-      <c r="U7" s="206"/>
-      <c r="V7" s="206"/>
-      <c r="W7" s="206"/>
-      <c r="X7" s="206"/>
-      <c r="Y7" s="206"/>
-      <c r="Z7" s="206"/>
-      <c r="AA7" s="206"/>
-      <c r="AB7" s="206"/>
-      <c r="AC7" s="206"/>
-      <c r="AD7" s="206"/>
-      <c r="AE7" s="206"/>
-      <c r="AF7" s="206"/>
-      <c r="AG7" s="206"/>
-      <c r="AH7" s="207"/>
-      <c r="AI7" s="199" t="s">
+      <c r="F7" s="205"/>
+      <c r="G7" s="205"/>
+      <c r="H7" s="205"/>
+      <c r="I7" s="205"/>
+      <c r="J7" s="205"/>
+      <c r="K7" s="205"/>
+      <c r="L7" s="205"/>
+      <c r="M7" s="205"/>
+      <c r="N7" s="205"/>
+      <c r="O7" s="205"/>
+      <c r="P7" s="205"/>
+      <c r="Q7" s="205"/>
+      <c r="R7" s="205"/>
+      <c r="S7" s="205"/>
+      <c r="T7" s="205"/>
+      <c r="U7" s="205"/>
+      <c r="V7" s="205"/>
+      <c r="W7" s="205"/>
+      <c r="X7" s="205"/>
+      <c r="Y7" s="205"/>
+      <c r="Z7" s="205"/>
+      <c r="AA7" s="205"/>
+      <c r="AB7" s="205"/>
+      <c r="AC7" s="205"/>
+      <c r="AD7" s="205"/>
+      <c r="AE7" s="205"/>
+      <c r="AF7" s="205"/>
+      <c r="AG7" s="205"/>
+      <c r="AH7" s="206"/>
+      <c r="AI7" s="198" t="s">
         <v>19</v>
       </c>
-      <c r="AJ7" s="200"/>
-      <c r="AK7" s="200"/>
-      <c r="AL7" s="201"/>
+      <c r="AJ7" s="199"/>
+      <c r="AK7" s="199"/>
+      <c r="AL7" s="200"/>
     </row>
     <row r="8" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="202"/>
-      <c r="B8" s="203"/>
-      <c r="C8" s="203"/>
-      <c r="D8" s="204"/>
-      <c r="E8" s="193" t="s">
+      <c r="A8" s="201"/>
+      <c r="B8" s="202"/>
+      <c r="C8" s="202"/>
+      <c r="D8" s="203"/>
+      <c r="E8" s="192" t="s">
         <v>199</v>
       </c>
-      <c r="F8" s="194"/>
-      <c r="G8" s="194"/>
-      <c r="H8" s="194"/>
-      <c r="I8" s="194"/>
-      <c r="J8" s="195"/>
-      <c r="K8" s="193" t="s">
+      <c r="F8" s="193"/>
+      <c r="G8" s="193"/>
+      <c r="H8" s="193"/>
+      <c r="I8" s="193"/>
+      <c r="J8" s="194"/>
+      <c r="K8" s="192" t="s">
         <v>201</v>
       </c>
-      <c r="L8" s="194"/>
-      <c r="M8" s="194"/>
-      <c r="N8" s="194"/>
-      <c r="O8" s="194"/>
-      <c r="P8" s="195"/>
-      <c r="Q8" s="193" t="s">
+      <c r="L8" s="193"/>
+      <c r="M8" s="193"/>
+      <c r="N8" s="193"/>
+      <c r="O8" s="193"/>
+      <c r="P8" s="194"/>
+      <c r="Q8" s="192" t="s">
         <v>202</v>
       </c>
-      <c r="R8" s="194"/>
-      <c r="S8" s="194"/>
-      <c r="T8" s="194"/>
-      <c r="U8" s="194"/>
-      <c r="V8" s="195"/>
-      <c r="W8" s="193" t="s">
+      <c r="R8" s="193"/>
+      <c r="S8" s="193"/>
+      <c r="T8" s="193"/>
+      <c r="U8" s="193"/>
+      <c r="V8" s="194"/>
+      <c r="W8" s="192" t="s">
         <v>203</v>
       </c>
-      <c r="X8" s="194"/>
-      <c r="Y8" s="194"/>
-      <c r="Z8" s="194"/>
-      <c r="AA8" s="194"/>
-      <c r="AB8" s="195"/>
-      <c r="AC8" s="193" t="s">
+      <c r="X8" s="193"/>
+      <c r="Y8" s="193"/>
+      <c r="Z8" s="193"/>
+      <c r="AA8" s="193"/>
+      <c r="AB8" s="194"/>
+      <c r="AC8" s="192" t="s">
         <v>200</v>
       </c>
-      <c r="AD8" s="194"/>
-      <c r="AE8" s="194"/>
-      <c r="AF8" s="194"/>
-      <c r="AG8" s="194"/>
-      <c r="AH8" s="195"/>
-      <c r="AI8" s="202"/>
-      <c r="AJ8" s="203"/>
-      <c r="AK8" s="203"/>
-      <c r="AL8" s="204"/>
+      <c r="AD8" s="193"/>
+      <c r="AE8" s="193"/>
+      <c r="AF8" s="193"/>
+      <c r="AG8" s="193"/>
+      <c r="AH8" s="194"/>
+      <c r="AI8" s="201"/>
+      <c r="AJ8" s="202"/>
+      <c r="AK8" s="202"/>
+      <c r="AL8" s="203"/>
     </row>
     <row r="9" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="196"/>
-      <c r="B9" s="197"/>
-      <c r="C9" s="197"/>
-      <c r="D9" s="198"/>
-      <c r="E9" s="193"/>
-      <c r="F9" s="194"/>
-      <c r="G9" s="194"/>
-      <c r="H9" s="194"/>
-      <c r="I9" s="194"/>
-      <c r="J9" s="195"/>
-      <c r="K9" s="193"/>
-      <c r="L9" s="194"/>
-      <c r="M9" s="194"/>
-      <c r="N9" s="194"/>
-      <c r="O9" s="194"/>
-      <c r="P9" s="195"/>
-      <c r="Q9" s="193"/>
-      <c r="R9" s="194"/>
-      <c r="S9" s="194"/>
-      <c r="T9" s="194"/>
-      <c r="U9" s="194"/>
-      <c r="V9" s="195"/>
-      <c r="W9" s="193"/>
-      <c r="X9" s="194"/>
-      <c r="Y9" s="194"/>
-      <c r="Z9" s="194"/>
-      <c r="AA9" s="194"/>
-      <c r="AB9" s="195"/>
-      <c r="AC9" s="193"/>
-      <c r="AD9" s="194"/>
-      <c r="AE9" s="194"/>
-      <c r="AF9" s="194"/>
-      <c r="AG9" s="194"/>
-      <c r="AH9" s="195"/>
-      <c r="AI9" s="193"/>
-      <c r="AJ9" s="194"/>
-      <c r="AK9" s="194"/>
-      <c r="AL9" s="195"/>
+      <c r="A9" s="195"/>
+      <c r="B9" s="196"/>
+      <c r="C9" s="196"/>
+      <c r="D9" s="197"/>
+      <c r="E9" s="192"/>
+      <c r="F9" s="193"/>
+      <c r="G9" s="193"/>
+      <c r="H9" s="193"/>
+      <c r="I9" s="193"/>
+      <c r="J9" s="194"/>
+      <c r="K9" s="192"/>
+      <c r="L9" s="193"/>
+      <c r="M9" s="193"/>
+      <c r="N9" s="193"/>
+      <c r="O9" s="193"/>
+      <c r="P9" s="194"/>
+      <c r="Q9" s="192"/>
+      <c r="R9" s="193"/>
+      <c r="S9" s="193"/>
+      <c r="T9" s="193"/>
+      <c r="U9" s="193"/>
+      <c r="V9" s="194"/>
+      <c r="W9" s="192"/>
+      <c r="X9" s="193"/>
+      <c r="Y9" s="193"/>
+      <c r="Z9" s="193"/>
+      <c r="AA9" s="193"/>
+      <c r="AB9" s="194"/>
+      <c r="AC9" s="192"/>
+      <c r="AD9" s="193"/>
+      <c r="AE9" s="193"/>
+      <c r="AF9" s="193"/>
+      <c r="AG9" s="193"/>
+      <c r="AH9" s="194"/>
+      <c r="AI9" s="192"/>
+      <c r="AJ9" s="193"/>
+      <c r="AK9" s="193"/>
+      <c r="AL9" s="194"/>
     </row>
     <row r="10" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="191"/>
-      <c r="B10" s="191"/>
-      <c r="C10" s="191"/>
-      <c r="D10" s="191"/>
+      <c r="A10" s="190"/>
+      <c r="B10" s="190"/>
+      <c r="C10" s="190"/>
+      <c r="D10" s="190"/>
       <c r="E10" s="150"/>
       <c r="F10" s="150"/>
       <c r="G10" s="150"/>
@@ -17203,10 +17212,10 @@
       <c r="AL10" s="150"/>
     </row>
     <row r="11" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="191"/>
-      <c r="B11" s="191"/>
-      <c r="C11" s="191"/>
-      <c r="D11" s="191"/>
+      <c r="A11" s="190"/>
+      <c r="B11" s="190"/>
+      <c r="C11" s="190"/>
+      <c r="D11" s="190"/>
       <c r="E11" s="150"/>
       <c r="F11" s="150"/>
       <c r="G11" s="150"/>
